--- a/fuel_cost_chungcheong.xlsx
+++ b/fuel_cost_chungcheong.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4732" uniqueCount="1768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4716" uniqueCount="1767">
   <si>
     <t xml:space="preserve">유류비 계산(혼유, 지역화폐 등)</t>
   </si>
@@ -5382,9 +5382,6 @@
   </si>
   <si>
     <t>현행화 일자: 2026-07-27</t>
-  </si>
-  <si>
-    <t>가격변동</t>
   </si>
 </sst>
 </file>
@@ -75858,164 +75855,64 @@
       </c>
     </row>
     <row r="4" s="20" customFormat="true" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>457</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>458</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>1767</v>
-      </c>
-      <c r="E4" s="27">
-        <v>1875</v>
-      </c>
-      <c r="F4" s="27">
-        <v>1875</v>
-      </c>
-      <c r="G4" s="27">
-        <f>IF(OR(E4="",F4=""),"",F4-E4)</f>
-        <v>0</v>
-      </c>
+      <c r="A4" s="25"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
       <c r="H4" s="27"/>
       <c r="I4" s="27"/>
-      <c r="J4" s="27" t="str">
-        <f>IF(OR(H4="",I4=""),"",I4-H4)</f>
-        <v/>
-      </c>
-      <c r="K4" s="27">
-        <v>1860</v>
-      </c>
-      <c r="L4" s="27">
-        <v>1855</v>
-      </c>
-      <c r="M4" s="27">
-        <f>IF(OR(K4="",L4=""),"",L4-K4)</f>
-        <v>-5</v>
-      </c>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
     </row>
     <row r="5" s="20" customFormat="true" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>1221</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>1222</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>1767</v>
-      </c>
-      <c r="E5" s="27">
-        <v>1844</v>
-      </c>
-      <c r="F5" s="27">
-        <v>1844</v>
-      </c>
-      <c r="G5" s="27">
-        <f>IF(OR(E5="",F5=""),"",F5-E5)</f>
-        <v>0</v>
-      </c>
+      <c r="A5" s="25"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="27"/>
       <c r="I5" s="27"/>
-      <c r="J5" s="27" t="str">
-        <f>IF(OR(H5="",I5=""),"",I5-H5)</f>
-        <v/>
-      </c>
-      <c r="K5" s="27">
-        <v>1834</v>
-      </c>
-      <c r="L5" s="27">
-        <v>1814</v>
-      </c>
-      <c r="M5" s="27">
-        <f>IF(OR(K5="",L5=""),"",L5-K5)</f>
-        <v>-20</v>
-      </c>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
     </row>
     <row r="6" s="20" customFormat="true" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>1319</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>1320</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>1767</v>
-      </c>
-      <c r="E6" s="27">
-        <v>1850</v>
-      </c>
-      <c r="F6" s="27">
-        <v>1850</v>
-      </c>
-      <c r="G6" s="27">
-        <f>IF(OR(E6="",F6=""),"",F6-E6)</f>
-        <v>0</v>
-      </c>
+      <c r="A6" s="25"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="27"/>
       <c r="I6" s="27"/>
-      <c r="J6" s="27" t="str">
-        <f>IF(OR(H6="",I6=""),"",I6-H6)</f>
-        <v/>
-      </c>
-      <c r="K6" s="27">
-        <v>1810</v>
-      </c>
-      <c r="L6" s="27">
-        <v>1790</v>
-      </c>
-      <c r="M6" s="27">
-        <f>IF(OR(K6="",L6=""),"",L6-K6)</f>
-        <v>-20</v>
-      </c>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
     </row>
     <row r="7" s="20" customFormat="true" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>1741</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>1742</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>1767</v>
-      </c>
-      <c r="E7" s="27">
-        <v>1997</v>
-      </c>
-      <c r="F7" s="27">
-        <v>1949</v>
-      </c>
-      <c r="G7" s="27">
-        <f>IF(OR(E7="",F7=""),"",F7-E7)</f>
-        <v>-48</v>
-      </c>
+      <c r="A7" s="25"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="27"/>
       <c r="I7" s="27"/>
-      <c r="J7" s="27" t="str">
-        <f>IF(OR(H7="",I7=""),"",I7-H7)</f>
-        <v/>
-      </c>
-      <c r="K7" s="27">
-        <v>1976</v>
-      </c>
-      <c r="L7" s="27">
-        <v>1929</v>
-      </c>
-      <c r="M7" s="27">
-        <f>IF(OR(K7="",L7=""),"",L7-K7)</f>
-        <v>-47</v>
-      </c>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
     </row>
     <row r="8" s="20" customFormat="true" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="25"/>
@@ -79561,7 +79458,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G4:G7">
+  <conditionalFormatting sqref="G4:G4">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
@@ -79569,7 +79466,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J7">
+  <conditionalFormatting sqref="J4:J4">
     <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
@@ -79577,7 +79474,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M7">
+  <conditionalFormatting sqref="M4:M4">
     <cfRule type="cellIs" priority="6" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>

--- a/fuel_cost_chungcheong.xlsx
+++ b/fuel_cost_chungcheong.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4714" uniqueCount="1764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4706" uniqueCount="1763">
   <si>
     <t>유류비 계산(혼유, 지역화폐 등)</t>
   </si>
@@ -5380,9 +5380,6 @@
   </si>
   <si>
     <t>경유 Δ</t>
-  </si>
-  <si>
-    <t>가격변동</t>
   </si>
   <si>
     <t>현행화 일자: 2026-08-01</t>
@@ -75509,7 +75506,7 @@
     </row>
     <row r="2" spans="1:13" s="17" customFormat="1" ht="21" customHeight="1">
       <c r="A2" s="20" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="17" customFormat="1" ht="27.75" customHeight="1">
@@ -75554,88 +75551,34 @@
       </c>
     </row>
     <row r="4" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A4" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>335</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>1762</v>
-      </c>
-      <c r="E4" s="23">
-        <v>1859</v>
-      </c>
-      <c r="F4" s="23">
-        <v>1859</v>
-      </c>
-      <c r="G4" s="23">
-        <f>IF(OR(E4="",F4=""),"",F4-E4)</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="23">
-        <v>2318</v>
-      </c>
-      <c r="I4" s="23">
-        <v>2298</v>
-      </c>
-      <c r="J4" s="23">
-        <f>IF(OR(H4="",I4=""),"",I4-H4)</f>
-        <v>-20</v>
-      </c>
-      <c r="K4" s="23">
-        <v>1859</v>
-      </c>
-      <c r="L4" s="23">
-        <v>1839</v>
-      </c>
-      <c r="M4" s="23">
-        <f>IF(OR(K4="",L4=""),"",L4-K4)</f>
-        <v>-20</v>
-      </c>
+      <c r="A4" s="21"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
     </row>
     <row r="5" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A5" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>422</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>423</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>1762</v>
-      </c>
-      <c r="E5" s="23">
-        <v>1823</v>
-      </c>
-      <c r="F5" s="23">
-        <v>1823</v>
-      </c>
-      <c r="G5" s="23">
-        <f>IF(OR(E5="",F5=""),"",F5-E5)</f>
-        <v>0</v>
-      </c>
+      <c r="A5" s="21"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
       <c r="H5" s="23"/>
       <c r="I5" s="23"/>
-      <c r="J5" s="23" t="str">
-        <f>IF(OR(H5="",I5=""),"",I5-H5)</f>
-        <v/>
-      </c>
-      <c r="K5" s="23">
-        <v>1812</v>
-      </c>
-      <c r="L5" s="23">
-        <v>1797</v>
-      </c>
-      <c r="M5" s="23">
-        <f>IF(OR(K5="",L5=""),"",L5-K5)</f>
-        <v>-15</v>
-      </c>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
     </row>
     <row r="6" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
       <c r="A6" s="21"/>
@@ -79212,7 +79155,7 @@
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <phoneticPr fontId="27" type="noConversion"/>
-  <conditionalFormatting sqref="G4:G5">
+  <conditionalFormatting sqref="G4:G4">
     <cfRule type="cellIs" dxfId="5" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -79220,7 +79163,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J5">
+  <conditionalFormatting sqref="J4:J4">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -79228,7 +79171,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M5">
+  <conditionalFormatting sqref="M4:M4">
     <cfRule type="cellIs" dxfId="1" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>

--- a/fuel_cost_chungcheong.xlsx
+++ b/fuel_cost_chungcheong.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4689" uniqueCount="1756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4685" uniqueCount="1755">
   <si>
     <t>유류비 계산(혼유, 지역화폐 등)</t>
   </si>
@@ -5359,9 +5359,6 @@
   </si>
   <si>
     <t>현행화 일자: 2026-08-02</t>
-  </si>
-  <si>
-    <t>가격변동</t>
   </si>
 </sst>
 </file>
@@ -75216,44 +75213,19 @@
       </c>
     </row>
     <row r="4" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A4" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>398</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>399</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>1755</v>
-      </c>
-      <c r="E4" s="23">
-        <v>1814</v>
-      </c>
-      <c r="F4" s="23">
-        <v>1814</v>
-      </c>
-      <c r="G4" s="23">
-        <f>IF(OR(E4="",F4=""),"",F4-E4)</f>
-        <v>0</v>
-      </c>
+      <c r="A4" s="21"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
       <c r="H4" s="23"/>
       <c r="I4" s="23"/>
-      <c r="J4" s="23" t="str">
-        <f>IF(OR(H4="",I4=""),"",I4-H4)</f>
-        <v/>
-      </c>
-      <c r="K4" s="23">
-        <v>1793</v>
-      </c>
-      <c r="L4" s="23">
-        <v>1803</v>
-      </c>
-      <c r="M4" s="23">
-        <f>IF(OR(K4="",L4=""),"",L4-K4)</f>
-        <v>10</v>
-      </c>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
     </row>
     <row r="5" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
       <c r="A5" s="21"/>

--- a/fuel_cost_chungcheong.xlsx
+++ b/fuel_cost_chungcheong.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4685" uniqueCount="1755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4737" uniqueCount="1756">
   <si>
     <t>유류비 계산(혼유, 지역화폐 등)</t>
   </si>
@@ -5359,6 +5359,9 @@
   </si>
   <si>
     <t>현행화 일자: 2026-08-02</t>
+  </si>
+  <si>
+    <t>가격변동</t>
   </si>
 </sst>
 </file>
@@ -13905,35 +13908,35 @@
         <v>92105</v>
       </c>
     </row>
-    <row r="103" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="103" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A103" s="12">
         <f t="shared" si="13"/>
         <v>89</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D103" s="16" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E103" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F103" s="12" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="G103" s="13">
-        <v>1886</v>
+        <v>1824</v>
       </c>
       <c r="H103" s="13">
-        <v>2250</v>
+        <v>2328</v>
       </c>
       <c r="I103" s="13"/>
       <c r="J103" s="13">
-        <v>1876</v>
+        <v>1798</v>
       </c>
       <c r="K103" s="13">
         <f t="shared" si="14"/>
@@ -13941,23 +13944,23 @@
       </c>
       <c r="L103" s="13">
         <f t="shared" si="15"/>
-        <v>1886</v>
+        <v>1824</v>
       </c>
       <c r="M103" s="13">
         <f t="shared" si="16"/>
-        <v>2250</v>
+        <v>2328</v>
       </c>
       <c r="N103" s="13">
         <f t="shared" si="17"/>
-        <v>1876</v>
+        <v>1798</v>
       </c>
       <c r="O103" s="13" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 47,150원 / 고급유 45,000원</v>
+        <v>휘발유 45,600원 / 고급유 46,560원</v>
       </c>
       <c r="P103" s="13">
         <f t="shared" si="19"/>
-        <v>92150</v>
+        <v>92160</v>
       </c>
       <c r="Q103" s="13"/>
       <c r="R103" s="14">
@@ -13970,50 +13973,50 @@
       </c>
       <c r="T103" s="13">
         <f t="shared" si="22"/>
-        <v>92150</v>
+        <v>92160</v>
       </c>
       <c r="U103" s="13">
         <f t="shared" si="23"/>
-        <v>2047.7777777777778</v>
+        <v>2048</v>
       </c>
       <c r="V103" s="13">
         <f t="shared" si="24"/>
-        <v>2047.7777777777778</v>
+        <v>2048</v>
       </c>
       <c r="W103" s="15">
         <f t="shared" si="25"/>
-        <v>92150</v>
-      </c>
-    </row>
-    <row r="104" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+        <v>92160</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A104" s="12">
         <f t="shared" si="13"/>
         <v>90</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="D104" s="16" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E104" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F104" s="12" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="G104" s="13">
-        <v>1824</v>
+        <v>1835</v>
       </c>
       <c r="H104" s="13">
-        <v>2328</v>
+        <v>2315</v>
       </c>
       <c r="I104" s="13"/>
       <c r="J104" s="13">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="K104" s="13">
         <f t="shared" si="14"/>
@@ -14021,23 +14024,23 @@
       </c>
       <c r="L104" s="13">
         <f t="shared" si="15"/>
-        <v>1824</v>
+        <v>1835</v>
       </c>
       <c r="M104" s="13">
         <f t="shared" si="16"/>
-        <v>2328</v>
+        <v>2315</v>
       </c>
       <c r="N104" s="13">
         <f t="shared" si="17"/>
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="O104" s="13" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,600원 / 고급유 46,560원</v>
+        <v>휘발유 45,875원 / 고급유 46,300원</v>
       </c>
       <c r="P104" s="13">
         <f t="shared" si="19"/>
-        <v>92160</v>
+        <v>92175</v>
       </c>
       <c r="Q104" s="13"/>
       <c r="R104" s="14">
@@ -14050,31 +14053,31 @@
       </c>
       <c r="T104" s="13">
         <f t="shared" si="22"/>
-        <v>92160</v>
+        <v>92175</v>
       </c>
       <c r="U104" s="13">
         <f t="shared" si="23"/>
-        <v>2048</v>
+        <v>2048.3333333333335</v>
       </c>
       <c r="V104" s="13">
         <f t="shared" si="24"/>
-        <v>2048</v>
+        <v>2048.3333333333335</v>
       </c>
       <c r="W104" s="15">
         <f t="shared" si="25"/>
-        <v>92160</v>
+        <v>92175</v>
       </c>
     </row>
     <row r="105" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A105" s="12">
         <f t="shared" si="13"/>
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B105" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>201</v>
+        <v>274</v>
       </c>
       <c r="D105" s="16" t="s">
         <v>71</v>
@@ -14083,7 +14086,7 @@
         <v>26</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>202</v>
+        <v>275</v>
       </c>
       <c r="G105" s="13">
         <v>1835</v>
@@ -14093,7 +14096,7 @@
       </c>
       <c r="I105" s="13"/>
       <c r="J105" s="13">
-        <v>1799</v>
+        <v>1815</v>
       </c>
       <c r="K105" s="13">
         <f t="shared" si="14"/>
@@ -14109,7 +14112,7 @@
       </c>
       <c r="N105" s="13">
         <f t="shared" si="17"/>
-        <v>1799</v>
+        <v>1815</v>
       </c>
       <c r="O105" s="13" t="str">
         <f t="shared" si="18"/>
@@ -14145,16 +14148,16 @@
         <v>92175</v>
       </c>
     </row>
-    <row r="106" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="106" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A106" s="12">
         <f t="shared" si="13"/>
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>274</v>
+        <v>205</v>
       </c>
       <c r="D106" s="16" t="s">
         <v>71</v>
@@ -14163,17 +14166,17 @@
         <v>26</v>
       </c>
       <c r="F106" s="12" t="s">
-        <v>275</v>
+        <v>206</v>
       </c>
       <c r="G106" s="13">
-        <v>1835</v>
+        <v>1845</v>
       </c>
       <c r="H106" s="13">
-        <v>2315</v>
+        <v>2303</v>
       </c>
       <c r="I106" s="13"/>
       <c r="J106" s="13">
-        <v>1815</v>
+        <v>1849</v>
       </c>
       <c r="K106" s="13">
         <f t="shared" si="14"/>
@@ -14181,23 +14184,23 @@
       </c>
       <c r="L106" s="13">
         <f t="shared" si="15"/>
-        <v>1835</v>
+        <v>1845</v>
       </c>
       <c r="M106" s="13">
         <f t="shared" si="16"/>
-        <v>2315</v>
+        <v>2303</v>
       </c>
       <c r="N106" s="13">
         <f t="shared" si="17"/>
-        <v>1815</v>
+        <v>1849</v>
       </c>
       <c r="O106" s="13" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,875원 / 고급유 46,300원</v>
+        <v>휘발유 46,125원 / 고급유 46,060원</v>
       </c>
       <c r="P106" s="13">
         <f t="shared" si="19"/>
-        <v>92175</v>
+        <v>92185</v>
       </c>
       <c r="Q106" s="13"/>
       <c r="R106" s="14">
@@ -14210,50 +14213,50 @@
       </c>
       <c r="T106" s="13">
         <f t="shared" si="22"/>
-        <v>92175</v>
+        <v>92185</v>
       </c>
       <c r="U106" s="13">
         <f t="shared" si="23"/>
-        <v>2048.3333333333335</v>
+        <v>2048.5555555555557</v>
       </c>
       <c r="V106" s="13">
         <f t="shared" si="24"/>
-        <v>2048.3333333333335</v>
+        <v>2048.5555555555557</v>
       </c>
       <c r="W106" s="15">
         <f t="shared" si="25"/>
-        <v>92175</v>
-      </c>
-    </row>
-    <row r="107" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+        <v>92185</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A107" s="12">
         <f t="shared" si="13"/>
         <v>93</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D107" s="16" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="E107" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F107" s="12" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="G107" s="13">
-        <v>1845</v>
+        <v>1814</v>
       </c>
       <c r="H107" s="13">
-        <v>2303</v>
+        <v>2346</v>
       </c>
       <c r="I107" s="13"/>
       <c r="J107" s="13">
-        <v>1849</v>
+        <v>1808</v>
       </c>
       <c r="K107" s="13">
         <f t="shared" si="14"/>
@@ -14261,23 +14264,23 @@
       </c>
       <c r="L107" s="13">
         <f t="shared" si="15"/>
-        <v>1845</v>
+        <v>1814</v>
       </c>
       <c r="M107" s="13">
         <f t="shared" si="16"/>
-        <v>2303</v>
+        <v>2346</v>
       </c>
       <c r="N107" s="13">
         <f t="shared" si="17"/>
-        <v>1849</v>
+        <v>1808</v>
       </c>
       <c r="O107" s="13" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 46,125원 / 고급유 46,060원</v>
+        <v>휘발유 45,350원 / 고급유 46,920원</v>
       </c>
       <c r="P107" s="13">
         <f t="shared" si="19"/>
-        <v>92185</v>
+        <v>92270</v>
       </c>
       <c r="Q107" s="13"/>
       <c r="R107" s="14">
@@ -14290,22 +14293,22 @@
       </c>
       <c r="T107" s="13">
         <f t="shared" si="22"/>
-        <v>92185</v>
+        <v>92270</v>
       </c>
       <c r="U107" s="13">
         <f t="shared" si="23"/>
-        <v>2048.5555555555557</v>
+        <v>2050.4444444444443</v>
       </c>
       <c r="V107" s="13">
         <f t="shared" si="24"/>
-        <v>2048.5555555555557</v>
+        <v>2050.4444444444443</v>
       </c>
       <c r="W107" s="15">
         <f t="shared" si="25"/>
-        <v>92185</v>
-      </c>
-    </row>
-    <row r="108" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+        <v>92270</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A108" s="12">
         <f t="shared" si="13"/>
         <v>94</v>
@@ -14314,26 +14317,26 @@
         <v>6</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D108" s="16" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E108" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F108" s="12" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G108" s="13">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="H108" s="13">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="I108" s="13"/>
       <c r="J108" s="13">
-        <v>1808</v>
+        <v>1799</v>
       </c>
       <c r="K108" s="13">
         <f t="shared" si="14"/>
@@ -14341,23 +14344,23 @@
       </c>
       <c r="L108" s="13">
         <f t="shared" si="15"/>
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="M108" s="13">
         <f t="shared" si="16"/>
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="N108" s="13">
         <f t="shared" si="17"/>
-        <v>1808</v>
+        <v>1799</v>
       </c>
       <c r="O108" s="13" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,350원 / 고급유 46,920원</v>
+        <v>휘발유 45,375원 / 고급유 46,900원</v>
       </c>
       <c r="P108" s="13">
         <f t="shared" si="19"/>
-        <v>92270</v>
+        <v>92275</v>
       </c>
       <c r="Q108" s="13"/>
       <c r="R108" s="14">
@@ -14370,19 +14373,19 @@
       </c>
       <c r="T108" s="13">
         <f t="shared" si="22"/>
-        <v>92270</v>
+        <v>92275</v>
       </c>
       <c r="U108" s="13">
         <f t="shared" si="23"/>
-        <v>2050.4444444444443</v>
+        <v>2050.5555555555557</v>
       </c>
       <c r="V108" s="13">
         <f t="shared" si="24"/>
-        <v>2050.4444444444443</v>
+        <v>2050.5555555555557</v>
       </c>
       <c r="W108" s="15">
         <f t="shared" si="25"/>
-        <v>92270</v>
+        <v>92275</v>
       </c>
     </row>
     <row r="109" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -14391,53 +14394,53 @@
         <v>95</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D109" s="16" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E109" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F109" s="12" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G109" s="13">
-        <v>1815</v>
+        <v>1854</v>
       </c>
       <c r="H109" s="13">
-        <v>2345</v>
+        <v>2319</v>
       </c>
       <c r="I109" s="13"/>
       <c r="J109" s="13">
-        <v>1799</v>
+        <v>1842</v>
       </c>
       <c r="K109" s="13">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L109" s="13">
         <f t="shared" si="15"/>
-        <v>1815</v>
+        <v>1844</v>
       </c>
       <c r="M109" s="13">
         <f t="shared" si="16"/>
-        <v>2345</v>
+        <v>2309</v>
       </c>
       <c r="N109" s="13">
         <f t="shared" si="17"/>
-        <v>1799</v>
+        <v>1832</v>
       </c>
       <c r="O109" s="13" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,375원 / 고급유 46,900원</v>
+        <v>휘발유 46,100원 / 고급유 46,180원</v>
       </c>
       <c r="P109" s="13">
         <f t="shared" si="19"/>
-        <v>92275</v>
+        <v>92280</v>
       </c>
       <c r="Q109" s="13"/>
       <c r="R109" s="14">
@@ -14450,31 +14453,31 @@
       </c>
       <c r="T109" s="13">
         <f t="shared" si="22"/>
-        <v>92275</v>
+        <v>92280</v>
       </c>
       <c r="U109" s="13">
         <f t="shared" si="23"/>
-        <v>2050.5555555555557</v>
+        <v>2050.6666666666665</v>
       </c>
       <c r="V109" s="13">
         <f t="shared" si="24"/>
-        <v>2050.5555555555557</v>
+        <v>2050.6666666666665</v>
       </c>
       <c r="W109" s="15">
         <f t="shared" si="25"/>
-        <v>92275</v>
+        <v>92280</v>
       </c>
     </row>
     <row r="110" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A110" s="12">
         <f t="shared" si="13"/>
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D110" s="16" t="s">
         <v>52</v>
@@ -14483,7 +14486,7 @@
         <v>26</v>
       </c>
       <c r="F110" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G110" s="13">
         <v>1854</v>
@@ -14493,7 +14496,7 @@
       </c>
       <c r="I110" s="13"/>
       <c r="J110" s="13">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="K110" s="13">
         <f t="shared" si="14"/>
@@ -14509,7 +14512,7 @@
       </c>
       <c r="N110" s="13">
         <f t="shared" si="17"/>
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="O110" s="13" t="str">
         <f t="shared" si="18"/>
@@ -14545,59 +14548,59 @@
         <v>92280</v>
       </c>
     </row>
-    <row r="111" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="111" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A111" s="12">
         <f t="shared" si="13"/>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D111" s="16" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E111" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F111" s="12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="G111" s="13">
         <v>1854</v>
       </c>
       <c r="H111" s="13">
-        <v>2319</v>
+        <v>2299</v>
       </c>
       <c r="I111" s="13"/>
       <c r="J111" s="13">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="K111" s="13">
         <f t="shared" si="14"/>
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="L111" s="13">
         <f t="shared" si="15"/>
-        <v>1844</v>
+        <v>1854</v>
       </c>
       <c r="M111" s="13">
         <f t="shared" si="16"/>
-        <v>2309</v>
+        <v>2299</v>
       </c>
       <c r="N111" s="13">
         <f t="shared" si="17"/>
-        <v>1834</v>
+        <v>1842</v>
       </c>
       <c r="O111" s="13" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 46,100원 / 고급유 46,180원</v>
+        <v>휘발유 46,350원 / 고급유 45,980원</v>
       </c>
       <c r="P111" s="13">
         <f t="shared" si="19"/>
-        <v>92280</v>
+        <v>92330</v>
       </c>
       <c r="Q111" s="13"/>
       <c r="R111" s="14">
@@ -14610,50 +14613,50 @@
       </c>
       <c r="T111" s="13">
         <f t="shared" si="22"/>
-        <v>92280</v>
+        <v>92330</v>
       </c>
       <c r="U111" s="13">
         <f t="shared" si="23"/>
-        <v>2050.6666666666665</v>
+        <v>2051.7777777777778</v>
       </c>
       <c r="V111" s="13">
         <f t="shared" si="24"/>
-        <v>2050.6666666666665</v>
+        <v>2051.7777777777778</v>
       </c>
       <c r="W111" s="15">
         <f t="shared" si="25"/>
-        <v>92280</v>
-      </c>
-    </row>
-    <row r="112" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+        <v>92330</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A112" s="12">
         <f t="shared" si="13"/>
         <v>98</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D112" s="16" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E112" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F112" s="12" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="G112" s="13">
-        <v>1854</v>
+        <v>1833</v>
       </c>
       <c r="H112" s="13">
-        <v>2299</v>
+        <v>2328</v>
       </c>
       <c r="I112" s="13"/>
       <c r="J112" s="13">
-        <v>1842</v>
+        <v>1819</v>
       </c>
       <c r="K112" s="13">
         <f t="shared" si="14"/>
@@ -14661,23 +14664,23 @@
       </c>
       <c r="L112" s="13">
         <f t="shared" si="15"/>
-        <v>1854</v>
+        <v>1833</v>
       </c>
       <c r="M112" s="13">
         <f t="shared" si="16"/>
-        <v>2299</v>
+        <v>2328</v>
       </c>
       <c r="N112" s="13">
         <f t="shared" si="17"/>
-        <v>1842</v>
+        <v>1819</v>
       </c>
       <c r="O112" s="13" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 46,350원 / 고급유 45,980원</v>
+        <v>휘발유 45,825원 / 고급유 46,560원</v>
       </c>
       <c r="P112" s="13">
         <f t="shared" si="19"/>
-        <v>92330</v>
+        <v>92385</v>
       </c>
       <c r="Q112" s="13"/>
       <c r="R112" s="14">
@@ -14690,22 +14693,22 @@
       </c>
       <c r="T112" s="13">
         <f t="shared" si="22"/>
-        <v>92330</v>
+        <v>92385</v>
       </c>
       <c r="U112" s="13">
         <f t="shared" si="23"/>
-        <v>2051.7777777777778</v>
+        <v>2053</v>
       </c>
       <c r="V112" s="13">
         <f t="shared" si="24"/>
-        <v>2051.7777777777778</v>
+        <v>2053</v>
       </c>
       <c r="W112" s="15">
         <f t="shared" si="25"/>
-        <v>92330</v>
-      </c>
-    </row>
-    <row r="113" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+        <v>92385</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A113" s="12">
         <f t="shared" si="13"/>
         <v>99</v>
@@ -14714,50 +14717,52 @@
         <v>6</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D113" s="16" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="E113" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F113" s="12" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G113" s="13">
-        <v>1833</v>
+        <v>1848</v>
       </c>
       <c r="H113" s="13">
-        <v>2328</v>
-      </c>
-      <c r="I113" s="13"/>
+        <v>2332</v>
+      </c>
+      <c r="I113" s="13" t="s">
+        <v>47</v>
+      </c>
       <c r="J113" s="13">
-        <v>1819</v>
+        <v>1838</v>
       </c>
       <c r="K113" s="13">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L113" s="13">
         <f t="shared" si="15"/>
-        <v>1833</v>
+        <v>1838</v>
       </c>
       <c r="M113" s="13">
         <f t="shared" si="16"/>
-        <v>2328</v>
+        <v>2322</v>
       </c>
       <c r="N113" s="13">
         <f t="shared" si="17"/>
-        <v>1819</v>
+        <v>1828</v>
       </c>
       <c r="O113" s="13" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,825원 / 고급유 46,560원</v>
+        <v>휘발유 45,950원 / 고급유 46,440원</v>
       </c>
       <c r="P113" s="13">
         <f t="shared" si="19"/>
-        <v>92385</v>
+        <v>92390</v>
       </c>
       <c r="Q113" s="13"/>
       <c r="R113" s="14">
@@ -14770,31 +14775,31 @@
       </c>
       <c r="T113" s="13">
         <f t="shared" si="22"/>
-        <v>92385</v>
+        <v>92390</v>
       </c>
       <c r="U113" s="13">
         <f t="shared" si="23"/>
-        <v>2053</v>
+        <v>2053.1111111111113</v>
       </c>
       <c r="V113" s="13">
         <f t="shared" si="24"/>
-        <v>2053</v>
+        <v>2053.1111111111113</v>
       </c>
       <c r="W113" s="15">
         <f t="shared" si="25"/>
-        <v>92385</v>
-      </c>
-    </row>
-    <row r="114" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+        <v>92390</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A114" s="12">
         <f t="shared" si="13"/>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B114" s="12" t="s">
         <v>6</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D114" s="16" t="s">
         <v>52</v>
@@ -14803,7 +14808,7 @@
         <v>26</v>
       </c>
       <c r="F114" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G114" s="13">
         <v>1848</v>
@@ -14867,16 +14872,16 @@
         <v>92390</v>
       </c>
     </row>
-    <row r="115" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="115" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A115" s="12">
         <f t="shared" si="13"/>
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="D115" s="16" t="s">
         <v>52</v>
@@ -14885,43 +14890,41 @@
         <v>26</v>
       </c>
       <c r="F115" s="12" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="G115" s="13">
-        <v>1848</v>
+        <v>1896</v>
       </c>
       <c r="H115" s="13">
-        <v>2332</v>
-      </c>
-      <c r="I115" s="13" t="s">
-        <v>47</v>
-      </c>
+        <v>2250</v>
+      </c>
+      <c r="I115" s="13"/>
       <c r="J115" s="13">
-        <v>1838</v>
+        <v>1876</v>
       </c>
       <c r="K115" s="13">
         <f t="shared" si="14"/>
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="L115" s="13">
         <f t="shared" si="15"/>
-        <v>1838</v>
+        <v>1896</v>
       </c>
       <c r="M115" s="13">
         <f t="shared" si="16"/>
-        <v>2322</v>
+        <v>2250</v>
       </c>
       <c r="N115" s="13">
         <f t="shared" si="17"/>
-        <v>1828</v>
+        <v>1876</v>
       </c>
       <c r="O115" s="13" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,950원 / 고급유 46,440원</v>
+        <v>휘발유 47,400원 / 고급유 45,000원</v>
       </c>
       <c r="P115" s="13">
         <f t="shared" si="19"/>
-        <v>92390</v>
+        <v>92400</v>
       </c>
       <c r="Q115" s="13"/>
       <c r="R115" s="14">
@@ -14934,19 +14937,19 @@
       </c>
       <c r="T115" s="13">
         <f t="shared" si="22"/>
-        <v>92390</v>
+        <v>92400</v>
       </c>
       <c r="U115" s="13">
         <f t="shared" si="23"/>
-        <v>2053.1111111111113</v>
+        <v>2053.3333333333335</v>
       </c>
       <c r="V115" s="13">
         <f t="shared" si="24"/>
-        <v>2053.1111111111113</v>
+        <v>2053.3333333333335</v>
       </c>
       <c r="W115" s="15">
         <f t="shared" si="25"/>
-        <v>92390</v>
+        <v>92400</v>
       </c>
     </row>
     <row r="116" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
@@ -21517,7 +21520,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="198" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="198" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A198" s="12" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -21526,16 +21529,16 @@
         <v>18</v>
       </c>
       <c r="C198" s="12" t="s">
-        <v>470</v>
-      </c>
-      <c r="D198" s="12" t="s">
-        <v>49</v>
+        <v>408</v>
+      </c>
+      <c r="D198" s="16" t="s">
+        <v>71</v>
       </c>
       <c r="E198" s="12" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F198" s="12" t="s">
-        <v>471</v>
+        <v>409</v>
       </c>
       <c r="G198" s="13">
         <v>1859</v>
@@ -21597,7 +21600,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="199" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="199" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A199" s="12" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -21606,16 +21609,16 @@
         <v>18</v>
       </c>
       <c r="C199" s="12" t="s">
-        <v>408</v>
-      </c>
-      <c r="D199" s="16" t="s">
-        <v>71</v>
+        <v>470</v>
+      </c>
+      <c r="D199" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="E199" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="F199" s="12" t="s">
-        <v>409</v>
+        <v>471</v>
       </c>
       <c r="G199" s="13">
         <v>1859</v>
@@ -21623,7 +21626,7 @@
       <c r="H199" s="13"/>
       <c r="I199" s="13"/>
       <c r="J199" s="13">
-        <v>1849</v>
+        <v>1869</v>
       </c>
       <c r="K199" s="13">
         <f t="shared" si="27"/>
@@ -21639,7 +21642,7 @@
       </c>
       <c r="N199" s="13">
         <f t="shared" si="30"/>
-        <v>1849</v>
+        <v>1869</v>
       </c>
       <c r="O199" s="13" t="str">
         <f t="shared" si="31"/>
@@ -23143,7 +23146,7 @@
       <c r="H218" s="13"/>
       <c r="I218" s="13"/>
       <c r="J218" s="13">
-        <v>1849</v>
+        <v>1854</v>
       </c>
       <c r="K218" s="13">
         <f t="shared" si="40"/>
@@ -23159,7 +23162,7 @@
       </c>
       <c r="N218" s="13">
         <f t="shared" si="43"/>
-        <v>1849</v>
+        <v>1854</v>
       </c>
       <c r="O218" s="13" t="str">
         <f t="shared" si="44"/>
@@ -24797,7 +24800,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="239" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="239" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A239" s="12" t="str">
         <f t="shared" si="39"/>
         <v/>
@@ -24806,16 +24809,16 @@
         <v>16</v>
       </c>
       <c r="C239" s="12" t="s">
-        <v>474</v>
+        <v>597</v>
       </c>
       <c r="D239" s="16" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="E239" s="12" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F239" s="12" t="s">
-        <v>475</v>
+        <v>598</v>
       </c>
       <c r="G239" s="13">
         <v>1880</v>
@@ -24823,7 +24826,7 @@
       <c r="H239" s="13"/>
       <c r="I239" s="13"/>
       <c r="J239" s="13">
-        <v>1860</v>
+        <v>1880</v>
       </c>
       <c r="K239" s="13">
         <f t="shared" si="40"/>
@@ -24839,7 +24842,7 @@
       </c>
       <c r="N239" s="13">
         <f t="shared" si="43"/>
-        <v>1860</v>
+        <v>1880</v>
       </c>
       <c r="O239" s="13" t="str">
         <f t="shared" si="44"/>
@@ -24877,7 +24880,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="240" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="240" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A240" s="12" t="str">
         <f t="shared" si="39"/>
         <v/>
@@ -24886,16 +24889,16 @@
         <v>16</v>
       </c>
       <c r="C240" s="12" t="s">
-        <v>597</v>
+        <v>474</v>
       </c>
       <c r="D240" s="16" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="E240" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="F240" s="12" t="s">
-        <v>598</v>
+        <v>475</v>
       </c>
       <c r="G240" s="13">
         <v>1880</v>
@@ -24903,7 +24906,7 @@
       <c r="H240" s="13"/>
       <c r="I240" s="13"/>
       <c r="J240" s="13">
-        <v>1880</v>
+        <v>1890</v>
       </c>
       <c r="K240" s="13">
         <f t="shared" si="40"/>
@@ -24919,7 +24922,7 @@
       </c>
       <c r="N240" s="13">
         <f t="shared" si="43"/>
-        <v>1880</v>
+        <v>1890</v>
       </c>
       <c r="O240" s="13" t="str">
         <f t="shared" si="44"/>
@@ -26743,7 +26746,7 @@
       <c r="H263" s="13"/>
       <c r="I263" s="13"/>
       <c r="J263" s="13">
-        <v>1847</v>
+        <v>1867</v>
       </c>
       <c r="K263" s="13">
         <f t="shared" si="40"/>
@@ -26759,7 +26762,7 @@
       </c>
       <c r="N263" s="13">
         <f t="shared" si="43"/>
-        <v>1847</v>
+        <v>1867</v>
       </c>
       <c r="O263" s="13" t="str">
         <f t="shared" si="44"/>
@@ -27043,27 +27046,27 @@
         <v/>
       </c>
       <c r="B267" s="12" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C267" s="12" t="s">
-        <v>531</v>
+        <v>599</v>
       </c>
       <c r="D267" s="16" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E267" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="F267" s="12" t="s">
-        <v>532</v>
+        <v>600</v>
       </c>
       <c r="G267" s="13">
-        <v>1890</v>
+        <v>1848</v>
       </c>
       <c r="H267" s="13"/>
       <c r="I267" s="13"/>
       <c r="J267" s="13">
-        <v>1880</v>
+        <v>1838</v>
       </c>
       <c r="K267" s="13">
         <f t="shared" si="40"/>
@@ -27071,7 +27074,7 @@
       </c>
       <c r="L267" s="13">
         <f t="shared" si="41"/>
-        <v>1890</v>
+        <v>1848</v>
       </c>
       <c r="M267" s="13" t="str">
         <f t="shared" si="42"/>
@@ -27079,7 +27082,7 @@
       </c>
       <c r="N267" s="13">
         <f t="shared" si="43"/>
-        <v>1880</v>
+        <v>1838</v>
       </c>
       <c r="O267" s="13" t="str">
         <f t="shared" si="44"/>
@@ -27117,7 +27120,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="268" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="268" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A268" s="12" t="str">
         <f t="shared" si="39"/>
         <v/>
@@ -27126,16 +27129,16 @@
         <v>18</v>
       </c>
       <c r="C268" s="12" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D268" s="16" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E268" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F268" s="12" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="G268" s="13">
         <v>1890</v>
@@ -27197,7 +27200,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="269" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="269" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A269" s="12" t="str">
         <f t="shared" si="39"/>
         <v/>
@@ -27206,16 +27209,16 @@
         <v>18</v>
       </c>
       <c r="C269" s="12" t="s">
-        <v>535</v>
-      </c>
-      <c r="D269" s="12" t="s">
-        <v>49</v>
+        <v>533</v>
+      </c>
+      <c r="D269" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E269" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F269" s="12" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="G269" s="13">
         <v>1890</v>
@@ -27223,7 +27226,7 @@
       <c r="H269" s="13"/>
       <c r="I269" s="13"/>
       <c r="J269" s="13">
-        <v>1890</v>
+        <v>1880</v>
       </c>
       <c r="K269" s="13">
         <f t="shared" si="40"/>
@@ -27239,7 +27242,7 @@
       </c>
       <c r="N269" s="13">
         <f t="shared" si="43"/>
-        <v>1890</v>
+        <v>1880</v>
       </c>
       <c r="O269" s="13" t="str">
         <f t="shared" si="44"/>
@@ -27277,25 +27280,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="270" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="270" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A270" s="12" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="B270" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C270" s="12" t="s">
-        <v>658</v>
-      </c>
-      <c r="D270" s="16" t="s">
-        <v>52</v>
+        <v>535</v>
+      </c>
+      <c r="D270" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="E270" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F270" s="12" t="s">
-        <v>659</v>
+        <v>536</v>
       </c>
       <c r="G270" s="13">
         <v>1890</v>
@@ -27366,16 +27369,16 @@
         <v>16</v>
       </c>
       <c r="C271" s="12" t="s">
-        <v>595</v>
+        <v>658</v>
       </c>
       <c r="D271" s="16" t="s">
         <v>52</v>
       </c>
       <c r="E271" s="12" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F271" s="12" t="s">
-        <v>596</v>
+        <v>659</v>
       </c>
       <c r="G271" s="13">
         <v>1890</v>
@@ -27383,7 +27386,7 @@
       <c r="H271" s="13"/>
       <c r="I271" s="13"/>
       <c r="J271" s="13">
-        <v>1900</v>
+        <v>1890</v>
       </c>
       <c r="K271" s="13">
         <f t="shared" ref="K271:K334" si="53">IF(AND(IFERROR(SEARCH("현대오일뱅크",$C271),0)&gt;0,IFERROR(SEARCH("직영",$C271),0)&gt;0),$B$13,0)</f>
@@ -27399,7 +27402,7 @@
       </c>
       <c r="N271" s="13">
         <f t="shared" ref="N271:N334" si="56">IF($J271="","",$J271+$K271)</f>
-        <v>1900</v>
+        <v>1890</v>
       </c>
       <c r="O271" s="13" t="str">
         <f t="shared" ref="O271:O334" si="57">IF($B$10=0,"",IFERROR(IF($B$4&gt;0,"휘발유 "&amp;TEXT(IF($L271="",1/0,$L271*$B$4),"#,##0")&amp;"원","")&amp;IF($B$5&gt;0,IF($B$4&gt;0," / ","")&amp;"고급유 "&amp;TEXT(IF($M271="",1/0,$M271*$B$5),"#,##0")&amp;"원","")&amp;IF($B$6&gt;0,IF(OR($B$4&gt;0,$B$5&gt;0)," / ","")&amp;"경유 "&amp;TEXT(IF($N271="",1/0,$N271*$B$6),"#,##0")&amp;"원",""),""))</f>
@@ -27443,27 +27446,27 @@
         <v/>
       </c>
       <c r="B272" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C272" s="12" t="s">
-        <v>622</v>
-      </c>
-      <c r="D272" s="12" t="s">
-        <v>49</v>
+        <v>595</v>
+      </c>
+      <c r="D272" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E272" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F272" s="12" t="s">
-        <v>623</v>
+        <v>596</v>
       </c>
       <c r="G272" s="13">
-        <v>1849</v>
+        <v>1890</v>
       </c>
       <c r="H272" s="13"/>
       <c r="I272" s="13"/>
       <c r="J272" s="13">
-        <v>1799</v>
+        <v>1900</v>
       </c>
       <c r="K272" s="13">
         <f t="shared" si="53"/>
@@ -27471,7 +27474,7 @@
       </c>
       <c r="L272" s="13">
         <f t="shared" si="54"/>
-        <v>1849</v>
+        <v>1890</v>
       </c>
       <c r="M272" s="13" t="str">
         <f t="shared" si="55"/>
@@ -27479,7 +27482,7 @@
       </c>
       <c r="N272" s="13">
         <f t="shared" si="56"/>
-        <v>1799</v>
+        <v>1900</v>
       </c>
       <c r="O272" s="13" t="str">
         <f t="shared" si="57"/>
@@ -27517,25 +27520,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="273" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="273" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A273" s="12" t="str">
         <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="B273" s="12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C273" s="12" t="s">
-        <v>539</v>
-      </c>
-      <c r="D273" s="16" t="s">
-        <v>52</v>
+        <v>622</v>
+      </c>
+      <c r="D273" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="E273" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F273" s="12" t="s">
-        <v>540</v>
+        <v>623</v>
       </c>
       <c r="G273" s="13">
         <v>1849</v>
@@ -27603,19 +27606,19 @@
         <v/>
       </c>
       <c r="B274" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C274" s="12" t="s">
-        <v>553</v>
+        <v>539</v>
       </c>
       <c r="D274" s="16" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E274" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F274" s="12" t="s">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="G274" s="13">
         <v>1849</v>
@@ -27623,7 +27626,7 @@
       <c r="H274" s="13"/>
       <c r="I274" s="13"/>
       <c r="J274" s="13">
-        <v>1809</v>
+        <v>1799</v>
       </c>
       <c r="K274" s="13">
         <f t="shared" si="53"/>
@@ -27639,7 +27642,7 @@
       </c>
       <c r="N274" s="13">
         <f t="shared" si="56"/>
-        <v>1809</v>
+        <v>1799</v>
       </c>
       <c r="O274" s="13" t="str">
         <f t="shared" si="57"/>
@@ -27677,7 +27680,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="275" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="275" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A275" s="12" t="str">
         <f t="shared" si="52"/>
         <v/>
@@ -27686,16 +27689,16 @@
         <v>10</v>
       </c>
       <c r="C275" s="12" t="s">
-        <v>616</v>
-      </c>
-      <c r="D275" s="12" t="s">
-        <v>49</v>
+        <v>553</v>
+      </c>
+      <c r="D275" s="16" t="s">
+        <v>59</v>
       </c>
       <c r="E275" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F275" s="12" t="s">
-        <v>617</v>
+        <v>554</v>
       </c>
       <c r="G275" s="13">
         <v>1849</v>
@@ -27703,7 +27706,7 @@
       <c r="H275" s="13"/>
       <c r="I275" s="13"/>
       <c r="J275" s="13">
-        <v>1819</v>
+        <v>1809</v>
       </c>
       <c r="K275" s="13">
         <f t="shared" si="53"/>
@@ -27719,7 +27722,7 @@
       </c>
       <c r="N275" s="13">
         <f t="shared" si="56"/>
-        <v>1819</v>
+        <v>1809</v>
       </c>
       <c r="O275" s="13" t="str">
         <f t="shared" si="57"/>
@@ -27757,25 +27760,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="276" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="276" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A276" s="12" t="str">
         <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="B276" s="12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C276" s="12" t="s">
-        <v>545</v>
-      </c>
-      <c r="D276" s="16" t="s">
-        <v>59</v>
+        <v>616</v>
+      </c>
+      <c r="D276" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="E276" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F276" s="12" t="s">
-        <v>546</v>
+        <v>617</v>
       </c>
       <c r="G276" s="13">
         <v>1849</v>
@@ -27783,7 +27786,7 @@
       <c r="H276" s="13"/>
       <c r="I276" s="13"/>
       <c r="J276" s="13">
-        <v>1834</v>
+        <v>1819</v>
       </c>
       <c r="K276" s="13">
         <f t="shared" si="53"/>
@@ -27799,7 +27802,7 @@
       </c>
       <c r="N276" s="13">
         <f t="shared" si="56"/>
-        <v>1834</v>
+        <v>1819</v>
       </c>
       <c r="O276" s="13" t="str">
         <f t="shared" si="57"/>
@@ -27837,7 +27840,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="277" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="277" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A277" s="12" t="str">
         <f t="shared" si="52"/>
         <v/>
@@ -27846,16 +27849,16 @@
         <v>6</v>
       </c>
       <c r="C277" s="12" t="s">
-        <v>547</v>
-      </c>
-      <c r="D277" s="12" t="s">
-        <v>49</v>
+        <v>545</v>
+      </c>
+      <c r="D277" s="16" t="s">
+        <v>59</v>
       </c>
       <c r="E277" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F277" s="12" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="G277" s="13">
         <v>1849</v>
@@ -27863,7 +27866,7 @@
       <c r="H277" s="13"/>
       <c r="I277" s="13"/>
       <c r="J277" s="13">
-        <v>1836</v>
+        <v>1834</v>
       </c>
       <c r="K277" s="13">
         <f t="shared" si="53"/>
@@ -27879,7 +27882,7 @@
       </c>
       <c r="N277" s="13">
         <f t="shared" si="56"/>
-        <v>1836</v>
+        <v>1834</v>
       </c>
       <c r="O277" s="13" t="str">
         <f t="shared" si="57"/>
@@ -27926,16 +27929,16 @@
         <v>6</v>
       </c>
       <c r="C278" s="12" t="s">
-        <v>549</v>
-      </c>
-      <c r="D278" s="16" t="s">
-        <v>52</v>
+        <v>547</v>
+      </c>
+      <c r="D278" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="E278" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="F278" s="12" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G278" s="13">
         <v>1849</v>
@@ -27943,7 +27946,7 @@
       <c r="H278" s="13"/>
       <c r="I278" s="13"/>
       <c r="J278" s="13">
-        <v>1839</v>
+        <v>1836</v>
       </c>
       <c r="K278" s="13">
         <f t="shared" si="53"/>
@@ -27959,7 +27962,7 @@
       </c>
       <c r="N278" s="13">
         <f t="shared" si="56"/>
-        <v>1839</v>
+        <v>1836</v>
       </c>
       <c r="O278" s="13" t="str">
         <f t="shared" si="57"/>
@@ -27997,25 +28000,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="279" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="279" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A279" s="12" t="str">
         <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="B279" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C279" s="12" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D279" s="16" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E279" s="12" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F279" s="12" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="G279" s="13">
         <v>1849</v>
@@ -28077,25 +28080,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="280" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="280" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A280" s="12" t="str">
         <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="B280" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C280" s="12" t="s">
-        <v>583</v>
+        <v>551</v>
       </c>
       <c r="D280" s="16" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E280" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F280" s="12" t="s">
-        <v>584</v>
+        <v>552</v>
       </c>
       <c r="G280" s="13">
         <v>1849</v>
@@ -28103,7 +28106,7 @@
       <c r="H280" s="13"/>
       <c r="I280" s="13"/>
       <c r="J280" s="13">
-        <v>1849</v>
+        <v>1839</v>
       </c>
       <c r="K280" s="13">
         <f t="shared" si="53"/>
@@ -28119,7 +28122,7 @@
       </c>
       <c r="N280" s="13">
         <f t="shared" si="56"/>
-        <v>1849</v>
+        <v>1839</v>
       </c>
       <c r="O280" s="13" t="str">
         <f t="shared" si="57"/>
@@ -28157,7 +28160,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="281" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="281" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A281" s="12" t="str">
         <f t="shared" si="52"/>
         <v/>
@@ -28166,16 +28169,16 @@
         <v>10</v>
       </c>
       <c r="C281" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="D281" s="12" t="s">
-        <v>45</v>
+        <v>583</v>
+      </c>
+      <c r="D281" s="16" t="s">
+        <v>71</v>
       </c>
       <c r="E281" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F281" s="12" t="s">
-        <v>645</v>
+        <v>584</v>
       </c>
       <c r="G281" s="13">
         <v>1849</v>
@@ -28243,27 +28246,27 @@
         <v/>
       </c>
       <c r="B282" s="12" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C282" s="12" t="s">
-        <v>450</v>
-      </c>
-      <c r="D282" s="16" t="s">
-        <v>52</v>
+        <v>644</v>
+      </c>
+      <c r="D282" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="E282" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F282" s="12" t="s">
-        <v>451</v>
+        <v>645</v>
       </c>
       <c r="G282" s="13">
-        <v>1892</v>
+        <v>1849</v>
       </c>
       <c r="H282" s="13"/>
       <c r="I282" s="13"/>
       <c r="J282" s="13">
-        <v>1882</v>
+        <v>1849</v>
       </c>
       <c r="K282" s="13">
         <f t="shared" si="53"/>
@@ -28271,7 +28274,7 @@
       </c>
       <c r="L282" s="13">
         <f t="shared" si="54"/>
-        <v>1892</v>
+        <v>1849</v>
       </c>
       <c r="M282" s="13" t="str">
         <f t="shared" si="55"/>
@@ -28279,7 +28282,7 @@
       </c>
       <c r="N282" s="13">
         <f t="shared" si="56"/>
-        <v>1882</v>
+        <v>1849</v>
       </c>
       <c r="O282" s="13" t="str">
         <f t="shared" si="57"/>
@@ -28323,27 +28326,27 @@
         <v/>
       </c>
       <c r="B283" s="12" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C283" s="12" t="s">
-        <v>555</v>
-      </c>
-      <c r="D283" s="12" t="s">
-        <v>45</v>
+        <v>450</v>
+      </c>
+      <c r="D283" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E283" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="F283" s="12" t="s">
-        <v>556</v>
+        <v>451</v>
       </c>
       <c r="G283" s="13">
-        <v>1852</v>
+        <v>1892</v>
       </c>
       <c r="H283" s="13"/>
       <c r="I283" s="13"/>
       <c r="J283" s="13">
-        <v>1839</v>
+        <v>1882</v>
       </c>
       <c r="K283" s="13">
         <f t="shared" si="53"/>
@@ -28351,7 +28354,7 @@
       </c>
       <c r="L283" s="13">
         <f t="shared" si="54"/>
-        <v>1852</v>
+        <v>1892</v>
       </c>
       <c r="M283" s="13" t="str">
         <f t="shared" si="55"/>
@@ -28359,7 +28362,7 @@
       </c>
       <c r="N283" s="13">
         <f t="shared" si="56"/>
-        <v>1839</v>
+        <v>1882</v>
       </c>
       <c r="O283" s="13" t="str">
         <f t="shared" si="57"/>
@@ -28397,33 +28400,33 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="284" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="284" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A284" s="12" t="str">
         <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="B284" s="12" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C284" s="12" t="s">
-        <v>557</v>
-      </c>
-      <c r="D284" s="16" t="s">
-        <v>59</v>
+        <v>555</v>
+      </c>
+      <c r="D284" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="E284" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F284" s="12" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="G284" s="13">
-        <v>1895</v>
+        <v>1852</v>
       </c>
       <c r="H284" s="13"/>
       <c r="I284" s="13"/>
       <c r="J284" s="13">
-        <v>1850</v>
+        <v>1839</v>
       </c>
       <c r="K284" s="13">
         <f t="shared" si="53"/>
@@ -28431,7 +28434,7 @@
       </c>
       <c r="L284" s="13">
         <f t="shared" si="54"/>
-        <v>1895</v>
+        <v>1852</v>
       </c>
       <c r="M284" s="13" t="str">
         <f t="shared" si="55"/>
@@ -28439,7 +28442,7 @@
       </c>
       <c r="N284" s="13">
         <f t="shared" si="56"/>
-        <v>1850</v>
+        <v>1839</v>
       </c>
       <c r="O284" s="13" t="str">
         <f t="shared" si="57"/>
@@ -28477,25 +28480,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="285" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="285" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A285" s="12" t="str">
         <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="B285" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C285" s="12" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D285" s="16" t="s">
         <v>59</v>
       </c>
       <c r="E285" s="12" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F285" s="12" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="G285" s="13">
         <v>1895</v>
@@ -28503,7 +28506,7 @@
       <c r="H285" s="13"/>
       <c r="I285" s="13"/>
       <c r="J285" s="13">
-        <v>1855</v>
+        <v>1850</v>
       </c>
       <c r="K285" s="13">
         <f t="shared" si="53"/>
@@ -28519,7 +28522,7 @@
       </c>
       <c r="N285" s="13">
         <f t="shared" si="56"/>
-        <v>1855</v>
+        <v>1850</v>
       </c>
       <c r="O285" s="13" t="str">
         <f t="shared" si="57"/>
@@ -28566,16 +28569,16 @@
         <v>18</v>
       </c>
       <c r="C286" s="12" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="D286" s="16" t="s">
         <v>59</v>
       </c>
       <c r="E286" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="F286" s="12" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G286" s="13">
         <v>1895</v>
@@ -28583,7 +28586,7 @@
       <c r="H286" s="13"/>
       <c r="I286" s="13"/>
       <c r="J286" s="13">
-        <v>1875</v>
+        <v>1855</v>
       </c>
       <c r="K286" s="13">
         <f t="shared" si="53"/>
@@ -28599,7 +28602,7 @@
       </c>
       <c r="N286" s="13">
         <f t="shared" si="56"/>
-        <v>1875</v>
+        <v>1855</v>
       </c>
       <c r="O286" s="13" t="str">
         <f t="shared" si="57"/>
@@ -28646,16 +28649,16 @@
         <v>18</v>
       </c>
       <c r="C287" s="12" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D287" s="16" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E287" s="12" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F287" s="12" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G287" s="13">
         <v>1895</v>
@@ -28726,16 +28729,16 @@
         <v>18</v>
       </c>
       <c r="C288" s="12" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D288" s="16" t="s">
         <v>71</v>
       </c>
       <c r="E288" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="F288" s="12" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G288" s="13">
         <v>1895</v>
@@ -28743,7 +28746,7 @@
       <c r="H288" s="13"/>
       <c r="I288" s="13"/>
       <c r="J288" s="13">
-        <v>1895</v>
+        <v>1875</v>
       </c>
       <c r="K288" s="13">
         <f t="shared" si="53"/>
@@ -28759,7 +28762,7 @@
       </c>
       <c r="N288" s="13">
         <f t="shared" si="56"/>
-        <v>1895</v>
+        <v>1875</v>
       </c>
       <c r="O288" s="13" t="str">
         <f t="shared" si="57"/>
@@ -28803,27 +28806,27 @@
         <v/>
       </c>
       <c r="B289" s="12" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C289" s="12" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="D289" s="16" t="s">
         <v>71</v>
       </c>
       <c r="E289" s="12" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F289" s="12" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="G289" s="13">
-        <v>1854</v>
+        <v>1895</v>
       </c>
       <c r="H289" s="13"/>
       <c r="I289" s="13"/>
       <c r="J289" s="13">
-        <v>1818</v>
+        <v>1895</v>
       </c>
       <c r="K289" s="13">
         <f t="shared" si="53"/>
@@ -28831,7 +28834,7 @@
       </c>
       <c r="L289" s="13">
         <f t="shared" si="54"/>
-        <v>1854</v>
+        <v>1895</v>
       </c>
       <c r="M289" s="13" t="str">
         <f t="shared" si="55"/>
@@ -28839,7 +28842,7 @@
       </c>
       <c r="N289" s="13">
         <f t="shared" si="56"/>
-        <v>1818</v>
+        <v>1895</v>
       </c>
       <c r="O289" s="13" t="str">
         <f t="shared" si="57"/>
@@ -28886,16 +28889,16 @@
         <v>10</v>
       </c>
       <c r="C290" s="12" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D290" s="16" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E290" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F290" s="12" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="G290" s="13">
         <v>1854</v>
@@ -28903,7 +28906,7 @@
       <c r="H290" s="13"/>
       <c r="I290" s="13"/>
       <c r="J290" s="13">
-        <v>1837</v>
+        <v>1818</v>
       </c>
       <c r="K290" s="13">
         <f t="shared" si="53"/>
@@ -28919,7 +28922,7 @@
       </c>
       <c r="N290" s="13">
         <f t="shared" si="56"/>
-        <v>1837</v>
+        <v>1818</v>
       </c>
       <c r="O290" s="13" t="str">
         <f t="shared" si="57"/>
@@ -28963,27 +28966,27 @@
         <v/>
       </c>
       <c r="B291" s="12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C291" s="12" t="s">
-        <v>577</v>
-      </c>
-      <c r="D291" s="12" t="s">
-        <v>49</v>
+        <v>571</v>
+      </c>
+      <c r="D291" s="16" t="s">
+        <v>59</v>
       </c>
       <c r="E291" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F291" s="12" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="G291" s="13">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="H291" s="13"/>
       <c r="I291" s="13"/>
       <c r="J291" s="13">
-        <v>1825</v>
+        <v>1829</v>
       </c>
       <c r="K291" s="13">
         <f t="shared" si="53"/>
@@ -28991,7 +28994,7 @@
       </c>
       <c r="L291" s="13">
         <f t="shared" si="54"/>
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="M291" s="13" t="str">
         <f t="shared" si="55"/>
@@ -28999,7 +29002,7 @@
       </c>
       <c r="N291" s="13">
         <f t="shared" si="56"/>
-        <v>1825</v>
+        <v>1829</v>
       </c>
       <c r="O291" s="13" t="str">
         <f t="shared" si="57"/>
@@ -29043,19 +29046,19 @@
         <v/>
       </c>
       <c r="B292" s="12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C292" s="12" t="s">
-        <v>579</v>
-      </c>
-      <c r="D292" s="16" t="s">
-        <v>52</v>
+        <v>577</v>
+      </c>
+      <c r="D292" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="E292" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F292" s="12" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="G292" s="13">
         <v>1855</v>
@@ -29063,7 +29066,7 @@
       <c r="H292" s="13"/>
       <c r="I292" s="13"/>
       <c r="J292" s="13">
-        <v>1839</v>
+        <v>1825</v>
       </c>
       <c r="K292" s="13">
         <f t="shared" si="53"/>
@@ -29079,7 +29082,7 @@
       </c>
       <c r="N292" s="13">
         <f t="shared" si="56"/>
-        <v>1839</v>
+        <v>1825</v>
       </c>
       <c r="O292" s="13" t="str">
         <f t="shared" si="57"/>
@@ -29117,25 +29120,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="293" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="293" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A293" s="12" t="str">
         <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="B293" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C293" s="12" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D293" s="16" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="E293" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F293" s="12" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G293" s="13">
         <v>1855</v>
@@ -29143,7 +29146,7 @@
       <c r="H293" s="13"/>
       <c r="I293" s="13"/>
       <c r="J293" s="13">
-        <v>1845</v>
+        <v>1839</v>
       </c>
       <c r="K293" s="13">
         <f t="shared" si="53"/>
@@ -29159,7 +29162,7 @@
       </c>
       <c r="N293" s="13">
         <f t="shared" si="56"/>
-        <v>1845</v>
+        <v>1839</v>
       </c>
       <c r="O293" s="13" t="str">
         <f t="shared" si="57"/>
@@ -29197,33 +29200,33 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="294" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="294" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A294" s="12" t="str">
         <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="B294" s="12" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C294" s="12" t="s">
-        <v>585</v>
-      </c>
-      <c r="D294" s="12" t="s">
-        <v>49</v>
+        <v>581</v>
+      </c>
+      <c r="D294" s="16" t="s">
+        <v>71</v>
       </c>
       <c r="E294" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F294" s="12" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="G294" s="13">
-        <v>1899</v>
+        <v>1855</v>
       </c>
       <c r="H294" s="13"/>
       <c r="I294" s="13"/>
       <c r="J294" s="13">
-        <v>1829</v>
+        <v>1845</v>
       </c>
       <c r="K294" s="13">
         <f t="shared" si="53"/>
@@ -29231,7 +29234,7 @@
       </c>
       <c r="L294" s="13">
         <f t="shared" si="54"/>
-        <v>1899</v>
+        <v>1855</v>
       </c>
       <c r="M294" s="13" t="str">
         <f t="shared" si="55"/>
@@ -29239,7 +29242,7 @@
       </c>
       <c r="N294" s="13">
         <f t="shared" si="56"/>
-        <v>1829</v>
+        <v>1845</v>
       </c>
       <c r="O294" s="13" t="str">
         <f t="shared" si="57"/>
@@ -29286,16 +29289,16 @@
         <v>18</v>
       </c>
       <c r="C295" s="12" t="s">
-        <v>589</v>
-      </c>
-      <c r="D295" s="16" t="s">
-        <v>59</v>
+        <v>585</v>
+      </c>
+      <c r="D295" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="E295" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F295" s="12" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="G295" s="13">
         <v>1899</v>
@@ -29303,7 +29306,7 @@
       <c r="H295" s="13"/>
       <c r="I295" s="13"/>
       <c r="J295" s="13">
-        <v>1869</v>
+        <v>1829</v>
       </c>
       <c r="K295" s="13">
         <f t="shared" si="53"/>
@@ -29319,7 +29322,7 @@
       </c>
       <c r="N295" s="13">
         <f t="shared" si="56"/>
-        <v>1869</v>
+        <v>1829</v>
       </c>
       <c r="O295" s="13" t="str">
         <f t="shared" si="57"/>
@@ -29366,7 +29369,7 @@
         <v>18</v>
       </c>
       <c r="C296" s="12" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D296" s="16" t="s">
         <v>59</v>
@@ -29375,7 +29378,7 @@
         <v>26</v>
       </c>
       <c r="F296" s="12" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G296" s="13">
         <v>1899</v>
@@ -29437,7 +29440,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="297" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="297" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A297" s="12" t="str">
         <f t="shared" si="52"/>
         <v/>
@@ -29446,16 +29449,16 @@
         <v>18</v>
       </c>
       <c r="C297" s="12" t="s">
-        <v>591</v>
-      </c>
-      <c r="D297" s="12" t="s">
-        <v>49</v>
+        <v>587</v>
+      </c>
+      <c r="D297" s="16" t="s">
+        <v>59</v>
       </c>
       <c r="E297" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="F297" s="12" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G297" s="13">
         <v>1899</v>
@@ -29463,7 +29466,7 @@
       <c r="H297" s="13"/>
       <c r="I297" s="13"/>
       <c r="J297" s="13">
-        <v>1899</v>
+        <v>1869</v>
       </c>
       <c r="K297" s="13">
         <f t="shared" si="53"/>
@@ -29479,7 +29482,7 @@
       </c>
       <c r="N297" s="13">
         <f t="shared" si="56"/>
-        <v>1899</v>
+        <v>1869</v>
       </c>
       <c r="O297" s="13" t="str">
         <f t="shared" si="57"/>
@@ -29517,33 +29520,33 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="298" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="298" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A298" s="12" t="str">
         <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="B298" s="12" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C298" s="12" t="s">
-        <v>688</v>
-      </c>
-      <c r="D298" s="16" t="s">
-        <v>71</v>
+        <v>591</v>
+      </c>
+      <c r="D298" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="E298" s="12" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F298" s="12" t="s">
-        <v>689</v>
+        <v>592</v>
       </c>
       <c r="G298" s="13">
-        <v>1857</v>
+        <v>1899</v>
       </c>
       <c r="H298" s="13"/>
       <c r="I298" s="13"/>
       <c r="J298" s="13">
-        <v>1827</v>
+        <v>1899</v>
       </c>
       <c r="K298" s="13">
         <f t="shared" si="53"/>
@@ -29551,7 +29554,7 @@
       </c>
       <c r="L298" s="13">
         <f t="shared" si="54"/>
-        <v>1857</v>
+        <v>1899</v>
       </c>
       <c r="M298" s="13" t="str">
         <f t="shared" si="55"/>
@@ -29559,7 +29562,7 @@
       </c>
       <c r="N298" s="13">
         <f t="shared" si="56"/>
-        <v>1827</v>
+        <v>1899</v>
       </c>
       <c r="O298" s="13" t="str">
         <f t="shared" si="57"/>
@@ -29603,27 +29606,27 @@
         <v/>
       </c>
       <c r="B299" s="12" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C299" s="12" t="s">
-        <v>593</v>
+        <v>688</v>
       </c>
       <c r="D299" s="16" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="E299" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="F299" s="12" t="s">
-        <v>594</v>
+        <v>689</v>
       </c>
       <c r="G299" s="13">
-        <v>1900</v>
+        <v>1857</v>
       </c>
       <c r="H299" s="13"/>
       <c r="I299" s="13"/>
       <c r="J299" s="13">
-        <v>1890</v>
+        <v>1827</v>
       </c>
       <c r="K299" s="13">
         <f t="shared" si="53"/>
@@ -29631,7 +29634,7 @@
       </c>
       <c r="L299" s="13">
         <f t="shared" si="54"/>
-        <v>1900</v>
+        <v>1857</v>
       </c>
       <c r="M299" s="13" t="str">
         <f t="shared" si="55"/>
@@ -29639,7 +29642,7 @@
       </c>
       <c r="N299" s="13">
         <f t="shared" si="56"/>
-        <v>1890</v>
+        <v>1827</v>
       </c>
       <c r="O299" s="13" t="str">
         <f t="shared" si="57"/>
@@ -29677,33 +29680,33 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="300" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="300" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A300" s="12" t="str">
         <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="B300" s="12" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C300" s="12" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="D300" s="16" t="s">
         <v>52</v>
       </c>
       <c r="E300" s="12" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F300" s="12" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="G300" s="13">
-        <v>1858</v>
+        <v>1900</v>
       </c>
       <c r="H300" s="13"/>
       <c r="I300" s="13"/>
       <c r="J300" s="13">
-        <v>1848</v>
+        <v>1890</v>
       </c>
       <c r="K300" s="13">
         <f t="shared" si="53"/>
@@ -29711,7 +29714,7 @@
       </c>
       <c r="L300" s="13">
         <f t="shared" si="54"/>
-        <v>1858</v>
+        <v>1900</v>
       </c>
       <c r="M300" s="13" t="str">
         <f t="shared" si="55"/>
@@ -29719,7 +29722,7 @@
       </c>
       <c r="N300" s="13">
         <f t="shared" si="56"/>
-        <v>1848</v>
+        <v>1890</v>
       </c>
       <c r="O300" s="13" t="str">
         <f t="shared" si="57"/>
@@ -30477,25 +30480,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="310" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="310" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A310" s="12" t="str">
         <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="B310" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C310" s="12" t="s">
-        <v>624</v>
+        <v>654</v>
       </c>
       <c r="D310" s="16" t="s">
         <v>59</v>
       </c>
       <c r="E310" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="F310" s="12" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="G310" s="13">
         <v>1866</v>
@@ -30503,7 +30506,7 @@
       <c r="H310" s="13"/>
       <c r="I310" s="13"/>
       <c r="J310" s="13">
-        <v>1831</v>
+        <v>1846</v>
       </c>
       <c r="K310" s="13">
         <f t="shared" si="53"/>
@@ -30519,7 +30522,7 @@
       </c>
       <c r="N310" s="13">
         <f t="shared" si="56"/>
-        <v>1831</v>
+        <v>1846</v>
       </c>
       <c r="O310" s="13" t="str">
         <f t="shared" si="57"/>
@@ -30557,25 +30560,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="311" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="311" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A311" s="12" t="str">
         <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="B311" s="12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C311" s="12" t="s">
-        <v>654</v>
+        <v>624</v>
       </c>
       <c r="D311" s="16" t="s">
         <v>59</v>
       </c>
       <c r="E311" s="12" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F311" s="12" t="s">
-        <v>655</v>
+        <v>625</v>
       </c>
       <c r="G311" s="13">
         <v>1866</v>
@@ -36397,25 +36400,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="384" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="384" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A384" s="12" t="str">
         <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="B384" s="12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C384" s="12" t="s">
-        <v>776</v>
-      </c>
-      <c r="D384" s="18" t="s">
-        <v>49</v>
+        <v>817</v>
+      </c>
+      <c r="D384" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E384" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="F384" s="12" t="s">
-        <v>777</v>
+        <v>818</v>
       </c>
       <c r="G384" s="13">
         <v>1899</v>
@@ -36477,7 +36480,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="385" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="385" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A385" s="12" t="str">
         <f t="shared" si="65"/>
         <v/>
@@ -36486,16 +36489,16 @@
         <v>10</v>
       </c>
       <c r="C385" s="12" t="s">
-        <v>817</v>
+        <v>795</v>
       </c>
       <c r="D385" s="16" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E385" s="12" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F385" s="12" t="s">
-        <v>818</v>
+        <v>796</v>
       </c>
       <c r="G385" s="13">
         <v>1899</v>
@@ -36557,7 +36560,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="386" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="386" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A386" s="12" t="str">
         <f t="shared" si="65"/>
         <v/>
@@ -36566,16 +36569,16 @@
         <v>10</v>
       </c>
       <c r="C386" s="12" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="D386" s="16" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E386" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F386" s="12" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="G386" s="13">
         <v>1899</v>
@@ -36637,25 +36640,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="387" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="387" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A387" s="12" t="str">
         <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="B387" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C387" s="12" t="s">
-        <v>799</v>
+        <v>768</v>
       </c>
       <c r="D387" s="16" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E387" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="F387" s="12" t="s">
-        <v>800</v>
+        <v>769</v>
       </c>
       <c r="G387" s="13">
         <v>1899</v>
@@ -36663,7 +36666,7 @@
       <c r="H387" s="13"/>
       <c r="I387" s="13"/>
       <c r="J387" s="13">
-        <v>1889</v>
+        <v>1897</v>
       </c>
       <c r="K387" s="13">
         <f t="shared" si="66"/>
@@ -36679,7 +36682,7 @@
       </c>
       <c r="N387" s="13">
         <f t="shared" si="69"/>
-        <v>1889</v>
+        <v>1897</v>
       </c>
       <c r="O387" s="13" t="str">
         <f t="shared" si="70"/>
@@ -36717,25 +36720,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="388" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="388" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A388" s="12" t="str">
         <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="B388" s="12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C388" s="12" t="s">
-        <v>768</v>
+        <v>778</v>
       </c>
       <c r="D388" s="16" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E388" s="12" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F388" s="12" t="s">
-        <v>769</v>
+        <v>779</v>
       </c>
       <c r="G388" s="13">
         <v>1899</v>
@@ -36743,7 +36746,7 @@
       <c r="H388" s="13"/>
       <c r="I388" s="13"/>
       <c r="J388" s="13">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="K388" s="13">
         <f t="shared" si="66"/>
@@ -36759,7 +36762,7 @@
       </c>
       <c r="N388" s="13">
         <f t="shared" si="69"/>
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="O388" s="13" t="str">
         <f t="shared" si="70"/>
@@ -36803,19 +36806,19 @@
         <v/>
       </c>
       <c r="B389" s="12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C389" s="12" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="D389" s="16" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E389" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F389" s="12" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="G389" s="13">
         <v>1899</v>
@@ -36823,7 +36826,7 @@
       <c r="H389" s="13"/>
       <c r="I389" s="13"/>
       <c r="J389" s="13">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="K389" s="13">
         <f t="shared" si="66"/>
@@ -36839,7 +36842,7 @@
       </c>
       <c r="N389" s="13">
         <f t="shared" si="69"/>
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="O389" s="13" t="str">
         <f t="shared" si="70"/>
@@ -36877,7 +36880,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="390" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="390" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A390" s="12" t="str">
         <f t="shared" si="65"/>
         <v/>
@@ -36886,16 +36889,16 @@
         <v>8</v>
       </c>
       <c r="C390" s="12" t="s">
-        <v>780</v>
-      </c>
-      <c r="D390" s="16" t="s">
-        <v>59</v>
+        <v>782</v>
+      </c>
+      <c r="D390" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="E390" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="F390" s="12" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="G390" s="13">
         <v>1899</v>
@@ -36957,16 +36960,16 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="391" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="391" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A391" s="12" t="str">
         <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="B391" s="12" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C391" s="12" t="s">
-        <v>782</v>
+        <v>710</v>
       </c>
       <c r="D391" s="12" t="s">
         <v>49</v>
@@ -36975,7 +36978,7 @@
         <v>26</v>
       </c>
       <c r="F391" s="12" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G391" s="13">
         <v>1899</v>
@@ -37046,16 +37049,16 @@
         <v>14</v>
       </c>
       <c r="C392" s="12" t="s">
-        <v>710</v>
-      </c>
-      <c r="D392" s="12" t="s">
-        <v>49</v>
+        <v>868</v>
+      </c>
+      <c r="D392" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E392" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F392" s="12" t="s">
-        <v>784</v>
+        <v>869</v>
       </c>
       <c r="G392" s="13">
         <v>1899</v>
@@ -37126,16 +37129,16 @@
         <v>14</v>
       </c>
       <c r="C393" s="12" t="s">
-        <v>868</v>
-      </c>
-      <c r="D393" s="16" t="s">
-        <v>52</v>
+        <v>863</v>
+      </c>
+      <c r="D393" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="E393" s="12" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F393" s="12" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="G393" s="13">
         <v>1899</v>
@@ -37197,7 +37200,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="394" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="394" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A394" s="12" t="str">
         <f t="shared" si="65"/>
         <v/>
@@ -37206,7 +37209,7 @@
         <v>14</v>
       </c>
       <c r="C394" s="12" t="s">
-        <v>863</v>
+        <v>811</v>
       </c>
       <c r="D394" s="12" t="s">
         <v>49</v>
@@ -37215,7 +37218,7 @@
         <v>62</v>
       </c>
       <c r="F394" s="12" t="s">
-        <v>864</v>
+        <v>812</v>
       </c>
       <c r="G394" s="13">
         <v>1899</v>
@@ -37277,25 +37280,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="395" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="395" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A395" s="12" t="str">
         <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="B395" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C395" s="12" t="s">
-        <v>811</v>
-      </c>
-      <c r="D395" s="12" t="s">
+        <v>785</v>
+      </c>
+      <c r="D395" s="18" t="s">
         <v>49</v>
       </c>
       <c r="E395" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="F395" s="12" t="s">
-        <v>812</v>
+        <v>786</v>
       </c>
       <c r="G395" s="13">
         <v>1899</v>
@@ -37357,7 +37360,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="396" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="396" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A396" s="12" t="str">
         <f t="shared" si="65"/>
         <v/>
@@ -37366,16 +37369,16 @@
         <v>12</v>
       </c>
       <c r="C396" s="12" t="s">
-        <v>785</v>
-      </c>
-      <c r="D396" s="18" t="s">
-        <v>49</v>
+        <v>787</v>
+      </c>
+      <c r="D396" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E396" s="12" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F396" s="12" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="G396" s="13">
         <v>1899</v>
@@ -37446,16 +37449,16 @@
         <v>12</v>
       </c>
       <c r="C397" s="12" t="s">
-        <v>787</v>
-      </c>
-      <c r="D397" s="16" t="s">
-        <v>52</v>
+        <v>776</v>
+      </c>
+      <c r="D397" s="18" t="s">
+        <v>49</v>
       </c>
       <c r="E397" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F397" s="12" t="s">
-        <v>788</v>
+        <v>777</v>
       </c>
       <c r="G397" s="13">
         <v>1899</v>
@@ -56945,19 +56948,19 @@
         <v/>
       </c>
       <c r="B646" s="12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C646" s="12" t="s">
-        <v>1251</v>
-      </c>
-      <c r="D646" s="16" t="s">
-        <v>71</v>
+        <v>1281</v>
+      </c>
+      <c r="D646" s="12" t="s">
+        <v>304</v>
       </c>
       <c r="E646" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F646" s="12" t="s">
-        <v>1252</v>
+        <v>1282</v>
       </c>
       <c r="G646" s="13">
         <v>1845</v>
@@ -57023,19 +57026,19 @@
         <v/>
       </c>
       <c r="B647" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C647" s="12" t="s">
-        <v>1281</v>
-      </c>
-      <c r="D647" s="12" t="s">
-        <v>304</v>
+        <v>1237</v>
+      </c>
+      <c r="D647" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E647" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F647" s="12" t="s">
-        <v>1282</v>
+        <v>1238</v>
       </c>
       <c r="G647" s="13">
         <v>1845</v>
@@ -57043,7 +57046,7 @@
       <c r="H647" s="13"/>
       <c r="I647" s="13"/>
       <c r="J647" s="13">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="K647" s="13">
         <f t="shared" si="118"/>
@@ -57059,7 +57062,7 @@
       </c>
       <c r="N647" s="13">
         <f t="shared" si="121"/>
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="O647" s="13" t="str">
         <f t="shared" si="122"/>
@@ -57095,7 +57098,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="648" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="648" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A648" s="12" t="str">
         <f t="shared" si="117"/>
         <v/>
@@ -57104,7 +57107,7 @@
         <v>12</v>
       </c>
       <c r="C648" s="12" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="D648" s="16" t="s">
         <v>52</v>
@@ -57113,7 +57116,7 @@
         <v>26</v>
       </c>
       <c r="F648" s="12" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="G648" s="13">
         <v>1845</v>
@@ -57173,25 +57176,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="649" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="649" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A649" s="12" t="str">
         <f t="shared" si="117"/>
         <v/>
       </c>
       <c r="B649" s="12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C649" s="12" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="D649" s="16" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E649" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F649" s="12" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="G649" s="13">
         <v>1845</v>
@@ -57199,7 +57202,7 @@
       <c r="H649" s="13"/>
       <c r="I649" s="13"/>
       <c r="J649" s="13">
-        <v>1835</v>
+        <v>1839</v>
       </c>
       <c r="K649" s="13">
         <f t="shared" si="118"/>
@@ -57215,7 +57218,7 @@
       </c>
       <c r="N649" s="13">
         <f t="shared" si="121"/>
-        <v>1835</v>
+        <v>1839</v>
       </c>
       <c r="O649" s="13" t="str">
         <f t="shared" si="122"/>
@@ -57251,25 +57254,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="650" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="650" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A650" s="12" t="str">
         <f t="shared" si="117"/>
         <v/>
       </c>
       <c r="B650" s="12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C650" s="12" t="s">
-        <v>1243</v>
-      </c>
-      <c r="D650" s="16" t="s">
-        <v>59</v>
+        <v>1497</v>
+      </c>
+      <c r="D650" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="E650" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F650" s="12" t="s">
-        <v>1244</v>
+        <v>1498</v>
       </c>
       <c r="G650" s="13">
         <v>1845</v>
@@ -57277,7 +57280,7 @@
       <c r="H650" s="13"/>
       <c r="I650" s="13"/>
       <c r="J650" s="13">
-        <v>1839</v>
+        <v>1845</v>
       </c>
       <c r="K650" s="13">
         <f t="shared" si="118"/>
@@ -57293,7 +57296,7 @@
       </c>
       <c r="N650" s="13">
         <f t="shared" si="121"/>
-        <v>1839</v>
+        <v>1845</v>
       </c>
       <c r="O650" s="13" t="str">
         <f t="shared" si="122"/>
@@ -57335,19 +57338,19 @@
         <v/>
       </c>
       <c r="B651" s="12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C651" s="12" t="s">
-        <v>1497</v>
+        <v>1249</v>
       </c>
       <c r="D651" s="12" t="s">
-        <v>49</v>
+        <v>749</v>
       </c>
       <c r="E651" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F651" s="12" t="s">
-        <v>1498</v>
+        <v>1250</v>
       </c>
       <c r="G651" s="13">
         <v>1845</v>
@@ -57413,19 +57416,19 @@
         <v/>
       </c>
       <c r="B652" s="12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C652" s="12" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D652" s="12" t="s">
-        <v>749</v>
+        <v>1251</v>
+      </c>
+      <c r="D652" s="16" t="s">
+        <v>71</v>
       </c>
       <c r="E652" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F652" s="12" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="G652" s="13">
         <v>1845</v>
@@ -57433,7 +57436,7 @@
       <c r="H652" s="13"/>
       <c r="I652" s="13"/>
       <c r="J652" s="13">
-        <v>1845</v>
+        <v>1849</v>
       </c>
       <c r="K652" s="13">
         <f t="shared" si="118"/>
@@ -57449,7 +57452,7 @@
       </c>
       <c r="N652" s="13">
         <f t="shared" si="121"/>
-        <v>1845</v>
+        <v>1849</v>
       </c>
       <c r="O652" s="13" t="str">
         <f t="shared" si="122"/>
@@ -57641,7 +57644,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="655" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="655" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A655" s="12" t="str">
         <f t="shared" ref="A655:A718" si="130">IF($T655="","",1+COUNTIF($W$15:$W$878,"&lt;"&amp;W655))</f>
         <v/>
@@ -57650,16 +57653,16 @@
         <v>10</v>
       </c>
       <c r="C655" s="12" t="s">
-        <v>1261</v>
+        <v>1389</v>
       </c>
       <c r="D655" s="16" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E655" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F655" s="12" t="s">
-        <v>1262</v>
+        <v>1390</v>
       </c>
       <c r="G655" s="13">
         <v>1848</v>
@@ -57667,7 +57670,7 @@
       <c r="H655" s="13"/>
       <c r="I655" s="13"/>
       <c r="J655" s="13">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="K655" s="13">
         <f t="shared" ref="K655:K684" si="131">IF(AND(IFERROR(SEARCH("현대오일뱅크",$C655),0)&gt;0,IFERROR(SEARCH("직영",$C655),0)&gt;0),$B$13,0)</f>
@@ -57683,7 +57686,7 @@
       </c>
       <c r="N655" s="13">
         <f t="shared" ref="N655:N718" si="134">IF($J655="","",$J655+$K655)</f>
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="O655" s="13" t="str">
         <f t="shared" ref="O655:O718" si="135">IF($B$10=0,"",IFERROR(IF($B$4&gt;0,"휘발유 "&amp;TEXT(IF($L655="",1/0,$L655*$B$4),"#,##0")&amp;"원","")&amp;IF($B$5&gt;0,IF($B$4&gt;0," / ","")&amp;"고급유 "&amp;TEXT(IF($M655="",1/0,$M655*$B$5),"#,##0")&amp;"원","")&amp;IF($B$6&gt;0,IF(OR($B$4&gt;0,$B$5&gt;0)," / ","")&amp;"경유 "&amp;TEXT(IF($N655="",1/0,$N655*$B$6),"#,##0")&amp;"원",""),""))</f>
@@ -57719,7 +57722,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="656" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="656" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A656" s="12" t="str">
         <f t="shared" si="130"/>
         <v/>
@@ -57728,16 +57731,16 @@
         <v>10</v>
       </c>
       <c r="C656" s="12" t="s">
-        <v>1389</v>
-      </c>
-      <c r="D656" s="16" t="s">
-        <v>52</v>
+        <v>1429</v>
+      </c>
+      <c r="D656" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="E656" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F656" s="12" t="s">
-        <v>1390</v>
+        <v>1430</v>
       </c>
       <c r="G656" s="13">
         <v>1848</v>
@@ -57803,19 +57806,19 @@
         <v/>
       </c>
       <c r="B657" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C657" s="12" t="s">
-        <v>1429</v>
-      </c>
-      <c r="D657" s="12" t="s">
-        <v>49</v>
+        <v>1453</v>
+      </c>
+      <c r="D657" s="16" t="s">
+        <v>71</v>
       </c>
       <c r="E657" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F657" s="12" t="s">
-        <v>1430</v>
+        <v>1454</v>
       </c>
       <c r="G657" s="13">
         <v>1848</v>
@@ -57823,7 +57826,7 @@
       <c r="H657" s="13"/>
       <c r="I657" s="13"/>
       <c r="J657" s="13">
-        <v>1819</v>
+        <v>1824</v>
       </c>
       <c r="K657" s="13">
         <f t="shared" si="131"/>
@@ -57839,7 +57842,7 @@
       </c>
       <c r="N657" s="13">
         <f t="shared" si="134"/>
-        <v>1819</v>
+        <v>1824</v>
       </c>
       <c r="O657" s="13" t="str">
         <f t="shared" si="135"/>
@@ -57881,19 +57884,19 @@
         <v/>
       </c>
       <c r="B658" s="12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C658" s="12" t="s">
-        <v>1453</v>
+        <v>1261</v>
       </c>
       <c r="D658" s="16" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E658" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F658" s="12" t="s">
-        <v>1454</v>
+        <v>1262</v>
       </c>
       <c r="G658" s="13">
         <v>1848</v>
@@ -57901,7 +57904,7 @@
       <c r="H658" s="13"/>
       <c r="I658" s="13"/>
       <c r="J658" s="13">
-        <v>1824</v>
+        <v>1848</v>
       </c>
       <c r="K658" s="13">
         <f t="shared" si="131"/>
@@ -57917,7 +57920,7 @@
       </c>
       <c r="N658" s="13">
         <f t="shared" si="134"/>
-        <v>1824</v>
+        <v>1848</v>
       </c>
       <c r="O658" s="13" t="str">
         <f t="shared" si="135"/>
@@ -57959,19 +57962,19 @@
         <v/>
       </c>
       <c r="B659" s="12" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C659" s="12" t="s">
-        <v>1491</v>
-      </c>
-      <c r="D659" s="16" t="s">
-        <v>52</v>
+        <v>1263</v>
+      </c>
+      <c r="D659" s="18" t="s">
+        <v>749</v>
       </c>
       <c r="E659" s="12" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F659" s="12" t="s">
-        <v>1492</v>
+        <v>1264</v>
       </c>
       <c r="G659" s="13">
         <v>1848</v>
@@ -57979,7 +57982,7 @@
       <c r="H659" s="13"/>
       <c r="I659" s="13"/>
       <c r="J659" s="13">
-        <v>1834</v>
+        <v>1855</v>
       </c>
       <c r="K659" s="13">
         <f t="shared" si="131"/>
@@ -57995,7 +57998,7 @@
       </c>
       <c r="N659" s="13">
         <f t="shared" si="134"/>
-        <v>1834</v>
+        <v>1855</v>
       </c>
       <c r="O659" s="13" t="str">
         <f t="shared" si="135"/>
@@ -58037,19 +58040,19 @@
         <v/>
       </c>
       <c r="B660" s="12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C660" s="12" t="s">
-        <v>1263</v>
-      </c>
-      <c r="D660" s="18" t="s">
-        <v>749</v>
+        <v>1491</v>
+      </c>
+      <c r="D660" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E660" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="F660" s="12" t="s">
-        <v>1264</v>
+        <v>1492</v>
       </c>
       <c r="G660" s="13">
         <v>1848</v>
@@ -58057,7 +58060,7 @@
       <c r="H660" s="13"/>
       <c r="I660" s="13"/>
       <c r="J660" s="13">
-        <v>1855</v>
+        <v>1884</v>
       </c>
       <c r="K660" s="13">
         <f t="shared" si="131"/>
@@ -58073,7 +58076,7 @@
       </c>
       <c r="N660" s="13">
         <f t="shared" si="134"/>
-        <v>1855</v>
+        <v>1884</v>
       </c>
       <c r="O660" s="13" t="str">
         <f t="shared" si="135"/>
@@ -73236,25 +73239,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="855" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="855" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A855" s="12" t="str">
         <f t="shared" si="174"/>
         <v/>
       </c>
       <c r="B855" s="12" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C855" s="12" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="D855" s="16" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="E855" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="F855" s="12" t="s">
-        <v>1694</v>
+        <v>1696</v>
       </c>
       <c r="G855" s="13">
         <v>1909</v>
@@ -73262,7 +73265,7 @@
       <c r="H855" s="13"/>
       <c r="I855" s="13"/>
       <c r="J855" s="13">
-        <v>1899</v>
+        <v>1890</v>
       </c>
       <c r="K855" s="13">
         <f t="shared" si="173"/>
@@ -73278,7 +73281,7 @@
       </c>
       <c r="N855" s="13">
         <f t="shared" si="177"/>
-        <v>1899</v>
+        <v>1890</v>
       </c>
       <c r="O855" s="13" t="str">
         <f t="shared" si="178"/>
@@ -73314,25 +73317,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="856" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="856" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A856" s="12" t="str">
         <f t="shared" si="174"/>
         <v/>
       </c>
       <c r="B856" s="12" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C856" s="12" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="D856" s="16" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="E856" s="12" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F856" s="12" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="G856" s="13">
         <v>1909</v>
@@ -75213,199 +75216,528 @@
       </c>
     </row>
     <row r="4" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A4" s="21"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
+      <c r="A4" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E4" s="23">
+        <v>1886</v>
+      </c>
+      <c r="F4" s="23">
+        <v>1896</v>
+      </c>
+      <c r="G4" s="23">
+        <f t="shared" ref="G4:G16" si="0">IF(OR(E4="",F4=""),"",F4-E4)</f>
+        <v>10</v>
+      </c>
+      <c r="H4" s="23">
+        <v>2250</v>
+      </c>
+      <c r="I4" s="23">
+        <v>2250</v>
+      </c>
+      <c r="J4" s="23">
+        <f t="shared" ref="J4:J16" si="1">IF(OR(H4="",I4=""),"",I4-H4)</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="23">
+        <v>1876</v>
+      </c>
+      <c r="L4" s="23">
+        <v>1876</v>
+      </c>
+      <c r="M4" s="23">
+        <f t="shared" ref="M4:M16" si="2">IF(OR(K4="",L4=""),"",L4-K4)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A5" s="21"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
+      <c r="A5" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>470</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>471</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E5" s="23">
+        <v>1859</v>
+      </c>
+      <c r="F5" s="23">
+        <v>1859</v>
+      </c>
+      <c r="G5" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H5" s="23"/>
       <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
+      <c r="J5" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K5" s="23">
+        <v>1849</v>
+      </c>
+      <c r="L5" s="23">
+        <v>1869</v>
+      </c>
+      <c r="M5" s="23">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="6" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A6" s="21"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
+      <c r="A6" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>436</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>437</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E6" s="23">
+        <v>1869</v>
+      </c>
+      <c r="F6" s="23">
+        <v>1869</v>
+      </c>
+      <c r="G6" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H6" s="23"/>
       <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
+      <c r="J6" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K6" s="23">
+        <v>1849</v>
+      </c>
+      <c r="L6" s="23">
+        <v>1854</v>
+      </c>
+      <c r="M6" s="23">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="7" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A7" s="21"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
+      <c r="A7" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>474</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>475</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E7" s="23">
+        <v>1880</v>
+      </c>
+      <c r="F7" s="23">
+        <v>1880</v>
+      </c>
+      <c r="G7" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H7" s="23"/>
       <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
+      <c r="J7" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K7" s="23">
+        <v>1860</v>
+      </c>
+      <c r="L7" s="23">
+        <v>1890</v>
+      </c>
+      <c r="M7" s="23">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
     </row>
     <row r="8" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A8" s="21"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
+      <c r="A8" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>523</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>524</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E8" s="23">
+        <v>1889</v>
+      </c>
+      <c r="F8" s="23">
+        <v>1889</v>
+      </c>
+      <c r="G8" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H8" s="23"/>
       <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
+      <c r="J8" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K8" s="23">
+        <v>1847</v>
+      </c>
+      <c r="L8" s="23">
+        <v>1867</v>
+      </c>
+      <c r="M8" s="23">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="9" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A9" s="21"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
+      <c r="A9" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>571</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>572</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E9" s="23">
+        <v>1854</v>
+      </c>
+      <c r="F9" s="23">
+        <v>1854</v>
+      </c>
+      <c r="G9" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H9" s="23"/>
       <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
+      <c r="J9" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K9" s="23">
+        <v>1837</v>
+      </c>
+      <c r="L9" s="23">
+        <v>1829</v>
+      </c>
+      <c r="M9" s="23">
+        <f t="shared" si="2"/>
+        <v>-8</v>
+      </c>
     </row>
     <row r="10" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A10" s="21"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
+      <c r="A10" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>599</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>600</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E10" s="23">
+        <v>1858</v>
+      </c>
+      <c r="F10" s="23">
+        <v>1848</v>
+      </c>
+      <c r="G10" s="23">
+        <f t="shared" si="0"/>
+        <v>-10</v>
+      </c>
       <c r="H10" s="23"/>
       <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
+      <c r="J10" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K10" s="23">
+        <v>1848</v>
+      </c>
+      <c r="L10" s="23">
+        <v>1838</v>
+      </c>
+      <c r="M10" s="23">
+        <f t="shared" si="2"/>
+        <v>-10</v>
+      </c>
     </row>
     <row r="11" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A11" s="21"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
+      <c r="A11" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>624</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>625</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E11" s="23">
+        <v>1866</v>
+      </c>
+      <c r="F11" s="23">
+        <v>1866</v>
+      </c>
+      <c r="G11" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H11" s="23"/>
       <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
+      <c r="J11" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K11" s="23">
+        <v>1831</v>
+      </c>
+      <c r="L11" s="23">
+        <v>1846</v>
+      </c>
+      <c r="M11" s="23">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A12" s="21"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
+      <c r="A12" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>776</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>777</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E12" s="23">
+        <v>1899</v>
+      </c>
+      <c r="F12" s="23">
+        <v>1899</v>
+      </c>
+      <c r="G12" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H12" s="23"/>
       <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
+      <c r="J12" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K12" s="23">
+        <v>1889</v>
+      </c>
+      <c r="L12" s="23">
+        <v>1899</v>
+      </c>
+      <c r="M12" s="23">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="13" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A13" s="21"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
+      <c r="A13" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E13" s="23">
+        <v>1845</v>
+      </c>
+      <c r="F13" s="23">
+        <v>1845</v>
+      </c>
+      <c r="G13" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H13" s="23"/>
       <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
+      <c r="J13" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K13" s="23">
+        <v>1834</v>
+      </c>
+      <c r="L13" s="23">
+        <v>1849</v>
+      </c>
+      <c r="M13" s="23">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
     </row>
     <row r="14" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A14" s="21"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
+      <c r="A14" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E14" s="23">
+        <v>1848</v>
+      </c>
+      <c r="F14" s="23">
+        <v>1848</v>
+      </c>
+      <c r="G14" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H14" s="23"/>
       <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
+      <c r="J14" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K14" s="23">
+        <v>1818</v>
+      </c>
+      <c r="L14" s="23">
+        <v>1848</v>
+      </c>
+      <c r="M14" s="23">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
     </row>
     <row r="15" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A15" s="21"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
+      <c r="A15" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E15" s="23">
+        <v>1848</v>
+      </c>
+      <c r="F15" s="23">
+        <v>1848</v>
+      </c>
+      <c r="G15" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H15" s="23"/>
       <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
+      <c r="J15" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K15" s="23">
+        <v>1834</v>
+      </c>
+      <c r="L15" s="23">
+        <v>1884</v>
+      </c>
+      <c r="M15" s="23">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
     </row>
     <row r="16" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A16" s="21"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
+      <c r="A16" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>1696</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E16" s="23">
+        <v>1909</v>
+      </c>
+      <c r="F16" s="23">
+        <v>1909</v>
+      </c>
+      <c r="G16" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H16" s="23"/>
       <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
+      <c r="J16" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K16" s="23">
+        <v>1899</v>
+      </c>
+      <c r="L16" s="23">
+        <v>1890</v>
+      </c>
+      <c r="M16" s="23">
+        <f t="shared" si="2"/>
+        <v>-9</v>
+      </c>
     </row>
     <row r="17" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
       <c r="A17" s="21"/>
@@ -78817,7 +79149,7 @@
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <phoneticPr fontId="27" type="noConversion"/>
-  <conditionalFormatting sqref="G4:G4">
+  <conditionalFormatting sqref="G4:G16">
     <cfRule type="cellIs" dxfId="5" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -78825,7 +79157,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J4">
+  <conditionalFormatting sqref="J4:J16">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -78833,7 +79165,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M4">
+  <conditionalFormatting sqref="M4:M16">
     <cfRule type="cellIs" dxfId="1" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>

--- a/fuel_cost_chungcheong.xlsx
+++ b/fuel_cost_chungcheong.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4799" uniqueCount="1765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4707" uniqueCount="1765">
   <si>
     <t>유류비 계산(혼유, 지역화폐 등)</t>
   </si>
@@ -44007,7 +44007,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="480" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="480" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A480" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
@@ -44016,7 +44016,7 @@
         <v>6</v>
       </c>
       <c r="C480" s="12" t="s">
-        <v>908</v>
+        <v>956</v>
       </c>
       <c r="D480" s="16" t="s">
         <v>61</v>
@@ -44025,7 +44025,7 @@
         <v>26</v>
       </c>
       <c r="F480" s="12" t="s">
-        <v>909</v>
+        <v>957</v>
       </c>
       <c r="G480" s="13">
         <v>1812</v>
@@ -44085,7 +44085,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="481" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="481" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A481" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
@@ -44094,24 +44094,24 @@
         <v>6</v>
       </c>
       <c r="C481" s="12" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D481" s="12" t="s">
-        <v>45</v>
+        <v>908</v>
+      </c>
+      <c r="D481" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="E481" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F481" s="12" t="s">
-        <v>1173</v>
+        <v>909</v>
       </c>
       <c r="G481" s="13">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H481" s="13"/>
       <c r="I481" s="13"/>
       <c r="J481" s="13">
-        <v>1799</v>
+        <v>1795</v>
       </c>
       <c r="K481" s="13">
         <f t="shared" si="92"/>
@@ -44119,7 +44119,7 @@
       </c>
       <c r="L481" s="13">
         <f t="shared" si="93"/>
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="M481" s="13" t="str">
         <f t="shared" si="94"/>
@@ -44127,7 +44127,7 @@
       </c>
       <c r="N481" s="13">
         <f t="shared" si="95"/>
-        <v>1799</v>
+        <v>1795</v>
       </c>
       <c r="O481" s="13" t="str">
         <f t="shared" si="96"/>
@@ -44163,7 +44163,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="482" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="482" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A482" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
@@ -44172,16 +44172,16 @@
         <v>6</v>
       </c>
       <c r="C482" s="12" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D482" s="16" t="s">
-        <v>61</v>
+        <v>1172</v>
+      </c>
+      <c r="D482" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="E482" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F482" s="12" t="s">
-        <v>1025</v>
+        <v>1173</v>
       </c>
       <c r="G482" s="13">
         <v>1813</v>
@@ -44189,7 +44189,7 @@
       <c r="H482" s="13"/>
       <c r="I482" s="13"/>
       <c r="J482" s="13">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="K482" s="13">
         <f t="shared" si="92"/>
@@ -44205,7 +44205,7 @@
       </c>
       <c r="N482" s="13">
         <f t="shared" si="95"/>
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="O482" s="13" t="str">
         <f t="shared" si="96"/>
@@ -44241,7 +44241,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="483" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="483" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A483" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
@@ -44250,16 +44250,16 @@
         <v>6</v>
       </c>
       <c r="C483" s="12" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D483" s="12" t="s">
-        <v>82</v>
+        <v>1024</v>
+      </c>
+      <c r="D483" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="E483" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F483" s="12" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="G483" s="13">
         <v>1813</v>
@@ -44319,7 +44319,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="484" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="484" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A484" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
@@ -44328,16 +44328,16 @@
         <v>6</v>
       </c>
       <c r="C484" s="12" t="s">
-        <v>1004</v>
-      </c>
-      <c r="D484" s="16" t="s">
-        <v>52</v>
+        <v>1026</v>
+      </c>
+      <c r="D484" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E484" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F484" s="12" t="s">
-        <v>1005</v>
+        <v>1027</v>
       </c>
       <c r="G484" s="13">
         <v>1813</v>
@@ -44345,7 +44345,7 @@
       <c r="H484" s="13"/>
       <c r="I484" s="13"/>
       <c r="J484" s="13">
-        <v>1813</v>
+        <v>1800</v>
       </c>
       <c r="K484" s="13">
         <f t="shared" si="92"/>
@@ -44361,7 +44361,7 @@
       </c>
       <c r="N484" s="13">
         <f t="shared" si="95"/>
-        <v>1813</v>
+        <v>1800</v>
       </c>
       <c r="O484" s="13" t="str">
         <f t="shared" si="96"/>
@@ -44403,27 +44403,27 @@
         <v/>
       </c>
       <c r="B485" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C485" s="12" t="s">
-        <v>910</v>
-      </c>
-      <c r="D485" s="12" t="s">
-        <v>82</v>
+        <v>1004</v>
+      </c>
+      <c r="D485" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E485" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F485" s="12" t="s">
-        <v>911</v>
+        <v>1005</v>
       </c>
       <c r="G485" s="13">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="H485" s="13"/>
       <c r="I485" s="13"/>
       <c r="J485" s="13">
-        <v>1788</v>
+        <v>1813</v>
       </c>
       <c r="K485" s="13">
         <f t="shared" si="92"/>
@@ -44431,7 +44431,7 @@
       </c>
       <c r="L485" s="13">
         <f t="shared" si="93"/>
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="M485" s="13" t="str">
         <f t="shared" si="94"/>
@@ -44439,7 +44439,7 @@
       </c>
       <c r="N485" s="13">
         <f t="shared" si="95"/>
-        <v>1788</v>
+        <v>1813</v>
       </c>
       <c r="O485" s="13" t="str">
         <f t="shared" si="96"/>
@@ -44484,16 +44484,16 @@
         <v>12</v>
       </c>
       <c r="C486" s="12" t="s">
-        <v>946</v>
-      </c>
-      <c r="D486" s="16" t="s">
-        <v>61</v>
+        <v>910</v>
+      </c>
+      <c r="D486" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E486" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F486" s="12" t="s">
-        <v>947</v>
+        <v>911</v>
       </c>
       <c r="G486" s="13">
         <v>1814</v>
@@ -44501,7 +44501,7 @@
       <c r="H486" s="13"/>
       <c r="I486" s="13"/>
       <c r="J486" s="13">
-        <v>1794</v>
+        <v>1788</v>
       </c>
       <c r="K486" s="13">
         <f t="shared" si="92"/>
@@ -44517,7 +44517,7 @@
       </c>
       <c r="N486" s="13">
         <f t="shared" si="95"/>
-        <v>1794</v>
+        <v>1788</v>
       </c>
       <c r="O486" s="13" t="str">
         <f t="shared" si="96"/>
@@ -44562,16 +44562,16 @@
         <v>12</v>
       </c>
       <c r="C487" s="12" t="s">
-        <v>1114</v>
+        <v>946</v>
       </c>
       <c r="D487" s="16" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="E487" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F487" s="12" t="s">
-        <v>1115</v>
+        <v>947</v>
       </c>
       <c r="G487" s="13">
         <v>1814</v>
@@ -44637,10 +44637,10 @@
         <v/>
       </c>
       <c r="B488" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C488" s="12" t="s">
-        <v>1176</v>
+        <v>1114</v>
       </c>
       <c r="D488" s="16" t="s">
         <v>49</v>
@@ -44649,7 +44649,7 @@
         <v>26</v>
       </c>
       <c r="F488" s="12" t="s">
-        <v>1177</v>
+        <v>1115</v>
       </c>
       <c r="G488" s="13">
         <v>1814</v>
@@ -44657,7 +44657,7 @@
       <c r="H488" s="13"/>
       <c r="I488" s="13"/>
       <c r="J488" s="13">
-        <v>1803</v>
+        <v>1794</v>
       </c>
       <c r="K488" s="13">
         <f t="shared" si="92"/>
@@ -44673,7 +44673,7 @@
       </c>
       <c r="N488" s="13">
         <f t="shared" si="95"/>
-        <v>1803</v>
+        <v>1794</v>
       </c>
       <c r="O488" s="13" t="str">
         <f t="shared" si="96"/>
@@ -44718,7 +44718,7 @@
         <v>10</v>
       </c>
       <c r="C489" s="12" t="s">
-        <v>1014</v>
+        <v>1176</v>
       </c>
       <c r="D489" s="16" t="s">
         <v>49</v>
@@ -44727,7 +44727,7 @@
         <v>26</v>
       </c>
       <c r="F489" s="12" t="s">
-        <v>1015</v>
+        <v>1177</v>
       </c>
       <c r="G489" s="13">
         <v>1814</v>
@@ -44796,7 +44796,7 @@
         <v>10</v>
       </c>
       <c r="C490" s="12" t="s">
-        <v>998</v>
+        <v>1014</v>
       </c>
       <c r="D490" s="16" t="s">
         <v>49</v>
@@ -44805,7 +44805,7 @@
         <v>26</v>
       </c>
       <c r="F490" s="12" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="G490" s="13">
         <v>1814</v>
@@ -44865,7 +44865,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="491" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="491" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A491" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
@@ -44874,7 +44874,7 @@
         <v>10</v>
       </c>
       <c r="C491" s="12" t="s">
-        <v>982</v>
+        <v>998</v>
       </c>
       <c r="D491" s="16" t="s">
         <v>49</v>
@@ -44883,7 +44883,7 @@
         <v>26</v>
       </c>
       <c r="F491" s="12" t="s">
-        <v>983</v>
+        <v>999</v>
       </c>
       <c r="G491" s="13">
         <v>1814</v>
@@ -44949,10 +44949,10 @@
         <v/>
       </c>
       <c r="B492" s="12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C492" s="12" t="s">
-        <v>1075</v>
+        <v>982</v>
       </c>
       <c r="D492" s="16" t="s">
         <v>49</v>
@@ -44961,7 +44961,7 @@
         <v>26</v>
       </c>
       <c r="F492" s="12" t="s">
-        <v>1076</v>
+        <v>983</v>
       </c>
       <c r="G492" s="13">
         <v>1814</v>
@@ -44969,7 +44969,7 @@
       <c r="H492" s="13"/>
       <c r="I492" s="13"/>
       <c r="J492" s="13">
-        <v>1814</v>
+        <v>1803</v>
       </c>
       <c r="K492" s="13">
         <f t="shared" si="92"/>
@@ -44985,7 +44985,7 @@
       </c>
       <c r="N492" s="13">
         <f t="shared" si="95"/>
-        <v>1814</v>
+        <v>1803</v>
       </c>
       <c r="O492" s="13" t="str">
         <f t="shared" si="96"/>
@@ -45021,25 +45021,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="493" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="493" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A493" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="B493" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C493" s="12" t="s">
-        <v>1091</v>
+        <v>1075</v>
       </c>
       <c r="D493" s="16" t="s">
-        <v>139</v>
+        <v>49</v>
       </c>
       <c r="E493" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F493" s="12" t="s">
-        <v>1092</v>
+        <v>1076</v>
       </c>
       <c r="G493" s="13">
         <v>1814</v>
@@ -45108,16 +45108,16 @@
         <v>12</v>
       </c>
       <c r="C494" s="12" t="s">
-        <v>920</v>
+        <v>1091</v>
       </c>
       <c r="D494" s="16" t="s">
-        <v>49</v>
+        <v>139</v>
       </c>
       <c r="E494" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F494" s="12" t="s">
-        <v>1118</v>
+        <v>1092</v>
       </c>
       <c r="G494" s="13">
         <v>1814</v>
@@ -45125,7 +45125,7 @@
       <c r="H494" s="13"/>
       <c r="I494" s="13"/>
       <c r="J494" s="13">
-        <v>1824</v>
+        <v>1814</v>
       </c>
       <c r="K494" s="13">
         <f t="shared" si="92"/>
@@ -45141,7 +45141,7 @@
       </c>
       <c r="N494" s="13">
         <f t="shared" si="95"/>
-        <v>1824</v>
+        <v>1814</v>
       </c>
       <c r="O494" s="13" t="str">
         <f t="shared" si="96"/>
@@ -45186,16 +45186,16 @@
         <v>12</v>
       </c>
       <c r="C495" s="12" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="D495" s="16" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="E495" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F495" s="12" t="s">
-        <v>913</v>
+        <v>1118</v>
       </c>
       <c r="G495" s="13">
         <v>1814</v>
@@ -45261,27 +45261,27 @@
         <v/>
       </c>
       <c r="B496" s="12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C496" s="12" t="s">
-        <v>1012</v>
+        <v>912</v>
       </c>
       <c r="D496" s="16" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="E496" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F496" s="12" t="s">
-        <v>1013</v>
+        <v>913</v>
       </c>
       <c r="G496" s="13">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="H496" s="13"/>
       <c r="I496" s="13"/>
       <c r="J496" s="13">
-        <v>1795</v>
+        <v>1824</v>
       </c>
       <c r="K496" s="13">
         <f t="shared" si="92"/>
@@ -45289,7 +45289,7 @@
       </c>
       <c r="L496" s="13">
         <f t="shared" si="93"/>
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="M496" s="13" t="str">
         <f t="shared" si="94"/>
@@ -45297,7 +45297,7 @@
       </c>
       <c r="N496" s="13">
         <f t="shared" si="95"/>
-        <v>1795</v>
+        <v>1824</v>
       </c>
       <c r="O496" s="13" t="str">
         <f t="shared" si="96"/>
@@ -45339,19 +45339,19 @@
         <v/>
       </c>
       <c r="B497" s="12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C497" s="12" t="s">
-        <v>1435</v>
-      </c>
-      <c r="D497" s="12" t="s">
-        <v>82</v>
+        <v>1012</v>
+      </c>
+      <c r="D497" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E497" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F497" s="12" t="s">
-        <v>1436</v>
+        <v>1013</v>
       </c>
       <c r="G497" s="13">
         <v>1815</v>
@@ -45417,19 +45417,19 @@
         <v/>
       </c>
       <c r="B498" s="12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C498" s="12" t="s">
-        <v>924</v>
-      </c>
-      <c r="D498" s="16" t="s">
-        <v>52</v>
+        <v>1435</v>
+      </c>
+      <c r="D498" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E498" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F498" s="12" t="s">
-        <v>925</v>
+        <v>1436</v>
       </c>
       <c r="G498" s="13">
         <v>1815</v>
@@ -45437,7 +45437,7 @@
       <c r="H498" s="13"/>
       <c r="I498" s="13"/>
       <c r="J498" s="13">
-        <v>1798</v>
+        <v>1795</v>
       </c>
       <c r="K498" s="13">
         <f t="shared" si="92"/>
@@ -45453,7 +45453,7 @@
       </c>
       <c r="N498" s="13">
         <f t="shared" si="95"/>
-        <v>1798</v>
+        <v>1795</v>
       </c>
       <c r="O498" s="13" t="str">
         <f t="shared" si="96"/>
@@ -45498,16 +45498,16 @@
         <v>6</v>
       </c>
       <c r="C499" s="12" t="s">
-        <v>1139</v>
-      </c>
-      <c r="D499" s="12" t="s">
-        <v>82</v>
+        <v>924</v>
+      </c>
+      <c r="D499" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E499" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F499" s="12" t="s">
-        <v>1140</v>
+        <v>925</v>
       </c>
       <c r="G499" s="13">
         <v>1815</v>
@@ -45515,7 +45515,7 @@
       <c r="H499" s="13"/>
       <c r="I499" s="13"/>
       <c r="J499" s="13">
-        <v>1802</v>
+        <v>1798</v>
       </c>
       <c r="K499" s="13">
         <f t="shared" si="92"/>
@@ -45531,7 +45531,7 @@
       </c>
       <c r="N499" s="13">
         <f t="shared" si="95"/>
-        <v>1802</v>
+        <v>1798</v>
       </c>
       <c r="O499" s="13" t="str">
         <f t="shared" si="96"/>
@@ -45567,7 +45567,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="500" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="500" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A500" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
@@ -45576,16 +45576,16 @@
         <v>6</v>
       </c>
       <c r="C500" s="12" t="s">
-        <v>932</v>
-      </c>
-      <c r="D500" s="16" t="s">
-        <v>49</v>
+        <v>1139</v>
+      </c>
+      <c r="D500" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E500" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F500" s="12" t="s">
-        <v>933</v>
+        <v>1140</v>
       </c>
       <c r="G500" s="13">
         <v>1815</v>
@@ -45593,7 +45593,7 @@
       <c r="H500" s="13"/>
       <c r="I500" s="13"/>
       <c r="J500" s="13">
-        <v>1805</v>
+        <v>1802</v>
       </c>
       <c r="K500" s="13">
         <f t="shared" si="92"/>
@@ -45609,7 +45609,7 @@
       </c>
       <c r="N500" s="13">
         <f t="shared" si="95"/>
-        <v>1805</v>
+        <v>1802</v>
       </c>
       <c r="O500" s="13" t="str">
         <f t="shared" si="96"/>
@@ -45645,16 +45645,16 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="501" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="501" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A501" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="B501" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C501" s="12" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="D501" s="16" t="s">
         <v>49</v>
@@ -45663,7 +45663,7 @@
         <v>26</v>
       </c>
       <c r="F501" s="12" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="G501" s="13">
         <v>1815</v>
@@ -45729,19 +45729,19 @@
         <v/>
       </c>
       <c r="B502" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C502" s="12" t="s">
-        <v>1192</v>
-      </c>
-      <c r="D502" s="12" t="s">
-        <v>82</v>
+        <v>934</v>
+      </c>
+      <c r="D502" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E502" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F502" s="12" t="s">
-        <v>1193</v>
+        <v>935</v>
       </c>
       <c r="G502" s="13">
         <v>1815</v>
@@ -45749,7 +45749,7 @@
       <c r="H502" s="13"/>
       <c r="I502" s="13"/>
       <c r="J502" s="13">
-        <v>1809</v>
+        <v>1805</v>
       </c>
       <c r="K502" s="13">
         <f t="shared" si="92"/>
@@ -45765,7 +45765,7 @@
       </c>
       <c r="N502" s="13">
         <f t="shared" si="95"/>
-        <v>1809</v>
+        <v>1805</v>
       </c>
       <c r="O502" s="13" t="str">
         <f t="shared" si="96"/>
@@ -45807,19 +45807,19 @@
         <v/>
       </c>
       <c r="B503" s="12" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C503" s="12" t="s">
-        <v>1042</v>
-      </c>
-      <c r="D503" s="16" t="s">
-        <v>49</v>
+        <v>1192</v>
+      </c>
+      <c r="D503" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E503" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F503" s="12" t="s">
-        <v>1043</v>
+        <v>1193</v>
       </c>
       <c r="G503" s="13">
         <v>1815</v>
@@ -45827,7 +45827,7 @@
       <c r="H503" s="13"/>
       <c r="I503" s="13"/>
       <c r="J503" s="13">
-        <v>1825</v>
+        <v>1809</v>
       </c>
       <c r="K503" s="13">
         <f t="shared" si="92"/>
@@ -45843,7 +45843,7 @@
       </c>
       <c r="N503" s="13">
         <f t="shared" si="95"/>
-        <v>1825</v>
+        <v>1809</v>
       </c>
       <c r="O503" s="13" t="str">
         <f t="shared" si="96"/>
@@ -45879,33 +45879,33 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="504" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="504" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A504" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="B504" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C504" s="12" t="s">
-        <v>948</v>
+        <v>1042</v>
       </c>
       <c r="D504" s="16" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E504" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F504" s="12" t="s">
-        <v>949</v>
+        <v>1043</v>
       </c>
       <c r="G504" s="13">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="H504" s="13"/>
       <c r="I504" s="13"/>
       <c r="J504" s="13">
-        <v>1809</v>
+        <v>1825</v>
       </c>
       <c r="K504" s="13">
         <f t="shared" si="92"/>
@@ -45913,7 +45913,7 @@
       </c>
       <c r="L504" s="13">
         <f t="shared" si="93"/>
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="M504" s="13" t="str">
         <f t="shared" si="94"/>
@@ -45921,7 +45921,7 @@
       </c>
       <c r="N504" s="13">
         <f t="shared" si="95"/>
-        <v>1809</v>
+        <v>1825</v>
       </c>
       <c r="O504" s="13" t="str">
         <f t="shared" si="96"/>
@@ -45957,33 +45957,33 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="505" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="505" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A505" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="B505" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C505" s="12" t="s">
-        <v>986</v>
-      </c>
-      <c r="D505" s="12" t="s">
-        <v>82</v>
+        <v>948</v>
+      </c>
+      <c r="D505" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E505" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F505" s="12" t="s">
-        <v>987</v>
+        <v>949</v>
       </c>
       <c r="G505" s="13">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="H505" s="13"/>
       <c r="I505" s="13"/>
       <c r="J505" s="13">
-        <v>1798</v>
+        <v>1809</v>
       </c>
       <c r="K505" s="13">
         <f t="shared" si="92"/>
@@ -45991,7 +45991,7 @@
       </c>
       <c r="L505" s="13">
         <f t="shared" si="93"/>
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="M505" s="13" t="str">
         <f t="shared" si="94"/>
@@ -45999,7 +45999,7 @@
       </c>
       <c r="N505" s="13">
         <f t="shared" si="95"/>
-        <v>1798</v>
+        <v>1809</v>
       </c>
       <c r="O505" s="13" t="str">
         <f t="shared" si="96"/>
@@ -46044,16 +46044,16 @@
         <v>14</v>
       </c>
       <c r="C506" s="12" t="s">
-        <v>988</v>
-      </c>
-      <c r="D506" s="16" t="s">
-        <v>61</v>
+        <v>986</v>
+      </c>
+      <c r="D506" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E506" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F506" s="12" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="G506" s="13">
         <v>1817</v>
@@ -46122,16 +46122,16 @@
         <v>14</v>
       </c>
       <c r="C507" s="12" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="D507" s="16" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E507" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F507" s="12" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="G507" s="13">
         <v>1817</v>
@@ -46200,16 +46200,16 @@
         <v>14</v>
       </c>
       <c r="C508" s="12" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="D508" s="16" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E508" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F508" s="12" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="G508" s="13">
         <v>1817</v>
@@ -46269,33 +46269,33 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="509" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="509" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A509" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="B509" s="12" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C509" s="12" t="s">
-        <v>1264</v>
+        <v>992</v>
       </c>
       <c r="D509" s="16" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E509" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F509" s="12" t="s">
-        <v>1265</v>
+        <v>993</v>
       </c>
       <c r="G509" s="13">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="H509" s="13"/>
       <c r="I509" s="13"/>
       <c r="J509" s="13">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="K509" s="13">
         <f t="shared" si="92"/>
@@ -46303,7 +46303,7 @@
       </c>
       <c r="L509" s="13">
         <f t="shared" si="93"/>
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="M509" s="13" t="str">
         <f t="shared" si="94"/>
@@ -46311,7 +46311,7 @@
       </c>
       <c r="N509" s="13">
         <f t="shared" si="95"/>
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="O509" s="13" t="str">
         <f t="shared" si="96"/>
@@ -46347,7 +46347,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="510" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="510" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A510" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
@@ -46356,7 +46356,7 @@
         <v>6</v>
       </c>
       <c r="C510" s="12" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="D510" s="16" t="s">
         <v>52</v>
@@ -46365,7 +46365,7 @@
         <v>26</v>
       </c>
       <c r="F510" s="12" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="G510" s="13">
         <v>1818</v>
@@ -46425,25 +46425,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="511" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="511" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A511" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="B511" s="12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C511" s="12" t="s">
-        <v>1344</v>
+        <v>1262</v>
       </c>
       <c r="D511" s="16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E511" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F511" s="12" t="s">
-        <v>1345</v>
+        <v>1263</v>
       </c>
       <c r="G511" s="13">
         <v>1818</v>
@@ -46503,16 +46503,16 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="512" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="512" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A512" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="B512" s="12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C512" s="12" t="s">
-        <v>936</v>
+        <v>1344</v>
       </c>
       <c r="D512" s="16" t="s">
         <v>49</v>
@@ -46521,7 +46521,7 @@
         <v>26</v>
       </c>
       <c r="F512" s="12" t="s">
-        <v>937</v>
+        <v>1345</v>
       </c>
       <c r="G512" s="13">
         <v>1818</v>
@@ -46529,7 +46529,7 @@
       <c r="H512" s="13"/>
       <c r="I512" s="13"/>
       <c r="J512" s="13">
-        <v>1805</v>
+        <v>1799</v>
       </c>
       <c r="K512" s="13">
         <f t="shared" si="92"/>
@@ -46545,7 +46545,7 @@
       </c>
       <c r="N512" s="13">
         <f t="shared" si="95"/>
-        <v>1805</v>
+        <v>1799</v>
       </c>
       <c r="O512" s="13" t="str">
         <f t="shared" si="96"/>
@@ -46581,33 +46581,33 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="513" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="513" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A513" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="B513" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C513" s="12" t="s">
-        <v>1061</v>
-      </c>
-      <c r="D513" s="12" t="s">
-        <v>82</v>
+        <v>936</v>
+      </c>
+      <c r="D513" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E513" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F513" s="12" t="s">
-        <v>1062</v>
+        <v>937</v>
       </c>
       <c r="G513" s="13">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="H513" s="13"/>
       <c r="I513" s="13"/>
       <c r="J513" s="13">
-        <v>1789</v>
+        <v>1805</v>
       </c>
       <c r="K513" s="13">
         <f t="shared" si="92"/>
@@ -46615,7 +46615,7 @@
       </c>
       <c r="L513" s="13">
         <f t="shared" si="93"/>
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="M513" s="13" t="str">
         <f t="shared" si="94"/>
@@ -46623,7 +46623,7 @@
       </c>
       <c r="N513" s="13">
         <f t="shared" si="95"/>
-        <v>1789</v>
+        <v>1805</v>
       </c>
       <c r="O513" s="13" t="str">
         <f t="shared" si="96"/>
@@ -46668,16 +46668,16 @@
         <v>14</v>
       </c>
       <c r="C514" s="12" t="s">
-        <v>1063</v>
-      </c>
-      <c r="D514" s="16" t="s">
-        <v>49</v>
+        <v>1061</v>
+      </c>
+      <c r="D514" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E514" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F514" s="12" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="G514" s="13">
         <v>1819</v>
@@ -46743,10 +46743,10 @@
         <v/>
       </c>
       <c r="B515" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C515" s="12" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="D515" s="16" t="s">
         <v>49</v>
@@ -46755,7 +46755,7 @@
         <v>26</v>
       </c>
       <c r="F515" s="12" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="G515" s="13">
         <v>1819</v>
@@ -46821,19 +46821,19 @@
         <v/>
       </c>
       <c r="B516" s="12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C516" s="12" t="s">
-        <v>1198</v>
-      </c>
-      <c r="D516" s="12" t="s">
-        <v>82</v>
+        <v>1065</v>
+      </c>
+      <c r="D516" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E516" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F516" s="12" t="s">
-        <v>1199</v>
+        <v>1066</v>
       </c>
       <c r="G516" s="13">
         <v>1819</v>
@@ -46841,7 +46841,7 @@
       <c r="H516" s="13"/>
       <c r="I516" s="13"/>
       <c r="J516" s="13">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="K516" s="13">
         <f t="shared" si="92"/>
@@ -46857,7 +46857,7 @@
       </c>
       <c r="N516" s="13">
         <f t="shared" si="95"/>
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="O516" s="13" t="str">
         <f t="shared" si="96"/>
@@ -46893,7 +46893,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="517" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="517" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A517" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
@@ -46902,16 +46902,16 @@
         <v>6</v>
       </c>
       <c r="C517" s="12" t="s">
-        <v>960</v>
-      </c>
-      <c r="D517" s="16" t="s">
-        <v>52</v>
+        <v>1198</v>
+      </c>
+      <c r="D517" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E517" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F517" s="12" t="s">
-        <v>961</v>
+        <v>1199</v>
       </c>
       <c r="G517" s="13">
         <v>1819</v>
@@ -46919,7 +46919,7 @@
       <c r="H517" s="13"/>
       <c r="I517" s="13"/>
       <c r="J517" s="13">
-        <v>1798</v>
+        <v>1791</v>
       </c>
       <c r="K517" s="13">
         <f t="shared" si="92"/>
@@ -46935,7 +46935,7 @@
       </c>
       <c r="N517" s="13">
         <f t="shared" si="95"/>
-        <v>1798</v>
+        <v>1791</v>
       </c>
       <c r="O517" s="13" t="str">
         <f t="shared" si="96"/>
@@ -46971,7 +46971,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="518" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="518" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A518" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
@@ -46980,16 +46980,16 @@
         <v>6</v>
       </c>
       <c r="C518" s="12" t="s">
-        <v>962</v>
-      </c>
-      <c r="D518" s="12" t="s">
-        <v>82</v>
+        <v>960</v>
+      </c>
+      <c r="D518" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E518" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F518" s="12" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="G518" s="13">
         <v>1819</v>
@@ -47049,25 +47049,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="519" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="519" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A519" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="B519" s="12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C519" s="12" t="s">
-        <v>954</v>
-      </c>
-      <c r="D519" s="16" t="s">
-        <v>49</v>
+        <v>962</v>
+      </c>
+      <c r="D519" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E519" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F519" s="12" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="G519" s="13">
         <v>1819</v>
@@ -47127,25 +47127,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="520" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="520" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A520" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="B520" s="12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C520" s="12" t="s">
-        <v>978</v>
+        <v>954</v>
       </c>
       <c r="D520" s="16" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E520" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F520" s="12" t="s">
-        <v>979</v>
+        <v>955</v>
       </c>
       <c r="G520" s="13">
         <v>1819</v>
@@ -47153,7 +47153,7 @@
       <c r="H520" s="13"/>
       <c r="I520" s="13"/>
       <c r="J520" s="13">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="K520" s="13">
         <f t="shared" si="92"/>
@@ -47169,7 +47169,7 @@
       </c>
       <c r="N520" s="13">
         <f t="shared" si="95"/>
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="O520" s="13" t="str">
         <f t="shared" si="96"/>
@@ -47205,7 +47205,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="521" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="521" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A521" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
@@ -47214,16 +47214,16 @@
         <v>6</v>
       </c>
       <c r="C521" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D521" s="12" t="s">
-        <v>45</v>
+        <v>978</v>
+      </c>
+      <c r="D521" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="E521" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F521" s="12" t="s">
-        <v>1202</v>
+        <v>979</v>
       </c>
       <c r="G521" s="13">
         <v>1819</v>
@@ -47283,25 +47283,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="522" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="522" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A522" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="B522" s="12" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C522" s="12" t="s">
-        <v>1083</v>
-      </c>
-      <c r="D522" s="16" t="s">
-        <v>49</v>
+        <v>90</v>
+      </c>
+      <c r="D522" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="E522" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F522" s="12" t="s">
-        <v>1084</v>
+        <v>1202</v>
       </c>
       <c r="G522" s="13">
         <v>1819</v>
@@ -47367,19 +47367,19 @@
         <v/>
       </c>
       <c r="B523" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C523" s="12" t="s">
-        <v>627</v>
-      </c>
-      <c r="D523" s="12" t="s">
-        <v>45</v>
+        <v>1083</v>
+      </c>
+      <c r="D523" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E523" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F523" s="12" t="s">
-        <v>1067</v>
+        <v>1084</v>
       </c>
       <c r="G523" s="13">
         <v>1819</v>
@@ -47439,7 +47439,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="524" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="524" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A524" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
@@ -47448,16 +47448,16 @@
         <v>10</v>
       </c>
       <c r="C524" s="12" t="s">
-        <v>1223</v>
-      </c>
-      <c r="D524" s="16" t="s">
-        <v>49</v>
+        <v>627</v>
+      </c>
+      <c r="D524" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="E524" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F524" s="12" t="s">
-        <v>1224</v>
+        <v>1067</v>
       </c>
       <c r="G524" s="13">
         <v>1819</v>
@@ -47517,7 +47517,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="525" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="525" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A525" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
@@ -47526,16 +47526,16 @@
         <v>10</v>
       </c>
       <c r="C525" s="12" t="s">
-        <v>976</v>
+        <v>1223</v>
       </c>
       <c r="D525" s="16" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E525" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F525" s="12" t="s">
-        <v>977</v>
+        <v>1224</v>
       </c>
       <c r="G525" s="13">
         <v>1819</v>
@@ -47595,7 +47595,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="526" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="526" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A526" s="12" t="str">
         <f t="shared" si="91"/>
         <v/>
@@ -47604,16 +47604,16 @@
         <v>10</v>
       </c>
       <c r="C526" s="12" t="s">
-        <v>1234</v>
-      </c>
-      <c r="D526" s="12" t="s">
-        <v>45</v>
+        <v>976</v>
+      </c>
+      <c r="D526" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="E526" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F526" s="12" t="s">
-        <v>1235</v>
+        <v>977</v>
       </c>
       <c r="G526" s="13">
         <v>1819</v>
@@ -47682,16 +47682,16 @@
         <v>10</v>
       </c>
       <c r="C527" s="12" t="s">
-        <v>1236</v>
-      </c>
-      <c r="D527" s="16" t="s">
-        <v>52</v>
+        <v>1234</v>
+      </c>
+      <c r="D527" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="E527" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F527" s="12" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="G527" s="13">
         <v>1819</v>
@@ -47757,19 +47757,19 @@
         <v/>
       </c>
       <c r="B528" s="12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C528" s="12" t="s">
-        <v>1125</v>
+        <v>1236</v>
       </c>
       <c r="D528" s="16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E528" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F528" s="12" t="s">
-        <v>1126</v>
+        <v>1237</v>
       </c>
       <c r="G528" s="13">
         <v>1819</v>
@@ -47777,7 +47777,7 @@
       <c r="H528" s="13"/>
       <c r="I528" s="13"/>
       <c r="J528" s="13">
-        <v>1807</v>
+        <v>1799</v>
       </c>
       <c r="K528" s="13">
         <f t="shared" si="105"/>
@@ -47793,7 +47793,7 @@
       </c>
       <c r="N528" s="13">
         <f t="shared" si="108"/>
-        <v>1807</v>
+        <v>1799</v>
       </c>
       <c r="O528" s="13" t="str">
         <f t="shared" si="109"/>
@@ -47829,25 +47829,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="529" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="529" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A529" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="B529" s="12" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C529" s="12" t="s">
-        <v>980</v>
-      </c>
-      <c r="D529" s="12" t="s">
-        <v>139</v>
+        <v>1125</v>
+      </c>
+      <c r="D529" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E529" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F529" s="12" t="s">
-        <v>981</v>
+        <v>1126</v>
       </c>
       <c r="G529" s="13">
         <v>1819</v>
@@ -47855,7 +47855,7 @@
       <c r="H529" s="13"/>
       <c r="I529" s="13"/>
       <c r="J529" s="13">
-        <v>1814</v>
+        <v>1807</v>
       </c>
       <c r="K529" s="13">
         <f t="shared" si="105"/>
@@ -47871,7 +47871,7 @@
       </c>
       <c r="N529" s="13">
         <f t="shared" si="108"/>
-        <v>1814</v>
+        <v>1807</v>
       </c>
       <c r="O529" s="13" t="str">
         <f t="shared" si="109"/>
@@ -47907,7 +47907,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="530" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="530" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A530" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
@@ -47916,16 +47916,16 @@
         <v>6</v>
       </c>
       <c r="C530" s="12" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D530" s="16" t="s">
-        <v>52</v>
+        <v>980</v>
+      </c>
+      <c r="D530" s="12" t="s">
+        <v>139</v>
       </c>
       <c r="E530" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F530" s="12" t="s">
-        <v>1088</v>
+        <v>981</v>
       </c>
       <c r="G530" s="13">
         <v>1819</v>
@@ -47985,25 +47985,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="531" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="531" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A531" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="B531" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C531" s="12" t="s">
-        <v>1036</v>
-      </c>
-      <c r="D531" s="12" t="s">
-        <v>82</v>
+        <v>1087</v>
+      </c>
+      <c r="D531" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E531" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F531" s="12" t="s">
-        <v>1037</v>
+        <v>1088</v>
       </c>
       <c r="G531" s="13">
         <v>1819</v>
@@ -48011,7 +48011,7 @@
       <c r="H531" s="13"/>
       <c r="I531" s="13"/>
       <c r="J531" s="13">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="K531" s="13">
         <f t="shared" si="105"/>
@@ -48027,7 +48027,7 @@
       </c>
       <c r="N531" s="13">
         <f t="shared" si="108"/>
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="O531" s="13" t="str">
         <f t="shared" si="109"/>
@@ -48069,19 +48069,19 @@
         <v/>
       </c>
       <c r="B532" s="12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C532" s="12" t="s">
-        <v>1509</v>
-      </c>
-      <c r="D532" s="16" t="s">
-        <v>49</v>
+        <v>1036</v>
+      </c>
+      <c r="D532" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E532" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F532" s="12" t="s">
-        <v>1510</v>
+        <v>1037</v>
       </c>
       <c r="G532" s="13">
         <v>1819</v>
@@ -48089,7 +48089,7 @@
       <c r="H532" s="13"/>
       <c r="I532" s="13"/>
       <c r="J532" s="13">
-        <v>1839</v>
+        <v>1815</v>
       </c>
       <c r="K532" s="13">
         <f t="shared" si="105"/>
@@ -48105,7 +48105,7 @@
       </c>
       <c r="N532" s="13">
         <f t="shared" si="108"/>
-        <v>1839</v>
+        <v>1815</v>
       </c>
       <c r="O532" s="13" t="str">
         <f t="shared" si="109"/>
@@ -48147,27 +48147,27 @@
         <v/>
       </c>
       <c r="B533" s="12" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C533" s="12" t="s">
-        <v>1119</v>
+        <v>1509</v>
       </c>
       <c r="D533" s="16" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E533" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F533" s="12" t="s">
-        <v>1120</v>
+        <v>1510</v>
       </c>
       <c r="G533" s="13">
-        <v>1822</v>
+        <v>1819</v>
       </c>
       <c r="H533" s="13"/>
       <c r="I533" s="13"/>
       <c r="J533" s="13">
-        <v>1802</v>
+        <v>1839</v>
       </c>
       <c r="K533" s="13">
         <f t="shared" si="105"/>
@@ -48175,7 +48175,7 @@
       </c>
       <c r="L533" s="13">
         <f t="shared" si="106"/>
-        <v>1822</v>
+        <v>1819</v>
       </c>
       <c r="M533" s="13" t="str">
         <f t="shared" si="107"/>
@@ -48183,7 +48183,7 @@
       </c>
       <c r="N533" s="13">
         <f t="shared" si="108"/>
-        <v>1802</v>
+        <v>1839</v>
       </c>
       <c r="O533" s="13" t="str">
         <f t="shared" si="109"/>
@@ -48225,27 +48225,27 @@
         <v/>
       </c>
       <c r="B534" s="12" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C534" s="12" t="s">
-        <v>1225</v>
-      </c>
-      <c r="D534" s="12" t="s">
-        <v>82</v>
+        <v>1119</v>
+      </c>
+      <c r="D534" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="E534" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F534" s="12" t="s">
-        <v>1226</v>
+        <v>1120</v>
       </c>
       <c r="G534" s="13">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="H534" s="13"/>
       <c r="I534" s="13"/>
       <c r="J534" s="13">
-        <v>1798</v>
+        <v>1802</v>
       </c>
       <c r="K534" s="13">
         <f t="shared" si="105"/>
@@ -48253,7 +48253,7 @@
       </c>
       <c r="L534" s="13">
         <f t="shared" si="106"/>
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="M534" s="13" t="str">
         <f t="shared" si="107"/>
@@ -48261,7 +48261,7 @@
       </c>
       <c r="N534" s="13">
         <f t="shared" si="108"/>
-        <v>1798</v>
+        <v>1802</v>
       </c>
       <c r="O534" s="13" t="str">
         <f t="shared" si="109"/>
@@ -48306,16 +48306,16 @@
         <v>10</v>
       </c>
       <c r="C535" s="12" t="s">
-        <v>1232</v>
+        <v>1225</v>
       </c>
       <c r="D535" s="12" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="E535" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F535" s="12" t="s">
-        <v>1233</v>
+        <v>1226</v>
       </c>
       <c r="G535" s="13">
         <v>1823</v>
@@ -48381,19 +48381,19 @@
         <v/>
       </c>
       <c r="B536" s="12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C536" s="12" t="s">
-        <v>990</v>
-      </c>
-      <c r="D536" s="16" t="s">
-        <v>49</v>
+        <v>1232</v>
+      </c>
+      <c r="D536" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="E536" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F536" s="12" t="s">
-        <v>991</v>
+        <v>1233</v>
       </c>
       <c r="G536" s="13">
         <v>1823</v>
@@ -48401,7 +48401,7 @@
       <c r="H536" s="13"/>
       <c r="I536" s="13"/>
       <c r="J536" s="13">
-        <v>1813</v>
+        <v>1798</v>
       </c>
       <c r="K536" s="13">
         <f t="shared" si="105"/>
@@ -48417,7 +48417,7 @@
       </c>
       <c r="N536" s="13">
         <f t="shared" si="108"/>
-        <v>1813</v>
+        <v>1798</v>
       </c>
       <c r="O536" s="13" t="str">
         <f t="shared" si="109"/>
@@ -48453,25 +48453,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="537" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="537" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A537" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="B537" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C537" s="12" t="s">
-        <v>1246</v>
-      </c>
-      <c r="D537" s="12" t="s">
-        <v>139</v>
+        <v>990</v>
+      </c>
+      <c r="D537" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E537" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F537" s="12" t="s">
-        <v>1247</v>
+        <v>991</v>
       </c>
       <c r="G537" s="13">
         <v>1823</v>
@@ -48479,7 +48479,7 @@
       <c r="H537" s="13"/>
       <c r="I537" s="13"/>
       <c r="J537" s="13">
-        <v>1823</v>
+        <v>1813</v>
       </c>
       <c r="K537" s="13">
         <f t="shared" si="105"/>
@@ -48495,7 +48495,7 @@
       </c>
       <c r="N537" s="13">
         <f t="shared" si="108"/>
-        <v>1823</v>
+        <v>1813</v>
       </c>
       <c r="O537" s="13" t="str">
         <f t="shared" si="109"/>
@@ -48531,7 +48531,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="538" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="538" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A538" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
@@ -48540,16 +48540,16 @@
         <v>10</v>
       </c>
       <c r="C538" s="12" t="s">
-        <v>984</v>
+        <v>1246</v>
       </c>
       <c r="D538" s="12" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="E538" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F538" s="12" t="s">
-        <v>985</v>
+        <v>1247</v>
       </c>
       <c r="G538" s="13">
         <v>1823</v>
@@ -48615,10 +48615,10 @@
         <v/>
       </c>
       <c r="B539" s="12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C539" s="12" t="s">
-        <v>996</v>
+        <v>984</v>
       </c>
       <c r="D539" s="12" t="s">
         <v>82</v>
@@ -48627,15 +48627,15 @@
         <v>26</v>
       </c>
       <c r="F539" s="12" t="s">
-        <v>997</v>
+        <v>985</v>
       </c>
       <c r="G539" s="13">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="H539" s="13"/>
       <c r="I539" s="13"/>
       <c r="J539" s="13">
-        <v>1814</v>
+        <v>1823</v>
       </c>
       <c r="K539" s="13">
         <f t="shared" si="105"/>
@@ -48643,7 +48643,7 @@
       </c>
       <c r="L539" s="13">
         <f t="shared" si="106"/>
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="M539" s="13" t="str">
         <f t="shared" si="107"/>
@@ -48651,7 +48651,7 @@
       </c>
       <c r="N539" s="13">
         <f t="shared" si="108"/>
-        <v>1814</v>
+        <v>1823</v>
       </c>
       <c r="O539" s="13" t="str">
         <f t="shared" si="109"/>
@@ -48687,25 +48687,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="540" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="540" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A540" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="B540" s="12" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C540" s="12" t="s">
-        <v>1756</v>
-      </c>
-      <c r="D540" s="16" t="s">
-        <v>49</v>
+        <v>996</v>
+      </c>
+      <c r="D540" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E540" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F540" s="12" t="s">
-        <v>1394</v>
+        <v>997</v>
       </c>
       <c r="G540" s="13">
         <v>1824</v>
@@ -48713,7 +48713,7 @@
       <c r="H540" s="13"/>
       <c r="I540" s="13"/>
       <c r="J540" s="13">
-        <v>1847</v>
+        <v>1814</v>
       </c>
       <c r="K540" s="13">
         <f t="shared" si="105"/>
@@ -48729,7 +48729,7 @@
       </c>
       <c r="N540" s="13">
         <f t="shared" si="108"/>
-        <v>1847</v>
+        <v>1814</v>
       </c>
       <c r="O540" s="13" t="str">
         <f t="shared" si="109"/>
@@ -48774,24 +48774,24 @@
         <v>18</v>
       </c>
       <c r="C541" s="12" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D541" s="12" t="s">
-        <v>82</v>
+        <v>1756</v>
+      </c>
+      <c r="D541" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E541" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F541" s="12" t="s">
-        <v>1007</v>
+        <v>1394</v>
       </c>
       <c r="G541" s="13">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="H541" s="13"/>
       <c r="I541" s="13"/>
       <c r="J541" s="13">
-        <v>1789</v>
+        <v>1847</v>
       </c>
       <c r="K541" s="13">
         <f t="shared" si="105"/>
@@ -48799,7 +48799,7 @@
       </c>
       <c r="L541" s="13">
         <f t="shared" si="106"/>
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="M541" s="13" t="str">
         <f t="shared" si="107"/>
@@ -48807,7 +48807,7 @@
       </c>
       <c r="N541" s="13">
         <f t="shared" si="108"/>
-        <v>1789</v>
+        <v>1847</v>
       </c>
       <c r="O541" s="13" t="str">
         <f t="shared" si="109"/>
@@ -48843,7 +48843,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="542" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="542" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A542" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
@@ -48852,16 +48852,16 @@
         <v>18</v>
       </c>
       <c r="C542" s="12" t="s">
-        <v>1008</v>
-      </c>
-      <c r="D542" s="16" t="s">
-        <v>49</v>
+        <v>1006</v>
+      </c>
+      <c r="D542" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E542" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F542" s="12" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G542" s="13">
         <v>1825</v>
@@ -48869,7 +48869,7 @@
       <c r="H542" s="13"/>
       <c r="I542" s="13"/>
       <c r="J542" s="13">
-        <v>1795</v>
+        <v>1789</v>
       </c>
       <c r="K542" s="13">
         <f t="shared" si="105"/>
@@ -48885,7 +48885,7 @@
       </c>
       <c r="N542" s="13">
         <f t="shared" si="108"/>
-        <v>1795</v>
+        <v>1789</v>
       </c>
       <c r="O542" s="13" t="str">
         <f t="shared" si="109"/>
@@ -48930,7 +48930,7 @@
         <v>18</v>
       </c>
       <c r="C543" s="12" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="D543" s="16" t="s">
         <v>49</v>
@@ -48939,7 +48939,7 @@
         <v>26</v>
       </c>
       <c r="F543" s="12" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="G543" s="13">
         <v>1825</v>
@@ -48999,7 +48999,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="544" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="544" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A544" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
@@ -49008,16 +49008,16 @@
         <v>18</v>
       </c>
       <c r="C544" s="12" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D544" s="12" t="s">
-        <v>82</v>
+        <v>1010</v>
+      </c>
+      <c r="D544" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E544" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F544" s="12" t="s">
-        <v>1041</v>
+        <v>1011</v>
       </c>
       <c r="G544" s="13">
         <v>1825</v>
@@ -49077,7 +49077,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="545" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="545" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A545" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
@@ -49086,16 +49086,16 @@
         <v>18</v>
       </c>
       <c r="C545" s="12" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D545" s="16" t="s">
-        <v>49</v>
+        <v>1040</v>
+      </c>
+      <c r="D545" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E545" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F545" s="12" t="s">
-        <v>1017</v>
+        <v>1041</v>
       </c>
       <c r="G545" s="13">
         <v>1825</v>
@@ -49103,7 +49103,7 @@
       <c r="H545" s="13"/>
       <c r="I545" s="13"/>
       <c r="J545" s="13">
-        <v>1799</v>
+        <v>1795</v>
       </c>
       <c r="K545" s="13">
         <f t="shared" si="105"/>
@@ -49119,7 +49119,7 @@
       </c>
       <c r="N545" s="13">
         <f t="shared" si="108"/>
-        <v>1799</v>
+        <v>1795</v>
       </c>
       <c r="O545" s="13" t="str">
         <f t="shared" si="109"/>
@@ -49164,16 +49164,16 @@
         <v>18</v>
       </c>
       <c r="C546" s="12" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D546" s="12" t="s">
-        <v>45</v>
+        <v>1016</v>
+      </c>
+      <c r="D546" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E546" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F546" s="12" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G546" s="13">
         <v>1825</v>
@@ -49239,19 +49239,19 @@
         <v/>
       </c>
       <c r="B547" s="12" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C547" s="12" t="s">
-        <v>443</v>
+        <v>1018</v>
       </c>
       <c r="D547" s="12" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E547" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F547" s="12" t="s">
-        <v>444</v>
+        <v>1019</v>
       </c>
       <c r="G547" s="13">
         <v>1825</v>
@@ -49259,7 +49259,7 @@
       <c r="H547" s="13"/>
       <c r="I547" s="13"/>
       <c r="J547" s="13">
-        <v>1805</v>
+        <v>1799</v>
       </c>
       <c r="K547" s="13">
         <f t="shared" si="105"/>
@@ -49275,7 +49275,7 @@
       </c>
       <c r="N547" s="13">
         <f t="shared" si="108"/>
-        <v>1805</v>
+        <v>1799</v>
       </c>
       <c r="O547" s="13" t="str">
         <f t="shared" si="109"/>
@@ -49311,25 +49311,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="548" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="548" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A548" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="B548" s="12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C548" s="12" t="s">
-        <v>1116</v>
-      </c>
-      <c r="D548" s="16" t="s">
-        <v>49</v>
+        <v>443</v>
+      </c>
+      <c r="D548" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E548" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F548" s="12" t="s">
-        <v>1117</v>
+        <v>444</v>
       </c>
       <c r="G548" s="13">
         <v>1825</v>
@@ -49337,7 +49337,7 @@
       <c r="H548" s="13"/>
       <c r="I548" s="13"/>
       <c r="J548" s="13">
-        <v>1808</v>
+        <v>1805</v>
       </c>
       <c r="K548" s="13">
         <f t="shared" si="105"/>
@@ -49353,7 +49353,7 @@
       </c>
       <c r="N548" s="13">
         <f t="shared" si="108"/>
-        <v>1808</v>
+        <v>1805</v>
       </c>
       <c r="O548" s="13" t="str">
         <f t="shared" si="109"/>
@@ -49389,25 +49389,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="549" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="549" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A549" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="B549" s="12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C549" s="12" t="s">
-        <v>1190</v>
-      </c>
-      <c r="D549" s="12" t="s">
-        <v>45</v>
+        <v>1116</v>
+      </c>
+      <c r="D549" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E549" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F549" s="12" t="s">
-        <v>1191</v>
+        <v>1117</v>
       </c>
       <c r="G549" s="13">
         <v>1825</v>
@@ -49473,19 +49473,19 @@
         <v/>
       </c>
       <c r="B550" s="12" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C550" s="12" t="s">
-        <v>1020</v>
-      </c>
-      <c r="D550" s="16" t="s">
-        <v>49</v>
+        <v>1190</v>
+      </c>
+      <c r="D550" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="E550" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F550" s="12" t="s">
-        <v>1021</v>
+        <v>1191</v>
       </c>
       <c r="G550" s="13">
         <v>1825</v>
@@ -49493,7 +49493,7 @@
       <c r="H550" s="13"/>
       <c r="I550" s="13"/>
       <c r="J550" s="13">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="K550" s="13">
         <f t="shared" si="105"/>
@@ -49509,7 +49509,7 @@
       </c>
       <c r="N550" s="13">
         <f t="shared" si="108"/>
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="O550" s="13" t="str">
         <f t="shared" si="109"/>
@@ -49551,10 +49551,10 @@
         <v/>
       </c>
       <c r="B551" s="12" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C551" s="12" t="s">
-        <v>1123</v>
+        <v>1020</v>
       </c>
       <c r="D551" s="16" t="s">
         <v>49</v>
@@ -49563,7 +49563,7 @@
         <v>26</v>
       </c>
       <c r="F551" s="12" t="s">
-        <v>1124</v>
+        <v>1021</v>
       </c>
       <c r="G551" s="13">
         <v>1825</v>
@@ -49629,19 +49629,19 @@
         <v/>
       </c>
       <c r="B552" s="12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C552" s="12" t="s">
-        <v>1028</v>
-      </c>
-      <c r="D552" s="12" t="s">
-        <v>308</v>
+        <v>1123</v>
+      </c>
+      <c r="D552" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E552" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F552" s="12" t="s">
-        <v>1029</v>
+        <v>1124</v>
       </c>
       <c r="G552" s="13">
         <v>1825</v>
@@ -49707,19 +49707,19 @@
         <v/>
       </c>
       <c r="B553" s="12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C553" s="12" t="s">
-        <v>1030</v>
-      </c>
-      <c r="D553" s="16" t="s">
-        <v>52</v>
+        <v>1028</v>
+      </c>
+      <c r="D553" s="12" t="s">
+        <v>308</v>
       </c>
       <c r="E553" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F553" s="12" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="G553" s="13">
         <v>1825</v>
@@ -49727,7 +49727,7 @@
       <c r="H553" s="13"/>
       <c r="I553" s="13"/>
       <c r="J553" s="13">
-        <v>1812</v>
+        <v>1809</v>
       </c>
       <c r="K553" s="13">
         <f t="shared" si="105"/>
@@ -49743,7 +49743,7 @@
       </c>
       <c r="N553" s="13">
         <f t="shared" si="108"/>
-        <v>1812</v>
+        <v>1809</v>
       </c>
       <c r="O553" s="13" t="str">
         <f t="shared" si="109"/>
@@ -49788,16 +49788,16 @@
         <v>6</v>
       </c>
       <c r="C554" s="12" t="s">
-        <v>1032</v>
-      </c>
-      <c r="D554" s="12" t="s">
-        <v>45</v>
+        <v>1030</v>
+      </c>
+      <c r="D554" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E554" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F554" s="12" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="G554" s="13">
         <v>1825</v>
@@ -49866,16 +49866,16 @@
         <v>6</v>
       </c>
       <c r="C555" s="12" t="s">
-        <v>838</v>
-      </c>
-      <c r="D555" s="16" t="s">
-        <v>49</v>
+        <v>1032</v>
+      </c>
+      <c r="D555" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="E555" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F555" s="12" t="s">
-        <v>1386</v>
+        <v>1033</v>
       </c>
       <c r="G555" s="13">
         <v>1825</v>
@@ -49883,7 +49883,7 @@
       <c r="H555" s="13"/>
       <c r="I555" s="13"/>
       <c r="J555" s="13">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="K555" s="13">
         <f t="shared" si="105"/>
@@ -49899,7 +49899,7 @@
       </c>
       <c r="N555" s="13">
         <f t="shared" si="108"/>
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="O555" s="13" t="str">
         <f t="shared" si="109"/>
@@ -49944,16 +49944,16 @@
         <v>6</v>
       </c>
       <c r="C556" s="12" t="s">
-        <v>1034</v>
-      </c>
-      <c r="D556" s="12" t="s">
-        <v>82</v>
+        <v>838</v>
+      </c>
+      <c r="D556" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E556" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F556" s="12" t="s">
-        <v>1035</v>
+        <v>1386</v>
       </c>
       <c r="G556" s="13">
         <v>1825</v>
@@ -50019,19 +50019,19 @@
         <v/>
       </c>
       <c r="B557" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C557" s="12" t="s">
-        <v>1038</v>
-      </c>
-      <c r="D557" s="16" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D557" s="12" t="s">
         <v>82</v>
       </c>
       <c r="E557" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F557" s="12" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="G557" s="13">
         <v>1825</v>
@@ -50039,7 +50039,7 @@
       <c r="H557" s="13"/>
       <c r="I557" s="13"/>
       <c r="J557" s="13">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="K557" s="13">
         <f t="shared" si="105"/>
@@ -50055,7 +50055,7 @@
       </c>
       <c r="N557" s="13">
         <f t="shared" si="108"/>
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="O557" s="13" t="str">
         <f t="shared" si="109"/>
@@ -50091,7 +50091,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="558" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="558" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A558" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
@@ -50100,16 +50100,16 @@
         <v>12</v>
       </c>
       <c r="C558" s="12" t="s">
-        <v>1158</v>
+        <v>1038</v>
       </c>
       <c r="D558" s="16" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="E558" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F558" s="12" t="s">
-        <v>1159</v>
+        <v>1039</v>
       </c>
       <c r="G558" s="13">
         <v>1825</v>
@@ -50169,25 +50169,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="559" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="559" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A559" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="B559" s="12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C559" s="12" t="s">
-        <v>1149</v>
-      </c>
-      <c r="D559" s="12" t="s">
-        <v>82</v>
+        <v>1158</v>
+      </c>
+      <c r="D559" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E559" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F559" s="12" t="s">
-        <v>1150</v>
+        <v>1159</v>
       </c>
       <c r="G559" s="13">
         <v>1825</v>
@@ -50195,7 +50195,7 @@
       <c r="H559" s="13"/>
       <c r="I559" s="13"/>
       <c r="J559" s="13">
-        <v>1819</v>
+        <v>1815</v>
       </c>
       <c r="K559" s="13">
         <f t="shared" si="105"/>
@@ -50211,7 +50211,7 @@
       </c>
       <c r="N559" s="13">
         <f t="shared" si="108"/>
-        <v>1819</v>
+        <v>1815</v>
       </c>
       <c r="O559" s="13" t="str">
         <f t="shared" si="109"/>
@@ -50247,25 +50247,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="560" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="560" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A560" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="B560" s="12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C560" s="12" t="s">
-        <v>1153</v>
-      </c>
-      <c r="D560" s="16" t="s">
-        <v>52</v>
+        <v>1149</v>
+      </c>
+      <c r="D560" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E560" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F560" s="12" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="G560" s="13">
         <v>1825</v>
@@ -50325,33 +50325,33 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="561" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="561" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A561" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="B561" s="12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C561" s="12" t="s">
-        <v>1554</v>
+        <v>1153</v>
       </c>
       <c r="D561" s="16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E561" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F561" s="12" t="s">
-        <v>1555</v>
+        <v>1154</v>
       </c>
       <c r="G561" s="13">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="H561" s="13"/>
       <c r="I561" s="13"/>
       <c r="J561" s="13">
-        <v>1814</v>
+        <v>1819</v>
       </c>
       <c r="K561" s="13">
         <f t="shared" si="105"/>
@@ -50359,7 +50359,7 @@
       </c>
       <c r="L561" s="13">
         <f t="shared" si="106"/>
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="M561" s="13" t="str">
         <f t="shared" si="107"/>
@@ -50367,7 +50367,7 @@
       </c>
       <c r="N561" s="13">
         <f t="shared" si="108"/>
-        <v>1814</v>
+        <v>1819</v>
       </c>
       <c r="O561" s="13" t="str">
         <f t="shared" si="109"/>
@@ -50409,19 +50409,19 @@
         <v/>
       </c>
       <c r="B562" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C562" s="12" t="s">
-        <v>1044</v>
+        <v>1554</v>
       </c>
       <c r="D562" s="16" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E562" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F562" s="12" t="s">
-        <v>1045</v>
+        <v>1555</v>
       </c>
       <c r="G562" s="13">
         <v>1827</v>
@@ -50429,7 +50429,7 @@
       <c r="H562" s="13"/>
       <c r="I562" s="13"/>
       <c r="J562" s="13">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="K562" s="13">
         <f t="shared" si="105"/>
@@ -50445,7 +50445,7 @@
       </c>
       <c r="N562" s="13">
         <f t="shared" si="108"/>
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="O562" s="13" t="str">
         <f t="shared" si="109"/>
@@ -50481,25 +50481,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="563" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="563" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A563" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="B563" s="12" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C563" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D563" s="12" t="s">
-        <v>82</v>
+        <v>1044</v>
+      </c>
+      <c r="D563" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="E563" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F563" s="12" t="s">
-        <v>1259</v>
+        <v>1045</v>
       </c>
       <c r="G563" s="13">
         <v>1827</v>
@@ -50507,7 +50507,7 @@
       <c r="H563" s="13"/>
       <c r="I563" s="13"/>
       <c r="J563" s="13">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="K563" s="13">
         <f t="shared" si="105"/>
@@ -50523,7 +50523,7 @@
       </c>
       <c r="N563" s="13">
         <f t="shared" si="108"/>
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="O563" s="13" t="str">
         <f t="shared" si="109"/>
@@ -50565,27 +50565,27 @@
         <v/>
       </c>
       <c r="B564" s="12" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C564" s="12" t="s">
-        <v>1332</v>
-      </c>
-      <c r="D564" s="16" t="s">
-        <v>49</v>
+        <v>112</v>
+      </c>
+      <c r="D564" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E564" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F564" s="12" t="s">
-        <v>1333</v>
+        <v>1259</v>
       </c>
       <c r="G564" s="13">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="H564" s="13"/>
       <c r="I564" s="13"/>
       <c r="J564" s="13">
-        <v>1805</v>
+        <v>1817</v>
       </c>
       <c r="K564" s="13">
         <f t="shared" si="105"/>
@@ -50593,7 +50593,7 @@
       </c>
       <c r="L564" s="13">
         <f t="shared" si="106"/>
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="M564" s="13" t="str">
         <f t="shared" si="107"/>
@@ -50601,7 +50601,7 @@
       </c>
       <c r="N564" s="13">
         <f t="shared" si="108"/>
-        <v>1805</v>
+        <v>1817</v>
       </c>
       <c r="O564" s="13" t="str">
         <f t="shared" si="109"/>
@@ -50643,19 +50643,19 @@
         <v/>
       </c>
       <c r="B565" s="12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C565" s="12" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D565" s="12" t="s">
-        <v>283</v>
+        <v>1332</v>
+      </c>
+      <c r="D565" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E565" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F565" s="12" t="s">
-        <v>1047</v>
+        <v>1333</v>
       </c>
       <c r="G565" s="13">
         <v>1828</v>
@@ -50663,7 +50663,7 @@
       <c r="H565" s="13"/>
       <c r="I565" s="13"/>
       <c r="J565" s="13">
-        <v>1812</v>
+        <v>1805</v>
       </c>
       <c r="K565" s="13">
         <f t="shared" si="105"/>
@@ -50679,7 +50679,7 @@
       </c>
       <c r="N565" s="13">
         <f t="shared" si="108"/>
-        <v>1812</v>
+        <v>1805</v>
       </c>
       <c r="O565" s="13" t="str">
         <f t="shared" si="109"/>
@@ -50724,16 +50724,16 @@
         <v>6</v>
       </c>
       <c r="C566" s="12" t="s">
-        <v>1104</v>
-      </c>
-      <c r="D566" s="16" t="s">
-        <v>61</v>
+        <v>1046</v>
+      </c>
+      <c r="D566" s="12" t="s">
+        <v>283</v>
       </c>
       <c r="E566" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F566" s="12" t="s">
-        <v>1105</v>
+        <v>1047</v>
       </c>
       <c r="G566" s="13">
         <v>1828</v>
@@ -50741,7 +50741,7 @@
       <c r="H566" s="13"/>
       <c r="I566" s="13"/>
       <c r="J566" s="13">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="K566" s="13">
         <f t="shared" si="105"/>
@@ -50757,7 +50757,7 @@
       </c>
       <c r="N566" s="13">
         <f t="shared" si="108"/>
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="O566" s="13" t="str">
         <f t="shared" si="109"/>
@@ -50802,16 +50802,16 @@
         <v>6</v>
       </c>
       <c r="C567" s="12" t="s">
-        <v>1048</v>
+        <v>1104</v>
       </c>
       <c r="D567" s="16" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="E567" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F567" s="12" t="s">
-        <v>1049</v>
+        <v>1105</v>
       </c>
       <c r="G567" s="13">
         <v>1828</v>
@@ -50880,7 +50880,7 @@
         <v>6</v>
       </c>
       <c r="C568" s="12" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D568" s="16" t="s">
         <v>49</v>
@@ -50889,7 +50889,7 @@
         <v>26</v>
       </c>
       <c r="F568" s="12" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="G568" s="13">
         <v>1828</v>
@@ -50949,16 +50949,16 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="569" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="569" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A569" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="B569" s="12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C569" s="12" t="s">
-        <v>1326</v>
+        <v>1050</v>
       </c>
       <c r="D569" s="16" t="s">
         <v>49</v>
@@ -50967,7 +50967,7 @@
         <v>26</v>
       </c>
       <c r="F569" s="12" t="s">
-        <v>1327</v>
+        <v>1051</v>
       </c>
       <c r="G569" s="13">
         <v>1828</v>
@@ -50975,7 +50975,7 @@
       <c r="H569" s="13"/>
       <c r="I569" s="13"/>
       <c r="J569" s="13">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="K569" s="13">
         <f t="shared" si="105"/>
@@ -50991,7 +50991,7 @@
       </c>
       <c r="N569" s="13">
         <f t="shared" si="108"/>
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="O569" s="13" t="str">
         <f t="shared" si="109"/>
@@ -51027,7 +51027,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="570" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="570" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A570" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
@@ -51036,16 +51036,16 @@
         <v>10</v>
       </c>
       <c r="C570" s="12" t="s">
-        <v>1328</v>
-      </c>
-      <c r="D570" s="12" t="s">
-        <v>82</v>
+        <v>1326</v>
+      </c>
+      <c r="D570" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E570" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F570" s="12" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="G570" s="13">
         <v>1828</v>
@@ -51105,25 +51105,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="571" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="571" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A571" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="B571" s="12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C571" s="12" t="s">
-        <v>1184</v>
-      </c>
-      <c r="D571" s="16" t="s">
-        <v>61</v>
+        <v>1328</v>
+      </c>
+      <c r="D571" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E571" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F571" s="12" t="s">
-        <v>1185</v>
+        <v>1329</v>
       </c>
       <c r="G571" s="13">
         <v>1828</v>
@@ -51131,7 +51131,7 @@
       <c r="H571" s="13"/>
       <c r="I571" s="13"/>
       <c r="J571" s="13">
-        <v>1818</v>
+        <v>1815</v>
       </c>
       <c r="K571" s="13">
         <f t="shared" si="105"/>
@@ -51147,7 +51147,7 @@
       </c>
       <c r="N571" s="13">
         <f t="shared" si="108"/>
-        <v>1818</v>
+        <v>1815</v>
       </c>
       <c r="O571" s="13" t="str">
         <f t="shared" si="109"/>
@@ -51183,16 +51183,16 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="572" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="572" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A572" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="B572" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C572" s="12" t="s">
-        <v>1052</v>
+        <v>1184</v>
       </c>
       <c r="D572" s="16" t="s">
         <v>61</v>
@@ -51201,7 +51201,7 @@
         <v>26</v>
       </c>
       <c r="F572" s="12" t="s">
-        <v>1053</v>
+        <v>1185</v>
       </c>
       <c r="G572" s="13">
         <v>1828</v>
@@ -51270,16 +51270,16 @@
         <v>10</v>
       </c>
       <c r="C573" s="12" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D573" s="12" t="s">
-        <v>82</v>
+        <v>1052</v>
+      </c>
+      <c r="D573" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="E573" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F573" s="12" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="G573" s="13">
         <v>1828</v>
@@ -51348,16 +51348,16 @@
         <v>10</v>
       </c>
       <c r="C574" s="12" t="s">
-        <v>350</v>
-      </c>
-      <c r="D574" s="16" t="s">
-        <v>49</v>
+        <v>1054</v>
+      </c>
+      <c r="D574" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E574" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F574" s="12" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G574" s="13">
         <v>1828</v>
@@ -51423,19 +51423,19 @@
         <v/>
       </c>
       <c r="B575" s="12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C575" s="12" t="s">
-        <v>1429</v>
+        <v>350</v>
       </c>
       <c r="D575" s="16" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E575" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F575" s="12" t="s">
-        <v>1430</v>
+        <v>1056</v>
       </c>
       <c r="G575" s="13">
         <v>1828</v>
@@ -51443,7 +51443,7 @@
       <c r="H575" s="13"/>
       <c r="I575" s="13"/>
       <c r="J575" s="13">
-        <v>1838</v>
+        <v>1818</v>
       </c>
       <c r="K575" s="13">
         <f t="shared" si="105"/>
@@ -51459,7 +51459,7 @@
       </c>
       <c r="N575" s="13">
         <f t="shared" si="108"/>
-        <v>1838</v>
+        <v>1818</v>
       </c>
       <c r="O575" s="13" t="str">
         <f t="shared" si="109"/>
@@ -51495,33 +51495,33 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="576" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="576" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A576" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="B576" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C576" s="12" t="s">
-        <v>1059</v>
+        <v>1429</v>
       </c>
       <c r="D576" s="16" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E576" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F576" s="12" t="s">
-        <v>1060</v>
+        <v>1430</v>
       </c>
       <c r="G576" s="13">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="H576" s="13"/>
       <c r="I576" s="13"/>
       <c r="J576" s="13">
-        <v>1798</v>
+        <v>1838</v>
       </c>
       <c r="K576" s="13">
         <f t="shared" si="105"/>
@@ -51529,7 +51529,7 @@
       </c>
       <c r="L576" s="13">
         <f t="shared" si="106"/>
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M576" s="13" t="str">
         <f t="shared" si="107"/>
@@ -51537,7 +51537,7 @@
       </c>
       <c r="N576" s="13">
         <f t="shared" si="108"/>
-        <v>1798</v>
+        <v>1838</v>
       </c>
       <c r="O576" s="13" t="str">
         <f t="shared" si="109"/>
@@ -51579,19 +51579,19 @@
         <v/>
       </c>
       <c r="B577" s="12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C577" s="12" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D577" s="12" t="s">
-        <v>82</v>
+        <v>1059</v>
+      </c>
+      <c r="D577" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E577" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F577" s="12" t="s">
-        <v>1074</v>
+        <v>1060</v>
       </c>
       <c r="G577" s="13">
         <v>1829</v>
@@ -51599,7 +51599,7 @@
       <c r="H577" s="13"/>
       <c r="I577" s="13"/>
       <c r="J577" s="13">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="K577" s="13">
         <f t="shared" si="105"/>
@@ -51615,7 +51615,7 @@
       </c>
       <c r="N577" s="13">
         <f t="shared" si="108"/>
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="O577" s="13" t="str">
         <f t="shared" si="109"/>
@@ -51651,25 +51651,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="578" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="578" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A578" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="B578" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C578" s="12" t="s">
-        <v>1194</v>
+        <v>1073</v>
       </c>
       <c r="D578" s="12" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="E578" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F578" s="12" t="s">
-        <v>1195</v>
+        <v>1074</v>
       </c>
       <c r="G578" s="13">
         <v>1829</v>
@@ -51729,7 +51729,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="579" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="579" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A579" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
@@ -51738,16 +51738,16 @@
         <v>10</v>
       </c>
       <c r="C579" s="12" t="s">
-        <v>1370</v>
-      </c>
-      <c r="D579" s="16" t="s">
-        <v>49</v>
+        <v>1194</v>
+      </c>
+      <c r="D579" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="E579" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F579" s="12" t="s">
-        <v>1371</v>
+        <v>1195</v>
       </c>
       <c r="G579" s="13">
         <v>1829</v>
@@ -51813,10 +51813,10 @@
         <v/>
       </c>
       <c r="B580" s="12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C580" s="12" t="s">
-        <v>1215</v>
+        <v>1370</v>
       </c>
       <c r="D580" s="16" t="s">
         <v>49</v>
@@ -51825,7 +51825,7 @@
         <v>26</v>
       </c>
       <c r="F580" s="12" t="s">
-        <v>1216</v>
+        <v>1371</v>
       </c>
       <c r="G580" s="13">
         <v>1829</v>
@@ -51833,7 +51833,7 @@
       <c r="H580" s="13"/>
       <c r="I580" s="13"/>
       <c r="J580" s="13">
-        <v>1809</v>
+        <v>1799</v>
       </c>
       <c r="K580" s="13">
         <f t="shared" si="105"/>
@@ -51849,7 +51849,7 @@
       </c>
       <c r="N580" s="13">
         <f t="shared" si="108"/>
-        <v>1809</v>
+        <v>1799</v>
       </c>
       <c r="O580" s="13" t="str">
         <f t="shared" si="109"/>
@@ -51891,19 +51891,19 @@
         <v/>
       </c>
       <c r="B581" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C581" s="12" t="s">
-        <v>1070</v>
+        <v>1215</v>
       </c>
       <c r="D581" s="16" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E581" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F581" s="12" t="s">
-        <v>1071</v>
+        <v>1216</v>
       </c>
       <c r="G581" s="13">
         <v>1829</v>
@@ -51969,19 +51969,19 @@
         <v/>
       </c>
       <c r="B582" s="12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C582" s="12" t="s">
-        <v>1106</v>
-      </c>
-      <c r="D582" s="12" t="s">
-        <v>82</v>
+        <v>1070</v>
+      </c>
+      <c r="D582" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E582" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F582" s="12" t="s">
-        <v>1107</v>
+        <v>1071</v>
       </c>
       <c r="G582" s="13">
         <v>1829</v>
@@ -51989,7 +51989,7 @@
       <c r="H582" s="13"/>
       <c r="I582" s="13"/>
       <c r="J582" s="13">
-        <v>1813</v>
+        <v>1809</v>
       </c>
       <c r="K582" s="13">
         <f t="shared" si="105"/>
@@ -52005,7 +52005,7 @@
       </c>
       <c r="N582" s="13">
         <f t="shared" si="108"/>
-        <v>1813</v>
+        <v>1809</v>
       </c>
       <c r="O582" s="13" t="str">
         <f t="shared" si="109"/>
@@ -52041,7 +52041,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="583" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="583" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A583" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
@@ -52050,7 +52050,7 @@
         <v>6</v>
       </c>
       <c r="C583" s="12" t="s">
-        <v>575</v>
+        <v>1106</v>
       </c>
       <c r="D583" s="12" t="s">
         <v>82</v>
@@ -52059,7 +52059,7 @@
         <v>26</v>
       </c>
       <c r="F583" s="12" t="s">
-        <v>1072</v>
+        <v>1107</v>
       </c>
       <c r="G583" s="13">
         <v>1829</v>
@@ -52119,7 +52119,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="584" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="584" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A584" s="12" t="str">
         <f t="shared" si="104"/>
         <v/>
@@ -52128,16 +52128,16 @@
         <v>6</v>
       </c>
       <c r="C584" s="12" t="s">
-        <v>1280</v>
-      </c>
-      <c r="D584" s="16" t="s">
-        <v>52</v>
+        <v>575</v>
+      </c>
+      <c r="D584" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E584" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F584" s="12" t="s">
-        <v>1281</v>
+        <v>1072</v>
       </c>
       <c r="G584" s="13">
         <v>1829</v>
@@ -52145,7 +52145,7 @@
       <c r="H584" s="13"/>
       <c r="I584" s="13"/>
       <c r="J584" s="13">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="K584" s="13">
         <f t="shared" si="105"/>
@@ -52161,7 +52161,7 @@
       </c>
       <c r="N584" s="13">
         <f t="shared" si="108"/>
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="O584" s="13" t="str">
         <f t="shared" si="109"/>
@@ -52203,10 +52203,10 @@
         <v/>
       </c>
       <c r="B585" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C585" s="12" t="s">
-        <v>1186</v>
+        <v>1280</v>
       </c>
       <c r="D585" s="16" t="s">
         <v>52</v>
@@ -52215,7 +52215,7 @@
         <v>26</v>
       </c>
       <c r="F585" s="12" t="s">
-        <v>1187</v>
+        <v>1281</v>
       </c>
       <c r="G585" s="13">
         <v>1829</v>
@@ -52223,7 +52223,7 @@
       <c r="H585" s="13"/>
       <c r="I585" s="13"/>
       <c r="J585" s="13">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="K585" s="13">
         <f t="shared" si="105"/>
@@ -52239,7 +52239,7 @@
       </c>
       <c r="N585" s="13">
         <f t="shared" si="108"/>
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="O585" s="13" t="str">
         <f t="shared" si="109"/>
@@ -52284,16 +52284,16 @@
         <v>8</v>
       </c>
       <c r="C586" s="12" t="s">
-        <v>1102</v>
-      </c>
-      <c r="D586" s="12" t="s">
-        <v>82</v>
+        <v>1186</v>
+      </c>
+      <c r="D586" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E586" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F586" s="12" t="s">
-        <v>1103</v>
+        <v>1187</v>
       </c>
       <c r="G586" s="13">
         <v>1829</v>
@@ -52359,19 +52359,19 @@
         <v/>
       </c>
       <c r="B587" s="12" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C587" s="12" t="s">
-        <v>1213</v>
-      </c>
-      <c r="D587" s="16" t="s">
-        <v>49</v>
+        <v>1102</v>
+      </c>
+      <c r="D587" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E587" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F587" s="12" t="s">
-        <v>1214</v>
+        <v>1103</v>
       </c>
       <c r="G587" s="13">
         <v>1829</v>
@@ -52379,7 +52379,7 @@
       <c r="H587" s="13"/>
       <c r="I587" s="13"/>
       <c r="J587" s="13">
-        <v>1819</v>
+        <v>1815</v>
       </c>
       <c r="K587" s="13">
         <f t="shared" si="105"/>
@@ -52395,7 +52395,7 @@
       </c>
       <c r="N587" s="13">
         <f t="shared" si="108"/>
-        <v>1819</v>
+        <v>1815</v>
       </c>
       <c r="O587" s="13" t="str">
         <f t="shared" si="109"/>
@@ -52437,10 +52437,10 @@
         <v/>
       </c>
       <c r="B588" s="12" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C588" s="12" t="s">
-        <v>1077</v>
+        <v>1213</v>
       </c>
       <c r="D588" s="16" t="s">
         <v>49</v>
@@ -52449,7 +52449,7 @@
         <v>26</v>
       </c>
       <c r="F588" s="12" t="s">
-        <v>1078</v>
+        <v>1214</v>
       </c>
       <c r="G588" s="13">
         <v>1829</v>
@@ -52518,16 +52518,16 @@
         <v>8</v>
       </c>
       <c r="C589" s="12" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="D589" s="16" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E589" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F589" s="12" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="G589" s="13">
         <v>1829</v>
@@ -52596,16 +52596,16 @@
         <v>8</v>
       </c>
       <c r="C590" s="12" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D590" s="12" t="s">
-        <v>45</v>
+        <v>1079</v>
+      </c>
+      <c r="D590" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="E590" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F590" s="12" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="G590" s="13">
         <v>1829</v>
@@ -52671,19 +52671,19 @@
         <v/>
       </c>
       <c r="B591" s="12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C591" s="12" t="s">
-        <v>1217</v>
-      </c>
-      <c r="D591" s="16" t="s">
-        <v>82</v>
+        <v>1081</v>
+      </c>
+      <c r="D591" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="E591" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F591" s="12" t="s">
-        <v>1218</v>
+        <v>1082</v>
       </c>
       <c r="G591" s="13">
         <v>1829</v>
@@ -52743,25 +52743,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="592" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="592" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A592" s="12" t="str">
         <f t="shared" si="117"/>
         <v/>
       </c>
       <c r="B592" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C592" s="12" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="D592" s="16" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="E592" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F592" s="12" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="G592" s="13">
         <v>1829</v>
@@ -52830,16 +52830,16 @@
         <v>10</v>
       </c>
       <c r="C593" s="12" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D593" s="12" t="s">
-        <v>82</v>
+        <v>1219</v>
+      </c>
+      <c r="D593" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E593" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F593" s="12" t="s">
-        <v>1228</v>
+        <v>1220</v>
       </c>
       <c r="G593" s="13">
         <v>1829</v>
@@ -52908,16 +52908,16 @@
         <v>10</v>
       </c>
       <c r="C594" s="12" t="s">
-        <v>1230</v>
-      </c>
-      <c r="D594" s="16" t="s">
-        <v>61</v>
+        <v>1227</v>
+      </c>
+      <c r="D594" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E594" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F594" s="12" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="G594" s="13">
         <v>1829</v>
@@ -52986,16 +52986,16 @@
         <v>10</v>
       </c>
       <c r="C595" s="12" t="s">
-        <v>1208</v>
+        <v>1230</v>
       </c>
       <c r="D595" s="16" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="E595" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F595" s="12" t="s">
-        <v>1209</v>
+        <v>1231</v>
       </c>
       <c r="G595" s="13">
         <v>1829</v>
@@ -53055,25 +53055,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="596" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="596" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A596" s="12" t="str">
         <f t="shared" si="117"/>
         <v/>
       </c>
       <c r="B596" s="12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C596" s="12" t="s">
-        <v>1085</v>
-      </c>
-      <c r="D596" s="12" t="s">
-        <v>139</v>
+        <v>1208</v>
+      </c>
+      <c r="D596" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E596" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F596" s="12" t="s">
-        <v>1086</v>
+        <v>1209</v>
       </c>
       <c r="G596" s="13">
         <v>1829</v>
@@ -53081,7 +53081,7 @@
       <c r="H596" s="13"/>
       <c r="I596" s="13"/>
       <c r="J596" s="13">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="K596" s="13">
         <f t="shared" si="118"/>
@@ -53097,7 +53097,7 @@
       </c>
       <c r="N596" s="13">
         <f t="shared" si="121"/>
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="O596" s="13" t="str">
         <f t="shared" si="122"/>
@@ -53139,10 +53139,10 @@
         <v/>
       </c>
       <c r="B597" s="12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C597" s="12" t="s">
-        <v>1022</v>
+        <v>1085</v>
       </c>
       <c r="D597" s="12" t="s">
         <v>139</v>
@@ -53151,7 +53151,7 @@
         <v>26</v>
       </c>
       <c r="F597" s="12" t="s">
-        <v>1023</v>
+        <v>1086</v>
       </c>
       <c r="G597" s="13">
         <v>1829</v>
@@ -53159,7 +53159,7 @@
       <c r="H597" s="13"/>
       <c r="I597" s="13"/>
       <c r="J597" s="13">
-        <v>1824</v>
+        <v>1820</v>
       </c>
       <c r="K597" s="13">
         <f t="shared" si="118"/>
@@ -53175,7 +53175,7 @@
       </c>
       <c r="N597" s="13">
         <f t="shared" si="121"/>
-        <v>1824</v>
+        <v>1820</v>
       </c>
       <c r="O597" s="13" t="str">
         <f t="shared" si="122"/>
@@ -53217,19 +53217,19 @@
         <v/>
       </c>
       <c r="B598" s="12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C598" s="12" t="s">
-        <v>1374</v>
-      </c>
-      <c r="D598" s="16" t="s">
-        <v>61</v>
+        <v>1022</v>
+      </c>
+      <c r="D598" s="12" t="s">
+        <v>139</v>
       </c>
       <c r="E598" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F598" s="12" t="s">
-        <v>1375</v>
+        <v>1023</v>
       </c>
       <c r="G598" s="13">
         <v>1829</v>
@@ -53237,7 +53237,7 @@
       <c r="H598" s="13"/>
       <c r="I598" s="13"/>
       <c r="J598" s="13">
-        <v>1828</v>
+        <v>1824</v>
       </c>
       <c r="K598" s="13">
         <f t="shared" si="118"/>
@@ -53253,7 +53253,7 @@
       </c>
       <c r="N598" s="13">
         <f t="shared" si="121"/>
-        <v>1828</v>
+        <v>1824</v>
       </c>
       <c r="O598" s="13" t="str">
         <f t="shared" si="122"/>
@@ -53289,25 +53289,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="599" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="599" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A599" s="12" t="str">
         <f t="shared" si="117"/>
         <v/>
       </c>
       <c r="B599" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C599" s="12" t="s">
-        <v>1089</v>
+        <v>1374</v>
       </c>
       <c r="D599" s="16" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="E599" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F599" s="12" t="s">
-        <v>1090</v>
+        <v>1375</v>
       </c>
       <c r="G599" s="13">
         <v>1829</v>
@@ -53315,7 +53315,7 @@
       <c r="H599" s="13"/>
       <c r="I599" s="13"/>
       <c r="J599" s="13">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="K599" s="13">
         <f t="shared" si="118"/>
@@ -53331,7 +53331,7 @@
       </c>
       <c r="N599" s="13">
         <f t="shared" si="121"/>
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="O599" s="13" t="str">
         <f t="shared" si="122"/>
@@ -53376,16 +53376,16 @@
         <v>12</v>
       </c>
       <c r="C600" s="12" t="s">
-        <v>370</v>
+        <v>1089</v>
       </c>
       <c r="D600" s="16" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E600" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F600" s="12" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="G600" s="13">
         <v>1829</v>
@@ -53445,25 +53445,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="601" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="601" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A601" s="12" t="str">
         <f t="shared" si="117"/>
         <v/>
       </c>
       <c r="B601" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C601" s="12" t="s">
-        <v>1094</v>
-      </c>
-      <c r="D601" s="12" t="s">
-        <v>82</v>
+        <v>370</v>
+      </c>
+      <c r="D601" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="E601" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F601" s="12" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="G601" s="13">
         <v>1829</v>
@@ -53532,16 +53532,16 @@
         <v>10</v>
       </c>
       <c r="C602" s="12" t="s">
-        <v>1352</v>
+        <v>1094</v>
       </c>
       <c r="D602" s="12" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="E602" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F602" s="12" t="s">
-        <v>1353</v>
+        <v>1095</v>
       </c>
       <c r="G602" s="13">
         <v>1829</v>
@@ -53601,7 +53601,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="603" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="603" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A603" s="12" t="str">
         <f t="shared" si="117"/>
         <v/>
@@ -53610,16 +53610,16 @@
         <v>10</v>
       </c>
       <c r="C603" s="12" t="s">
-        <v>1316</v>
-      </c>
-      <c r="D603" s="16" t="s">
-        <v>52</v>
+        <v>1352</v>
+      </c>
+      <c r="D603" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="E603" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F603" s="12" t="s">
-        <v>1317</v>
+        <v>1353</v>
       </c>
       <c r="G603" s="13">
         <v>1829</v>
@@ -53679,25 +53679,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="604" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="604" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A604" s="12" t="str">
         <f t="shared" si="117"/>
         <v/>
       </c>
       <c r="B604" s="12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C604" s="12" t="s">
-        <v>1096</v>
+        <v>1316</v>
       </c>
       <c r="D604" s="16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E604" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F604" s="12" t="s">
-        <v>1097</v>
+        <v>1317</v>
       </c>
       <c r="G604" s="13">
         <v>1829</v>
@@ -53705,7 +53705,7 @@
       <c r="H604" s="13"/>
       <c r="I604" s="13"/>
       <c r="J604" s="13">
-        <v>1837</v>
+        <v>1829</v>
       </c>
       <c r="K604" s="13">
         <f t="shared" si="118"/>
@@ -53721,7 +53721,7 @@
       </c>
       <c r="N604" s="13">
         <f t="shared" si="121"/>
-        <v>1837</v>
+        <v>1829</v>
       </c>
       <c r="O604" s="13" t="str">
         <f t="shared" si="122"/>
@@ -53757,7 +53757,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="605" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="605" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A605" s="12" t="str">
         <f t="shared" si="117"/>
         <v/>
@@ -53766,16 +53766,16 @@
         <v>12</v>
       </c>
       <c r="C605" s="12" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="D605" s="16" t="s">
-        <v>139</v>
+        <v>49</v>
       </c>
       <c r="E605" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F605" s="12" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="G605" s="13">
         <v>1829</v>
@@ -53835,7 +53835,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="606" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="606" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A606" s="12" t="str">
         <f t="shared" si="117"/>
         <v/>
@@ -53844,7 +53844,7 @@
         <v>12</v>
       </c>
       <c r="C606" s="12" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="D606" s="16" t="s">
         <v>139</v>
@@ -53853,7 +53853,7 @@
         <v>26</v>
       </c>
       <c r="F606" s="12" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="G606" s="13">
         <v>1829</v>
@@ -53919,27 +53919,27 @@
         <v/>
       </c>
       <c r="B607" s="12" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C607" s="12" t="s">
-        <v>1378</v>
-      </c>
-      <c r="D607" s="12" t="s">
-        <v>283</v>
+        <v>1100</v>
+      </c>
+      <c r="D607" s="16" t="s">
+        <v>139</v>
       </c>
       <c r="E607" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F607" s="12" t="s">
-        <v>1379</v>
+        <v>1101</v>
       </c>
       <c r="G607" s="13">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="H607" s="13"/>
       <c r="I607" s="13"/>
       <c r="J607" s="13">
-        <v>1790</v>
+        <v>1837</v>
       </c>
       <c r="K607" s="13">
         <f t="shared" si="118"/>
@@ -53947,7 +53947,7 @@
       </c>
       <c r="L607" s="13">
         <f t="shared" si="119"/>
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="M607" s="13" t="str">
         <f t="shared" si="120"/>
@@ -53955,7 +53955,7 @@
       </c>
       <c r="N607" s="13">
         <f t="shared" si="121"/>
-        <v>1790</v>
+        <v>1837</v>
       </c>
       <c r="O607" s="13" t="str">
         <f t="shared" si="122"/>
@@ -53991,7 +53991,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="608" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="608" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A608" s="12" t="str">
         <f t="shared" si="117"/>
         <v/>
@@ -54000,7 +54000,7 @@
         <v>16</v>
       </c>
       <c r="C608" s="12" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="D608" s="12" t="s">
         <v>283</v>
@@ -54009,7 +54009,7 @@
         <v>26</v>
       </c>
       <c r="F608" s="12" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="G608" s="13">
         <v>1830</v>
@@ -54069,25 +54069,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="609" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="609" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A609" s="12" t="str">
         <f t="shared" si="117"/>
         <v/>
       </c>
       <c r="B609" s="12" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C609" s="12" t="s">
-        <v>1143</v>
-      </c>
-      <c r="D609" s="16" t="s">
-        <v>49</v>
+        <v>1380</v>
+      </c>
+      <c r="D609" s="12" t="s">
+        <v>283</v>
       </c>
       <c r="E609" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F609" s="12" t="s">
-        <v>1144</v>
+        <v>1381</v>
       </c>
       <c r="G609" s="13">
         <v>1830</v>
@@ -54095,7 +54095,7 @@
       <c r="H609" s="13"/>
       <c r="I609" s="13"/>
       <c r="J609" s="13">
-        <v>1810</v>
+        <v>1790</v>
       </c>
       <c r="K609" s="13">
         <f t="shared" si="118"/>
@@ -54111,7 +54111,7 @@
       </c>
       <c r="N609" s="13">
         <f t="shared" si="121"/>
-        <v>1810</v>
+        <v>1790</v>
       </c>
       <c r="O609" s="13" t="str">
         <f t="shared" si="122"/>
@@ -54147,25 +54147,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="610" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="610" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A610" s="12" t="str">
         <f t="shared" si="117"/>
         <v/>
       </c>
       <c r="B610" s="12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C610" s="12" t="s">
-        <v>515</v>
-      </c>
-      <c r="D610" s="12" t="s">
-        <v>82</v>
+        <v>1143</v>
+      </c>
+      <c r="D610" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E610" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F610" s="12" t="s">
-        <v>1203</v>
+        <v>1144</v>
       </c>
       <c r="G610" s="13">
         <v>1830</v>
@@ -54173,7 +54173,7 @@
       <c r="H610" s="13"/>
       <c r="I610" s="13"/>
       <c r="J610" s="13">
-        <v>1819</v>
+        <v>1810</v>
       </c>
       <c r="K610" s="13">
         <f t="shared" si="118"/>
@@ -54189,7 +54189,7 @@
       </c>
       <c r="N610" s="13">
         <f t="shared" si="121"/>
-        <v>1819</v>
+        <v>1810</v>
       </c>
       <c r="O610" s="13" t="str">
         <f t="shared" si="122"/>
@@ -54225,33 +54225,33 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="611" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="611" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A611" s="12" t="str">
         <f t="shared" si="117"/>
         <v/>
       </c>
       <c r="B611" s="12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C611" s="12" t="s">
-        <v>1358</v>
+        <v>515</v>
       </c>
       <c r="D611" s="12" t="s">
-        <v>308</v>
+        <v>82</v>
       </c>
       <c r="E611" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F611" s="12" t="s">
-        <v>1359</v>
+        <v>1203</v>
       </c>
       <c r="G611" s="13">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="H611" s="13"/>
       <c r="I611" s="13"/>
       <c r="J611" s="13">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="K611" s="13">
         <f t="shared" si="118"/>
@@ -54259,7 +54259,7 @@
       </c>
       <c r="L611" s="13">
         <f t="shared" si="119"/>
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="M611" s="13" t="str">
         <f t="shared" si="120"/>
@@ -54267,7 +54267,7 @@
       </c>
       <c r="N611" s="13">
         <f t="shared" si="121"/>
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="O611" s="13" t="str">
         <f t="shared" si="122"/>
@@ -54309,10 +54309,10 @@
         <v/>
       </c>
       <c r="B612" s="12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C612" s="12" t="s">
-        <v>1108</v>
+        <v>1358</v>
       </c>
       <c r="D612" s="12" t="s">
         <v>308</v>
@@ -54321,7 +54321,7 @@
         <v>26</v>
       </c>
       <c r="F612" s="12" t="s">
-        <v>1109</v>
+        <v>1359</v>
       </c>
       <c r="G612" s="13">
         <v>1831</v>
@@ -54329,7 +54329,7 @@
       <c r="H612" s="13"/>
       <c r="I612" s="13"/>
       <c r="J612" s="13">
-        <v>1824</v>
+        <v>1818</v>
       </c>
       <c r="K612" s="13">
         <f t="shared" si="118"/>
@@ -54345,7 +54345,7 @@
       </c>
       <c r="N612" s="13">
         <f t="shared" si="121"/>
-        <v>1824</v>
+        <v>1818</v>
       </c>
       <c r="O612" s="13" t="str">
         <f t="shared" si="122"/>
@@ -54387,27 +54387,27 @@
         <v/>
       </c>
       <c r="B613" s="12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C613" s="12" t="s">
-        <v>956</v>
-      </c>
-      <c r="D613" s="16" t="s">
-        <v>61</v>
+        <v>1108</v>
+      </c>
+      <c r="D613" s="12" t="s">
+        <v>308</v>
       </c>
       <c r="E613" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F613" s="12" t="s">
-        <v>957</v>
+        <v>1109</v>
       </c>
       <c r="G613" s="13">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="H613" s="13"/>
       <c r="I613" s="13"/>
       <c r="J613" s="13">
-        <v>1795</v>
+        <v>1824</v>
       </c>
       <c r="K613" s="13">
         <f t="shared" si="118"/>
@@ -54415,7 +54415,7 @@
       </c>
       <c r="L613" s="13">
         <f t="shared" si="119"/>
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="M613" s="13" t="str">
         <f t="shared" si="120"/>
@@ -54423,7 +54423,7 @@
       </c>
       <c r="N613" s="13">
         <f t="shared" si="121"/>
-        <v>1795</v>
+        <v>1824</v>
       </c>
       <c r="O613" s="13" t="str">
         <f t="shared" si="122"/>
@@ -63740,25 +63740,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="733" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="733" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A733" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B733" s="12" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C733" s="12" t="s">
-        <v>1304</v>
-      </c>
-      <c r="D733" s="12" t="s">
-        <v>82</v>
+        <v>1468</v>
+      </c>
+      <c r="D733" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E733" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F733" s="12" t="s">
-        <v>1305</v>
+        <v>1469</v>
       </c>
       <c r="G733" s="13">
         <v>1855</v>
@@ -63818,25 +63818,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="734" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="734" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A734" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B734" s="12" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C734" s="12" t="s">
-        <v>1468</v>
-      </c>
-      <c r="D734" s="16" t="s">
-        <v>49</v>
+        <v>1298</v>
+      </c>
+      <c r="D734" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E734" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F734" s="12" t="s">
-        <v>1469</v>
+        <v>1299</v>
       </c>
       <c r="G734" s="13">
         <v>1855</v>
@@ -63844,7 +63844,7 @@
       <c r="H734" s="13"/>
       <c r="I734" s="13"/>
       <c r="J734" s="13">
-        <v>1835</v>
+        <v>1845</v>
       </c>
       <c r="K734" s="13">
         <f t="shared" si="155"/>
@@ -63860,7 +63860,7 @@
       </c>
       <c r="N734" s="13">
         <f t="shared" si="146"/>
-        <v>1835</v>
+        <v>1845</v>
       </c>
       <c r="O734" s="13" t="str">
         <f t="shared" si="147"/>
@@ -63902,19 +63902,19 @@
         <v/>
       </c>
       <c r="B735" s="12" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C735" s="12" t="s">
-        <v>1298</v>
+        <v>1758</v>
       </c>
       <c r="D735" s="12" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="E735" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F735" s="12" t="s">
-        <v>1299</v>
+        <v>1759</v>
       </c>
       <c r="G735" s="13">
         <v>1855</v>
@@ -63980,19 +63980,19 @@
         <v/>
       </c>
       <c r="B736" s="12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C736" s="12" t="s">
-        <v>1758</v>
+        <v>1300</v>
       </c>
       <c r="D736" s="12" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="E736" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F736" s="12" t="s">
-        <v>1759</v>
+        <v>1301</v>
       </c>
       <c r="G736" s="13">
         <v>1855</v>
@@ -64058,19 +64058,19 @@
         <v/>
       </c>
       <c r="B737" s="12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C737" s="12" t="s">
-        <v>1300</v>
+        <v>1419</v>
       </c>
       <c r="D737" s="12" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="E737" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F737" s="12" t="s">
-        <v>1301</v>
+        <v>1420</v>
       </c>
       <c r="G737" s="13">
         <v>1855</v>
@@ -64078,7 +64078,7 @@
       <c r="H737" s="13"/>
       <c r="I737" s="13"/>
       <c r="J737" s="13">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="K737" s="13">
         <f t="shared" si="155"/>
@@ -64094,7 +64094,7 @@
       </c>
       <c r="N737" s="13">
         <f t="shared" si="146"/>
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="O737" s="13" t="str">
         <f t="shared" si="147"/>
@@ -64136,19 +64136,19 @@
         <v/>
       </c>
       <c r="B738" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C738" s="12" t="s">
-        <v>1419</v>
-      </c>
-      <c r="D738" s="12" t="s">
-        <v>139</v>
+        <v>1421</v>
+      </c>
+      <c r="D738" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E738" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F738" s="12" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="G738" s="13">
         <v>1855</v>
@@ -64156,7 +64156,7 @@
       <c r="H738" s="13"/>
       <c r="I738" s="13"/>
       <c r="J738" s="13">
-        <v>1846</v>
+        <v>1855</v>
       </c>
       <c r="K738" s="13">
         <f t="shared" si="155"/>
@@ -64172,7 +64172,7 @@
       </c>
       <c r="N738" s="13">
         <f t="shared" si="146"/>
-        <v>1846</v>
+        <v>1855</v>
       </c>
       <c r="O738" s="13" t="str">
         <f t="shared" si="147"/>
@@ -64214,27 +64214,27 @@
         <v/>
       </c>
       <c r="B739" s="12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C739" s="12" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="D739" s="16" t="s">
         <v>49</v>
       </c>
       <c r="E739" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F739" s="12" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="G739" s="13">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="H739" s="13"/>
       <c r="I739" s="13"/>
       <c r="J739" s="13">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="K739" s="13">
         <f t="shared" si="155"/>
@@ -64242,7 +64242,7 @@
       </c>
       <c r="L739" s="13">
         <f t="shared" si="144"/>
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="M739" s="13" t="str">
         <f t="shared" si="145"/>
@@ -64250,7 +64250,7 @@
       </c>
       <c r="N739" s="13">
         <f t="shared" si="146"/>
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="O739" s="13" t="str">
         <f t="shared" si="147"/>
@@ -64295,7 +64295,7 @@
         <v>12</v>
       </c>
       <c r="C740" s="12" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="D740" s="16" t="s">
         <v>49</v>
@@ -64304,7 +64304,7 @@
         <v>70</v>
       </c>
       <c r="F740" s="12" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="G740" s="13">
         <v>1856</v>
@@ -64370,27 +64370,27 @@
         <v/>
       </c>
       <c r="B741" s="12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C741" s="12" t="s">
-        <v>1425</v>
-      </c>
-      <c r="D741" s="16" t="s">
-        <v>49</v>
+        <v>1342</v>
+      </c>
+      <c r="D741" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E741" s="12" t="s">
         <v>70</v>
       </c>
       <c r="F741" s="12" t="s">
-        <v>1426</v>
+        <v>1541</v>
       </c>
       <c r="G741" s="13">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="H741" s="13"/>
       <c r="I741" s="13"/>
       <c r="J741" s="13">
-        <v>1856</v>
+        <v>1837</v>
       </c>
       <c r="K741" s="13">
         <f t="shared" si="155"/>
@@ -64398,7 +64398,7 @@
       </c>
       <c r="L741" s="13">
         <f t="shared" si="144"/>
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="M741" s="13" t="str">
         <f t="shared" si="145"/>
@@ -64406,7 +64406,7 @@
       </c>
       <c r="N741" s="13">
         <f t="shared" si="146"/>
-        <v>1856</v>
+        <v>1837</v>
       </c>
       <c r="O741" s="13" t="str">
         <f t="shared" si="147"/>
@@ -64442,16 +64442,16 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="742" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="742" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A742" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B742" s="12" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C742" s="12" t="s">
-        <v>1342</v>
+        <v>378</v>
       </c>
       <c r="D742" s="12" t="s">
         <v>82</v>
@@ -64460,15 +64460,15 @@
         <v>70</v>
       </c>
       <c r="F742" s="12" t="s">
-        <v>1541</v>
+        <v>1428</v>
       </c>
       <c r="G742" s="13">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="H742" s="13"/>
       <c r="I742" s="13"/>
       <c r="J742" s="13">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="K742" s="13">
         <f t="shared" si="155"/>
@@ -64476,7 +64476,7 @@
       </c>
       <c r="L742" s="13">
         <f t="shared" si="144"/>
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="M742" s="13" t="str">
         <f t="shared" si="145"/>
@@ -64484,7 +64484,7 @@
       </c>
       <c r="N742" s="13">
         <f t="shared" si="146"/>
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="O742" s="13" t="str">
         <f t="shared" si="147"/>
@@ -64520,25 +64520,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="743" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="743" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A743" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B743" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C743" s="12" t="s">
-        <v>378</v>
+        <v>1180</v>
       </c>
       <c r="D743" s="12" t="s">
         <v>82</v>
       </c>
       <c r="E743" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F743" s="12" t="s">
-        <v>1428</v>
+        <v>1181</v>
       </c>
       <c r="G743" s="13">
         <v>1858</v>
@@ -64546,7 +64546,7 @@
       <c r="H743" s="13"/>
       <c r="I743" s="13"/>
       <c r="J743" s="13">
-        <v>1835</v>
+        <v>1838</v>
       </c>
       <c r="K743" s="13">
         <f t="shared" si="155"/>
@@ -64562,7 +64562,7 @@
       </c>
       <c r="N743" s="13">
         <f t="shared" si="146"/>
-        <v>1835</v>
+        <v>1838</v>
       </c>
       <c r="O743" s="13" t="str">
         <f t="shared" si="147"/>
@@ -64598,16 +64598,16 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="744" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="744" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A744" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B744" s="12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C744" s="12" t="s">
-        <v>1180</v>
+        <v>1431</v>
       </c>
       <c r="D744" s="12" t="s">
         <v>82</v>
@@ -64616,7 +64616,7 @@
         <v>26</v>
       </c>
       <c r="F744" s="12" t="s">
-        <v>1181</v>
+        <v>1432</v>
       </c>
       <c r="G744" s="13">
         <v>1858</v>
@@ -64676,7 +64676,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="745" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="745" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A745" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
@@ -64685,16 +64685,16 @@
         <v>10</v>
       </c>
       <c r="C745" s="12" t="s">
-        <v>1431</v>
-      </c>
-      <c r="D745" s="12" t="s">
-        <v>82</v>
+        <v>1433</v>
+      </c>
+      <c r="D745" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="E745" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F745" s="12" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="G745" s="13">
         <v>1858</v>
@@ -64702,7 +64702,7 @@
       <c r="H745" s="13"/>
       <c r="I745" s="13"/>
       <c r="J745" s="13">
-        <v>1838</v>
+        <v>1849</v>
       </c>
       <c r="K745" s="13">
         <f t="shared" si="155"/>
@@ -64718,7 +64718,7 @@
       </c>
       <c r="N745" s="13">
         <f t="shared" si="146"/>
-        <v>1838</v>
+        <v>1849</v>
       </c>
       <c r="O745" s="13" t="str">
         <f t="shared" si="147"/>
@@ -64763,24 +64763,24 @@
         <v>10</v>
       </c>
       <c r="C746" s="12" t="s">
-        <v>1433</v>
-      </c>
-      <c r="D746" s="16" t="s">
-        <v>61</v>
+        <v>1753</v>
+      </c>
+      <c r="D746" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="E746" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F746" s="12" t="s">
-        <v>1434</v>
+        <v>1443</v>
       </c>
       <c r="G746" s="13">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="H746" s="13"/>
       <c r="I746" s="13"/>
       <c r="J746" s="13">
-        <v>1849</v>
+        <v>1809</v>
       </c>
       <c r="K746" s="13">
         <f t="shared" si="155"/>
@@ -64788,7 +64788,7 @@
       </c>
       <c r="L746" s="13">
         <f t="shared" si="144"/>
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="M746" s="13" t="str">
         <f t="shared" si="145"/>
@@ -64796,7 +64796,7 @@
       </c>
       <c r="N746" s="13">
         <f t="shared" si="146"/>
-        <v>1849</v>
+        <v>1809</v>
       </c>
       <c r="O746" s="13" t="str">
         <f t="shared" si="147"/>
@@ -64832,25 +64832,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="747" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="747" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A747" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B747" s="12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C747" s="12" t="s">
-        <v>1753</v>
-      </c>
-      <c r="D747" s="12" t="s">
-        <v>45</v>
+        <v>1437</v>
+      </c>
+      <c r="D747" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E747" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F747" s="12" t="s">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="G747" s="13">
         <v>1859</v>
@@ -64858,7 +64858,7 @@
       <c r="H747" s="13"/>
       <c r="I747" s="13"/>
       <c r="J747" s="13">
-        <v>1809</v>
+        <v>1814</v>
       </c>
       <c r="K747" s="13">
         <f t="shared" si="155"/>
@@ -64874,7 +64874,7 @@
       </c>
       <c r="N747" s="13">
         <f t="shared" si="146"/>
-        <v>1809</v>
+        <v>1814</v>
       </c>
       <c r="O747" s="13" t="str">
         <f t="shared" si="147"/>
@@ -64910,25 +64910,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="748" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="748" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A748" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B748" s="12" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C748" s="12" t="s">
-        <v>1437</v>
-      </c>
-      <c r="D748" s="16" t="s">
-        <v>52</v>
+        <v>1489</v>
+      </c>
+      <c r="D748" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E748" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F748" s="12" t="s">
-        <v>1438</v>
+        <v>1490</v>
       </c>
       <c r="G748" s="13">
         <v>1859</v>
@@ -64936,7 +64936,7 @@
       <c r="H748" s="13"/>
       <c r="I748" s="13"/>
       <c r="J748" s="13">
-        <v>1814</v>
+        <v>1819</v>
       </c>
       <c r="K748" s="13">
         <f t="shared" si="155"/>
@@ -64952,7 +64952,7 @@
       </c>
       <c r="N748" s="13">
         <f t="shared" si="146"/>
-        <v>1814</v>
+        <v>1819</v>
       </c>
       <c r="O748" s="13" t="str">
         <f t="shared" si="147"/>
@@ -64988,16 +64988,16 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="749" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="749" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A749" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B749" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C749" s="12" t="s">
-        <v>1489</v>
+        <v>1439</v>
       </c>
       <c r="D749" s="12" t="s">
         <v>82</v>
@@ -65006,7 +65006,7 @@
         <v>70</v>
       </c>
       <c r="F749" s="12" t="s">
-        <v>1490</v>
+        <v>1440</v>
       </c>
       <c r="G749" s="13">
         <v>1859</v>
@@ -65014,7 +65014,7 @@
       <c r="H749" s="13"/>
       <c r="I749" s="13"/>
       <c r="J749" s="13">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="K749" s="13">
         <f t="shared" si="155"/>
@@ -65030,7 +65030,7 @@
       </c>
       <c r="N749" s="13">
         <f t="shared" si="146"/>
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="O749" s="13" t="str">
         <f t="shared" si="147"/>
@@ -65066,16 +65066,16 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="750" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="750" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A750" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B750" s="12" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C750" s="12" t="s">
-        <v>1439</v>
+        <v>1454</v>
       </c>
       <c r="D750" s="12" t="s">
         <v>82</v>
@@ -65084,7 +65084,7 @@
         <v>70</v>
       </c>
       <c r="F750" s="12" t="s">
-        <v>1440</v>
+        <v>1455</v>
       </c>
       <c r="G750" s="13">
         <v>1859</v>
@@ -65092,7 +65092,7 @@
       <c r="H750" s="13"/>
       <c r="I750" s="13"/>
       <c r="J750" s="13">
-        <v>1820</v>
+        <v>1839</v>
       </c>
       <c r="K750" s="13">
         <f t="shared" si="155"/>
@@ -65108,7 +65108,7 @@
       </c>
       <c r="N750" s="13">
         <f t="shared" si="146"/>
-        <v>1820</v>
+        <v>1839</v>
       </c>
       <c r="O750" s="13" t="str">
         <f t="shared" si="147"/>
@@ -65150,19 +65150,19 @@
         <v/>
       </c>
       <c r="B751" s="12" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C751" s="12" t="s">
-        <v>1454</v>
-      </c>
-      <c r="D751" s="12" t="s">
-        <v>82</v>
+        <v>1566</v>
+      </c>
+      <c r="D751" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E751" s="12" t="s">
         <v>70</v>
       </c>
       <c r="F751" s="12" t="s">
-        <v>1455</v>
+        <v>1567</v>
       </c>
       <c r="G751" s="13">
         <v>1859</v>
@@ -65222,25 +65222,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="752" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="752" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A752" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B752" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C752" s="12" t="s">
-        <v>1566</v>
+        <v>1296</v>
       </c>
       <c r="D752" s="16" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="E752" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F752" s="12" t="s">
-        <v>1567</v>
+        <v>1297</v>
       </c>
       <c r="G752" s="13">
         <v>1859</v>
@@ -65248,10 +65248,10 @@
       <c r="H752" s="13"/>
       <c r="I752" s="13"/>
       <c r="J752" s="13">
-        <v>1839</v>
+        <v>1849</v>
       </c>
       <c r="K752" s="13">
-        <f t="shared" ref="K752:K759" si="156">IF(AND(IFERROR(SEARCH("현대오일뱅크",$C752),0)&gt;0,IFERROR(SEARCH("직영",$C752),0)&gt;0),$B$13,0)</f>
+        <f t="shared" ref="K752:K758" si="156">IF(AND(IFERROR(SEARCH("현대오일뱅크",$C752),0)&gt;0,IFERROR(SEARCH("직영",$C752),0)&gt;0),$B$13,0)</f>
         <v>0</v>
       </c>
       <c r="L752" s="13">
@@ -65264,7 +65264,7 @@
       </c>
       <c r="N752" s="13">
         <f t="shared" si="146"/>
-        <v>1839</v>
+        <v>1849</v>
       </c>
       <c r="O752" s="13" t="str">
         <f t="shared" si="147"/>
@@ -65300,25 +65300,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="753" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="753" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A753" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B753" s="12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C753" s="12" t="s">
-        <v>1296</v>
-      </c>
-      <c r="D753" s="16" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D753" s="12" t="s">
         <v>82</v>
       </c>
       <c r="E753" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F753" s="12" t="s">
-        <v>1297</v>
+        <v>1449</v>
       </c>
       <c r="G753" s="13">
         <v>1859</v>
@@ -65387,16 +65387,16 @@
         <v>10</v>
       </c>
       <c r="C754" s="12" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="D754" s="12" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="E754" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F754" s="12" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="G754" s="13">
         <v>1859</v>
@@ -65462,19 +65462,19 @@
         <v/>
       </c>
       <c r="B755" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C755" s="12" t="s">
-        <v>1450</v>
-      </c>
-      <c r="D755" s="12" t="s">
-        <v>139</v>
+        <v>1456</v>
+      </c>
+      <c r="D755" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E755" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F755" s="12" t="s">
-        <v>1451</v>
+        <v>1457</v>
       </c>
       <c r="G755" s="13">
         <v>1859</v>
@@ -65482,7 +65482,7 @@
       <c r="H755" s="13"/>
       <c r="I755" s="13"/>
       <c r="J755" s="13">
-        <v>1849</v>
+        <v>1869</v>
       </c>
       <c r="K755" s="13">
         <f t="shared" si="156"/>
@@ -65498,7 +65498,7 @@
       </c>
       <c r="N755" s="13">
         <f t="shared" si="146"/>
-        <v>1849</v>
+        <v>1869</v>
       </c>
       <c r="O755" s="13" t="str">
         <f t="shared" si="147"/>
@@ -65543,16 +65543,16 @@
         <v>14</v>
       </c>
       <c r="C756" s="12" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D756" s="16" t="s">
-        <v>49</v>
+        <v>1458</v>
+      </c>
+      <c r="D756" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E756" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F756" s="12" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="G756" s="13">
         <v>1859</v>
@@ -65612,33 +65612,33 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="757" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="757" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A757" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B757" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C757" s="12" t="s">
-        <v>1458</v>
-      </c>
-      <c r="D757" s="12" t="s">
-        <v>82</v>
+        <v>1515</v>
+      </c>
+      <c r="D757" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E757" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F757" s="12" t="s">
-        <v>1459</v>
+        <v>1516</v>
       </c>
       <c r="G757" s="13">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="H757" s="13"/>
       <c r="I757" s="13"/>
       <c r="J757" s="13">
-        <v>1869</v>
+        <v>1820</v>
       </c>
       <c r="K757" s="13">
         <f t="shared" si="156"/>
@@ -65646,7 +65646,7 @@
       </c>
       <c r="L757" s="13">
         <f t="shared" si="144"/>
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="M757" s="13" t="str">
         <f t="shared" si="145"/>
@@ -65654,7 +65654,7 @@
       </c>
       <c r="N757" s="13">
         <f t="shared" si="146"/>
-        <v>1869</v>
+        <v>1820</v>
       </c>
       <c r="O757" s="13" t="str">
         <f t="shared" si="147"/>
@@ -65690,7 +65690,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="758" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="758" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A758" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
@@ -65699,7 +65699,7 @@
         <v>16</v>
       </c>
       <c r="C758" s="12" t="s">
-        <v>1515</v>
+        <v>1602</v>
       </c>
       <c r="D758" s="16" t="s">
         <v>49</v>
@@ -65708,7 +65708,7 @@
         <v>26</v>
       </c>
       <c r="F758" s="12" t="s">
-        <v>1516</v>
+        <v>1603</v>
       </c>
       <c r="G758" s="13">
         <v>1860</v>
@@ -65716,7 +65716,7 @@
       <c r="H758" s="13"/>
       <c r="I758" s="13"/>
       <c r="J758" s="13">
-        <v>1820</v>
+        <v>1830</v>
       </c>
       <c r="K758" s="13">
         <f t="shared" si="156"/>
@@ -65732,7 +65732,7 @@
       </c>
       <c r="N758" s="13">
         <f t="shared" si="146"/>
-        <v>1820</v>
+        <v>1830</v>
       </c>
       <c r="O758" s="13" t="str">
         <f t="shared" si="147"/>
@@ -65774,10 +65774,10 @@
         <v/>
       </c>
       <c r="B759" s="12" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C759" s="12" t="s">
-        <v>1602</v>
+        <v>1464</v>
       </c>
       <c r="D759" s="16" t="s">
         <v>49</v>
@@ -65786,23 +65786,22 @@
         <v>26</v>
       </c>
       <c r="F759" s="12" t="s">
-        <v>1603</v>
+        <v>1465</v>
       </c>
       <c r="G759" s="13">
-        <v>1860</v>
+        <v>1864</v>
       </c>
       <c r="H759" s="13"/>
       <c r="I759" s="13"/>
       <c r="J759" s="13">
-        <v>1830</v>
+        <v>1854</v>
       </c>
       <c r="K759" s="13">
-        <f t="shared" si="156"/>
         <v>0</v>
       </c>
       <c r="L759" s="13">
         <f t="shared" si="144"/>
-        <v>1860</v>
+        <v>1864</v>
       </c>
       <c r="M759" s="13" t="str">
         <f t="shared" si="145"/>
@@ -65810,7 +65809,7 @@
       </c>
       <c r="N759" s="13">
         <f t="shared" si="146"/>
-        <v>1830</v>
+        <v>1854</v>
       </c>
       <c r="O759" s="13" t="str">
         <f t="shared" si="147"/>
@@ -65852,34 +65851,35 @@
         <v/>
       </c>
       <c r="B760" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C760" s="12" t="s">
-        <v>1464</v>
+        <v>565</v>
       </c>
       <c r="D760" s="16" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="E760" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F760" s="12" t="s">
-        <v>1465</v>
+        <v>1470</v>
       </c>
       <c r="G760" s="13">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="H760" s="13"/>
       <c r="I760" s="13"/>
       <c r="J760" s="13">
-        <v>1854</v>
+        <v>1845</v>
       </c>
       <c r="K760" s="13">
+        <f>IF(AND(IFERROR(SEARCH("현대오일뱅크",$C760),0)&gt;0,IFERROR(SEARCH("직영",$C760),0)&gt;0),$B$13,0)</f>
         <v>0</v>
       </c>
       <c r="L760" s="13">
         <f t="shared" si="144"/>
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="M760" s="13" t="str">
         <f t="shared" si="145"/>
@@ -65887,7 +65887,7 @@
       </c>
       <c r="N760" s="13">
         <f t="shared" si="146"/>
-        <v>1854</v>
+        <v>1845</v>
       </c>
       <c r="O760" s="13" t="str">
         <f t="shared" si="147"/>
@@ -65929,19 +65929,19 @@
         <v/>
       </c>
       <c r="B761" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C761" s="12" t="s">
-        <v>565</v>
+        <v>1576</v>
       </c>
       <c r="D761" s="16" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E761" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F761" s="12" t="s">
-        <v>1470</v>
+        <v>1577</v>
       </c>
       <c r="G761" s="13">
         <v>1865</v>
@@ -66007,19 +66007,19 @@
         <v/>
       </c>
       <c r="B762" s="12" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C762" s="12" t="s">
-        <v>1576</v>
+        <v>1473</v>
       </c>
       <c r="D762" s="16" t="s">
         <v>49</v>
       </c>
       <c r="E762" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F762" s="12" t="s">
-        <v>1577</v>
+        <v>1474</v>
       </c>
       <c r="G762" s="13">
         <v>1865</v>
@@ -66027,7 +66027,7 @@
       <c r="H762" s="13"/>
       <c r="I762" s="13"/>
       <c r="J762" s="13">
-        <v>1845</v>
+        <v>1857</v>
       </c>
       <c r="K762" s="13">
         <f>IF(AND(IFERROR(SEARCH("현대오일뱅크",$C762),0)&gt;0,IFERROR(SEARCH("직영",$C762),0)&gt;0),$B$13,0)</f>
@@ -66043,7 +66043,7 @@
       </c>
       <c r="N762" s="13">
         <f t="shared" si="146"/>
-        <v>1845</v>
+        <v>1857</v>
       </c>
       <c r="O762" s="13" t="str">
         <f t="shared" si="147"/>
@@ -66079,16 +66079,16 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="763" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="763" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A763" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B763" s="12" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C763" s="12" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="D763" s="16" t="s">
         <v>49</v>
@@ -66097,23 +66097,22 @@
         <v>70</v>
       </c>
       <c r="F763" s="12" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="G763" s="13">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="H763" s="13"/>
       <c r="I763" s="13"/>
       <c r="J763" s="13">
-        <v>1857</v>
+        <v>1850</v>
       </c>
       <c r="K763" s="13">
-        <f>IF(AND(IFERROR(SEARCH("현대오일뱅크",$C763),0)&gt;0,IFERROR(SEARCH("직영",$C763),0)&gt;0),$B$13,0)</f>
         <v>0</v>
       </c>
       <c r="L763" s="13">
         <f t="shared" si="144"/>
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="M763" s="13" t="str">
         <f t="shared" si="145"/>
@@ -66121,7 +66120,7 @@
       </c>
       <c r="N763" s="13">
         <f t="shared" si="146"/>
-        <v>1857</v>
+        <v>1850</v>
       </c>
       <c r="O763" s="13" t="str">
         <f t="shared" si="147"/>
@@ -66157,40 +66156,41 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="764" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="764" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A764" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B764" s="12" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C764" s="12" t="s">
-        <v>1475</v>
+        <v>1535</v>
       </c>
       <c r="D764" s="16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E764" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F764" s="12" t="s">
-        <v>1476</v>
+        <v>1536</v>
       </c>
       <c r="G764" s="13">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="H764" s="13"/>
       <c r="I764" s="13"/>
       <c r="J764" s="13">
-        <v>1850</v>
+        <v>1853</v>
       </c>
       <c r="K764" s="13">
+        <f t="shared" ref="K764:K785" si="157">IF(AND(IFERROR(SEARCH("현대오일뱅크",$C764),0)&gt;0,IFERROR(SEARCH("직영",$C764),0)&gt;0),$B$13,0)</f>
         <v>0</v>
       </c>
       <c r="L764" s="13">
         <f t="shared" si="144"/>
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="M764" s="13" t="str">
         <f t="shared" si="145"/>
@@ -66198,7 +66198,7 @@
       </c>
       <c r="N764" s="13">
         <f t="shared" si="146"/>
-        <v>1850</v>
+        <v>1853</v>
       </c>
       <c r="O764" s="13" t="str">
         <f t="shared" si="147"/>
@@ -66234,25 +66234,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="765" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="765" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A765" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B765" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C765" s="12" t="s">
-        <v>1535</v>
+        <v>1481</v>
       </c>
       <c r="D765" s="16" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E765" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F765" s="12" t="s">
-        <v>1536</v>
+        <v>1482</v>
       </c>
       <c r="G765" s="13">
         <v>1867</v>
@@ -66260,10 +66260,10 @@
       <c r="H765" s="13"/>
       <c r="I765" s="13"/>
       <c r="J765" s="13">
-        <v>1853</v>
+        <v>1867</v>
       </c>
       <c r="K765" s="13">
-        <f t="shared" ref="K765:K786" si="157">IF(AND(IFERROR(SEARCH("현대오일뱅크",$C765),0)&gt;0,IFERROR(SEARCH("직영",$C765),0)&gt;0),$B$13,0)</f>
+        <f t="shared" si="157"/>
         <v>0</v>
       </c>
       <c r="L765" s="13">
@@ -66276,7 +66276,7 @@
       </c>
       <c r="N765" s="13">
         <f t="shared" si="146"/>
-        <v>1853</v>
+        <v>1867</v>
       </c>
       <c r="O765" s="13" t="str">
         <f t="shared" si="147"/>
@@ -66312,33 +66312,33 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="766" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="766" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A766" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B766" s="12" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C766" s="12" t="s">
-        <v>1481</v>
-      </c>
-      <c r="D766" s="16" t="s">
-        <v>49</v>
+        <v>1653</v>
+      </c>
+      <c r="D766" s="12" t="s">
+        <v>139</v>
       </c>
       <c r="E766" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F766" s="12" t="s">
-        <v>1482</v>
+        <v>1654</v>
       </c>
       <c r="G766" s="13">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="H766" s="13"/>
       <c r="I766" s="13"/>
       <c r="J766" s="13">
-        <v>1867</v>
+        <v>1838</v>
       </c>
       <c r="K766" s="13">
         <f t="shared" si="157"/>
@@ -66346,7 +66346,7 @@
       </c>
       <c r="L766" s="13">
         <f t="shared" si="144"/>
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="M766" s="13" t="str">
         <f t="shared" si="145"/>
@@ -66354,7 +66354,7 @@
       </c>
       <c r="N766" s="13">
         <f t="shared" si="146"/>
-        <v>1867</v>
+        <v>1838</v>
       </c>
       <c r="O766" s="13" t="str">
         <f t="shared" si="147"/>
@@ -66396,19 +66396,19 @@
         <v/>
       </c>
       <c r="B767" s="12" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C767" s="12" t="s">
-        <v>1653</v>
-      </c>
-      <c r="D767" s="12" t="s">
-        <v>139</v>
+        <v>1485</v>
+      </c>
+      <c r="D767" s="16" t="s">
+        <v>82</v>
       </c>
       <c r="E767" s="12" t="s">
         <v>70</v>
       </c>
       <c r="F767" s="12" t="s">
-        <v>1654</v>
+        <v>1486</v>
       </c>
       <c r="G767" s="13">
         <v>1868</v>
@@ -66416,7 +66416,7 @@
       <c r="H767" s="13"/>
       <c r="I767" s="13"/>
       <c r="J767" s="13">
-        <v>1838</v>
+        <v>1848</v>
       </c>
       <c r="K767" s="13">
         <f t="shared" si="157"/>
@@ -66432,7 +66432,7 @@
       </c>
       <c r="N767" s="13">
         <f t="shared" si="146"/>
-        <v>1838</v>
+        <v>1848</v>
       </c>
       <c r="O767" s="13" t="str">
         <f t="shared" si="147"/>
@@ -66474,27 +66474,27 @@
         <v/>
       </c>
       <c r="B768" s="12" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C768" s="12" t="s">
-        <v>1485</v>
-      </c>
-      <c r="D768" s="16" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D768" s="12" t="s">
         <v>82</v>
       </c>
       <c r="E768" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F768" s="12" t="s">
-        <v>1486</v>
+        <v>1500</v>
       </c>
       <c r="G768" s="13">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="H768" s="13"/>
       <c r="I768" s="13"/>
       <c r="J768" s="13">
-        <v>1848</v>
+        <v>1833</v>
       </c>
       <c r="K768" s="13">
         <f t="shared" si="157"/>
@@ -66502,7 +66502,7 @@
       </c>
       <c r="L768" s="13">
         <f t="shared" si="144"/>
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="M768" s="13" t="str">
         <f t="shared" si="145"/>
@@ -66510,7 +66510,7 @@
       </c>
       <c r="N768" s="13">
         <f t="shared" si="146"/>
-        <v>1848</v>
+        <v>1833</v>
       </c>
       <c r="O768" s="13" t="str">
         <f t="shared" si="147"/>
@@ -66546,7 +66546,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="769" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="769" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A769" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
@@ -66555,7 +66555,7 @@
         <v>18</v>
       </c>
       <c r="C769" s="12" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="D769" s="12" t="s">
         <v>82</v>
@@ -66564,7 +66564,7 @@
         <v>26</v>
       </c>
       <c r="F769" s="12" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="G769" s="13">
         <v>1869</v>
@@ -66624,7 +66624,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="770" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="770" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A770" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
@@ -66633,7 +66633,7 @@
         <v>18</v>
       </c>
       <c r="C770" s="12" t="s">
-        <v>1501</v>
+        <v>1537</v>
       </c>
       <c r="D770" s="12" t="s">
         <v>82</v>
@@ -66642,7 +66642,7 @@
         <v>26</v>
       </c>
       <c r="F770" s="12" t="s">
-        <v>1502</v>
+        <v>1538</v>
       </c>
       <c r="G770" s="13">
         <v>1869</v>
@@ -66650,7 +66650,7 @@
       <c r="H770" s="13"/>
       <c r="I770" s="13"/>
       <c r="J770" s="13">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="K770" s="13">
         <f t="shared" si="157"/>
@@ -66666,7 +66666,7 @@
       </c>
       <c r="N770" s="13">
         <f t="shared" si="146"/>
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="O770" s="13" t="str">
         <f t="shared" si="147"/>
@@ -66711,16 +66711,16 @@
         <v>18</v>
       </c>
       <c r="C771" s="12" t="s">
-        <v>1537</v>
-      </c>
-      <c r="D771" s="12" t="s">
-        <v>82</v>
+        <v>1491</v>
+      </c>
+      <c r="D771" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E771" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F771" s="12" t="s">
-        <v>1538</v>
+        <v>1492</v>
       </c>
       <c r="G771" s="13">
         <v>1869</v>
@@ -66728,7 +66728,7 @@
       <c r="H771" s="13"/>
       <c r="I771" s="13"/>
       <c r="J771" s="13">
-        <v>1834</v>
+        <v>1839</v>
       </c>
       <c r="K771" s="13">
         <f t="shared" si="157"/>
@@ -66744,7 +66744,7 @@
       </c>
       <c r="N771" s="13">
         <f t="shared" si="146"/>
-        <v>1834</v>
+        <v>1839</v>
       </c>
       <c r="O771" s="13" t="str">
         <f t="shared" si="147"/>
@@ -66780,25 +66780,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="772" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="772" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A772" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B772" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C772" s="12" t="s">
-        <v>1491</v>
-      </c>
-      <c r="D772" s="16" t="s">
-        <v>49</v>
+        <v>1493</v>
+      </c>
+      <c r="D772" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E772" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F772" s="12" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="G772" s="13">
         <v>1869</v>
@@ -66858,7 +66858,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="773" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="773" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A773" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
@@ -66867,7 +66867,7 @@
         <v>14</v>
       </c>
       <c r="C773" s="12" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="D773" s="12" t="s">
         <v>82</v>
@@ -66876,7 +66876,7 @@
         <v>26</v>
       </c>
       <c r="F773" s="12" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="G773" s="13">
         <v>1869</v>
@@ -66936,16 +66936,16 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="774" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="774" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A774" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B774" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C774" s="12" t="s">
-        <v>1495</v>
+        <v>1503</v>
       </c>
       <c r="D774" s="12" t="s">
         <v>82</v>
@@ -66954,7 +66954,7 @@
         <v>26</v>
       </c>
       <c r="F774" s="12" t="s">
-        <v>1496</v>
+        <v>1504</v>
       </c>
       <c r="G774" s="13">
         <v>1869</v>
@@ -66962,7 +66962,7 @@
       <c r="H774" s="13"/>
       <c r="I774" s="13"/>
       <c r="J774" s="13">
-        <v>1839</v>
+        <v>1849</v>
       </c>
       <c r="K774" s="13">
         <f t="shared" si="157"/>
@@ -66978,7 +66978,7 @@
       </c>
       <c r="N774" s="13">
         <f t="shared" si="146"/>
-        <v>1839</v>
+        <v>1849</v>
       </c>
       <c r="O774" s="13" t="str">
         <f t="shared" si="147"/>
@@ -67020,19 +67020,19 @@
         <v/>
       </c>
       <c r="B775" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C775" s="12" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="D775" s="12" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="E775" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F775" s="12" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="G775" s="13">
         <v>1869</v>
@@ -67098,19 +67098,19 @@
         <v/>
       </c>
       <c r="B776" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C776" s="12" t="s">
-        <v>1505</v>
-      </c>
-      <c r="D776" s="12" t="s">
-        <v>139</v>
+        <v>1507</v>
+      </c>
+      <c r="D776" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E776" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F776" s="12" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="G776" s="13">
         <v>1869</v>
@@ -67118,7 +67118,7 @@
       <c r="H776" s="13"/>
       <c r="I776" s="13"/>
       <c r="J776" s="13">
-        <v>1849</v>
+        <v>1859</v>
       </c>
       <c r="K776" s="13">
         <f t="shared" si="157"/>
@@ -67134,7 +67134,7 @@
       </c>
       <c r="N776" s="13">
         <f t="shared" si="146"/>
-        <v>1849</v>
+        <v>1859</v>
       </c>
       <c r="O776" s="13" t="str">
         <f t="shared" si="147"/>
@@ -67170,25 +67170,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="777" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="777" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A777" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B777" s="12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C777" s="12" t="s">
-        <v>1507</v>
+        <v>1679</v>
       </c>
       <c r="D777" s="16" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E777" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F777" s="12" t="s">
-        <v>1508</v>
+        <v>1680</v>
       </c>
       <c r="G777" s="13">
         <v>1869</v>
@@ -67254,19 +67254,19 @@
         <v/>
       </c>
       <c r="B778" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C778" s="12" t="s">
-        <v>1679</v>
-      </c>
-      <c r="D778" s="16" t="s">
-        <v>49</v>
+        <v>1511</v>
+      </c>
+      <c r="D778" s="12" t="s">
+        <v>139</v>
       </c>
       <c r="E778" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F778" s="12" t="s">
-        <v>1680</v>
+        <v>1512</v>
       </c>
       <c r="G778" s="13">
         <v>1869</v>
@@ -67274,7 +67274,7 @@
       <c r="H778" s="13"/>
       <c r="I778" s="13"/>
       <c r="J778" s="13">
-        <v>1859</v>
+        <v>1869</v>
       </c>
       <c r="K778" s="13">
         <f t="shared" si="157"/>
@@ -67290,7 +67290,7 @@
       </c>
       <c r="N778" s="13">
         <f t="shared" si="146"/>
-        <v>1859</v>
+        <v>1869</v>
       </c>
       <c r="O778" s="13" t="str">
         <f t="shared" si="147"/>
@@ -67326,33 +67326,33 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="779" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="779" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A779" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B779" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C779" s="12" t="s">
-        <v>1511</v>
-      </c>
-      <c r="D779" s="12" t="s">
-        <v>139</v>
+        <v>1513</v>
+      </c>
+      <c r="D779" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E779" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F779" s="12" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="G779" s="13">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="H779" s="13"/>
       <c r="I779" s="13"/>
       <c r="J779" s="13">
-        <v>1869</v>
+        <v>1830</v>
       </c>
       <c r="K779" s="13">
         <f t="shared" si="157"/>
@@ -67360,7 +67360,7 @@
       </c>
       <c r="L779" s="13">
         <f t="shared" si="144"/>
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="M779" s="13" t="str">
         <f t="shared" si="145"/>
@@ -67368,7 +67368,7 @@
       </c>
       <c r="N779" s="13">
         <f t="shared" si="146"/>
-        <v>1869</v>
+        <v>1830</v>
       </c>
       <c r="O779" s="13" t="str">
         <f t="shared" si="147"/>
@@ -67413,16 +67413,16 @@
         <v>16</v>
       </c>
       <c r="C780" s="12" t="s">
-        <v>1513</v>
-      </c>
-      <c r="D780" s="16" t="s">
-        <v>52</v>
+        <v>1517</v>
+      </c>
+      <c r="D780" s="12" t="s">
+        <v>139</v>
       </c>
       <c r="E780" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F780" s="12" t="s">
-        <v>1514</v>
+        <v>1518</v>
       </c>
       <c r="G780" s="13">
         <v>1870</v>
@@ -67482,16 +67482,16 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="781" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="781" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A781" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B781" s="12" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C781" s="12" t="s">
-        <v>1517</v>
+        <v>1521</v>
       </c>
       <c r="D781" s="12" t="s">
         <v>139</v>
@@ -67500,7 +67500,7 @@
         <v>70</v>
       </c>
       <c r="F781" s="12" t="s">
-        <v>1518</v>
+        <v>1522</v>
       </c>
       <c r="G781" s="13">
         <v>1870</v>
@@ -67508,7 +67508,7 @@
       <c r="H781" s="13"/>
       <c r="I781" s="13"/>
       <c r="J781" s="13">
-        <v>1830</v>
+        <v>1850</v>
       </c>
       <c r="K781" s="13">
         <f t="shared" si="157"/>
@@ -67524,7 +67524,7 @@
       </c>
       <c r="N781" s="13">
         <f t="shared" si="146"/>
-        <v>1830</v>
+        <v>1850</v>
       </c>
       <c r="O781" s="13" t="str">
         <f t="shared" si="147"/>
@@ -67560,25 +67560,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="782" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="782" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A782" s="12" t="str">
         <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="B782" s="12" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C782" s="12" t="s">
-        <v>1521</v>
-      </c>
-      <c r="D782" s="12" t="s">
-        <v>139</v>
+        <v>1523</v>
+      </c>
+      <c r="D782" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E782" s="12" t="s">
         <v>70</v>
       </c>
       <c r="F782" s="12" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="G782" s="13">
         <v>1870</v>
@@ -67644,19 +67644,19 @@
         <v/>
       </c>
       <c r="B783" s="12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C783" s="12" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="D783" s="16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E783" s="12" t="s">
         <v>70</v>
       </c>
       <c r="F783" s="12" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="G783" s="13">
         <v>1870</v>
@@ -67664,7 +67664,7 @@
       <c r="H783" s="13"/>
       <c r="I783" s="13"/>
       <c r="J783" s="13">
-        <v>1850</v>
+        <v>1860</v>
       </c>
       <c r="K783" s="13">
         <f t="shared" si="157"/>
@@ -67680,7 +67680,7 @@
       </c>
       <c r="N783" s="13">
         <f t="shared" ref="N783:N846" si="161">IF($J783="","",$J783+$K783)</f>
-        <v>1850</v>
+        <v>1860</v>
       </c>
       <c r="O783" s="13" t="str">
         <f t="shared" ref="O783:O846" si="162">IF($B$10=0,"",IFERROR(IF($B$4&gt;0,"휘발유 "&amp;TEXT(IF($L783="",1/0,$L783*$B$4),"#,##0")&amp;"원","")&amp;IF($B$5&gt;0,IF($B$4&gt;0," / ","")&amp;"고급유 "&amp;TEXT(IF($M783="",1/0,$M783*$B$5),"#,##0")&amp;"원","")&amp;IF($B$6&gt;0,IF(OR($B$4&gt;0,$B$5&gt;0)," / ","")&amp;"경유 "&amp;TEXT(IF($N783="",1/0,$N783*$B$6),"#,##0")&amp;"원",""),""))</f>
@@ -67722,19 +67722,19 @@
         <v/>
       </c>
       <c r="B784" s="12" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C784" s="12" t="s">
-        <v>1525</v>
-      </c>
-      <c r="D784" s="16" t="s">
-        <v>52</v>
+        <v>1527</v>
+      </c>
+      <c r="D784" s="12" t="s">
+        <v>139</v>
       </c>
       <c r="E784" s="12" t="s">
         <v>70</v>
       </c>
       <c r="F784" s="12" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="G784" s="13">
         <v>1870</v>
@@ -67742,7 +67742,7 @@
       <c r="H784" s="13"/>
       <c r="I784" s="13"/>
       <c r="J784" s="13">
-        <v>1860</v>
+        <v>1870</v>
       </c>
       <c r="K784" s="13">
         <f t="shared" si="157"/>
@@ -67758,7 +67758,7 @@
       </c>
       <c r="N784" s="13">
         <f t="shared" si="161"/>
-        <v>1860</v>
+        <v>1870</v>
       </c>
       <c r="O784" s="13" t="str">
         <f t="shared" si="162"/>
@@ -67800,27 +67800,27 @@
         <v/>
       </c>
       <c r="B785" s="12" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C785" s="12" t="s">
-        <v>1527</v>
-      </c>
-      <c r="D785" s="12" t="s">
-        <v>139</v>
+        <v>1529</v>
+      </c>
+      <c r="D785" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E785" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F785" s="12" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="G785" s="13">
-        <v>1870</v>
+        <v>2080</v>
       </c>
       <c r="H785" s="13"/>
       <c r="I785" s="13"/>
       <c r="J785" s="13">
-        <v>1870</v>
+        <v>1807</v>
       </c>
       <c r="K785" s="13">
         <f t="shared" si="157"/>
@@ -67828,7 +67828,7 @@
       </c>
       <c r="L785" s="13">
         <f t="shared" si="159"/>
-        <v>1870</v>
+        <v>2080</v>
       </c>
       <c r="M785" s="13" t="str">
         <f t="shared" si="160"/>
@@ -67836,7 +67836,7 @@
       </c>
       <c r="N785" s="13">
         <f t="shared" si="161"/>
-        <v>1870</v>
+        <v>1807</v>
       </c>
       <c r="O785" s="13" t="str">
         <f t="shared" si="162"/>
@@ -67846,7 +67846,9 @@
         <f t="shared" si="163"/>
         <v/>
       </c>
-      <c r="Q785" s="13"/>
+      <c r="Q785" s="13" t="s">
+        <v>47</v>
+      </c>
       <c r="R785" s="14" t="str">
         <f t="shared" si="164"/>
         <v/>
@@ -67881,32 +67883,31 @@
         <v>10</v>
       </c>
       <c r="C786" s="12" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="D786" s="16" t="s">
         <v>49</v>
       </c>
       <c r="E786" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F786" s="12" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="G786" s="13">
-        <v>2080</v>
+        <v>1874</v>
       </c>
       <c r="H786" s="13"/>
       <c r="I786" s="13"/>
       <c r="J786" s="13">
-        <v>1807</v>
+        <v>1854</v>
       </c>
       <c r="K786" s="13">
-        <f t="shared" si="157"/>
         <v>0</v>
       </c>
       <c r="L786" s="13">
         <f t="shared" si="159"/>
-        <v>2080</v>
+        <v>1874</v>
       </c>
       <c r="M786" s="13" t="str">
         <f t="shared" si="160"/>
@@ -67914,7 +67915,7 @@
       </c>
       <c r="N786" s="13">
         <f t="shared" si="161"/>
-        <v>1807</v>
+        <v>1854</v>
       </c>
       <c r="O786" s="13" t="str">
         <f t="shared" si="162"/>
@@ -67924,9 +67925,7 @@
         <f t="shared" si="163"/>
         <v/>
       </c>
-      <c r="Q786" s="13" t="s">
-        <v>47</v>
-      </c>
+      <c r="Q786" s="13"/>
       <c r="R786" s="14" t="str">
         <f t="shared" si="164"/>
         <v/>
@@ -67958,19 +67957,19 @@
         <v/>
       </c>
       <c r="B787" s="12" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C787" s="12" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="D787" s="16" t="s">
         <v>49</v>
       </c>
       <c r="E787" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F787" s="12" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="G787" s="13">
         <v>1874</v>
@@ -67978,9 +67977,10 @@
       <c r="H787" s="13"/>
       <c r="I787" s="13"/>
       <c r="J787" s="13">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="K787" s="13">
+        <f>IF(AND(IFERROR(SEARCH("현대오일뱅크",$C787),0)&gt;0,IFERROR(SEARCH("직영",$C787),0)&gt;0),$B$13,0)</f>
         <v>0</v>
       </c>
       <c r="L787" s="13">
@@ -67993,7 +67993,7 @@
       </c>
       <c r="N787" s="13">
         <f t="shared" si="161"/>
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="O787" s="13" t="str">
         <f t="shared" si="162"/>
@@ -68035,22 +68035,22 @@
         <v/>
       </c>
       <c r="B788" s="12" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C788" s="12" t="s">
-        <v>1533</v>
-      </c>
-      <c r="D788" s="16" t="s">
-        <v>49</v>
+        <v>1539</v>
+      </c>
+      <c r="D788" s="12" t="s">
+        <v>139</v>
       </c>
       <c r="E788" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F788" s="12" t="s">
-        <v>1534</v>
+        <v>1540</v>
       </c>
       <c r="G788" s="13">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="H788" s="13"/>
       <c r="I788" s="13"/>
@@ -68063,7 +68063,7 @@
       </c>
       <c r="L788" s="13">
         <f t="shared" si="159"/>
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="M788" s="13" t="str">
         <f t="shared" si="160"/>
@@ -68107,7 +68107,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="789" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="789" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A789" s="12" t="str">
         <f t="shared" si="158"/>
         <v/>
@@ -68116,16 +68116,16 @@
         <v>8</v>
       </c>
       <c r="C789" s="12" t="s">
-        <v>1539</v>
+        <v>1542</v>
       </c>
       <c r="D789" s="12" t="s">
         <v>139</v>
       </c>
       <c r="E789" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F789" s="12" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="G789" s="13">
         <v>1875</v>
@@ -68133,7 +68133,7 @@
       <c r="H789" s="13"/>
       <c r="I789" s="13"/>
       <c r="J789" s="13">
-        <v>1855</v>
+        <v>1859</v>
       </c>
       <c r="K789" s="13">
         <f>IF(AND(IFERROR(SEARCH("현대오일뱅크",$C789),0)&gt;0,IFERROR(SEARCH("직영",$C789),0)&gt;0),$B$13,0)</f>
@@ -68149,7 +68149,7 @@
       </c>
       <c r="N789" s="13">
         <f t="shared" si="161"/>
-        <v>1855</v>
+        <v>1859</v>
       </c>
       <c r="O789" s="13" t="str">
         <f t="shared" si="162"/>
@@ -68185,25 +68185,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="790" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="790" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A790" s="12" t="str">
         <f t="shared" si="158"/>
         <v/>
       </c>
       <c r="B790" s="12" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C790" s="12" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="D790" s="12" t="s">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="E790" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F790" s="12" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="G790" s="13">
         <v>1875</v>
@@ -68211,7 +68211,7 @@
       <c r="H790" s="13"/>
       <c r="I790" s="13"/>
       <c r="J790" s="13">
-        <v>1859</v>
+        <v>1868</v>
       </c>
       <c r="K790" s="13">
         <f>IF(AND(IFERROR(SEARCH("현대오일뱅크",$C790),0)&gt;0,IFERROR(SEARCH("직영",$C790),0)&gt;0),$B$13,0)</f>
@@ -68227,7 +68227,7 @@
       </c>
       <c r="N790" s="13">
         <f t="shared" si="161"/>
-        <v>1859</v>
+        <v>1868</v>
       </c>
       <c r="O790" s="13" t="str">
         <f t="shared" si="162"/>
@@ -68269,19 +68269,19 @@
         <v/>
       </c>
       <c r="B791" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C791" s="12" t="s">
-        <v>1544</v>
-      </c>
-      <c r="D791" s="12" t="s">
-        <v>82</v>
+        <v>1546</v>
+      </c>
+      <c r="D791" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E791" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F791" s="12" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="G791" s="13">
         <v>1875</v>
@@ -68289,10 +68289,9 @@
       <c r="H791" s="13"/>
       <c r="I791" s="13"/>
       <c r="J791" s="13">
-        <v>1868</v>
+        <v>1870</v>
       </c>
       <c r="K791" s="13">
-        <f>IF(AND(IFERROR(SEARCH("현대오일뱅크",$C791),0)&gt;0,IFERROR(SEARCH("직영",$C791),0)&gt;0),$B$13,0)</f>
         <v>0</v>
       </c>
       <c r="L791" s="13">
@@ -68305,7 +68304,7 @@
       </c>
       <c r="N791" s="13">
         <f t="shared" si="161"/>
-        <v>1868</v>
+        <v>1870</v>
       </c>
       <c r="O791" s="13" t="str">
         <f t="shared" si="162"/>
@@ -68350,7 +68349,7 @@
         <v>12</v>
       </c>
       <c r="C792" s="12" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="D792" s="16" t="s">
         <v>49</v>
@@ -68359,7 +68358,7 @@
         <v>70</v>
       </c>
       <c r="F792" s="12" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="G792" s="13">
         <v>1875</v>
@@ -68418,7 +68417,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="793" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="793" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A793" s="12" t="str">
         <f t="shared" si="158"/>
         <v/>
@@ -68427,7 +68426,7 @@
         <v>12</v>
       </c>
       <c r="C793" s="12" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="D793" s="16" t="s">
         <v>49</v>
@@ -68436,7 +68435,7 @@
         <v>70</v>
       </c>
       <c r="F793" s="12" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="G793" s="13">
         <v>1875</v>
@@ -68495,25 +68494,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="794" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="794" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A794" s="12" t="str">
         <f t="shared" si="158"/>
         <v/>
       </c>
       <c r="B794" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C794" s="12" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="D794" s="16" t="s">
         <v>49</v>
       </c>
       <c r="E794" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F794" s="12" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="G794" s="13">
         <v>1875</v>
@@ -68521,9 +68520,10 @@
       <c r="H794" s="13"/>
       <c r="I794" s="13"/>
       <c r="J794" s="13">
-        <v>1870</v>
+        <v>1875</v>
       </c>
       <c r="K794" s="13">
+        <f t="shared" ref="K794:K825" si="170">IF(AND(IFERROR(SEARCH("현대오일뱅크",$C794),0)&gt;0,IFERROR(SEARCH("직영",$C794),0)&gt;0),$B$13,0)</f>
         <v>0</v>
       </c>
       <c r="L794" s="13">
@@ -68536,7 +68536,7 @@
       </c>
       <c r="N794" s="13">
         <f t="shared" si="161"/>
-        <v>1870</v>
+        <v>1875</v>
       </c>
       <c r="O794" s="13" t="str">
         <f t="shared" si="162"/>
@@ -68578,35 +68578,35 @@
         <v/>
       </c>
       <c r="B795" s="12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C795" s="12" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
       <c r="D795" s="16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E795" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F795" s="12" t="s">
-        <v>1553</v>
+        <v>1557</v>
       </c>
       <c r="G795" s="13">
-        <v>1875</v>
+        <v>1878</v>
       </c>
       <c r="H795" s="13"/>
       <c r="I795" s="13"/>
       <c r="J795" s="13">
-        <v>1875</v>
+        <v>1822</v>
       </c>
       <c r="K795" s="13">
-        <f t="shared" ref="K795:K826" si="170">IF(AND(IFERROR(SEARCH("현대오일뱅크",$C795),0)&gt;0,IFERROR(SEARCH("직영",$C795),0)&gt;0),$B$13,0)</f>
+        <f t="shared" si="170"/>
         <v>0</v>
       </c>
       <c r="L795" s="13">
         <f t="shared" si="159"/>
-        <v>1875</v>
+        <v>1878</v>
       </c>
       <c r="M795" s="13" t="str">
         <f t="shared" si="160"/>
@@ -68614,7 +68614,7 @@
       </c>
       <c r="N795" s="13">
         <f t="shared" si="161"/>
-        <v>1875</v>
+        <v>1822</v>
       </c>
       <c r="O795" s="13" t="str">
         <f t="shared" si="162"/>
@@ -68656,19 +68656,19 @@
         <v/>
       </c>
       <c r="B796" s="12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C796" s="12" t="s">
-        <v>1556</v>
-      </c>
-      <c r="D796" s="16" t="s">
-        <v>52</v>
+        <v>1657</v>
+      </c>
+      <c r="D796" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E796" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F796" s="12" t="s">
-        <v>1557</v>
+        <v>1658</v>
       </c>
       <c r="G796" s="13">
         <v>1878</v>
@@ -68676,7 +68676,7 @@
       <c r="H796" s="13"/>
       <c r="I796" s="13"/>
       <c r="J796" s="13">
-        <v>1822</v>
+        <v>1877</v>
       </c>
       <c r="K796" s="13">
         <f t="shared" si="170"/>
@@ -68692,7 +68692,7 @@
       </c>
       <c r="N796" s="13">
         <f t="shared" si="161"/>
-        <v>1822</v>
+        <v>1877</v>
       </c>
       <c r="O796" s="13" t="str">
         <f t="shared" si="162"/>
@@ -68728,7 +68728,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="797" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="797" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A797" s="12" t="str">
         <f t="shared" si="158"/>
         <v/>
@@ -68737,7 +68737,7 @@
         <v>14</v>
       </c>
       <c r="C797" s="12" t="s">
-        <v>1657</v>
+        <v>1558</v>
       </c>
       <c r="D797" s="12" t="s">
         <v>82</v>
@@ -68746,7 +68746,7 @@
         <v>26</v>
       </c>
       <c r="F797" s="12" t="s">
-        <v>1658</v>
+        <v>1559</v>
       </c>
       <c r="G797" s="13">
         <v>1878</v>
@@ -68754,7 +68754,7 @@
       <c r="H797" s="13"/>
       <c r="I797" s="13"/>
       <c r="J797" s="13">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="K797" s="13">
         <f t="shared" si="170"/>
@@ -68770,7 +68770,7 @@
       </c>
       <c r="N797" s="13">
         <f t="shared" si="161"/>
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="O797" s="13" t="str">
         <f t="shared" si="162"/>
@@ -68806,7 +68806,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="798" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="798" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A798" s="12" t="str">
         <f t="shared" si="158"/>
         <v/>
@@ -68815,7 +68815,7 @@
         <v>14</v>
       </c>
       <c r="C798" s="12" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="D798" s="12" t="s">
         <v>82</v>
@@ -68824,15 +68824,15 @@
         <v>26</v>
       </c>
       <c r="F798" s="12" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="G798" s="13">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="H798" s="13"/>
       <c r="I798" s="13"/>
       <c r="J798" s="13">
-        <v>1878</v>
+        <v>1865</v>
       </c>
       <c r="K798" s="13">
         <f t="shared" si="170"/>
@@ -68840,7 +68840,7 @@
       </c>
       <c r="L798" s="13">
         <f t="shared" si="159"/>
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="M798" s="13" t="str">
         <f t="shared" si="160"/>
@@ -68848,7 +68848,7 @@
       </c>
       <c r="N798" s="13">
         <f t="shared" si="161"/>
-        <v>1878</v>
+        <v>1865</v>
       </c>
       <c r="O798" s="13" t="str">
         <f t="shared" si="162"/>
@@ -68893,16 +68893,16 @@
         <v>14</v>
       </c>
       <c r="C799" s="12" t="s">
-        <v>1560</v>
-      </c>
-      <c r="D799" s="12" t="s">
-        <v>82</v>
+        <v>1562</v>
+      </c>
+      <c r="D799" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="E799" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F799" s="12" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="G799" s="13">
         <v>1879</v>
@@ -68968,19 +68968,19 @@
         <v/>
       </c>
       <c r="B800" s="12" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C800" s="12" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="D800" s="16" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E800" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F800" s="12" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="G800" s="13">
         <v>1879</v>
@@ -68988,7 +68988,7 @@
       <c r="H800" s="13"/>
       <c r="I800" s="13"/>
       <c r="J800" s="13">
-        <v>1865</v>
+        <v>1869</v>
       </c>
       <c r="K800" s="13">
         <f t="shared" si="170"/>
@@ -69004,7 +69004,7 @@
       </c>
       <c r="N800" s="13">
         <f t="shared" si="161"/>
-        <v>1865</v>
+        <v>1869</v>
       </c>
       <c r="O800" s="13" t="str">
         <f t="shared" si="162"/>
@@ -69040,25 +69040,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="801" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="801" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A801" s="12" t="str">
         <f t="shared" si="158"/>
         <v/>
       </c>
       <c r="B801" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C801" s="12" t="s">
-        <v>1564</v>
+        <v>1497</v>
       </c>
       <c r="D801" s="16" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E801" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F801" s="12" t="s">
-        <v>1565</v>
+        <v>1498</v>
       </c>
       <c r="G801" s="13">
         <v>1879</v>
@@ -69127,7 +69127,7 @@
         <v>14</v>
       </c>
       <c r="C802" s="12" t="s">
-        <v>1497</v>
+        <v>1568</v>
       </c>
       <c r="D802" s="16" t="s">
         <v>49</v>
@@ -69136,7 +69136,7 @@
         <v>70</v>
       </c>
       <c r="F802" s="12" t="s">
-        <v>1498</v>
+        <v>1569</v>
       </c>
       <c r="G802" s="13">
         <v>1879</v>
@@ -69196,7 +69196,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="803" spans="1:23" s="17" customFormat="1" ht="28.5" customHeight="1">
+    <row r="803" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A803" s="12" t="str">
         <f t="shared" si="158"/>
         <v/>
@@ -69205,16 +69205,16 @@
         <v>14</v>
       </c>
       <c r="C803" s="12" t="s">
-        <v>1568</v>
+        <v>1689</v>
       </c>
       <c r="D803" s="16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E803" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F803" s="12" t="s">
-        <v>1569</v>
+        <v>1690</v>
       </c>
       <c r="G803" s="13">
         <v>1879</v>
@@ -69274,7 +69274,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="804" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="804" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A804" s="12" t="str">
         <f t="shared" si="158"/>
         <v/>
@@ -69283,16 +69283,16 @@
         <v>14</v>
       </c>
       <c r="C804" s="12" t="s">
-        <v>1689</v>
+        <v>1570</v>
       </c>
       <c r="D804" s="16" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E804" s="12" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F804" s="12" t="s">
-        <v>1690</v>
+        <v>1571</v>
       </c>
       <c r="G804" s="13">
         <v>1879</v>
@@ -69300,7 +69300,7 @@
       <c r="H804" s="13"/>
       <c r="I804" s="13"/>
       <c r="J804" s="13">
-        <v>1869</v>
+        <v>1879</v>
       </c>
       <c r="K804" s="13">
         <f t="shared" si="170"/>
@@ -69316,7 +69316,7 @@
       </c>
       <c r="N804" s="13">
         <f t="shared" si="161"/>
-        <v>1869</v>
+        <v>1879</v>
       </c>
       <c r="O804" s="13" t="str">
         <f t="shared" si="162"/>
@@ -69358,27 +69358,27 @@
         <v/>
       </c>
       <c r="B805" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C805" s="12" t="s">
-        <v>1570</v>
-      </c>
-      <c r="D805" s="16" t="s">
-        <v>49</v>
+        <v>1574</v>
+      </c>
+      <c r="D805" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E805" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F805" s="12" t="s">
-        <v>1571</v>
+        <v>1575</v>
       </c>
       <c r="G805" s="13">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="H805" s="13"/>
       <c r="I805" s="13"/>
       <c r="J805" s="13">
-        <v>1879</v>
+        <v>1825</v>
       </c>
       <c r="K805" s="13">
         <f t="shared" si="170"/>
@@ -69386,7 +69386,7 @@
       </c>
       <c r="L805" s="13">
         <f t="shared" si="159"/>
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="M805" s="13" t="str">
         <f t="shared" si="160"/>
@@ -69394,7 +69394,7 @@
       </c>
       <c r="N805" s="13">
         <f t="shared" si="161"/>
-        <v>1879</v>
+        <v>1825</v>
       </c>
       <c r="O805" s="13" t="str">
         <f t="shared" si="162"/>
@@ -69430,16 +69430,16 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="806" spans="1:23" s="8" customFormat="1" ht="28.5" customHeight="1">
+    <row r="806" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A806" s="12" t="str">
         <f t="shared" si="158"/>
         <v/>
       </c>
       <c r="B806" s="12" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C806" s="12" t="s">
-        <v>1574</v>
+        <v>1304</v>
       </c>
       <c r="D806" s="12" t="s">
         <v>82</v>
@@ -69448,7 +69448,7 @@
         <v>26</v>
       </c>
       <c r="F806" s="12" t="s">
-        <v>1575</v>
+        <v>1305</v>
       </c>
       <c r="G806" s="13">
         <v>1885</v>
@@ -69456,7 +69456,7 @@
       <c r="H806" s="13"/>
       <c r="I806" s="13"/>
       <c r="J806" s="13">
-        <v>1825</v>
+        <v>1835</v>
       </c>
       <c r="K806" s="13">
         <f t="shared" si="170"/>
@@ -69472,7 +69472,7 @@
       </c>
       <c r="N806" s="13">
         <f t="shared" si="161"/>
-        <v>1825</v>
+        <v>1835</v>
       </c>
       <c r="O806" s="13" t="str">
         <f t="shared" si="162"/>
@@ -71019,7 +71019,7 @@
         <v>1880</v>
       </c>
       <c r="K826" s="13">
-        <f t="shared" si="170"/>
+        <f t="shared" ref="K826:K857" si="171">IF(AND(IFERROR(SEARCH("현대오일뱅크",$C826),0)&gt;0,IFERROR(SEARCH("직영",$C826),0)&gt;0),$B$13,0)</f>
         <v>0</v>
       </c>
       <c r="L826" s="13">
@@ -71097,7 +71097,7 @@
         <v>1880</v>
       </c>
       <c r="K827" s="13">
-        <f t="shared" ref="K827:K858" si="171">IF(AND(IFERROR(SEARCH("현대오일뱅크",$C827),0)&gt;0,IFERROR(SEARCH("직영",$C827),0)&gt;0),$B$13,0)</f>
+        <f t="shared" si="171"/>
         <v>0</v>
       </c>
       <c r="L827" s="13">
@@ -73515,7 +73515,7 @@
         <v>1899</v>
       </c>
       <c r="K858" s="13">
-        <f t="shared" si="171"/>
+        <f t="shared" ref="K858:K882" si="184">IF(AND(IFERROR(SEARCH("현대오일뱅크",$C858),0)&gt;0,IFERROR(SEARCH("직영",$C858),0)&gt;0),$B$13,0)</f>
         <v>0</v>
       </c>
       <c r="L858" s="13">
@@ -73593,7 +73593,7 @@
         <v>1899</v>
       </c>
       <c r="K859" s="13">
-        <f t="shared" ref="K859:K882" si="184">IF(AND(IFERROR(SEARCH("현대오일뱅크",$C859),0)&gt;0,IFERROR(SEARCH("직영",$C859),0)&gt;0),$B$13,0)</f>
+        <f t="shared" si="184"/>
         <v>0</v>
       </c>
       <c r="L859" s="13">
@@ -75542,1027 +75542,428 @@
     </row>
     <row r="4" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
       <c r="A4" s="20" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>108</v>
+        <v>956</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>109</v>
+        <v>957</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>1764</v>
       </c>
       <c r="E4" s="22">
-        <v>1819</v>
+        <v>1832</v>
       </c>
       <c r="F4" s="22">
-        <v>1819</v>
+        <v>1812</v>
       </c>
       <c r="G4" s="22">
-        <f t="shared" ref="G4:G28" si="0">IF(OR(E4="",F4=""),"",F4-E4)</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="22">
-        <v>2259</v>
-      </c>
-      <c r="I4" s="22">
-        <v>2259</v>
-      </c>
-      <c r="J4" s="22">
-        <f t="shared" ref="J4:J28" si="1">IF(OR(H4="",I4=""),"",I4-H4)</f>
-        <v>0</v>
+        <f>IF(OR(E4="",F4=""),"",F4-E4)</f>
+        <v>-20</v>
+      </c>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22" t="str">
+        <f>IF(OR(H4="",I4=""),"",I4-H4)</f>
+        <v/>
       </c>
       <c r="K4" s="22">
-        <v>1819</v>
+        <v>1795</v>
       </c>
       <c r="L4" s="22">
-        <v>1849</v>
+        <v>1795</v>
       </c>
       <c r="M4" s="22">
-        <f t="shared" ref="M4:M28" si="2">IF(OR(K4="",L4=""),"",L4-K4)</f>
-        <v>30</v>
+        <f>IF(OR(K4="",L4=""),"",L4-K4)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
       <c r="A5" s="20" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>120</v>
+        <v>1304</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>121</v>
+        <v>1305</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>1764</v>
       </c>
       <c r="E5" s="22">
-        <v>1849</v>
+        <v>1855</v>
       </c>
       <c r="F5" s="22">
-        <v>1849</v>
+        <v>1885</v>
       </c>
       <c r="G5" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="22">
-        <v>2179</v>
-      </c>
-      <c r="I5" s="22">
-        <v>2199</v>
-      </c>
-      <c r="J5" s="22">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f>IF(OR(E5="",F5=""),"",F5-E5)</f>
+        <v>30</v>
+      </c>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22" t="str">
+        <f>IF(OR(H5="",I5=""),"",I5-H5)</f>
+        <v/>
       </c>
       <c r="K5" s="22">
-        <v>1839</v>
+        <v>1835</v>
       </c>
       <c r="L5" s="22">
-        <v>1839</v>
+        <v>1835</v>
       </c>
       <c r="M5" s="22">
-        <f t="shared" si="2"/>
+        <f>IF(OR(K5="",L5=""),"",L5-K5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A6" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E6" s="22">
-        <v>1788</v>
-      </c>
-      <c r="F6" s="22">
-        <v>1788</v>
-      </c>
-      <c r="G6" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="22">
-        <v>2295</v>
-      </c>
-      <c r="I6" s="22">
-        <v>2295</v>
-      </c>
-      <c r="J6" s="22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="22">
-        <v>1798</v>
-      </c>
-      <c r="L6" s="22">
-        <v>1795</v>
-      </c>
-      <c r="M6" s="22">
-        <f t="shared" si="2"/>
-        <v>-3</v>
-      </c>
+      <c r="A6" s="20"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
     </row>
     <row r="7" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A7" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E7" s="22">
-        <v>1845</v>
-      </c>
-      <c r="F7" s="22">
-        <v>1845</v>
-      </c>
-      <c r="G7" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="22">
-        <v>2249</v>
-      </c>
-      <c r="I7" s="22">
-        <v>2249</v>
-      </c>
-      <c r="J7" s="22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K7" s="22">
-        <v>1834</v>
-      </c>
-      <c r="L7" s="22">
-        <v>1849</v>
-      </c>
-      <c r="M7" s="22">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
+      <c r="A7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
     </row>
     <row r="8" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A8" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>354</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>355</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E8" s="22">
-        <v>1885</v>
-      </c>
-      <c r="F8" s="22">
-        <v>1865</v>
-      </c>
-      <c r="G8" s="22">
-        <f t="shared" si="0"/>
-        <v>-20</v>
-      </c>
-      <c r="H8" s="22">
-        <v>2225</v>
-      </c>
-      <c r="I8" s="22">
-        <v>2225</v>
-      </c>
-      <c r="J8" s="22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K8" s="22">
-        <v>1855</v>
-      </c>
-      <c r="L8" s="22">
-        <v>1855</v>
-      </c>
-      <c r="M8" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="A8" s="20"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
     </row>
     <row r="9" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A9" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>370</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>371</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E9" s="22">
-        <v>1875</v>
-      </c>
-      <c r="F9" s="22">
-        <v>1875</v>
-      </c>
-      <c r="G9" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="22">
-        <v>2419</v>
-      </c>
-      <c r="I9" s="22">
-        <v>2419</v>
-      </c>
-      <c r="J9" s="22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="22">
-        <v>1855</v>
-      </c>
-      <c r="L9" s="22">
-        <v>1865</v>
-      </c>
-      <c r="M9" s="22">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+      <c r="A9" s="20"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="22"/>
     </row>
     <row r="10" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A10" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>461</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>462</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E10" s="22">
-        <v>1850</v>
-      </c>
-      <c r="F10" s="22">
-        <v>1870</v>
-      </c>
-      <c r="G10" s="22">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
+      <c r="A10" s="20"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
       <c r="H10" s="22"/>
       <c r="I10" s="22"/>
-      <c r="J10" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="22">
-        <v>1820</v>
-      </c>
-      <c r="L10" s="22">
-        <v>1820</v>
-      </c>
-      <c r="M10" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
     </row>
     <row r="11" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A11" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>445</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>446</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E11" s="22">
-        <v>1857</v>
-      </c>
-      <c r="F11" s="22">
-        <v>1857</v>
-      </c>
-      <c r="G11" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A11" s="20"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
       <c r="H11" s="22"/>
       <c r="I11" s="22"/>
-      <c r="J11" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="22">
-        <v>1812</v>
-      </c>
-      <c r="L11" s="22">
-        <v>1827</v>
-      </c>
-      <c r="M11" s="22">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="22"/>
     </row>
     <row r="12" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A12" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>475</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>476</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E12" s="22">
-        <v>1829</v>
-      </c>
-      <c r="F12" s="22">
-        <v>1829</v>
-      </c>
-      <c r="G12" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A12" s="20"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
       <c r="H12" s="22"/>
       <c r="I12" s="22"/>
-      <c r="J12" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="22">
-        <v>1812</v>
-      </c>
-      <c r="L12" s="22">
-        <v>1827</v>
-      </c>
-      <c r="M12" s="22">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
     </row>
     <row r="13" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A13" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>531</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>532</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E13" s="22">
-        <v>1838</v>
-      </c>
-      <c r="F13" s="22">
-        <v>1843</v>
-      </c>
-      <c r="G13" s="22">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
+      <c r="A13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
       <c r="H13" s="22"/>
       <c r="I13" s="22"/>
-      <c r="J13" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="22">
-        <v>1828</v>
-      </c>
-      <c r="L13" s="22">
-        <v>1828</v>
-      </c>
-      <c r="M13" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
     </row>
     <row r="14" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A14" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>625</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>626</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E14" s="22">
-        <v>1838</v>
-      </c>
-      <c r="F14" s="22">
-        <v>1838</v>
-      </c>
-      <c r="G14" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A14" s="20"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
       <c r="H14" s="22"/>
       <c r="I14" s="22"/>
-      <c r="J14" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="22">
-        <v>1978</v>
-      </c>
-      <c r="L14" s="22">
-        <v>1828</v>
-      </c>
-      <c r="M14" s="22">
-        <f t="shared" si="2"/>
-        <v>-150</v>
-      </c>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
     </row>
     <row r="15" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A15" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>675</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>676</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E15" s="22">
-        <v>1858</v>
-      </c>
-      <c r="F15" s="22">
-        <v>1858</v>
-      </c>
-      <c r="G15" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A15" s="20"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
       <c r="H15" s="22"/>
       <c r="I15" s="22"/>
-      <c r="J15" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="22">
-        <v>1868</v>
-      </c>
-      <c r="L15" s="22">
-        <v>1848</v>
-      </c>
-      <c r="M15" s="22">
-        <f t="shared" si="2"/>
-        <v>-20</v>
-      </c>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
     </row>
     <row r="16" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A16" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>697</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>698</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E16" s="22">
-        <v>1885</v>
-      </c>
-      <c r="F16" s="22">
-        <v>1885</v>
-      </c>
-      <c r="G16" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A16" s="20"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
       <c r="H16" s="22"/>
       <c r="I16" s="22"/>
-      <c r="J16" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="22">
-        <v>1845</v>
-      </c>
-      <c r="L16" s="22">
-        <v>1875</v>
-      </c>
-      <c r="M16" s="22">
-        <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
     </row>
     <row r="17" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A17" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>705</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>706</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E17" s="22">
-        <v>1887</v>
-      </c>
-      <c r="F17" s="22">
-        <v>1887</v>
-      </c>
-      <c r="G17" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A17" s="20"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
       <c r="H17" s="22"/>
       <c r="I17" s="22"/>
-      <c r="J17" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="22">
-        <v>1853</v>
-      </c>
-      <c r="L17" s="22">
-        <v>1868</v>
-      </c>
-      <c r="M17" s="22">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
     </row>
     <row r="18" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A18" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>758</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>759</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E18" s="22">
-        <v>1898</v>
-      </c>
-      <c r="F18" s="22">
-        <v>1898</v>
-      </c>
-      <c r="G18" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A18" s="20"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
       <c r="H18" s="22"/>
       <c r="I18" s="22"/>
-      <c r="J18" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="22">
-        <v>1863</v>
-      </c>
-      <c r="L18" s="22">
-        <v>1878</v>
-      </c>
-      <c r="M18" s="22">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
     </row>
     <row r="19" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A19" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>1173</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E19" s="22">
-        <v>1803</v>
-      </c>
-      <c r="F19" s="22">
-        <v>1813</v>
-      </c>
-      <c r="G19" s="22">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
+      <c r="A19" s="20"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
       <c r="H19" s="22"/>
       <c r="I19" s="22"/>
-      <c r="J19" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="22">
-        <v>1799</v>
-      </c>
-      <c r="L19" s="22">
-        <v>1799</v>
-      </c>
-      <c r="M19" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="22"/>
     </row>
     <row r="20" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A20" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>956</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>957</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E20" s="22">
-        <v>1812</v>
-      </c>
-      <c r="F20" s="22">
-        <v>1832</v>
-      </c>
-      <c r="G20" s="22">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
+      <c r="A20" s="20"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
       <c r="H20" s="22"/>
       <c r="I20" s="22"/>
-      <c r="J20" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="22">
-        <v>1795</v>
-      </c>
-      <c r="L20" s="22">
-        <v>1795</v>
-      </c>
-      <c r="M20" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22"/>
     </row>
     <row r="21" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A21" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="21" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E21" s="22">
-        <v>1814</v>
-      </c>
-      <c r="F21" s="22">
-        <v>1834</v>
-      </c>
-      <c r="G21" s="22">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
+      <c r="A21" s="20"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
       <c r="H21" s="22"/>
       <c r="I21" s="22"/>
-      <c r="J21" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="22">
-        <v>1814</v>
-      </c>
-      <c r="L21" s="22">
-        <v>1814</v>
-      </c>
-      <c r="M21" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="22"/>
     </row>
     <row r="22" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A22" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="21" t="s">
-        <v>1336</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>1337</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E22" s="22">
-        <v>1838</v>
-      </c>
-      <c r="F22" s="22">
-        <v>1838</v>
-      </c>
-      <c r="G22" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A22" s="20"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
       <c r="H22" s="22"/>
       <c r="I22" s="22"/>
-      <c r="J22" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="22">
-        <v>1818</v>
-      </c>
-      <c r="L22" s="22">
-        <v>1848</v>
-      </c>
-      <c r="M22" s="22">
-        <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22"/>
     </row>
     <row r="23" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A23" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" s="21" t="s">
-        <v>1240</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>1241</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E23" s="22">
-        <v>1840</v>
-      </c>
-      <c r="F23" s="22">
-        <v>1840</v>
-      </c>
-      <c r="G23" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A23" s="20"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
       <c r="H23" s="22"/>
       <c r="I23" s="22"/>
-      <c r="J23" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="22">
-        <v>1815</v>
-      </c>
-      <c r="L23" s="22">
-        <v>1830</v>
-      </c>
-      <c r="M23" s="22">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
     </row>
     <row r="24" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A24" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="21" t="s">
-        <v>1689</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>1690</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E24" s="22">
-        <v>1879</v>
-      </c>
-      <c r="F24" s="22">
-        <v>1879</v>
-      </c>
-      <c r="G24" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A24" s="20"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
       <c r="H24" s="22"/>
       <c r="I24" s="22"/>
-      <c r="J24" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="22">
-        <v>1899</v>
-      </c>
-      <c r="L24" s="22">
-        <v>1869</v>
-      </c>
-      <c r="M24" s="22">
-        <f t="shared" si="2"/>
-        <v>-30</v>
-      </c>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="22"/>
     </row>
     <row r="25" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A25" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="21" t="s">
-        <v>1594</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>1595</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E25" s="22">
-        <v>1889</v>
-      </c>
-      <c r="F25" s="22">
-        <v>1889</v>
-      </c>
-      <c r="G25" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A25" s="20"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
       <c r="H25" s="22"/>
       <c r="I25" s="22"/>
-      <c r="J25" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="22">
-        <v>1864</v>
-      </c>
-      <c r="L25" s="22">
-        <v>1879</v>
-      </c>
-      <c r="M25" s="22">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="22"/>
     </row>
     <row r="26" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A26" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" s="21" t="s">
-        <v>1685</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>1686</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E26" s="22">
-        <v>1899</v>
-      </c>
-      <c r="F26" s="22">
-        <v>1899</v>
-      </c>
-      <c r="G26" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A26" s="20"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
       <c r="H26" s="22"/>
       <c r="I26" s="22"/>
-      <c r="J26" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="22">
-        <v>1948</v>
-      </c>
-      <c r="L26" s="22">
-        <v>1898</v>
-      </c>
-      <c r="M26" s="22">
-        <f t="shared" si="2"/>
-        <v>-50</v>
-      </c>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="22"/>
     </row>
     <row r="27" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A27" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" s="21" t="s">
-        <v>489</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>1700</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E27" s="22">
-        <v>1909</v>
-      </c>
-      <c r="F27" s="22">
-        <v>1909</v>
-      </c>
-      <c r="G27" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A27" s="20"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
       <c r="H27" s="22"/>
       <c r="I27" s="22"/>
-      <c r="J27" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="22">
-        <v>1859</v>
-      </c>
-      <c r="L27" s="22">
-        <v>1889</v>
-      </c>
-      <c r="M27" s="22">
-        <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
     </row>
     <row r="28" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A28" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" s="21" t="s">
-        <v>1701</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>1702</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E28" s="22">
-        <v>1909</v>
-      </c>
-      <c r="F28" s="22">
-        <v>1909</v>
-      </c>
-      <c r="G28" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A28" s="20"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
       <c r="H28" s="22"/>
       <c r="I28" s="22"/>
-      <c r="J28" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="22">
-        <v>1860</v>
-      </c>
-      <c r="L28" s="22">
-        <v>1899</v>
-      </c>
-      <c r="M28" s="22">
-        <f t="shared" si="2"/>
-        <v>39</v>
-      </c>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22"/>
     </row>
     <row r="29" spans="1:13" s="17" customFormat="1" ht="25.5" customHeight="1">
       <c r="A29" s="20"/>
@@ -79794,7 +79195,7 @@
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
-  <conditionalFormatting sqref="G4:G28">
+  <conditionalFormatting sqref="G4:G5">
     <cfRule type="cellIs" dxfId="5" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -79802,7 +79203,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J28">
+  <conditionalFormatting sqref="J4:J5">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -79810,7 +79211,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M28">
+  <conditionalFormatting sqref="M4:M5">
     <cfRule type="cellIs" dxfId="1" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>

--- a/fuel_cost_chungcheong.xlsx
+++ b/fuel_cost_chungcheong.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4845" uniqueCount="1765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4697" uniqueCount="1762">
   <si>
     <t>유류비 계산(혼유, 지역화폐 등)</t>
   </si>
@@ -3639,12 +3639,6 @@
     <t>충남 아산시 영인면 아산로 987</t>
   </si>
   <si>
-    <t>영풍에너지 주식회사</t>
-  </si>
-  <si>
-    <t>대전 대덕구 신탄진로 584 (상서동)</t>
-  </si>
-  <si>
     <t>영호주유소</t>
   </si>
   <si>
@@ -5386,9 +5380,6 @@
   </si>
   <si>
     <t>가격변동</t>
-  </si>
-  <si>
-    <t>폐업</t>
   </si>
 </sst>
 </file>
@@ -6789,7 +6780,7 @@
         <v>16</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>48</v>
@@ -6798,7 +6789,7 @@
         <v>26</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="G15" s="12">
         <v>1830</v>
@@ -7117,7 +7108,7 @@
         <v>6</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>60</v>
@@ -7126,7 +7117,7 @@
         <v>26</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="G19" s="12">
         <v>1829</v>
@@ -7199,7 +7190,7 @@
         <v>6</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>45</v>
@@ -7208,7 +7199,7 @@
         <v>26</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="G20" s="12">
         <v>1810</v>
@@ -7445,7 +7436,7 @@
         <v>12</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="D23" s="15" t="s">
         <v>80</v>
@@ -7454,7 +7445,7 @@
         <v>26</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="G23" s="12">
         <v>1819</v>
@@ -7609,7 +7600,7 @@
         <v>6</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="D25" s="15" t="s">
         <v>60</v>
@@ -7618,7 +7609,7 @@
         <v>26</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="G25" s="12">
         <v>1824</v>
@@ -7773,7 +7764,7 @@
         <v>16</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="D27" s="15" t="s">
         <v>60</v>
@@ -7782,7 +7773,7 @@
         <v>26</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="G27" s="12">
         <v>1890</v>
@@ -8019,7 +8010,7 @@
         <v>10</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="D30" s="15" t="s">
         <v>60</v>
@@ -8028,7 +8019,7 @@
         <v>26</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="G30" s="12">
         <v>1834</v>
@@ -8593,7 +8584,7 @@
         <v>12</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="D37" s="15" t="s">
         <v>80</v>
@@ -8602,7 +8593,7 @@
         <v>26</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="G37" s="12">
         <v>1865</v>
@@ -8757,7 +8748,7 @@
         <v>6</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="D39" s="15" t="s">
         <v>80</v>
@@ -8766,7 +8757,7 @@
         <v>26</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="G39" s="12">
         <v>1849</v>
@@ -9167,7 +9158,7 @@
         <v>10</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="D44" s="15" t="s">
         <v>60</v>
@@ -9176,7 +9167,7 @@
         <v>26</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="G44" s="12">
         <v>1898</v>
@@ -9331,7 +9322,7 @@
         <v>10</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D46" s="15" t="s">
         <v>60</v>
@@ -9340,7 +9331,7 @@
         <v>61</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="G46" s="12">
         <v>1898</v>
@@ -9413,7 +9404,7 @@
         <v>14</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="D47" s="15" t="s">
         <v>60</v>
@@ -9422,7 +9413,7 @@
         <v>26</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="G47" s="12">
         <v>1899</v>
@@ -9495,7 +9486,7 @@
         <v>10</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="D48" s="15" t="s">
         <v>60</v>
@@ -9504,7 +9495,7 @@
         <v>26</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="G48" s="12">
         <v>1818</v>
@@ -9655,7 +9646,7 @@
         <v>12</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="D50" s="15" t="s">
         <v>45</v>
@@ -9664,7 +9655,7 @@
         <v>26</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="G50" s="12">
         <v>1799</v>
@@ -9815,7 +9806,7 @@
         <v>10</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="D52" s="11" t="s">
         <v>45</v>
@@ -9824,7 +9815,7 @@
         <v>26</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="G52" s="12">
         <v>1827</v>
@@ -10295,7 +10286,7 @@
         <v>6</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="D58" s="15" t="s">
         <v>45</v>
@@ -10304,7 +10295,7 @@
         <v>26</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="G58" s="12">
         <v>1814</v>
@@ -10375,7 +10366,7 @@
         <v>6</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="D59" s="15" t="s">
         <v>45</v>
@@ -10384,7 +10375,7 @@
         <v>26</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="G59" s="12">
         <v>1814</v>
@@ -11095,7 +11086,7 @@
         <v>6</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="D68" s="15" t="s">
         <v>80</v>
@@ -11104,7 +11095,7 @@
         <v>26</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="G68" s="12">
         <v>1818</v>
@@ -11495,7 +11486,7 @@
         <v>6</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="D73" s="15" t="s">
         <v>80</v>
@@ -11504,7 +11495,7 @@
         <v>26</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="G73" s="12">
         <v>1820</v>
@@ -11575,7 +11566,7 @@
         <v>10</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="D74" s="11" t="s">
         <v>48</v>
@@ -11584,7 +11575,7 @@
         <v>26</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="G74" s="12">
         <v>1829</v>
@@ -11895,7 +11886,7 @@
         <v>6</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="D78" s="15" t="s">
         <v>45</v>
@@ -11904,7 +11895,7 @@
         <v>26</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
       <c r="G78" s="12">
         <v>1835</v>
@@ -12215,7 +12206,7 @@
         <v>10</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="D82" s="11" t="s">
         <v>71</v>
@@ -12224,7 +12215,7 @@
         <v>26</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="G82" s="12">
         <v>1819</v>
@@ -12535,7 +12526,7 @@
         <v>6</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="D86" s="15" t="s">
         <v>60</v>
@@ -12544,7 +12535,7 @@
         <v>61</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="G86" s="12">
         <v>1828</v>
@@ -12775,7 +12766,7 @@
         <v>6</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="D89" s="15" t="s">
         <v>45</v>
@@ -12784,7 +12775,7 @@
         <v>26</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="G89" s="12">
         <v>1805</v>
@@ -12855,7 +12846,7 @@
         <v>6</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="D90" s="15" t="s">
         <v>60</v>
@@ -12864,7 +12855,7 @@
         <v>26</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="G90" s="12">
         <v>1845</v>
@@ -12935,7 +12926,7 @@
         <v>6</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="D91" s="15" t="s">
         <v>60</v>
@@ -12944,7 +12935,7 @@
         <v>26</v>
       </c>
       <c r="F91" s="11" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="G91" s="12">
         <v>1845</v>
@@ -13015,7 +13006,7 @@
         <v>6</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="D92" s="15" t="s">
         <v>60</v>
@@ -13024,7 +13015,7 @@
         <v>26</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="G92" s="12">
         <v>1845</v>
@@ -13335,7 +13326,7 @@
         <v>6</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="D96" s="15" t="s">
         <v>80</v>
@@ -13344,7 +13335,7 @@
         <v>26</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="G96" s="12">
         <v>1815</v>
@@ -13577,7 +13568,7 @@
         <v>10</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="D99" s="15" t="s">
         <v>60</v>
@@ -13586,7 +13577,7 @@
         <v>26</v>
       </c>
       <c r="F99" s="11" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="G99" s="12">
         <v>1845</v>
@@ -13657,7 +13648,7 @@
         <v>10</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="D100" s="11" t="s">
         <v>57</v>
@@ -13666,7 +13657,7 @@
         <v>26</v>
       </c>
       <c r="F100" s="11" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="G100" s="12">
         <v>1829</v>
@@ -13737,7 +13728,7 @@
         <v>6</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="D101" s="15" t="s">
         <v>45</v>
@@ -13746,7 +13737,7 @@
         <v>26</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="G101" s="12">
         <v>1822</v>
@@ -13977,7 +13968,7 @@
         <v>12</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="D104" s="15" t="s">
         <v>60</v>
@@ -13986,7 +13977,7 @@
         <v>26</v>
       </c>
       <c r="F104" s="11" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="G104" s="12">
         <v>1829</v>
@@ -14057,7 +14048,7 @@
         <v>14</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="D105" s="15" t="s">
         <v>60</v>
@@ -14066,7 +14057,7 @@
         <v>26</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="G105" s="12">
         <v>1839</v>
@@ -14137,7 +14128,7 @@
         <v>18</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="D106" s="15" t="s">
         <v>80</v>
@@ -14146,7 +14137,7 @@
         <v>26</v>
       </c>
       <c r="F106" s="11" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="G106" s="12">
         <v>1822</v>
@@ -14217,7 +14208,7 @@
         <v>10</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="D107" s="11" t="s">
         <v>48</v>
@@ -14226,7 +14217,7 @@
         <v>26</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="G107" s="12">
         <v>1823</v>
@@ -14617,7 +14608,7 @@
         <v>14</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="D112" s="15" t="s">
         <v>80</v>
@@ -14626,7 +14617,7 @@
         <v>26</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="G112" s="12">
         <v>1844</v>
@@ -14937,7 +14928,7 @@
         <v>12</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="D116" s="15" t="s">
         <v>60</v>
@@ -14946,7 +14937,7 @@
         <v>26</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="G116" s="12">
         <v>1845</v>
@@ -15257,7 +15248,7 @@
         <v>10</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="D120" s="15" t="s">
         <v>80</v>
@@ -15266,7 +15257,7 @@
         <v>26</v>
       </c>
       <c r="F120" s="11" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="G120" s="12">
         <v>1848</v>
@@ -15337,7 +15328,7 @@
         <v>10</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="D121" s="15" t="s">
         <v>80</v>
@@ -15346,7 +15337,7 @@
         <v>26</v>
       </c>
       <c r="F121" s="11" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="G121" s="12">
         <v>1828</v>
@@ -15577,7 +15568,7 @@
         <v>6</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="D124" s="15" t="s">
         <v>60</v>
@@ -15586,7 +15577,7 @@
         <v>26</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="G124" s="12">
         <v>1825</v>
@@ -15657,7 +15648,7 @@
         <v>6</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="D125" s="15" t="s">
         <v>60</v>
@@ -15666,7 +15657,7 @@
         <v>26</v>
       </c>
       <c r="F125" s="11" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="G125" s="12">
         <v>1845</v>
@@ -15737,7 +15728,7 @@
         <v>6</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="D126" s="15" t="s">
         <v>60</v>
@@ -15746,7 +15737,7 @@
         <v>26</v>
       </c>
       <c r="F126" s="11" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="G126" s="12">
         <v>1845</v>
@@ -15817,7 +15808,7 @@
         <v>10</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="D127" s="15" t="s">
         <v>60</v>
@@ -15826,7 +15817,7 @@
         <v>61</v>
       </c>
       <c r="F127" s="11" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="G127" s="12">
         <v>1845</v>
@@ -15977,7 +15968,7 @@
         <v>6</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="D129" s="15" t="s">
         <v>45</v>
@@ -15986,7 +15977,7 @@
         <v>26</v>
       </c>
       <c r="F129" s="11" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="G129" s="12">
         <v>1809</v>
@@ -16057,7 +16048,7 @@
         <v>6</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="D130" s="15" t="s">
         <v>60</v>
@@ -16066,7 +16057,7 @@
         <v>26</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="G130" s="12">
         <v>1830</v>
@@ -16137,7 +16128,7 @@
         <v>10</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="D131" s="15" t="s">
         <v>60</v>
@@ -16146,7 +16137,7 @@
         <v>26</v>
       </c>
       <c r="F131" s="11" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="G131" s="12">
         <v>1835</v>
@@ -16941,7 +16932,7 @@
         <v>14</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="D141" s="15" t="s">
         <v>60</v>
@@ -16950,7 +16941,7 @@
         <v>26</v>
       </c>
       <c r="F141" s="11" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="G141" s="12">
         <v>1845</v>
@@ -17261,7 +17252,7 @@
         <v>12</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="D145" s="15" t="s">
         <v>60</v>
@@ -17270,7 +17261,7 @@
         <v>26</v>
       </c>
       <c r="F145" s="11" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="G145" s="12">
         <v>1865</v>
@@ -17341,7 +17332,7 @@
         <v>10</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="D146" s="15" t="s">
         <v>60</v>
@@ -17350,7 +17341,7 @@
         <v>26</v>
       </c>
       <c r="F146" s="11" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="G146" s="12">
         <v>1845</v>
@@ -17421,7 +17412,7 @@
         <v>10</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="D147" s="15" t="s">
         <v>60</v>
@@ -17430,7 +17421,7 @@
         <v>26</v>
       </c>
       <c r="F147" s="11" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="G147" s="12">
         <v>1845</v>
@@ -17501,7 +17492,7 @@
         <v>6</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="D148" s="15" t="s">
         <v>45</v>
@@ -17510,7 +17501,7 @@
         <v>61</v>
       </c>
       <c r="F148" s="11" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="G148" s="12">
         <v>1866</v>
@@ -18543,7 +18534,7 @@
         <v>14</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="D161" s="15" t="s">
         <v>60</v>
@@ -18552,7 +18543,7 @@
         <v>26</v>
       </c>
       <c r="F161" s="11" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="G161" s="12">
         <v>1845</v>
@@ -18703,7 +18694,7 @@
         <v>12</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="D163" s="11" t="s">
         <v>104</v>
@@ -18712,7 +18703,7 @@
         <v>26</v>
       </c>
       <c r="F163" s="11" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="G163" s="12">
         <v>1834</v>
@@ -18865,7 +18856,7 @@
         <v>14</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="D165" s="15" t="s">
         <v>80</v>
@@ -18874,7 +18865,7 @@
         <v>26</v>
       </c>
       <c r="F165" s="11" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="G165" s="12">
         <v>1859</v>
@@ -19185,7 +19176,7 @@
         <v>10</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="D169" s="15" t="s">
         <v>80</v>
@@ -19194,7 +19185,7 @@
         <v>26</v>
       </c>
       <c r="F169" s="11" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="G169" s="12">
         <v>1825</v>
@@ -19587,7 +19578,7 @@
         <v>14</v>
       </c>
       <c r="C174" s="11" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="D174" s="15" t="s">
         <v>60</v>
@@ -19596,7 +19587,7 @@
         <v>26</v>
       </c>
       <c r="F174" s="11" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="G174" s="12">
         <v>1875</v>
@@ -19749,7 +19740,7 @@
         <v>14</v>
       </c>
       <c r="C176" s="11" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="D176" s="11" t="s">
         <v>57</v>
@@ -19758,7 +19749,7 @@
         <v>26</v>
       </c>
       <c r="F176" s="11" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="G176" s="12">
         <v>1875</v>
@@ -20229,7 +20220,7 @@
         <v>16</v>
       </c>
       <c r="C182" s="11" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="D182" s="15" t="s">
         <v>45</v>
@@ -20238,7 +20229,7 @@
         <v>26</v>
       </c>
       <c r="F182" s="11" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="G182" s="12">
         <v>1830</v>
@@ -20309,7 +20300,7 @@
         <v>12</v>
       </c>
       <c r="C183" s="11" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="D183" s="15" t="s">
         <v>60</v>
@@ -20318,7 +20309,7 @@
         <v>26</v>
       </c>
       <c r="F183" s="11" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="G183" s="12">
         <v>1799</v>
@@ -20389,7 +20380,7 @@
         <v>6</v>
       </c>
       <c r="C184" s="11" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="D184" s="11" t="s">
         <v>57</v>
@@ -20398,7 +20389,7 @@
         <v>26</v>
       </c>
       <c r="F184" s="11" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="G184" s="12">
         <v>1805</v>
@@ -20549,7 +20540,7 @@
         <v>6</v>
       </c>
       <c r="C186" s="11" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="D186" s="15" t="s">
         <v>80</v>
@@ -20558,7 +20549,7 @@
         <v>26</v>
       </c>
       <c r="F186" s="11" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="G186" s="12">
         <v>1807</v>
@@ -21029,7 +21020,7 @@
         <v>16</v>
       </c>
       <c r="C192" s="11" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="D192" s="15" t="s">
         <v>45</v>
@@ -21038,7 +21029,7 @@
         <v>26</v>
       </c>
       <c r="F192" s="11" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="G192" s="12">
         <v>1850</v>
@@ -21269,7 +21260,7 @@
         <v>12</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="D195" s="15" t="s">
         <v>57</v>
@@ -21278,7 +21269,7 @@
         <v>26</v>
       </c>
       <c r="F195" s="11" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="G195" s="12">
         <v>1809</v>
@@ -21509,7 +21500,7 @@
         <v>6</v>
       </c>
       <c r="C198" s="11" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="D198" s="11" t="s">
         <v>48</v>
@@ -21518,7 +21509,7 @@
         <v>26</v>
       </c>
       <c r="F198" s="11" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="G198" s="12">
         <v>1813</v>
@@ -21669,7 +21660,7 @@
         <v>18</v>
       </c>
       <c r="C200" s="11" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D200" s="15" t="s">
         <v>80</v>
@@ -21678,7 +21669,7 @@
         <v>61</v>
       </c>
       <c r="F200" s="11" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="G200" s="12">
         <v>1855</v>
@@ -22309,7 +22300,7 @@
         <v>18</v>
       </c>
       <c r="C208" s="11" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="D208" s="15" t="s">
         <v>60</v>
@@ -22318,7 +22309,7 @@
         <v>61</v>
       </c>
       <c r="F208" s="11" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="G208" s="12">
         <v>1857</v>
@@ -22389,7 +22380,7 @@
         <v>18</v>
       </c>
       <c r="C209" s="11" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="D209" s="15" t="s">
         <v>80</v>
@@ -22398,7 +22389,7 @@
         <v>61</v>
       </c>
       <c r="F209" s="11" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="G209" s="12">
         <v>1857</v>
@@ -22709,7 +22700,7 @@
         <v>18</v>
       </c>
       <c r="C213" s="11" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="D213" s="15" t="s">
         <v>60</v>
@@ -22718,7 +22709,7 @@
         <v>61</v>
       </c>
       <c r="F213" s="11" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="G213" s="12">
         <v>1859</v>
@@ -22869,7 +22860,7 @@
         <v>12</v>
       </c>
       <c r="C215" s="11" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="D215" s="15" t="s">
         <v>45</v>
@@ -22878,7 +22869,7 @@
         <v>26</v>
       </c>
       <c r="F215" s="11" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="G215" s="12">
         <v>1818</v>
@@ -23126,7 +23117,7 @@
       <c r="H218" s="12"/>
       <c r="I218" s="12"/>
       <c r="J218" s="12">
-        <v>1809</v>
+        <v>1799</v>
       </c>
       <c r="K218" s="12">
         <f t="shared" si="40"/>
@@ -23142,7 +23133,7 @@
       </c>
       <c r="N218" s="12">
         <f t="shared" si="43"/>
-        <v>1809</v>
+        <v>1799</v>
       </c>
       <c r="O218" s="12" t="str">
         <f t="shared" si="44"/>
@@ -23189,7 +23180,7 @@
         <v>6</v>
       </c>
       <c r="C219" s="11" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="D219" s="15" t="s">
         <v>80</v>
@@ -23198,7 +23189,7 @@
         <v>61</v>
       </c>
       <c r="F219" s="11" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="G219" s="12">
         <v>1819</v>
@@ -23269,7 +23260,7 @@
         <v>18</v>
       </c>
       <c r="C220" s="11" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="D220" s="11" t="s">
         <v>57</v>
@@ -23278,7 +23269,7 @@
         <v>26</v>
       </c>
       <c r="F220" s="11" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="G220" s="12">
         <v>1862</v>
@@ -23349,7 +23340,7 @@
         <v>16</v>
       </c>
       <c r="C221" s="11" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="D221" s="15" t="s">
         <v>80</v>
@@ -23358,7 +23349,7 @@
         <v>26</v>
       </c>
       <c r="F221" s="11" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="G221" s="12">
         <v>1865</v>
@@ -23429,7 +23420,7 @@
         <v>18</v>
       </c>
       <c r="C222" s="11" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="D222" s="11" t="s">
         <v>57</v>
@@ -23438,7 +23429,7 @@
         <v>61</v>
       </c>
       <c r="F222" s="11" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="G222" s="12">
         <v>1865</v>
@@ -23669,7 +23660,7 @@
         <v>8</v>
       </c>
       <c r="C225" s="11" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="D225" s="15" t="s">
         <v>80</v>
@@ -23678,7 +23669,7 @@
         <v>26</v>
       </c>
       <c r="F225" s="11" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="G225" s="12">
         <v>1824</v>
@@ -24149,7 +24140,7 @@
         <v>16</v>
       </c>
       <c r="C231" s="11" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="D231" s="15" t="s">
         <v>80</v>
@@ -24158,7 +24149,7 @@
         <v>61</v>
       </c>
       <c r="F231" s="11" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="G231" s="12">
         <v>1869</v>
@@ -24469,7 +24460,7 @@
         <v>18</v>
       </c>
       <c r="C235" s="11" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="D235" s="11" t="s">
         <v>57</v>
@@ -24478,7 +24469,7 @@
         <v>61</v>
       </c>
       <c r="F235" s="11" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="G235" s="12">
         <v>1870</v>
@@ -24629,7 +24620,7 @@
         <v>6</v>
       </c>
       <c r="C237" s="11" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="D237" s="15" t="s">
         <v>45</v>
@@ -24638,7 +24629,7 @@
         <v>26</v>
       </c>
       <c r="F237" s="11" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="G237" s="12">
         <v>1829</v>
@@ -25189,7 +25180,7 @@
         <v>6</v>
       </c>
       <c r="C244" s="11" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="D244" s="11" t="s">
         <v>48</v>
@@ -25198,7 +25189,7 @@
         <v>26</v>
       </c>
       <c r="F244" s="11" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="G244" s="12">
         <v>1832</v>
@@ -25269,7 +25260,7 @@
         <v>6</v>
       </c>
       <c r="C245" s="11" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="D245" s="15" t="s">
         <v>45</v>
@@ -25278,7 +25269,7 @@
         <v>26</v>
       </c>
       <c r="F245" s="11" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="G245" s="12">
         <v>1833</v>
@@ -25749,7 +25740,7 @@
         <v>18</v>
       </c>
       <c r="C251" s="11" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="D251" s="15" t="s">
         <v>80</v>
@@ -25758,7 +25749,7 @@
         <v>26</v>
       </c>
       <c r="F251" s="11" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="G251" s="12">
         <v>1877</v>
@@ -26389,7 +26380,7 @@
         <v>10</v>
       </c>
       <c r="C259" s="11" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="D259" s="11" t="s">
         <v>95</v>
@@ -26398,7 +26389,7 @@
         <v>26</v>
       </c>
       <c r="F259" s="11" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="G259" s="12">
         <v>1838</v>
@@ -26469,7 +26460,7 @@
         <v>18</v>
       </c>
       <c r="C260" s="11" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="D260" s="15" t="s">
         <v>60</v>
@@ -26478,7 +26469,7 @@
         <v>61</v>
       </c>
       <c r="F260" s="11" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="G260" s="12">
         <v>1880</v>
@@ -26549,7 +26540,7 @@
         <v>16</v>
       </c>
       <c r="C261" s="11" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="D261" s="15" t="s">
         <v>80</v>
@@ -26558,7 +26549,7 @@
         <v>61</v>
       </c>
       <c r="F261" s="11" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="G261" s="12">
         <v>1880</v>
@@ -26869,7 +26860,7 @@
         <v>10</v>
       </c>
       <c r="C265" s="11" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="D265" s="11" t="s">
         <v>57</v>
@@ -26878,7 +26869,7 @@
         <v>26</v>
       </c>
       <c r="F265" s="11" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="G265" s="12">
         <v>1839</v>
@@ -27109,7 +27100,7 @@
         <v>10</v>
       </c>
       <c r="C268" s="11" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="D268" s="15" t="s">
         <v>80</v>
@@ -27118,7 +27109,7 @@
         <v>61</v>
       </c>
       <c r="F268" s="11" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="G268" s="12">
         <v>1839</v>
@@ -27189,7 +27180,7 @@
         <v>10</v>
       </c>
       <c r="C269" s="11" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="D269" s="15" t="s">
         <v>45</v>
@@ -27198,7 +27189,7 @@
         <v>26</v>
       </c>
       <c r="F269" s="11" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="G269" s="12">
         <v>1839</v>
@@ -27349,7 +27340,7 @@
         <v>10</v>
       </c>
       <c r="C271" s="11" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="D271" s="11" t="s">
         <v>57</v>
@@ -27358,7 +27349,7 @@
         <v>26</v>
       </c>
       <c r="F271" s="11" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="G271" s="12">
         <v>1844</v>
@@ -27429,7 +27420,7 @@
         <v>6</v>
       </c>
       <c r="C272" s="11" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="D272" s="15" t="s">
         <v>60</v>
@@ -27438,7 +27429,7 @@
         <v>26</v>
       </c>
       <c r="F272" s="11" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="G272" s="12">
         <v>1844</v>
@@ -28069,7 +28060,7 @@
         <v>16</v>
       </c>
       <c r="C280" s="11" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="D280" s="15" t="s">
         <v>80</v>
@@ -28078,7 +28069,7 @@
         <v>61</v>
       </c>
       <c r="F280" s="11" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="G280" s="12">
         <v>1890</v>
@@ -28149,7 +28140,7 @@
         <v>18</v>
       </c>
       <c r="C281" s="11" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="D281" s="15" t="s">
         <v>45</v>
@@ -28158,7 +28149,7 @@
         <v>61</v>
       </c>
       <c r="F281" s="11" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="G281" s="12">
         <v>1890</v>
@@ -28229,7 +28220,7 @@
         <v>18</v>
       </c>
       <c r="C282" s="11" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="D282" s="11" t="s">
         <v>57</v>
@@ -28238,7 +28229,7 @@
         <v>61</v>
       </c>
       <c r="F282" s="11" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="G282" s="12">
         <v>1890</v>
@@ -28949,7 +28940,7 @@
         <v>12</v>
       </c>
       <c r="C291" s="11" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="D291" s="15" t="s">
         <v>80</v>
@@ -28958,7 +28949,7 @@
         <v>26</v>
       </c>
       <c r="F291" s="11" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="G291" s="12">
         <v>1849</v>
@@ -29109,7 +29100,7 @@
         <v>18</v>
       </c>
       <c r="C293" s="11" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="D293" s="15" t="s">
         <v>60</v>
@@ -29118,7 +29109,7 @@
         <v>26</v>
       </c>
       <c r="F293" s="11" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="G293" s="12">
         <v>1895</v>
@@ -29189,7 +29180,7 @@
         <v>18</v>
       </c>
       <c r="C294" s="11" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="D294" s="15" t="s">
         <v>60</v>
@@ -29198,7 +29189,7 @@
         <v>61</v>
       </c>
       <c r="F294" s="11" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="G294" s="12">
         <v>1895</v>
@@ -29349,7 +29340,7 @@
         <v>8</v>
       </c>
       <c r="C296" s="11" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="D296" s="11" t="s">
         <v>57</v>
@@ -29358,7 +29349,7 @@
         <v>26</v>
       </c>
       <c r="F296" s="11" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="G296" s="12">
         <v>1855</v>
@@ -29429,7 +29420,7 @@
         <v>8</v>
       </c>
       <c r="C297" s="11" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="D297" s="15" t="s">
         <v>60</v>
@@ -29438,7 +29429,7 @@
         <v>26</v>
       </c>
       <c r="F297" s="11" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="G297" s="12">
         <v>1855</v>
@@ -29509,7 +29500,7 @@
         <v>6</v>
       </c>
       <c r="C298" s="11" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="D298" s="15" t="s">
         <v>45</v>
@@ -29518,7 +29509,7 @@
         <v>26</v>
       </c>
       <c r="F298" s="11" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="G298" s="12">
         <v>1855</v>
@@ -29909,7 +29900,7 @@
         <v>18</v>
       </c>
       <c r="C303" s="11" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="D303" s="11" t="s">
         <v>57</v>
@@ -29918,7 +29909,7 @@
         <v>61</v>
       </c>
       <c r="F303" s="11" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="G303" s="12">
         <v>1899</v>
@@ -30069,7 +30060,7 @@
         <v>10</v>
       </c>
       <c r="C305" s="11" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="D305" s="11" t="s">
         <v>57</v>
@@ -30078,7 +30069,7 @@
         <v>61</v>
       </c>
       <c r="F305" s="11" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="G305" s="12">
         <v>1857</v>
@@ -30149,7 +30140,7 @@
         <v>12</v>
       </c>
       <c r="C306" s="11" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="D306" s="15" t="s">
         <v>57</v>
@@ -30158,7 +30149,7 @@
         <v>26</v>
       </c>
       <c r="F306" s="11" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="G306" s="12">
         <v>1857</v>
@@ -30309,7 +30300,7 @@
         <v>14</v>
       </c>
       <c r="C308" s="11" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="D308" s="15" t="s">
         <v>60</v>
@@ -30318,7 +30309,7 @@
         <v>61</v>
       </c>
       <c r="F308" s="11" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="G308" s="12">
         <v>1858</v>
@@ -30709,7 +30700,7 @@
         <v>6</v>
       </c>
       <c r="C313" s="11" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="D313" s="11" t="s">
         <v>95</v>
@@ -30718,7 +30709,7 @@
         <v>61</v>
       </c>
       <c r="F313" s="11" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="G313" s="12">
         <v>1859</v>
@@ -31429,7 +31420,7 @@
         <v>12</v>
       </c>
       <c r="C322" s="11" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="D322" s="15" t="s">
         <v>80</v>
@@ -31438,7 +31429,7 @@
         <v>26</v>
       </c>
       <c r="F322" s="11" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="G322" s="12">
         <v>1865</v>
@@ -31669,7 +31660,7 @@
         <v>8</v>
       </c>
       <c r="C325" s="11" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="D325" s="15" t="s">
         <v>60</v>
@@ -31678,7 +31669,7 @@
         <v>26</v>
       </c>
       <c r="F325" s="11" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="G325" s="12">
         <v>1867</v>
@@ -32309,7 +32300,7 @@
         <v>10</v>
       </c>
       <c r="C333" s="11" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="D333" s="15" t="s">
         <v>80</v>
@@ -32318,7 +32309,7 @@
         <v>61</v>
       </c>
       <c r="F333" s="11" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="G333" s="12">
         <v>1869</v>
@@ -32469,7 +32460,7 @@
         <v>12</v>
       </c>
       <c r="C335" s="11" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="D335" s="15" t="s">
         <v>80</v>
@@ -32478,7 +32469,7 @@
         <v>26</v>
       </c>
       <c r="F335" s="11" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="G335" s="12">
         <v>1869</v>
@@ -32709,7 +32700,7 @@
         <v>8</v>
       </c>
       <c r="C338" s="11" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="D338" s="15" t="s">
         <v>45</v>
@@ -32718,7 +32709,7 @@
         <v>61</v>
       </c>
       <c r="F338" s="11" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="G338" s="12">
         <v>1875</v>
@@ -32869,7 +32860,7 @@
         <v>8</v>
       </c>
       <c r="C340" s="11" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="D340" s="11" t="s">
         <v>57</v>
@@ -32878,7 +32869,7 @@
         <v>61</v>
       </c>
       <c r="F340" s="11" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="G340" s="12">
         <v>1875</v>
@@ -32949,7 +32940,7 @@
         <v>12</v>
       </c>
       <c r="C341" s="11" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="D341" s="15" t="s">
         <v>45</v>
@@ -32958,7 +32949,7 @@
         <v>61</v>
       </c>
       <c r="F341" s="11" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="G341" s="12">
         <v>1878</v>
@@ -33029,7 +33020,7 @@
         <v>14</v>
       </c>
       <c r="C342" s="11" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="D342" s="11" t="s">
         <v>57</v>
@@ -33038,7 +33029,7 @@
         <v>61</v>
       </c>
       <c r="F342" s="11" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="G342" s="12">
         <v>1878</v>
@@ -33429,7 +33420,7 @@
         <v>8</v>
       </c>
       <c r="C347" s="11" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="D347" s="11" t="s">
         <v>57</v>
@@ -33438,7 +33429,7 @@
         <v>26</v>
       </c>
       <c r="F347" s="11" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="G347" s="12">
         <v>1879</v>
@@ -33509,7 +33500,7 @@
         <v>14</v>
       </c>
       <c r="C348" s="11" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="D348" s="11" t="s">
         <v>71</v>
@@ -33518,7 +33509,7 @@
         <v>26</v>
       </c>
       <c r="F348" s="11" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="G348" s="12">
         <v>1879</v>
@@ -33589,7 +33580,7 @@
         <v>10</v>
       </c>
       <c r="C349" s="11" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="D349" s="15" t="s">
         <v>45</v>
@@ -33598,7 +33589,7 @@
         <v>61</v>
       </c>
       <c r="F349" s="11" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="G349" s="12">
         <v>1879</v>
@@ -33829,7 +33820,7 @@
         <v>6</v>
       </c>
       <c r="C352" s="11" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="D352" s="11" t="s">
         <v>57</v>
@@ -33838,7 +33829,7 @@
         <v>26</v>
       </c>
       <c r="F352" s="11" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="G352" s="12">
         <v>1883</v>
@@ -33909,7 +33900,7 @@
         <v>10</v>
       </c>
       <c r="C353" s="11" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="D353" s="15" t="s">
         <v>45</v>
@@ -33918,7 +33909,7 @@
         <v>26</v>
       </c>
       <c r="F353" s="11" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="G353" s="12">
         <v>1884</v>
@@ -34069,7 +34060,7 @@
         <v>14</v>
       </c>
       <c r="C355" s="11" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="D355" s="15" t="s">
         <v>60</v>
@@ -34078,7 +34069,7 @@
         <v>26</v>
       </c>
       <c r="F355" s="11" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="G355" s="12">
         <v>1887</v>
@@ -34229,7 +34220,7 @@
         <v>14</v>
       </c>
       <c r="C357" s="11" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="D357" s="15" t="s">
         <v>45</v>
@@ -34238,7 +34229,7 @@
         <v>26</v>
       </c>
       <c r="F357" s="11" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="G357" s="12">
         <v>1889</v>
@@ -34389,7 +34380,7 @@
         <v>10</v>
       </c>
       <c r="C359" s="11" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="D359" s="15" t="s">
         <v>45</v>
@@ -34398,7 +34389,7 @@
         <v>26</v>
       </c>
       <c r="F359" s="11" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="G359" s="12">
         <v>1890</v>
@@ -34549,7 +34540,7 @@
         <v>8</v>
       </c>
       <c r="C361" s="11" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="D361" s="15" t="s">
         <v>45</v>
@@ -34558,7 +34549,7 @@
         <v>26</v>
       </c>
       <c r="F361" s="11" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="G361" s="12">
         <v>1890</v>
@@ -34709,7 +34700,7 @@
         <v>12</v>
       </c>
       <c r="C363" s="11" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="D363" s="15" t="s">
         <v>45</v>
@@ -34718,7 +34709,7 @@
         <v>26</v>
       </c>
       <c r="F363" s="11" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="G363" s="12">
         <v>1891</v>
@@ -34869,7 +34860,7 @@
         <v>6</v>
       </c>
       <c r="C365" s="11" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="D365" s="11" t="s">
         <v>57</v>
@@ -34878,7 +34869,7 @@
         <v>61</v>
       </c>
       <c r="F365" s="11" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="G365" s="12">
         <v>1895</v>
@@ -35109,7 +35100,7 @@
         <v>10</v>
       </c>
       <c r="C368" s="11" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D368" s="15" t="s">
         <v>45</v>
@@ -35118,7 +35109,7 @@
         <v>61</v>
       </c>
       <c r="F368" s="11" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="G368" s="12">
         <v>1895</v>
@@ -35589,7 +35580,7 @@
         <v>8</v>
       </c>
       <c r="C374" s="11" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="D374" s="15" t="s">
         <v>45</v>
@@ -35598,7 +35589,7 @@
         <v>61</v>
       </c>
       <c r="F374" s="11" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="G374" s="12">
         <v>1895</v>
@@ -35669,7 +35660,7 @@
         <v>6</v>
       </c>
       <c r="C375" s="11" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="D375" s="11" t="s">
         <v>57</v>
@@ -35678,7 +35669,7 @@
         <v>26</v>
       </c>
       <c r="F375" s="11" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="G375" s="12">
         <v>1895</v>
@@ -36309,7 +36300,7 @@
         <v>12</v>
       </c>
       <c r="C383" s="11" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="D383" s="15" t="s">
         <v>60</v>
@@ -36318,7 +36309,7 @@
         <v>61</v>
       </c>
       <c r="F383" s="11" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="G383" s="12">
         <v>1898</v>
@@ -36709,7 +36700,7 @@
         <v>10</v>
       </c>
       <c r="C388" s="11" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="D388" s="11" t="s">
         <v>57</v>
@@ -36718,7 +36709,7 @@
         <v>26</v>
       </c>
       <c r="F388" s="11" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="G388" s="12">
         <v>1898</v>
@@ -36789,7 +36780,7 @@
         <v>6</v>
       </c>
       <c r="C389" s="11" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="D389" s="15" t="s">
         <v>80</v>
@@ -36798,7 +36789,7 @@
         <v>26</v>
       </c>
       <c r="F389" s="11" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="G389" s="12">
         <v>1899</v>
@@ -37189,7 +37180,7 @@
         <v>10</v>
       </c>
       <c r="C394" s="11" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="D394" s="15" t="s">
         <v>60</v>
@@ -37198,7 +37189,7 @@
         <v>61</v>
       </c>
       <c r="F394" s="11" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="G394" s="12">
         <v>1899</v>
@@ -37269,7 +37260,7 @@
         <v>14</v>
       </c>
       <c r="C395" s="11" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="D395" s="11" t="s">
         <v>57</v>
@@ -37278,7 +37269,7 @@
         <v>61</v>
       </c>
       <c r="F395" s="11" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="G395" s="12">
         <v>1899</v>
@@ -37509,7 +37500,7 @@
         <v>10</v>
       </c>
       <c r="C398" s="11" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="D398" s="15" t="s">
         <v>45</v>
@@ -37518,7 +37509,7 @@
         <v>61</v>
       </c>
       <c r="F398" s="11" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="G398" s="12">
         <v>1899</v>
@@ -37589,7 +37580,7 @@
         <v>10</v>
       </c>
       <c r="C399" s="11" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="D399" s="15" t="s">
         <v>45</v>
@@ -37598,7 +37589,7 @@
         <v>61</v>
       </c>
       <c r="F399" s="11" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="G399" s="12">
         <v>1899</v>
@@ -37989,7 +37980,7 @@
         <v>14</v>
       </c>
       <c r="C404" s="11" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D404" s="11" t="s">
         <v>57</v>
@@ -37998,7 +37989,7 @@
         <v>61</v>
       </c>
       <c r="F404" s="11" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="G404" s="12">
         <v>1899</v>
@@ -38309,7 +38300,7 @@
         <v>12</v>
       </c>
       <c r="C408" s="11" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="D408" s="15" t="s">
         <v>57</v>
@@ -38318,7 +38309,7 @@
         <v>26</v>
       </c>
       <c r="F408" s="11" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="G408" s="12">
         <v>1899</v>
@@ -38469,7 +38460,7 @@
         <v>10</v>
       </c>
       <c r="C410" s="11" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="D410" s="11" t="s">
         <v>57</v>
@@ -38478,7 +38469,7 @@
         <v>61</v>
       </c>
       <c r="F410" s="11" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="G410" s="12">
         <v>1899</v>
@@ -38549,7 +38540,7 @@
         <v>10</v>
       </c>
       <c r="C411" s="11" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="D411" s="15" t="s">
         <v>80</v>
@@ -38558,7 +38549,7 @@
         <v>61</v>
       </c>
       <c r="F411" s="11" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="G411" s="12">
         <v>1899</v>
@@ -39349,7 +39340,7 @@
         <v>10</v>
       </c>
       <c r="C421" s="11" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="D421" s="11" t="s">
         <v>57</v>
@@ -39358,7 +39349,7 @@
         <v>61</v>
       </c>
       <c r="F421" s="11" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="G421" s="12">
         <v>1938</v>
@@ -39429,7 +39420,7 @@
         <v>10</v>
       </c>
       <c r="C422" s="11" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="D422" s="15" t="s">
         <v>80</v>
@@ -39438,7 +39429,7 @@
         <v>61</v>
       </c>
       <c r="F422" s="11" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="G422" s="12">
         <v>1939</v>
@@ -40069,7 +40060,7 @@
         <v>12</v>
       </c>
       <c r="C430" s="11" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="D430" s="15" t="s">
         <v>80</v>
@@ -40078,7 +40069,7 @@
         <v>61</v>
       </c>
       <c r="F430" s="11" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="G430" s="12">
         <v>1958</v>
@@ -40149,7 +40140,7 @@
         <v>12</v>
       </c>
       <c r="C431" s="11" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="D431" s="15" t="s">
         <v>60</v>
@@ -40158,7 +40149,7 @@
         <v>61</v>
       </c>
       <c r="F431" s="11" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="G431" s="12">
         <v>1960</v>
@@ -40543,7 +40534,7 @@
         <v>12</v>
       </c>
       <c r="C436" s="11" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D436" s="15" t="s">
         <v>57</v>
@@ -40552,7 +40543,7 @@
         <v>26</v>
       </c>
       <c r="F436" s="11" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="G436" s="12">
         <v>1789</v>
@@ -40621,7 +40612,7 @@
         <v>12</v>
       </c>
       <c r="C437" s="11" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="D437" s="15" t="s">
         <v>57</v>
@@ -40630,7 +40621,7 @@
         <v>26</v>
       </c>
       <c r="F437" s="11" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="G437" s="12">
         <v>1789</v>
@@ -41171,7 +41162,7 @@
         <v>12</v>
       </c>
       <c r="C444" s="11" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="D444" s="11" t="s">
         <v>104</v>
@@ -41180,7 +41171,7 @@
         <v>26</v>
       </c>
       <c r="F444" s="11" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="G444" s="12">
         <v>1799</v>
@@ -41249,7 +41240,7 @@
         <v>12</v>
       </c>
       <c r="C445" s="11" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="D445" s="15" t="s">
         <v>45</v>
@@ -41258,7 +41249,7 @@
         <v>61</v>
       </c>
       <c r="F445" s="11" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="G445" s="12">
         <v>1999</v>
@@ -41407,7 +41398,7 @@
         <v>6</v>
       </c>
       <c r="C447" s="11" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="D447" s="15" t="s">
         <v>80</v>
@@ -41416,7 +41407,7 @@
         <v>26</v>
       </c>
       <c r="F447" s="11" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="G447" s="12">
         <v>1805</v>
@@ -41485,7 +41476,7 @@
         <v>6</v>
       </c>
       <c r="C448" s="11" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="D448" s="15" t="s">
         <v>80</v>
@@ -41494,7 +41485,7 @@
         <v>26</v>
       </c>
       <c r="F448" s="11" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="G448" s="12">
         <v>1805</v>
@@ -41953,7 +41944,7 @@
         <v>6</v>
       </c>
       <c r="C454" s="11" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="D454" s="15" t="s">
         <v>45</v>
@@ -41962,7 +41953,7 @@
         <v>26</v>
       </c>
       <c r="F454" s="11" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="G454" s="12">
         <v>1807</v>
@@ -42421,7 +42412,7 @@
         <v>14</v>
       </c>
       <c r="C460" s="11" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="D460" s="15" t="s">
         <v>45</v>
@@ -42430,7 +42421,7 @@
         <v>26</v>
       </c>
       <c r="F460" s="11" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="G460" s="12">
         <v>1809</v>
@@ -42733,7 +42724,7 @@
         <v>6</v>
       </c>
       <c r="C464" s="11" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="D464" s="15" t="s">
         <v>45</v>
@@ -42742,7 +42733,7 @@
         <v>26</v>
       </c>
       <c r="F464" s="11" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="G464" s="12">
         <v>1809</v>
@@ -43123,7 +43114,7 @@
         <v>6</v>
       </c>
       <c r="C469" s="11" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="D469" s="11" t="s">
         <v>57</v>
@@ -43132,7 +43123,7 @@
         <v>26</v>
       </c>
       <c r="F469" s="11" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="G469" s="12">
         <v>1809</v>
@@ -43201,7 +43192,7 @@
         <v>12</v>
       </c>
       <c r="C470" s="11" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="D470" s="15" t="s">
         <v>80</v>
@@ -43210,7 +43201,7 @@
         <v>26</v>
       </c>
       <c r="F470" s="11" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="G470" s="12">
         <v>1809</v>
@@ -43357,7 +43348,7 @@
         <v>6</v>
       </c>
       <c r="C472" s="11" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="D472" s="11" t="s">
         <v>57</v>
@@ -43366,7 +43357,7 @@
         <v>26</v>
       </c>
       <c r="F472" s="11" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="G472" s="12">
         <v>1809</v>
@@ -43669,7 +43660,7 @@
         <v>14</v>
       </c>
       <c r="C476" s="11" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="D476" s="15" t="s">
         <v>45</v>
@@ -43678,7 +43669,7 @@
         <v>26</v>
       </c>
       <c r="F476" s="11" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="G476" s="12">
         <v>1809</v>
@@ -44059,7 +44050,7 @@
         <v>12</v>
       </c>
       <c r="C481" s="11" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="D481" s="15" t="s">
         <v>45</v>
@@ -44068,7 +44059,7 @@
         <v>26</v>
       </c>
       <c r="F481" s="11" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="G481" s="12">
         <v>1812</v>
@@ -44215,7 +44206,7 @@
         <v>6</v>
       </c>
       <c r="C483" s="11" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="D483" s="15" t="s">
         <v>60</v>
@@ -44224,7 +44215,7 @@
         <v>26</v>
       </c>
       <c r="F483" s="11" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="G483" s="12">
         <v>1812</v>
@@ -44371,7 +44362,7 @@
         <v>6</v>
       </c>
       <c r="C485" s="11" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="D485" s="15" t="s">
         <v>60</v>
@@ -44380,7 +44371,7 @@
         <v>26</v>
       </c>
       <c r="F485" s="11" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="G485" s="12">
         <v>1813</v>
@@ -44449,7 +44440,7 @@
         <v>6</v>
       </c>
       <c r="C486" s="11" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="D486" s="11" t="s">
         <v>57</v>
@@ -44458,7 +44449,7 @@
         <v>26</v>
       </c>
       <c r="F486" s="11" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="G486" s="12">
         <v>1813</v>
@@ -45073,7 +45064,7 @@
         <v>10</v>
       </c>
       <c r="C494" s="11" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="D494" s="15" t="s">
         <v>45</v>
@@ -45082,7 +45073,7 @@
         <v>26</v>
       </c>
       <c r="F494" s="11" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="G494" s="12">
         <v>1814</v>
@@ -45229,7 +45220,7 @@
         <v>6</v>
       </c>
       <c r="C496" s="11" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="D496" s="15" t="s">
         <v>45</v>
@@ -45238,7 +45229,7 @@
         <v>26</v>
       </c>
       <c r="F496" s="11" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="G496" s="12">
         <v>1814</v>
@@ -45541,7 +45532,7 @@
         <v>6</v>
       </c>
       <c r="C500" s="11" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D500" s="15" t="s">
         <v>80</v>
@@ -45550,7 +45541,7 @@
         <v>26</v>
       </c>
       <c r="F500" s="11" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="G500" s="12">
         <v>1815</v>
@@ -45619,7 +45610,7 @@
         <v>10</v>
       </c>
       <c r="C501" s="11" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="D501" s="11" t="s">
         <v>57</v>
@@ -45628,7 +45619,7 @@
         <v>61</v>
       </c>
       <c r="F501" s="11" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="G501" s="12">
         <v>1815</v>
@@ -46009,7 +46000,7 @@
         <v>12</v>
       </c>
       <c r="C506" s="11" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="D506" s="15" t="s">
         <v>45</v>
@@ -46018,7 +46009,7 @@
         <v>26</v>
       </c>
       <c r="F506" s="11" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="G506" s="12">
         <v>1815</v>
@@ -46087,7 +46078,7 @@
         <v>14</v>
       </c>
       <c r="C507" s="11" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="D507" s="11" t="s">
         <v>57</v>
@@ -46096,7 +46087,7 @@
         <v>26</v>
       </c>
       <c r="F507" s="11" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="G507" s="12">
         <v>1815</v>
@@ -46165,7 +46156,7 @@
         <v>6</v>
       </c>
       <c r="C508" s="11" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="D508" s="15" t="s">
         <v>45</v>
@@ -46174,7 +46165,7 @@
         <v>26</v>
       </c>
       <c r="F508" s="11" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="G508" s="12">
         <v>1815</v>
@@ -46555,7 +46546,7 @@
         <v>14</v>
       </c>
       <c r="C513" s="11" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="D513" s="15" t="s">
         <v>60</v>
@@ -46564,7 +46555,7 @@
         <v>26</v>
       </c>
       <c r="F513" s="11" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="G513" s="12">
         <v>1817</v>
@@ -46867,7 +46858,7 @@
         <v>6</v>
       </c>
       <c r="C517" s="11" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="D517" s="11" t="s">
         <v>57</v>
@@ -46876,7 +46867,7 @@
         <v>26</v>
       </c>
       <c r="F517" s="11" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="G517" s="12">
         <v>1818</v>
@@ -46945,7 +46936,7 @@
         <v>6</v>
       </c>
       <c r="C518" s="11" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="D518" s="11" t="s">
         <v>57</v>
@@ -46954,7 +46945,7 @@
         <v>26</v>
       </c>
       <c r="F518" s="11" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="G518" s="12">
         <v>1818</v>
@@ -47101,7 +47092,7 @@
         <v>6</v>
       </c>
       <c r="C520" s="11" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="D520" s="11" t="s">
         <v>57</v>
@@ -47110,7 +47101,7 @@
         <v>26</v>
       </c>
       <c r="F520" s="11" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="G520" s="12">
         <v>1819</v>
@@ -47413,7 +47404,7 @@
         <v>10</v>
       </c>
       <c r="C524" s="11" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="D524" s="15" t="s">
         <v>45</v>
@@ -47422,7 +47413,7 @@
         <v>26</v>
       </c>
       <c r="F524" s="11" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="G524" s="12">
         <v>1819</v>
@@ -47959,7 +47950,7 @@
         <v>10</v>
       </c>
       <c r="C531" s="11" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="D531" s="15" t="s">
         <v>60</v>
@@ -47968,7 +47959,7 @@
         <v>26</v>
       </c>
       <c r="F531" s="11" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="G531" s="12">
         <v>1819</v>
@@ -48037,7 +48028,7 @@
         <v>10</v>
       </c>
       <c r="C532" s="11" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="D532" s="11" t="s">
         <v>71</v>
@@ -48046,7 +48037,7 @@
         <v>26</v>
       </c>
       <c r="F532" s="11" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="G532" s="12">
         <v>1819</v>
@@ -48115,7 +48106,7 @@
         <v>10</v>
       </c>
       <c r="C533" s="11" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="D533" s="11" t="s">
         <v>48</v>
@@ -48124,7 +48115,7 @@
         <v>26</v>
       </c>
       <c r="F533" s="11" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="G533" s="12">
         <v>1819</v>
@@ -48193,7 +48184,7 @@
         <v>10</v>
       </c>
       <c r="C534" s="11" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="D534" s="15" t="s">
         <v>80</v>
@@ -48202,7 +48193,7 @@
         <v>26</v>
       </c>
       <c r="F534" s="11" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="G534" s="12">
         <v>1819</v>
@@ -49207,7 +49198,7 @@
         <v>10</v>
       </c>
       <c r="C547" s="11" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="D547" s="15" t="s">
         <v>80</v>
@@ -49216,7 +49207,7 @@
         <v>26</v>
       </c>
       <c r="F547" s="11" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="G547" s="12">
         <v>1825</v>
@@ -49441,7 +49432,7 @@
         <v>18</v>
       </c>
       <c r="C550" s="11" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="D550" s="11" t="s">
         <v>57</v>
@@ -49450,7 +49441,7 @@
         <v>26</v>
       </c>
       <c r="F550" s="11" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="G550" s="12">
         <v>1825</v>
@@ -49831,7 +49822,7 @@
         <v>10</v>
       </c>
       <c r="C555" s="11" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="D555" s="11" t="s">
         <v>48</v>
@@ -49840,7 +49831,7 @@
         <v>26</v>
       </c>
       <c r="F555" s="11" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="G555" s="12">
         <v>1825</v>
@@ -49909,7 +49900,7 @@
         <v>10</v>
       </c>
       <c r="C556" s="11" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="D556" s="11" t="s">
         <v>57</v>
@@ -49918,7 +49909,7 @@
         <v>26</v>
       </c>
       <c r="F556" s="11" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="G556" s="12">
         <v>1825</v>
@@ -49987,7 +49978,7 @@
         <v>6</v>
       </c>
       <c r="C557" s="11" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="D557" s="15" t="s">
         <v>45</v>
@@ -49996,7 +49987,7 @@
         <v>26</v>
       </c>
       <c r="F557" s="11" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="G557" s="12">
         <v>1825</v>
@@ -50143,7 +50134,7 @@
         <v>10</v>
       </c>
       <c r="C559" s="11" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="D559" s="11" t="s">
         <v>57</v>
@@ -50221,7 +50212,7 @@
         <v>18</v>
       </c>
       <c r="C560" s="11" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="D560" s="15" t="s">
         <v>45</v>
@@ -50230,7 +50221,7 @@
         <v>26</v>
       </c>
       <c r="F560" s="11" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="G560" s="12">
         <v>1825</v>
@@ -50845,7 +50836,7 @@
         <v>6</v>
       </c>
       <c r="C568" s="11" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="D568" s="11" t="s">
         <v>57</v>
@@ -50854,7 +50845,7 @@
         <v>26</v>
       </c>
       <c r="F568" s="11" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="G568" s="12">
         <v>1825</v>
@@ -50923,7 +50914,7 @@
         <v>6</v>
       </c>
       <c r="C569" s="11" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="D569" s="11" t="s">
         <v>57</v>
@@ -50932,7 +50923,7 @@
         <v>26</v>
       </c>
       <c r="F569" s="11" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="G569" s="12">
         <v>1825</v>
@@ -51079,7 +51070,7 @@
         <v>12</v>
       </c>
       <c r="C571" s="11" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="D571" s="15" t="s">
         <v>45</v>
@@ -51088,7 +51079,7 @@
         <v>26</v>
       </c>
       <c r="F571" s="11" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="G571" s="12">
         <v>1825</v>
@@ -51235,7 +51226,7 @@
         <v>12</v>
       </c>
       <c r="C573" s="11" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="D573" s="15" t="s">
         <v>60</v>
@@ -51244,7 +51235,7 @@
         <v>26</v>
       </c>
       <c r="F573" s="11" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="G573" s="12">
         <v>1827</v>
@@ -51313,7 +51304,7 @@
         <v>18</v>
       </c>
       <c r="C574" s="11" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="D574" s="11" t="s">
         <v>57</v>
@@ -51322,7 +51313,7 @@
         <v>26</v>
       </c>
       <c r="F574" s="11" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="G574" s="12">
         <v>1827</v>
@@ -51391,7 +51382,7 @@
         <v>8</v>
       </c>
       <c r="C575" s="11" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="D575" s="15" t="s">
         <v>45</v>
@@ -51400,7 +51391,7 @@
         <v>26</v>
       </c>
       <c r="F575" s="11" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="G575" s="12">
         <v>1828</v>
@@ -51469,7 +51460,7 @@
         <v>6</v>
       </c>
       <c r="C576" s="11" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="D576" s="11" t="s">
         <v>95</v>
@@ -51478,7 +51469,7 @@
         <v>61</v>
       </c>
       <c r="F576" s="11" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="G576" s="12">
         <v>1828</v>
@@ -51703,7 +51694,7 @@
         <v>10</v>
       </c>
       <c r="C579" s="11" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="D579" s="15" t="s">
         <v>45</v>
@@ -51712,7 +51703,7 @@
         <v>26</v>
       </c>
       <c r="F579" s="11" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="G579" s="12">
         <v>1828</v>
@@ -51781,7 +51772,7 @@
         <v>10</v>
       </c>
       <c r="C580" s="11" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="D580" s="11" t="s">
         <v>57</v>
@@ -51790,7 +51781,7 @@
         <v>26</v>
       </c>
       <c r="F580" s="11" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="G580" s="12">
         <v>1828</v>
@@ -51859,7 +51850,7 @@
         <v>12</v>
       </c>
       <c r="C581" s="11" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="D581" s="15" t="s">
         <v>60</v>
@@ -51868,7 +51859,7 @@
         <v>26</v>
       </c>
       <c r="F581" s="11" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="G581" s="12">
         <v>1828</v>
@@ -52093,7 +52084,7 @@
         <v>10</v>
       </c>
       <c r="C584" s="11" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="D584" s="15" t="s">
         <v>45</v>
@@ -52102,7 +52093,7 @@
         <v>61</v>
       </c>
       <c r="F584" s="11" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="G584" s="12">
         <v>1828</v>
@@ -52249,7 +52240,7 @@
         <v>12</v>
       </c>
       <c r="C586" s="11" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="D586" s="15" t="s">
         <v>60</v>
@@ -52258,7 +52249,7 @@
         <v>26</v>
       </c>
       <c r="F586" s="11" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="G586" s="12">
         <v>1829</v>
@@ -52405,7 +52396,7 @@
         <v>14</v>
       </c>
       <c r="C588" s="11" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="D588" s="11" t="s">
         <v>57</v>
@@ -52414,7 +52405,7 @@
         <v>61</v>
       </c>
       <c r="F588" s="11" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="G588" s="12">
         <v>1829</v>
@@ -53263,7 +53254,7 @@
         <v>18</v>
       </c>
       <c r="C599" s="11" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="D599" s="15" t="s">
         <v>45</v>
@@ -53272,7 +53263,7 @@
         <v>26</v>
       </c>
       <c r="F599" s="11" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="G599" s="12">
         <v>1829</v>
@@ -53497,7 +53488,7 @@
         <v>8</v>
       </c>
       <c r="C602" s="11" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="D602" s="11" t="s">
         <v>48</v>
@@ -53506,7 +53497,7 @@
         <v>26</v>
       </c>
       <c r="F602" s="11" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="G602" s="12">
         <v>1829</v>
@@ -53575,7 +53566,7 @@
         <v>12</v>
       </c>
       <c r="C603" s="11" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="D603" s="15" t="s">
         <v>57</v>
@@ -53584,7 +53575,7 @@
         <v>26</v>
       </c>
       <c r="F603" s="11" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="G603" s="12">
         <v>1829</v>
@@ -53809,7 +53800,7 @@
         <v>10</v>
       </c>
       <c r="C606" s="11" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="D606" s="15" t="s">
         <v>60</v>
@@ -53818,7 +53809,7 @@
         <v>26</v>
       </c>
       <c r="F606" s="11" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="G606" s="12">
         <v>1829</v>
@@ -53887,7 +53878,7 @@
         <v>10</v>
       </c>
       <c r="C607" s="11" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="D607" s="15" t="s">
         <v>45</v>
@@ -53896,7 +53887,7 @@
         <v>26</v>
       </c>
       <c r="F607" s="11" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="G607" s="12">
         <v>1829</v>
@@ -54433,7 +54424,7 @@
         <v>12</v>
       </c>
       <c r="C614" s="11" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="D614" s="15" t="s">
         <v>45</v>
@@ -54442,7 +54433,7 @@
         <v>26</v>
       </c>
       <c r="F614" s="11" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="G614" s="12">
         <v>1829</v>
@@ -54511,7 +54502,7 @@
         <v>12</v>
       </c>
       <c r="C615" s="11" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="D615" s="15" t="s">
         <v>71</v>
@@ -54520,7 +54511,7 @@
         <v>26</v>
       </c>
       <c r="F615" s="11" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="G615" s="12">
         <v>1829</v>
@@ -54589,7 +54580,7 @@
         <v>12</v>
       </c>
       <c r="C616" s="11" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="D616" s="15" t="s">
         <v>71</v>
@@ -54598,7 +54589,7 @@
         <v>26</v>
       </c>
       <c r="F616" s="11" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="G616" s="12">
         <v>1829</v>
@@ -54901,7 +54892,7 @@
         <v>6</v>
       </c>
       <c r="C620" s="11" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="D620" s="11" t="s">
         <v>57</v>
@@ -54910,7 +54901,7 @@
         <v>26</v>
       </c>
       <c r="F620" s="11" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="G620" s="12">
         <v>1830</v>
@@ -55369,7 +55360,7 @@
         <v>14</v>
       </c>
       <c r="C626" s="11" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="D626" s="11" t="s">
         <v>57</v>
@@ -55378,7 +55369,7 @@
         <v>26</v>
       </c>
       <c r="F626" s="11" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="G626" s="12">
         <v>1833</v>
@@ -55447,7 +55438,7 @@
         <v>12</v>
       </c>
       <c r="C627" s="11" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="D627" s="11" t="s">
         <v>57</v>
@@ -55456,7 +55447,7 @@
         <v>26</v>
       </c>
       <c r="F627" s="11" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="G627" s="12">
         <v>1834</v>
@@ -55915,7 +55906,7 @@
         <v>6</v>
       </c>
       <c r="C633" s="11" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="D633" s="15" t="s">
         <v>60</v>
@@ -55924,7 +55915,7 @@
         <v>26</v>
       </c>
       <c r="F633" s="11" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="G633" s="12">
         <v>1835</v>
@@ -55993,7 +55984,7 @@
         <v>6</v>
       </c>
       <c r="C634" s="11" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="D634" s="15" t="s">
         <v>60</v>
@@ -56002,7 +55993,7 @@
         <v>26</v>
       </c>
       <c r="F634" s="11" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="G634" s="12">
         <v>1835</v>
@@ -56461,7 +56452,7 @@
         <v>10</v>
       </c>
       <c r="C640" s="11" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="D640" s="11" t="s">
         <v>104</v>
@@ -56470,7 +56461,7 @@
         <v>26</v>
       </c>
       <c r="F640" s="11" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="G640" s="12">
         <v>1835</v>
@@ -56617,7 +56608,7 @@
         <v>10</v>
       </c>
       <c r="C642" s="11" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="D642" s="15" t="s">
         <v>80</v>
@@ -56626,7 +56617,7 @@
         <v>26</v>
       </c>
       <c r="F642" s="11" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="G642" s="12">
         <v>1836</v>
@@ -57007,7 +56998,7 @@
         <v>10</v>
       </c>
       <c r="C647" s="11" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="D647" s="15" t="s">
         <v>80</v>
@@ -57016,7 +57007,7 @@
         <v>26</v>
       </c>
       <c r="F647" s="11" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="G647" s="12">
         <v>1838</v>
@@ -57163,7 +57154,7 @@
         <v>14</v>
       </c>
       <c r="C649" s="11" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="D649" s="15" t="s">
         <v>45</v>
@@ -57172,7 +57163,7 @@
         <v>26</v>
       </c>
       <c r="F649" s="11" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="G649" s="12">
         <v>1839</v>
@@ -57241,7 +57232,7 @@
         <v>10</v>
       </c>
       <c r="C650" s="11" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="D650" s="15" t="s">
         <v>80</v>
@@ -57250,7 +57241,7 @@
         <v>26</v>
       </c>
       <c r="F650" s="11" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="G650" s="12">
         <v>1839</v>
@@ -57397,7 +57388,7 @@
         <v>10</v>
       </c>
       <c r="C652" s="11" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="D652" s="15" t="s">
         <v>45</v>
@@ -57406,7 +57397,7 @@
         <v>61</v>
       </c>
       <c r="F652" s="11" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="G652" s="12">
         <v>1839</v>
@@ -58177,7 +58168,7 @@
         <v>10</v>
       </c>
       <c r="C662" s="11" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="D662" s="11" t="s">
         <v>104</v>
@@ -58186,7 +58177,7 @@
         <v>26</v>
       </c>
       <c r="F662" s="11" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="G662" s="12">
         <v>1839</v>
@@ -58411,7 +58402,7 @@
         <v>10</v>
       </c>
       <c r="C665" s="11" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="D665" s="11" t="s">
         <v>104</v>
@@ -58420,7 +58411,7 @@
         <v>26</v>
       </c>
       <c r="F665" s="11" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="G665" s="12">
         <v>1839</v>
@@ -58489,7 +58480,7 @@
         <v>10</v>
       </c>
       <c r="C666" s="11" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="D666" s="15" t="s">
         <v>80</v>
@@ -58498,7 +58489,7 @@
         <v>26</v>
       </c>
       <c r="F666" s="11" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="G666" s="12">
         <v>1839</v>
@@ -59269,7 +59260,7 @@
         <v>6</v>
       </c>
       <c r="C676" s="11" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="D676" s="15" t="s">
         <v>60</v>
@@ -59278,7 +59269,7 @@
         <v>26</v>
       </c>
       <c r="F676" s="11" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="G676" s="12">
         <v>1840</v>
@@ -59347,7 +59338,7 @@
         <v>8</v>
       </c>
       <c r="C677" s="11" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="D677" s="15" t="s">
         <v>60</v>
@@ -59356,7 +59347,7 @@
         <v>26</v>
       </c>
       <c r="F677" s="11" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="G677" s="12">
         <v>1841</v>
@@ -59659,7 +59650,7 @@
         <v>18</v>
       </c>
       <c r="C681" s="11" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="D681" s="11" t="s">
         <v>57</v>
@@ -59668,7 +59659,7 @@
         <v>26</v>
       </c>
       <c r="F681" s="11" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="G681" s="12">
         <v>1842</v>
@@ -59815,7 +59806,7 @@
         <v>10</v>
       </c>
       <c r="C683" s="11" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="D683" s="11" t="s">
         <v>48</v>
@@ -59824,7 +59815,7 @@
         <v>61</v>
       </c>
       <c r="F683" s="11" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="G683" s="12">
         <v>1844</v>
@@ -59971,7 +59962,7 @@
         <v>10</v>
       </c>
       <c r="C685" s="11" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="D685" s="15" t="s">
         <v>60</v>
@@ -59980,7 +59971,7 @@
         <v>26</v>
       </c>
       <c r="F685" s="11" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="G685" s="12">
         <v>1844</v>
@@ -60049,7 +60040,7 @@
         <v>6</v>
       </c>
       <c r="C686" s="11" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="D686" s="15" t="s">
         <v>45</v>
@@ -60058,7 +60049,7 @@
         <v>26</v>
       </c>
       <c r="F686" s="11" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="G686" s="12">
         <v>1844</v>
@@ -60127,7 +60118,7 @@
         <v>18</v>
       </c>
       <c r="C687" s="11" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="D687" s="11" t="s">
         <v>104</v>
@@ -60136,7 +60127,7 @@
         <v>26</v>
       </c>
       <c r="F687" s="11" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="G687" s="12">
         <v>1844</v>
@@ -60205,7 +60196,7 @@
         <v>18</v>
       </c>
       <c r="C688" s="11" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="D688" s="11" t="s">
         <v>104</v>
@@ -60214,7 +60205,7 @@
         <v>26</v>
       </c>
       <c r="F688" s="11" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="G688" s="12">
         <v>1844</v>
@@ -60361,7 +60352,7 @@
         <v>10</v>
       </c>
       <c r="C690" s="11" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="D690" s="11" t="s">
         <v>71</v>
@@ -60370,7 +60361,7 @@
         <v>26</v>
       </c>
       <c r="F690" s="11" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="G690" s="12">
         <v>1844</v>
@@ -60595,7 +60586,7 @@
         <v>18</v>
       </c>
       <c r="C693" s="11" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="D693" s="15" t="s">
         <v>45</v>
@@ -60604,7 +60595,7 @@
         <v>61</v>
       </c>
       <c r="F693" s="11" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="G693" s="12">
         <v>1845</v>
@@ -61063,7 +61054,7 @@
         <v>8</v>
       </c>
       <c r="C699" s="11" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="D699" s="15" t="s">
         <v>60</v>
@@ -61072,7 +61063,7 @@
         <v>26</v>
       </c>
       <c r="F699" s="11" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="G699" s="12">
         <v>1845</v>
@@ -61219,7 +61210,7 @@
         <v>10</v>
       </c>
       <c r="C701" s="11" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D701" s="15" t="s">
         <v>80</v>
@@ -61228,7 +61219,7 @@
         <v>26</v>
       </c>
       <c r="F701" s="11" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="G701" s="12">
         <v>1847</v>
@@ -61609,7 +61600,7 @@
         <v>12</v>
       </c>
       <c r="C706" s="11" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="D706" s="15" t="s">
         <v>80</v>
@@ -61618,7 +61609,7 @@
         <v>61</v>
       </c>
       <c r="F706" s="11" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="G706" s="12">
         <v>1848</v>
@@ -61843,7 +61834,7 @@
         <v>12</v>
       </c>
       <c r="C709" s="11" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="D709" s="15" t="s">
         <v>71</v>
@@ -61852,7 +61843,7 @@
         <v>26</v>
       </c>
       <c r="F709" s="11" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="G709" s="12">
         <v>1848</v>
@@ -62389,7 +62380,7 @@
         <v>10</v>
       </c>
       <c r="C716" s="11" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="D716" s="15" t="s">
         <v>45</v>
@@ -62398,7 +62389,7 @@
         <v>26</v>
       </c>
       <c r="F716" s="11" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="G716" s="12">
         <v>1849</v>
@@ -62545,7 +62536,7 @@
         <v>12</v>
       </c>
       <c r="C718" s="11" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="D718" s="15" t="s">
         <v>71</v>
@@ -62554,7 +62545,7 @@
         <v>26</v>
       </c>
       <c r="F718" s="11" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="G718" s="12">
         <v>1849</v>
@@ -62701,7 +62692,7 @@
         <v>6</v>
       </c>
       <c r="C720" s="11" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="D720" s="15" t="s">
         <v>45</v>
@@ -62710,7 +62701,7 @@
         <v>26</v>
       </c>
       <c r="F720" s="11" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="G720" s="12">
         <v>1850</v>
@@ -63636,7 +63627,7 @@
         <v>12</v>
       </c>
       <c r="C732" s="11" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="D732" s="15" t="s">
         <v>60</v>
@@ -63645,7 +63636,7 @@
         <v>26</v>
       </c>
       <c r="F732" s="11" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="G732" s="12">
         <v>1854</v>
@@ -63714,7 +63705,7 @@
         <v>12</v>
       </c>
       <c r="C733" s="11" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="D733" s="15" t="s">
         <v>60</v>
@@ -63723,7 +63714,7 @@
         <v>26</v>
       </c>
       <c r="F733" s="11" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="G733" s="12">
         <v>1854</v>
@@ -64026,7 +64017,7 @@
         <v>10</v>
       </c>
       <c r="C737" s="11" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="D737" s="11" t="s">
         <v>57</v>
@@ -64035,7 +64026,7 @@
         <v>26</v>
       </c>
       <c r="F737" s="11" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="G737" s="12">
         <v>1855</v>
@@ -64260,7 +64251,7 @@
         <v>14</v>
       </c>
       <c r="C740" s="11" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="D740" s="15" t="s">
         <v>60</v>
@@ -64269,7 +64260,7 @@
         <v>61</v>
       </c>
       <c r="F740" s="11" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="G740" s="12">
         <v>1855</v>
@@ -64650,7 +64641,7 @@
         <v>12</v>
       </c>
       <c r="C745" s="11" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="D745" s="15" t="s">
         <v>45</v>
@@ -64659,7 +64650,7 @@
         <v>61</v>
       </c>
       <c r="F745" s="11" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="G745" s="12">
         <v>1856</v>
@@ -64884,7 +64875,7 @@
         <v>8</v>
       </c>
       <c r="C748" s="11" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D748" s="11" t="s">
         <v>57</v>
@@ -64893,7 +64884,7 @@
         <v>61</v>
       </c>
       <c r="F748" s="11" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="G748" s="12">
         <v>1858</v>
@@ -65118,7 +65109,7 @@
         <v>10</v>
       </c>
       <c r="C751" s="11" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="D751" s="15" t="s">
         <v>60</v>
@@ -65127,7 +65118,7 @@
         <v>61</v>
       </c>
       <c r="F751" s="11" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="G751" s="12">
         <v>1858</v>
@@ -65352,7 +65343,7 @@
         <v>18</v>
       </c>
       <c r="C754" s="11" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="D754" s="11" t="s">
         <v>57</v>
@@ -65361,7 +65352,7 @@
         <v>61</v>
       </c>
       <c r="F754" s="11" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="G754" s="12">
         <v>1859</v>
@@ -65742,7 +65733,7 @@
         <v>10</v>
       </c>
       <c r="C759" s="11" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="D759" s="11" t="s">
         <v>71</v>
@@ -65751,7 +65742,7 @@
         <v>61</v>
       </c>
       <c r="F759" s="11" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="G759" s="12">
         <v>1859</v>
@@ -65898,7 +65889,7 @@
         <v>14</v>
       </c>
       <c r="C761" s="11" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="D761" s="11" t="s">
         <v>57</v>
@@ -65907,7 +65898,7 @@
         <v>26</v>
       </c>
       <c r="F761" s="11" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="G761" s="12">
         <v>1859</v>
@@ -66054,7 +66045,7 @@
         <v>16</v>
       </c>
       <c r="C763" s="11" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="D763" s="11" t="s">
         <v>71</v>
@@ -66063,7 +66054,7 @@
         <v>61</v>
       </c>
       <c r="F763" s="11" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="G763" s="12">
         <v>1860</v>
@@ -66132,7 +66123,7 @@
         <v>16</v>
       </c>
       <c r="C764" s="11" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="D764" s="15" t="s">
         <v>45</v>
@@ -66141,7 +66132,7 @@
         <v>26</v>
       </c>
       <c r="F764" s="11" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="G764" s="12">
         <v>1860</v>
@@ -66287,7 +66278,7 @@
         <v>16</v>
       </c>
       <c r="C766" s="11" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="D766" s="11" t="s">
         <v>57</v>
@@ -66296,7 +66287,7 @@
         <v>26</v>
       </c>
       <c r="F766" s="11" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="G766" s="12">
         <v>1865</v>
@@ -66443,7 +66434,7 @@
         <v>6</v>
       </c>
       <c r="C768" s="11" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="D768" s="15" t="s">
         <v>45</v>
@@ -66452,7 +66443,7 @@
         <v>61</v>
       </c>
       <c r="F768" s="11" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="G768" s="12">
         <v>1866</v>
@@ -66520,7 +66511,7 @@
         <v>14</v>
       </c>
       <c r="C769" s="11" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="D769" s="15" t="s">
         <v>80</v>
@@ -66529,7 +66520,7 @@
         <v>26</v>
       </c>
       <c r="F769" s="11" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="G769" s="12">
         <v>1867</v>
@@ -66598,7 +66589,7 @@
         <v>12</v>
       </c>
       <c r="C770" s="11" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="D770" s="15" t="s">
         <v>45</v>
@@ -66607,7 +66598,7 @@
         <v>26</v>
       </c>
       <c r="F770" s="11" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="G770" s="12">
         <v>1867</v>
@@ -66676,7 +66667,7 @@
         <v>18</v>
       </c>
       <c r="C771" s="11" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="D771" s="11" t="s">
         <v>71</v>
@@ -66685,7 +66676,7 @@
         <v>61</v>
       </c>
       <c r="F771" s="11" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="G771" s="12">
         <v>1868</v>
@@ -66754,7 +66745,7 @@
         <v>12</v>
       </c>
       <c r="C772" s="11" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="D772" s="15" t="s">
         <v>57</v>
@@ -66763,7 +66754,7 @@
         <v>61</v>
       </c>
       <c r="F772" s="11" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="G772" s="12">
         <v>1868</v>
@@ -66988,7 +66979,7 @@
         <v>18</v>
       </c>
       <c r="C775" s="11" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="D775" s="11" t="s">
         <v>57</v>
@@ -66997,7 +66988,7 @@
         <v>26</v>
       </c>
       <c r="F775" s="11" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="G775" s="12">
         <v>1869</v>
@@ -67066,7 +67057,7 @@
         <v>18</v>
       </c>
       <c r="C776" s="11" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="D776" s="15" t="s">
         <v>45</v>
@@ -67075,7 +67066,7 @@
         <v>61</v>
       </c>
       <c r="F776" s="11" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="G776" s="12">
         <v>1869</v>
@@ -67300,7 +67291,7 @@
         <v>12</v>
       </c>
       <c r="C779" s="11" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="D779" s="15" t="s">
         <v>80</v>
@@ -67309,7 +67300,7 @@
         <v>26</v>
       </c>
       <c r="F779" s="11" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="G779" s="12">
         <v>1869</v>
@@ -67690,7 +67681,7 @@
         <v>12</v>
       </c>
       <c r="C784" s="11" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="D784" s="15" t="s">
         <v>45</v>
@@ -67699,7 +67690,7 @@
         <v>61</v>
       </c>
       <c r="F784" s="11" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="G784" s="12">
         <v>1870</v>
@@ -67846,7 +67837,7 @@
         <v>18</v>
       </c>
       <c r="C786" s="11" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="D786" s="11" t="s">
         <v>71</v>
@@ -67855,7 +67846,7 @@
         <v>61</v>
       </c>
       <c r="F786" s="11" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="G786" s="12">
         <v>1870</v>
@@ -68235,7 +68226,7 @@
         <v>16</v>
       </c>
       <c r="C791" s="11" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="D791" s="11" t="s">
         <v>71</v>
@@ -68244,7 +68235,7 @@
         <v>26</v>
       </c>
       <c r="F791" s="11" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="G791" s="12">
         <v>1875</v>
@@ -68313,7 +68304,7 @@
         <v>14</v>
       </c>
       <c r="C792" s="11" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="D792" s="11" t="s">
         <v>57</v>
@@ -68322,7 +68313,7 @@
         <v>26</v>
       </c>
       <c r="F792" s="11" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="G792" s="12">
         <v>1875</v>
@@ -68778,7 +68769,7 @@
         <v>14</v>
       </c>
       <c r="C798" s="11" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="D798" s="11" t="s">
         <v>57</v>
@@ -68787,7 +68778,7 @@
         <v>26</v>
       </c>
       <c r="F798" s="11" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="G798" s="12">
         <v>1878</v>
@@ -69012,7 +69003,7 @@
         <v>14</v>
       </c>
       <c r="C801" s="11" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="D801" s="15" t="s">
         <v>60</v>
@@ -69021,7 +69012,7 @@
         <v>26</v>
       </c>
       <c r="F801" s="11" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="G801" s="12">
         <v>1879</v>
@@ -69090,7 +69081,7 @@
         <v>18</v>
       </c>
       <c r="C802" s="11" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="D802" s="15" t="s">
         <v>80</v>
@@ -69099,7 +69090,7 @@
         <v>26</v>
       </c>
       <c r="F802" s="11" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="G802" s="12">
         <v>1879</v>
@@ -69168,7 +69159,7 @@
         <v>14</v>
       </c>
       <c r="C803" s="11" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="D803" s="15" t="s">
         <v>45</v>
@@ -69177,7 +69168,7 @@
         <v>61</v>
       </c>
       <c r="F803" s="11" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="G803" s="12">
         <v>1879</v>
@@ -69324,7 +69315,7 @@
         <v>14</v>
       </c>
       <c r="C805" s="11" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="D805" s="15" t="s">
         <v>80</v>
@@ -69333,7 +69324,7 @@
         <v>26</v>
       </c>
       <c r="F805" s="11" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="G805" s="12">
         <v>1879</v>
@@ -69402,7 +69393,7 @@
         <v>18</v>
       </c>
       <c r="C806" s="11" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="D806" s="15" t="s">
         <v>45</v>
@@ -69411,7 +69402,7 @@
         <v>61</v>
       </c>
       <c r="F806" s="11" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="G806" s="12">
         <v>1885</v>
@@ -69636,7 +69627,7 @@
         <v>18</v>
       </c>
       <c r="C809" s="11" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="D809" s="11" t="s">
         <v>57</v>
@@ -69645,7 +69636,7 @@
         <v>61</v>
       </c>
       <c r="F809" s="11" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="G809" s="12">
         <v>1887</v>
@@ -69870,7 +69861,7 @@
         <v>10</v>
       </c>
       <c r="C812" s="11" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D812" s="11" t="s">
         <v>57</v>
@@ -69879,7 +69870,7 @@
         <v>26</v>
       </c>
       <c r="F812" s="11" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="G812" s="12">
         <v>1889</v>
@@ -70026,7 +70017,7 @@
         <v>14</v>
       </c>
       <c r="C814" s="11" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="D814" s="15" t="s">
         <v>45</v>
@@ -70035,7 +70026,7 @@
         <v>61</v>
       </c>
       <c r="F814" s="11" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="G814" s="12">
         <v>1889</v>
@@ -70182,7 +70173,7 @@
         <v>10</v>
       </c>
       <c r="C816" s="11" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="D816" s="15" t="s">
         <v>60</v>
@@ -70191,7 +70182,7 @@
         <v>61</v>
       </c>
       <c r="F816" s="11" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="G816" s="12">
         <v>1889</v>
@@ -70338,7 +70329,7 @@
         <v>10</v>
       </c>
       <c r="C818" s="11" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="D818" s="15" t="s">
         <v>45</v>
@@ -70347,7 +70338,7 @@
         <v>26</v>
       </c>
       <c r="F818" s="11" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="G818" s="12">
         <v>1889</v>
@@ -70494,7 +70485,7 @@
         <v>16</v>
       </c>
       <c r="C820" s="11" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="D820" s="11" t="s">
         <v>71</v>
@@ -70503,7 +70494,7 @@
         <v>26</v>
       </c>
       <c r="F820" s="11" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="G820" s="12">
         <v>1890</v>
@@ -70572,7 +70563,7 @@
         <v>16</v>
       </c>
       <c r="C821" s="11" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="D821" s="11" t="s">
         <v>71</v>
@@ -70581,7 +70572,7 @@
         <v>61</v>
       </c>
       <c r="F821" s="11" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="G821" s="12">
         <v>1890</v>
@@ -70728,7 +70719,7 @@
         <v>16</v>
       </c>
       <c r="C823" s="11" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="D823" s="11" t="s">
         <v>71</v>
@@ -70737,7 +70728,7 @@
         <v>61</v>
       </c>
       <c r="F823" s="11" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="G823" s="12">
         <v>1890</v>
@@ -70806,7 +70797,7 @@
         <v>16</v>
       </c>
       <c r="C824" s="11" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="D824" s="11" t="s">
         <v>71</v>
@@ -70815,7 +70806,7 @@
         <v>61</v>
       </c>
       <c r="F824" s="11" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="G824" s="12">
         <v>1890</v>
@@ -70884,7 +70875,7 @@
         <v>16</v>
       </c>
       <c r="C825" s="11" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="D825" s="11" t="s">
         <v>71</v>
@@ -70893,7 +70884,7 @@
         <v>26</v>
       </c>
       <c r="F825" s="11" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="G825" s="12">
         <v>1890</v>
@@ -70962,7 +70953,7 @@
         <v>18</v>
       </c>
       <c r="C826" s="11" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="D826" s="11" t="s">
         <v>71</v>
@@ -70971,7 +70962,7 @@
         <v>61</v>
       </c>
       <c r="F826" s="11" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="G826" s="12">
         <v>1890</v>
@@ -71118,7 +71109,7 @@
         <v>10</v>
       </c>
       <c r="C828" s="11" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="D828" s="15" t="s">
         <v>80</v>
@@ -71127,7 +71118,7 @@
         <v>61</v>
       </c>
       <c r="F828" s="11" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="G828" s="12">
         <v>1895</v>
@@ -71352,7 +71343,7 @@
         <v>16</v>
       </c>
       <c r="C831" s="11" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="D831" s="11" t="s">
         <v>57</v>
@@ -71361,7 +71352,7 @@
         <v>26</v>
       </c>
       <c r="F831" s="11" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="G831" s="12">
         <v>1895</v>
@@ -71508,7 +71499,7 @@
         <v>10</v>
       </c>
       <c r="C833" s="11" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="D833" s="15" t="s">
         <v>60</v>
@@ -71517,7 +71508,7 @@
         <v>61</v>
       </c>
       <c r="F833" s="11" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="G833" s="12">
         <v>1895</v>
@@ -71586,7 +71577,7 @@
         <v>10</v>
       </c>
       <c r="C834" s="11" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="D834" s="11" t="s">
         <v>57</v>
@@ -71595,7 +71586,7 @@
         <v>61</v>
       </c>
       <c r="F834" s="11" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="G834" s="12">
         <v>1895</v>
@@ -71742,7 +71733,7 @@
         <v>10</v>
       </c>
       <c r="C836" s="11" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="D836" s="15" t="s">
         <v>45</v>
@@ -71751,7 +71742,7 @@
         <v>61</v>
       </c>
       <c r="F836" s="11" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="G836" s="12">
         <v>1895</v>
@@ -71820,7 +71811,7 @@
         <v>18</v>
       </c>
       <c r="C837" s="11" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D837" s="11" t="s">
         <v>71</v>
@@ -71829,7 +71820,7 @@
         <v>61</v>
       </c>
       <c r="F837" s="11" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="G837" s="12">
         <v>1895</v>
@@ -72054,7 +72045,7 @@
         <v>12</v>
       </c>
       <c r="C840" s="11" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="D840" s="15" t="s">
         <v>60</v>
@@ -72063,7 +72054,7 @@
         <v>61</v>
       </c>
       <c r="F840" s="11" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="G840" s="12">
         <v>1897</v>
@@ -72210,7 +72201,7 @@
         <v>12</v>
       </c>
       <c r="C842" s="11" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="D842" s="15" t="s">
         <v>45</v>
@@ -72219,7 +72210,7 @@
         <v>26</v>
       </c>
       <c r="F842" s="11" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="G842" s="12">
         <v>1898</v>
@@ -72288,7 +72279,7 @@
         <v>14</v>
       </c>
       <c r="C843" s="11" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="D843" s="11" t="s">
         <v>57</v>
@@ -72297,7 +72288,7 @@
         <v>61</v>
       </c>
       <c r="F843" s="11" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="G843" s="12">
         <v>1898</v>
@@ -72366,7 +72357,7 @@
         <v>16</v>
       </c>
       <c r="C844" s="11" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="D844" s="15" t="s">
         <v>45</v>
@@ -72375,7 +72366,7 @@
         <v>26</v>
       </c>
       <c r="F844" s="11" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="G844" s="12">
         <v>1899</v>
@@ -72912,7 +72903,7 @@
         <v>14</v>
       </c>
       <c r="C851" s="11" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="D851" s="11" t="s">
         <v>71</v>
@@ -72921,7 +72912,7 @@
         <v>61</v>
       </c>
       <c r="F851" s="11" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="G851" s="12">
         <v>1899</v>
@@ -73068,7 +73059,7 @@
         <v>14</v>
       </c>
       <c r="C853" s="11" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="D853" s="15" t="s">
         <v>45</v>
@@ -73077,7 +73068,7 @@
         <v>26</v>
       </c>
       <c r="F853" s="11" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="G853" s="12">
         <v>1899</v>
@@ -73536,7 +73527,7 @@
         <v>10</v>
       </c>
       <c r="C859" s="11" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="D859" s="15" t="s">
         <v>80</v>
@@ -73545,7 +73536,7 @@
         <v>61</v>
       </c>
       <c r="F859" s="11" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="G859" s="12">
         <v>1908</v>
@@ -74160,7 +74151,7 @@
         <v>18</v>
       </c>
       <c r="C867" s="11" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="D867" s="11" t="s">
         <v>57</v>
@@ -74169,7 +74160,7 @@
         <v>61</v>
       </c>
       <c r="F867" s="11" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="G867" s="12">
         <v>1929</v>
@@ -74472,7 +74463,7 @@
         <v>12</v>
       </c>
       <c r="C871" s="11" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="D871" s="15" t="s">
         <v>57</v>
@@ -74481,7 +74472,7 @@
         <v>26</v>
       </c>
       <c r="F871" s="11" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="G871" s="12">
         <v>1955</v>
@@ -74550,7 +74541,7 @@
         <v>6</v>
       </c>
       <c r="C872" s="11" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="D872" s="15" t="s">
         <v>80</v>
@@ -74559,7 +74550,7 @@
         <v>26</v>
       </c>
       <c r="F872" s="11" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="G872" s="12">
         <v>1977</v>
@@ -74862,7 +74853,7 @@
         <v>12</v>
       </c>
       <c r="C876" s="11" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="D876" s="15" t="s">
         <v>60</v>
@@ -74871,7 +74862,7 @@
         <v>61</v>
       </c>
       <c r="F876" s="11" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="G876" s="12">
         <v>2098</v>
@@ -75360,7 +75351,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="16" customFormat="1" ht="21.75" customHeight="1">
       <c r="A1" s="23" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -75377,7 +75368,7 @@
     </row>
     <row r="2" spans="1:13" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="16" customFormat="1" ht="27.75" customHeight="1">
@@ -75391,48 +75382,48 @@
         <v>27</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>1743</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1744</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>1745</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>1746</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>1747</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>1748</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>1749</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>1750</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>1751</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>1752</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>1753</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>1754</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
       <c r="A4" s="19" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>1302</v>
+        <v>362</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>1303</v>
+        <v>363</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="E4" s="26">
         <v>1819</v>
@@ -75441,1517 +75432,580 @@
         <v>1819</v>
       </c>
       <c r="G4" s="26">
-        <f t="shared" ref="G4:G41" si="0">IF(OR(E4="",F4=""),"",F4-E4)</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="26">
-        <v>2259</v>
-      </c>
-      <c r="I4" s="26">
-        <v>2259</v>
-      </c>
-      <c r="J4" s="26">
-        <f t="shared" ref="J4:J41" si="1">IF(OR(H4="",I4=""),"",I4-H4)</f>
-        <v>0</v>
+        <f>IF(OR(E4="",F4=""),"",F4-E4)</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26" t="str">
+        <f>IF(OR(H4="",I4=""),"",I4-H4)</f>
+        <v/>
       </c>
       <c r="K4" s="26">
-        <v>1849</v>
+        <v>1809</v>
       </c>
       <c r="L4" s="26">
-        <v>1819</v>
+        <v>1799</v>
       </c>
       <c r="M4" s="26">
-        <f t="shared" ref="M4:M41" si="2">IF(OR(K4="",L4=""),"",L4-K4)</f>
-        <v>-30</v>
+        <f>IF(OR(K4="",L4=""),"",L4-K4)</f>
+        <v>-10</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A5" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>580</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>581</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E5" s="26">
-        <v>1819</v>
-      </c>
-      <c r="F5" s="26">
-        <v>1819</v>
-      </c>
-      <c r="G5" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="26">
-        <v>2260</v>
-      </c>
-      <c r="I5" s="26">
-        <v>2260</v>
-      </c>
-      <c r="J5" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="26">
-        <v>1798</v>
-      </c>
-      <c r="L5" s="26">
-        <v>1799</v>
-      </c>
-      <c r="M5" s="26">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="A5" s="19"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
     </row>
     <row r="6" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A6" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>878</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>879</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E6" s="26">
-        <v>1815</v>
-      </c>
-      <c r="F6" s="26">
-        <v>1815</v>
-      </c>
-      <c r="G6" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="26">
-        <v>2280</v>
-      </c>
-      <c r="I6" s="26">
-        <v>2260</v>
-      </c>
-      <c r="J6" s="26">
-        <f t="shared" si="1"/>
-        <v>-20</v>
-      </c>
-      <c r="K6" s="26">
-        <v>1799</v>
-      </c>
-      <c r="L6" s="26">
-        <v>1795</v>
-      </c>
-      <c r="M6" s="26">
-        <f t="shared" si="2"/>
-        <v>-4</v>
-      </c>
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
     </row>
     <row r="7" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A7" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E7" s="26">
-        <v>1788</v>
-      </c>
+      <c r="A7" s="19"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="26"/>
       <c r="F7" s="26"/>
-      <c r="G7" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H7" s="26">
-        <v>2295</v>
-      </c>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
       <c r="I7" s="26"/>
-      <c r="J7" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="26">
-        <v>1795</v>
-      </c>
-      <c r="L7" s="26">
-        <v>1795</v>
-      </c>
-      <c r="M7" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
     </row>
     <row r="8" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A8" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E8" s="26">
-        <v>1869</v>
-      </c>
-      <c r="F8" s="26">
-        <v>1839</v>
-      </c>
-      <c r="G8" s="26">
-        <f t="shared" si="0"/>
-        <v>-30</v>
-      </c>
-      <c r="H8" s="26">
-        <v>2329</v>
-      </c>
-      <c r="I8" s="26">
-        <v>2279</v>
-      </c>
-      <c r="J8" s="26">
-        <f t="shared" si="1"/>
-        <v>-50</v>
-      </c>
-      <c r="K8" s="26">
-        <v>1839</v>
-      </c>
-      <c r="L8" s="26">
-        <v>1819</v>
-      </c>
-      <c r="M8" s="26">
-        <f t="shared" si="2"/>
-        <v>-20</v>
-      </c>
+      <c r="A8" s="19"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
     </row>
     <row r="9" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A9" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>1601</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>1602</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E9" s="26">
-        <v>1809</v>
-      </c>
-      <c r="F9" s="26">
-        <v>1809</v>
-      </c>
-      <c r="G9" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A9" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
       <c r="H9" s="26"/>
       <c r="I9" s="26"/>
-      <c r="J9" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="26">
-        <v>1799</v>
-      </c>
-      <c r="L9" s="26">
-        <v>1809</v>
-      </c>
-      <c r="M9" s="26">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
     </row>
     <row r="10" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A10" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>1660</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>1661</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E10" s="26">
-        <v>1869</v>
-      </c>
-      <c r="F10" s="26">
-        <v>1869</v>
-      </c>
-      <c r="G10" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="26"/>
       <c r="I10" s="26"/>
-      <c r="J10" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="26">
-        <v>1849</v>
-      </c>
-      <c r="L10" s="26">
-        <v>1854</v>
-      </c>
-      <c r="M10" s="26">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
     </row>
     <row r="11" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A11" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>702</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>703</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E11" s="26">
-        <v>1828</v>
-      </c>
-      <c r="F11" s="26">
-        <v>1828</v>
-      </c>
-      <c r="G11" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A11" s="19"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
-      <c r="J11" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="26">
-        <v>1799</v>
-      </c>
-      <c r="L11" s="26">
-        <v>1784</v>
-      </c>
-      <c r="M11" s="26">
-        <f t="shared" si="2"/>
-        <v>-15</v>
-      </c>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
     </row>
     <row r="12" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A12" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>904</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>905</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E12" s="26">
-        <v>1870</v>
-      </c>
-      <c r="F12" s="26">
-        <v>1890</v>
-      </c>
-      <c r="G12" s="26">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
+      <c r="A12" s="19"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="26"/>
       <c r="I12" s="26"/>
-      <c r="J12" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="26">
-        <v>1850</v>
-      </c>
-      <c r="L12" s="26">
-        <v>1850</v>
-      </c>
-      <c r="M12" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
     </row>
     <row r="13" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A13" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>374</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>375</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E13" s="26">
-        <v>1849</v>
-      </c>
-      <c r="F13" s="26">
-        <v>1849</v>
-      </c>
-      <c r="G13" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A13" s="19"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
       <c r="H13" s="26"/>
       <c r="I13" s="26"/>
-      <c r="J13" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="26">
-        <v>1900</v>
-      </c>
-      <c r="L13" s="26">
-        <v>1819</v>
-      </c>
-      <c r="M13" s="26">
-        <f t="shared" si="2"/>
-        <v>-81</v>
-      </c>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
     </row>
     <row r="14" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A14" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>1292</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>1293</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E14" s="26">
-        <v>1869</v>
-      </c>
-      <c r="F14" s="26">
-        <v>1869</v>
-      </c>
-      <c r="G14" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A14" s="19"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
-      <c r="J14" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="26">
-        <v>1870</v>
-      </c>
-      <c r="L14" s="26">
-        <v>1859</v>
-      </c>
-      <c r="M14" s="26">
-        <f t="shared" si="2"/>
-        <v>-11</v>
-      </c>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
     </row>
     <row r="15" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A15" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>1073</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>1074</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E15" s="26">
-        <v>1879</v>
-      </c>
-      <c r="F15" s="26">
-        <v>1879</v>
-      </c>
-      <c r="G15" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
       <c r="H15" s="26"/>
       <c r="I15" s="26"/>
-      <c r="J15" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="26">
-        <v>1869</v>
-      </c>
-      <c r="L15" s="26">
-        <v>1919</v>
-      </c>
-      <c r="M15" s="26">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
     </row>
     <row r="16" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A16" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>751</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>752</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E16" s="26">
-        <v>1879</v>
-      </c>
-      <c r="F16" s="26">
-        <v>1879</v>
-      </c>
-      <c r="G16" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A16" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
       <c r="H16" s="26"/>
       <c r="I16" s="26"/>
-      <c r="J16" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="26">
-        <v>1889</v>
-      </c>
-      <c r="L16" s="26">
-        <v>1859</v>
-      </c>
-      <c r="M16" s="26">
-        <f t="shared" si="2"/>
-        <v>-30</v>
-      </c>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
     </row>
     <row r="17" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A17" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>1320</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>1321</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E17" s="26">
-        <v>1887</v>
-      </c>
-      <c r="F17" s="26">
-        <v>1887</v>
-      </c>
-      <c r="G17" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A17" s="19"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
       <c r="H17" s="26"/>
       <c r="I17" s="26"/>
-      <c r="J17" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="26">
-        <v>1868</v>
-      </c>
-      <c r="L17" s="26">
-        <v>1853</v>
-      </c>
-      <c r="M17" s="26">
-        <f t="shared" si="2"/>
-        <v>-15</v>
-      </c>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
     </row>
     <row r="18" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A18" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>380</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>381</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E18" s="26">
-        <v>1895</v>
-      </c>
-      <c r="F18" s="26">
-        <v>1895</v>
-      </c>
-      <c r="G18" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A18" s="19"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
       <c r="H18" s="26"/>
       <c r="I18" s="26"/>
-      <c r="J18" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="26">
-        <v>1853</v>
-      </c>
-      <c r="L18" s="26">
-        <v>1868</v>
-      </c>
-      <c r="M18" s="26">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
     </row>
     <row r="19" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A19" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>1676</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>1677</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E19" s="26">
-        <v>1989</v>
-      </c>
-      <c r="F19" s="26">
-        <v>1865</v>
-      </c>
-      <c r="G19" s="26">
-        <f t="shared" si="0"/>
-        <v>-124</v>
-      </c>
+      <c r="A19" s="19"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
-      <c r="J19" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="26">
-        <v>1825</v>
-      </c>
-      <c r="L19" s="26">
-        <v>1825</v>
-      </c>
-      <c r="M19" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
     </row>
     <row r="20" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A20" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>1278</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>1279</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E20" s="26">
-        <v>1817</v>
-      </c>
-      <c r="F20" s="26">
-        <v>1817</v>
-      </c>
-      <c r="G20" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A20" s="19"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
       <c r="H20" s="26"/>
       <c r="I20" s="26"/>
-      <c r="J20" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="26">
-        <v>1808</v>
-      </c>
-      <c r="L20" s="26">
-        <v>1798</v>
-      </c>
-      <c r="M20" s="26">
-        <f t="shared" si="2"/>
-        <v>-10</v>
-      </c>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
     </row>
     <row r="21" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A21" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>490</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>491</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E21" s="26">
-        <v>1819</v>
-      </c>
-      <c r="F21" s="26">
-        <v>1819</v>
-      </c>
-      <c r="G21" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A21" s="19"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
       <c r="H21" s="26"/>
       <c r="I21" s="26"/>
-      <c r="J21" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="26">
-        <v>1807</v>
-      </c>
-      <c r="L21" s="26">
-        <v>1798</v>
-      </c>
-      <c r="M21" s="26">
-        <f t="shared" si="2"/>
-        <v>-9</v>
-      </c>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="26"/>
+      <c r="M21" s="26"/>
     </row>
     <row r="22" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A22" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>1539</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>1540</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E22" s="26">
-        <v>1829</v>
-      </c>
-      <c r="F22" s="26">
-        <v>1819</v>
-      </c>
-      <c r="G22" s="26">
-        <f t="shared" si="0"/>
-        <v>-10</v>
-      </c>
+      <c r="A22" s="19"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
       <c r="H22" s="26"/>
       <c r="I22" s="26"/>
-      <c r="J22" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="26">
-        <v>1824</v>
-      </c>
-      <c r="L22" s="26">
-        <v>1799</v>
-      </c>
-      <c r="M22" s="26">
-        <f t="shared" si="2"/>
-        <v>-25</v>
-      </c>
+      <c r="J22" s="26"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
     </row>
     <row r="23" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A23" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>1759</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>1760</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E23" s="26">
-        <v>1834</v>
-      </c>
-      <c r="F23" s="26">
-        <v>1799</v>
-      </c>
-      <c r="G23" s="26">
-        <f t="shared" si="0"/>
-        <v>-35</v>
-      </c>
+      <c r="A23" s="19"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
       <c r="H23" s="26"/>
       <c r="I23" s="26"/>
-      <c r="J23" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="26">
-        <v>1824</v>
-      </c>
-      <c r="L23" s="26">
-        <v>1824</v>
-      </c>
-      <c r="M23" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
     </row>
     <row r="24" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A24" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>727</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>729</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E24" s="26">
-        <v>1835</v>
-      </c>
-      <c r="F24" s="26">
-        <v>1825</v>
-      </c>
-      <c r="G24" s="26">
-        <f t="shared" si="0"/>
-        <v>-10</v>
-      </c>
+      <c r="A24" s="19"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
       <c r="H24" s="26"/>
       <c r="I24" s="26"/>
-      <c r="J24" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="26">
-        <v>1813</v>
-      </c>
-      <c r="L24" s="26">
-        <v>1813</v>
-      </c>
-      <c r="M24" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
     </row>
     <row r="25" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A25" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>1368</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>1370</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E25" s="26">
-        <v>1842</v>
-      </c>
-      <c r="F25" s="26">
-        <v>1842</v>
-      </c>
-      <c r="G25" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A25" s="19"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
       <c r="H25" s="26"/>
       <c r="I25" s="26"/>
-      <c r="J25" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="26">
-        <v>1850</v>
-      </c>
-      <c r="L25" s="26">
-        <v>1832</v>
-      </c>
-      <c r="M25" s="26">
-        <f t="shared" si="2"/>
-        <v>-18</v>
-      </c>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="26"/>
     </row>
     <row r="26" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A26" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>1221</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>1222</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E26" s="26">
-        <v>1845</v>
-      </c>
-      <c r="F26" s="26">
-        <v>1825</v>
-      </c>
-      <c r="G26" s="26">
-        <f t="shared" si="0"/>
-        <v>-20</v>
-      </c>
+      <c r="A26" s="19"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
       <c r="H26" s="26"/>
       <c r="I26" s="26"/>
-      <c r="J26" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="26">
-        <v>1815</v>
-      </c>
-      <c r="L26" s="26">
-        <v>1799</v>
-      </c>
-      <c r="M26" s="26">
-        <f t="shared" si="2"/>
-        <v>-16</v>
-      </c>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
     </row>
     <row r="27" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A27" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>1611</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>1612</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E27" s="26">
-        <v>1848</v>
-      </c>
-      <c r="F27" s="26">
-        <v>1848</v>
-      </c>
-      <c r="G27" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A27" s="19"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
       <c r="H27" s="26"/>
       <c r="I27" s="26"/>
-      <c r="J27" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="26">
-        <v>1823</v>
-      </c>
-      <c r="L27" s="26">
-        <v>1838</v>
-      </c>
-      <c r="M27" s="26">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
     </row>
     <row r="28" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A28" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>710</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>711</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E28" s="26">
-        <v>1849</v>
-      </c>
-      <c r="F28" s="26">
-        <v>1849</v>
-      </c>
-      <c r="G28" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A28" s="19"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
       <c r="H28" s="26"/>
       <c r="I28" s="26"/>
-      <c r="J28" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="26">
-        <v>1834</v>
-      </c>
-      <c r="L28" s="26">
-        <v>1799</v>
-      </c>
-      <c r="M28" s="26">
-        <f t="shared" si="2"/>
-        <v>-35</v>
-      </c>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
     </row>
     <row r="29" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A29" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>459</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>460</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E29" s="26">
-        <v>1850</v>
-      </c>
-      <c r="F29" s="26">
-        <v>1870</v>
-      </c>
-      <c r="G29" s="26">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
+      <c r="A29" s="19"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
       <c r="H29" s="26"/>
       <c r="I29" s="26"/>
-      <c r="J29" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="26">
-        <v>1860</v>
-      </c>
-      <c r="L29" s="26">
-        <v>1860</v>
-      </c>
-      <c r="M29" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
     </row>
     <row r="30" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A30" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>1114</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E30" s="26">
-        <v>1855</v>
-      </c>
-      <c r="F30" s="26">
-        <v>1835</v>
-      </c>
-      <c r="G30" s="26">
-        <f t="shared" si="0"/>
-        <v>-20</v>
-      </c>
+      <c r="A30" s="19"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="26"/>
       <c r="I30" s="26"/>
-      <c r="J30" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="26">
-        <v>1835</v>
-      </c>
-      <c r="L30" s="26">
-        <v>1815</v>
-      </c>
-      <c r="M30" s="26">
-        <f t="shared" si="2"/>
-        <v>-20</v>
-      </c>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
     </row>
     <row r="31" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A31" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E31" s="26">
-        <v>1858</v>
-      </c>
-      <c r="F31" s="26">
-        <v>1838</v>
-      </c>
-      <c r="G31" s="26">
-        <f t="shared" si="0"/>
-        <v>-20</v>
-      </c>
+      <c r="A31" s="19"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
       <c r="H31" s="26"/>
       <c r="I31" s="26"/>
-      <c r="J31" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="26">
-        <v>1838</v>
-      </c>
-      <c r="L31" s="26">
-        <v>1818</v>
-      </c>
-      <c r="M31" s="26">
-        <f t="shared" si="2"/>
-        <v>-20</v>
-      </c>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
     </row>
     <row r="32" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A32" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>1352</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>1353</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E32" s="26">
-        <v>1858</v>
-      </c>
-      <c r="F32" s="26">
-        <v>1878</v>
-      </c>
-      <c r="G32" s="26">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
+      <c r="A32" s="19"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="26"/>
       <c r="I32" s="26"/>
-      <c r="J32" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="26">
-        <v>1857</v>
-      </c>
-      <c r="L32" s="26">
-        <v>1877</v>
-      </c>
-      <c r="M32" s="26">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
+      <c r="J32" s="26"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
     </row>
     <row r="33" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A33" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E33" s="26">
-        <v>1869</v>
-      </c>
-      <c r="F33" s="26">
-        <v>1839</v>
-      </c>
-      <c r="G33" s="26">
-        <f t="shared" si="0"/>
-        <v>-30</v>
-      </c>
+      <c r="A33" s="19"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
       <c r="H33" s="26"/>
       <c r="I33" s="26"/>
-      <c r="J33" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="26">
-        <v>1839</v>
-      </c>
-      <c r="L33" s="26">
-        <v>1819</v>
-      </c>
-      <c r="M33" s="26">
-        <f t="shared" si="2"/>
-        <v>-20</v>
-      </c>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
     </row>
     <row r="34" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A34" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E34" s="26">
-        <v>1869</v>
-      </c>
-      <c r="F34" s="26">
-        <v>1839</v>
-      </c>
-      <c r="G34" s="26">
-        <f t="shared" si="0"/>
-        <v>-30</v>
-      </c>
+      <c r="A34" s="19"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="26"/>
       <c r="I34" s="26"/>
-      <c r="J34" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="26">
-        <v>1839</v>
-      </c>
-      <c r="L34" s="26">
-        <v>1819</v>
-      </c>
-      <c r="M34" s="26">
-        <f t="shared" si="2"/>
-        <v>-20</v>
-      </c>
+      <c r="J34" s="26"/>
+      <c r="K34" s="26"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
     </row>
     <row r="35" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A35" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B35" s="20" t="s">
-        <v>1674</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>1675</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E35" s="26">
-        <v>1879</v>
-      </c>
-      <c r="F35" s="26">
-        <v>1879</v>
-      </c>
-      <c r="G35" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A35" s="19"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
       <c r="H35" s="26"/>
       <c r="I35" s="26"/>
-      <c r="J35" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="26">
-        <v>1869</v>
-      </c>
-      <c r="L35" s="26">
-        <v>1899</v>
-      </c>
-      <c r="M35" s="26">
-        <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
+      <c r="J35" s="26"/>
+      <c r="K35" s="26"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="26"/>
     </row>
     <row r="36" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A36" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D36" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E36" s="26">
-        <v>1886</v>
-      </c>
-      <c r="F36" s="26">
-        <v>1828</v>
-      </c>
-      <c r="G36" s="26">
-        <f t="shared" si="0"/>
-        <v>-58</v>
-      </c>
+      <c r="A36" s="19"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
       <c r="H36" s="26"/>
       <c r="I36" s="26"/>
-      <c r="J36" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="26">
-        <v>1818</v>
-      </c>
-      <c r="L36" s="26">
-        <v>1818</v>
-      </c>
-      <c r="M36" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J36" s="26"/>
+      <c r="K36" s="26"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="26"/>
     </row>
     <row r="37" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A37" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>757</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>758</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E37" s="26">
-        <v>1897</v>
-      </c>
-      <c r="F37" s="26">
-        <v>1897</v>
-      </c>
-      <c r="G37" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A37" s="19"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
       <c r="H37" s="26"/>
       <c r="I37" s="26"/>
-      <c r="J37" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="26">
-        <v>1887</v>
-      </c>
-      <c r="L37" s="26">
-        <v>1872</v>
-      </c>
-      <c r="M37" s="26">
-        <f t="shared" si="2"/>
-        <v>-15</v>
-      </c>
+      <c r="J37" s="26"/>
+      <c r="K37" s="26"/>
+      <c r="L37" s="26"/>
+      <c r="M37" s="26"/>
     </row>
     <row r="38" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A38" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>788</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>789</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E38" s="26">
-        <v>2199</v>
-      </c>
-      <c r="F38" s="26">
-        <v>1859</v>
-      </c>
-      <c r="G38" s="26">
-        <f t="shared" si="0"/>
-        <v>-340</v>
-      </c>
+      <c r="A38" s="19"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
       <c r="H38" s="26"/>
       <c r="I38" s="26"/>
-      <c r="J38" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="26">
-        <v>2199</v>
-      </c>
-      <c r="L38" s="26">
-        <v>1849</v>
-      </c>
-      <c r="M38" s="26">
-        <f t="shared" si="2"/>
-        <v>-350</v>
-      </c>
+      <c r="J38" s="26"/>
+      <c r="K38" s="26"/>
+      <c r="L38" s="26"/>
+      <c r="M38" s="26"/>
     </row>
     <row r="39" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A39" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>1595</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>1596</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E39" s="26">
-        <v>2098</v>
-      </c>
-      <c r="F39" s="26">
-        <v>2098</v>
-      </c>
-      <c r="G39" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A39" s="19"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
       <c r="H39" s="26"/>
       <c r="I39" s="26"/>
-      <c r="J39" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="26">
-        <v>2095</v>
-      </c>
-      <c r="L39" s="26">
-        <v>1995</v>
-      </c>
-      <c r="M39" s="26">
-        <f t="shared" si="2"/>
-        <v>-100</v>
-      </c>
+      <c r="J39" s="26"/>
+      <c r="K39" s="26"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="26"/>
     </row>
     <row r="40" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A40" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="C40" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>1763</v>
-      </c>
+      <c r="A40" s="19"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
       <c r="E40" s="26"/>
       <c r="F40" s="26"/>
-      <c r="G40" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H40" s="26">
-        <v>2357</v>
-      </c>
-      <c r="I40" s="26">
-        <v>2357</v>
-      </c>
-      <c r="J40" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K40" s="26">
-        <v>1897</v>
-      </c>
-      <c r="L40" s="26">
-        <v>1837</v>
-      </c>
-      <c r="M40" s="26">
-        <f t="shared" si="2"/>
-        <v>-60</v>
-      </c>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="26"/>
+      <c r="K40" s="26"/>
+      <c r="L40" s="26"/>
+      <c r="M40" s="26"/>
     </row>
     <row r="41" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A41" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" s="20" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>1182</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E41" s="26">
-        <v>1828</v>
-      </c>
+      <c r="A41" s="19"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="26"/>
       <c r="F41" s="26"/>
-      <c r="G41" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="G41" s="26"/>
       <c r="H41" s="26"/>
       <c r="I41" s="26"/>
-      <c r="J41" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="26">
-        <v>1813</v>
-      </c>
+      <c r="J41" s="26"/>
+      <c r="K41" s="26"/>
       <c r="L41" s="26"/>
-      <c r="M41" s="26" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="M41" s="26"/>
     </row>
     <row r="42" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
       <c r="A42" s="19"/>
@@ -79988,7 +79042,7 @@
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
-  <conditionalFormatting sqref="G4:G41">
+  <conditionalFormatting sqref="G4">
     <cfRule type="cellIs" dxfId="5" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -79996,7 +79050,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J41">
+  <conditionalFormatting sqref="J4">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -80004,7 +79058,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M41">
+  <conditionalFormatting sqref="M4">
     <cfRule type="cellIs" dxfId="1" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>

--- a/fuel_cost_chungcheong.xlsx
+++ b/fuel_cost_chungcheong.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4833" uniqueCount="1767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4697" uniqueCount="1764">
   <si>
     <t>유류비 계산(혼유, 지역화폐 등)</t>
   </si>
@@ -5136,9 +5136,6 @@
     <t>충북 청주시 흥덕구 엘지로 11</t>
   </si>
   <si>
-    <t>세종시 부강면 시목부강로 423</t>
-  </si>
-  <si>
     <t>충북 청주시 청원구 오창읍 두릉유리로 204</t>
   </si>
   <si>
@@ -5389,12 +5386,6 @@
   </si>
   <si>
     <t>현행화 일자: 2026-09-03</t>
-  </si>
-  <si>
-    <t>가격변동</t>
-  </si>
-  <si>
-    <t>폐업</t>
   </si>
 </sst>
 </file>
@@ -9821,7 +9812,7 @@
         <v>10</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="D52" s="11" t="s">
         <v>45</v>
@@ -9830,7 +9821,7 @@
         <v>26</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="G52" s="12">
         <v>1827</v>
@@ -10221,7 +10212,7 @@
         <v>6</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="D57" s="15" t="s">
         <v>45</v>
@@ -10230,7 +10221,7 @@
         <v>26</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="G57" s="12">
         <v>1825</v>
@@ -13903,7 +13894,7 @@
         <v>6</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="D103" s="15" t="s">
         <v>45</v>
@@ -13912,7 +13903,7 @@
         <v>26</v>
       </c>
       <c r="F103" s="11" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="G103" s="12">
         <v>1822</v>
@@ -17587,7 +17578,7 @@
         <v>6</v>
       </c>
       <c r="C149" s="11" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="D149" s="15" t="s">
         <v>45</v>
@@ -17596,7 +17587,7 @@
         <v>61</v>
       </c>
       <c r="F149" s="11" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="G149" s="12">
         <v>1866</v>
@@ -18951,7 +18942,7 @@
         <v>14</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="D166" s="15" t="s">
         <v>80</v>
@@ -18960,7 +18951,7 @@
         <v>26</v>
       </c>
       <c r="F166" s="11" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="G166" s="12">
         <v>1859</v>
@@ -20315,7 +20306,7 @@
         <v>16</v>
       </c>
       <c r="C183" s="11" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="D183" s="15" t="s">
         <v>45</v>
@@ -20324,7 +20315,7 @@
         <v>26</v>
       </c>
       <c r="F183" s="11" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="G183" s="12">
         <v>1830</v>
@@ -24795,7 +24786,7 @@
         <v>6</v>
       </c>
       <c r="C239" s="11" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="D239" s="15" t="s">
         <v>45</v>
@@ -24804,7 +24795,7 @@
         <v>26</v>
       </c>
       <c r="F239" s="11" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="G239" s="12">
         <v>1829</v>
@@ -26635,7 +26626,7 @@
         <v>16</v>
       </c>
       <c r="C262" s="11" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="D262" s="15" t="s">
         <v>80</v>
@@ -26644,7 +26635,7 @@
         <v>61</v>
       </c>
       <c r="F262" s="11" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="G262" s="12">
         <v>1880</v>
@@ -27115,7 +27106,7 @@
         <v>10</v>
       </c>
       <c r="C268" s="11" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="D268" s="15" t="s">
         <v>80</v>
@@ -27124,7 +27115,7 @@
         <v>61</v>
       </c>
       <c r="F268" s="11" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="G268" s="12">
         <v>1839</v>
@@ -27195,7 +27186,7 @@
         <v>10</v>
       </c>
       <c r="C269" s="11" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="D269" s="15" t="s">
         <v>45</v>
@@ -27204,7 +27195,7 @@
         <v>26</v>
       </c>
       <c r="F269" s="11" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="G269" s="12">
         <v>1839</v>
@@ -27355,7 +27346,7 @@
         <v>10</v>
       </c>
       <c r="C271" s="11" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="D271" s="11" t="s">
         <v>57</v>
@@ -27364,7 +27355,7 @@
         <v>26</v>
       </c>
       <c r="F271" s="11" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="G271" s="12">
         <v>1844</v>
@@ -28155,7 +28146,7 @@
         <v>18</v>
       </c>
       <c r="C281" s="11" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="D281" s="15" t="s">
         <v>45</v>
@@ -28164,7 +28155,7 @@
         <v>61</v>
       </c>
       <c r="F281" s="11" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="G281" s="12">
         <v>1890</v>
@@ -29355,7 +29346,7 @@
         <v>8</v>
       </c>
       <c r="C296" s="11" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="D296" s="11" t="s">
         <v>57</v>
@@ -29364,7 +29355,7 @@
         <v>26</v>
       </c>
       <c r="F296" s="11" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="G296" s="12">
         <v>1855</v>
@@ -29435,7 +29426,7 @@
         <v>8</v>
       </c>
       <c r="C297" s="11" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="D297" s="15" t="s">
         <v>60</v>
@@ -29444,7 +29435,7 @@
         <v>26</v>
       </c>
       <c r="F297" s="11" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="G297" s="12">
         <v>1855</v>
@@ -29915,7 +29906,7 @@
         <v>18</v>
       </c>
       <c r="C303" s="11" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="D303" s="11" t="s">
         <v>57</v>
@@ -29924,7 +29915,7 @@
         <v>61</v>
       </c>
       <c r="F303" s="11" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="G303" s="12">
         <v>1899</v>
@@ -32635,7 +32626,7 @@
         <v>8</v>
       </c>
       <c r="C337" s="11" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="D337" s="15" t="s">
         <v>45</v>
@@ -32644,7 +32635,7 @@
         <v>61</v>
       </c>
       <c r="F337" s="11" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="G337" s="12">
         <v>1875</v>
@@ -34235,7 +34226,7 @@
         <v>14</v>
       </c>
       <c r="C357" s="11" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="D357" s="15" t="s">
         <v>45</v>
@@ -34244,7 +34235,7 @@
         <v>26</v>
       </c>
       <c r="F357" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="G357" s="12">
         <v>1889</v>
@@ -34395,7 +34386,7 @@
         <v>10</v>
       </c>
       <c r="C359" s="11" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="D359" s="15" t="s">
         <v>45</v>
@@ -34404,7 +34395,7 @@
         <v>26</v>
       </c>
       <c r="F359" s="11" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="G359" s="12">
         <v>1890</v>
@@ -36635,7 +36626,7 @@
         <v>10</v>
       </c>
       <c r="C387" s="11" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="D387" s="11" t="s">
         <v>57</v>
@@ -36644,7 +36635,7 @@
         <v>26</v>
       </c>
       <c r="F387" s="11" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="G387" s="12">
         <v>1898</v>
@@ -37195,7 +37186,7 @@
         <v>14</v>
       </c>
       <c r="C394" s="11" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="D394" s="11" t="s">
         <v>57</v>
@@ -37204,7 +37195,7 @@
         <v>61</v>
       </c>
       <c r="F394" s="11" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="G394" s="12">
         <v>1899</v>
@@ -40075,7 +40066,7 @@
         <v>12</v>
       </c>
       <c r="C430" s="11" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="D430" s="15" t="s">
         <v>60</v>
@@ -40084,7 +40075,7 @@
         <v>61</v>
       </c>
       <c r="F430" s="11" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="G430" s="12">
         <v>1960</v>
@@ -41017,7 +41008,7 @@
         <v>12</v>
       </c>
       <c r="C442" s="11" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="D442" s="11" t="s">
         <v>104</v>
@@ -41026,7 +41017,7 @@
         <v>26</v>
       </c>
       <c r="F442" s="11" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="G442" s="12">
         <v>1799</v>
@@ -42345,7 +42336,7 @@
         <v>14</v>
       </c>
       <c r="C459" s="11" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="D459" s="15" t="s">
         <v>45</v>
@@ -42354,7 +42345,7 @@
         <v>26</v>
       </c>
       <c r="F459" s="11" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="G459" s="12">
         <v>1809</v>
@@ -48039,7 +48030,7 @@
         <v>10</v>
       </c>
       <c r="C532" s="11" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="D532" s="15" t="s">
         <v>80</v>
@@ -48048,7 +48039,7 @@
         <v>26</v>
       </c>
       <c r="F532" s="11" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="G532" s="12">
         <v>1819</v>
@@ -48819,7 +48810,7 @@
         <v>10</v>
       </c>
       <c r="C542" s="11" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="D542" s="11" t="s">
         <v>48</v>
@@ -48828,7 +48819,7 @@
         <v>26</v>
       </c>
       <c r="F542" s="11" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="G542" s="12">
         <v>1823</v>
@@ -50379,7 +50370,7 @@
         <v>10</v>
       </c>
       <c r="C562" s="11" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="D562" s="11" t="s">
         <v>57</v>
@@ -51393,7 +51384,7 @@
         <v>12</v>
       </c>
       <c r="C575" s="11" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="D575" s="15" t="s">
         <v>45</v>
@@ -51402,7 +51393,7 @@
         <v>26</v>
       </c>
       <c r="F575" s="11" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="G575" s="12">
         <v>1825</v>
@@ -52017,7 +52008,7 @@
         <v>6</v>
       </c>
       <c r="C583" s="11" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="D583" s="11" t="s">
         <v>45</v>
@@ -52026,7 +52017,7 @@
         <v>26</v>
       </c>
       <c r="F583" s="11" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="G583" s="12">
         <v>1828</v>
@@ -52494,7 +52485,7 @@
         <v>61</v>
       </c>
       <c r="F589" s="11" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="G589" s="12">
         <v>1828</v>
@@ -54435,7 +54426,7 @@
         <v>10</v>
       </c>
       <c r="C614" s="11" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="D614" s="15" t="s">
         <v>45</v>
@@ -54444,7 +54435,7 @@
         <v>26</v>
       </c>
       <c r="F614" s="11" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="G614" s="12">
         <v>1829</v>
@@ -57711,7 +57702,7 @@
         <v>10</v>
       </c>
       <c r="C656" s="11" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="D656" s="15" t="s">
         <v>45</v>
@@ -57720,7 +57711,7 @@
         <v>61</v>
       </c>
       <c r="F656" s="11" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="G656" s="12">
         <v>1839</v>
@@ -64652,7 +64643,7 @@
         <v>12</v>
       </c>
       <c r="C745" s="11" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="D745" s="15" t="s">
         <v>45</v>
@@ -64661,7 +64652,7 @@
         <v>61</v>
       </c>
       <c r="F745" s="11" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="G745" s="12">
         <v>1856</v>
@@ -66523,7 +66514,7 @@
         <v>6</v>
       </c>
       <c r="C769" s="11" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="D769" s="15" t="s">
         <v>45</v>
@@ -66532,7 +66523,7 @@
         <v>61</v>
       </c>
       <c r="F769" s="11" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="G769" s="12">
         <v>1866</v>
@@ -67380,7 +67371,7 @@
         <v>12</v>
       </c>
       <c r="C780" s="11" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="D780" s="15" t="s">
         <v>80</v>
@@ -67389,7 +67380,7 @@
         <v>26</v>
       </c>
       <c r="F780" s="11" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="G780" s="12">
         <v>1869</v>
@@ -71510,7 +71501,7 @@
         <v>16</v>
       </c>
       <c r="C833" s="11" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="D833" s="11" t="s">
         <v>57</v>
@@ -71519,7 +71510,7 @@
         <v>26</v>
       </c>
       <c r="F833" s="11" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="G833" s="12">
         <v>1895</v>
@@ -71744,7 +71735,7 @@
         <v>10</v>
       </c>
       <c r="C836" s="11" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="D836" s="11" t="s">
         <v>57</v>
@@ -71753,7 +71744,7 @@
         <v>61</v>
       </c>
       <c r="F836" s="11" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="G836" s="12">
         <v>1895</v>
@@ -72368,7 +72359,7 @@
         <v>14</v>
       </c>
       <c r="C844" s="11" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="D844" s="11" t="s">
         <v>57</v>
@@ -72377,7 +72368,7 @@
         <v>61</v>
       </c>
       <c r="F844" s="11" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="G844" s="12">
         <v>1898</v>
@@ -74552,7 +74543,7 @@
         <v>6</v>
       </c>
       <c r="C872" s="11" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="D872" s="15" t="s">
         <v>80</v>
@@ -74561,7 +74552,7 @@
         <v>26</v>
       </c>
       <c r="F872" s="11" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="G872" s="12">
         <v>1977</v>
@@ -75444,7 +75435,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="16" customFormat="1" ht="21.75" customHeight="1">
       <c r="A1" s="23" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -75461,7 +75452,7 @@
     </row>
     <row r="2" spans="1:13" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="16" customFormat="1" ht="27.75" customHeight="1">
@@ -75475,1409 +75466,545 @@
         <v>27</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>1742</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>1743</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>1744</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>1745</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>1746</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>1747</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>1748</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>1749</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>1750</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>1751</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>1752</v>
-      </c>
     </row>
     <row r="4" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A4" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>1300</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>1301</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E4" s="26">
-        <v>1819</v>
-      </c>
-      <c r="F4" s="26">
-        <v>1819</v>
-      </c>
-      <c r="G4" s="26">
-        <f t="shared" ref="G4:G37" si="0">IF(OR(E4="",F4=""),"",F4-E4)</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="26">
-        <v>2259</v>
-      </c>
-      <c r="I4" s="26">
-        <v>2259</v>
-      </c>
-      <c r="J4" s="26">
-        <f t="shared" ref="J4:J37" si="1">IF(OR(H4="",I4=""),"",I4-H4)</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="26">
-        <v>1869</v>
-      </c>
-      <c r="L4" s="26">
-        <v>1819</v>
-      </c>
-      <c r="M4" s="26">
-        <f t="shared" ref="M4:M37" si="2">IF(OR(K4="",L4=""),"",L4-K4)</f>
-        <v>-50</v>
-      </c>
+      <c r="A4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
     </row>
     <row r="5" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A5" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E5" s="26">
-        <v>1839</v>
-      </c>
-      <c r="F5" s="26">
-        <v>1849</v>
-      </c>
-      <c r="G5" s="26">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="H5" s="26">
-        <v>2328</v>
-      </c>
-      <c r="I5" s="26">
-        <v>2328</v>
-      </c>
-      <c r="J5" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="26">
-        <v>1829</v>
-      </c>
-      <c r="L5" s="26">
-        <v>1839</v>
-      </c>
-      <c r="M5" s="26">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+      <c r="A5" s="19"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
     </row>
     <row r="6" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A6" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>614</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>615</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E6" s="26">
-        <v>1865</v>
-      </c>
-      <c r="F6" s="26">
-        <v>1885</v>
-      </c>
-      <c r="G6" s="26">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="H6" s="26">
-        <v>2225</v>
-      </c>
-      <c r="I6" s="26">
-        <v>2225</v>
-      </c>
-      <c r="J6" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="26">
-        <v>1855</v>
-      </c>
-      <c r="L6" s="26">
-        <v>1855</v>
-      </c>
-      <c r="M6" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
     </row>
     <row r="7" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A7" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>1636</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>1637</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E7" s="26">
-        <v>1829</v>
-      </c>
-      <c r="F7" s="26">
-        <v>1819</v>
-      </c>
-      <c r="G7" s="26">
-        <f t="shared" si="0"/>
-        <v>-10</v>
-      </c>
-      <c r="H7" s="26">
-        <v>2285</v>
-      </c>
-      <c r="I7" s="26">
-        <v>2245</v>
-      </c>
-      <c r="J7" s="26">
-        <f t="shared" si="1"/>
-        <v>-40</v>
-      </c>
-      <c r="K7" s="26">
-        <v>1819</v>
-      </c>
-      <c r="L7" s="26">
-        <v>1799</v>
-      </c>
-      <c r="M7" s="26">
-        <f t="shared" si="2"/>
-        <v>-20</v>
-      </c>
+      <c r="A7" s="19"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
     </row>
     <row r="8" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A8" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>1511</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>1512</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E8" s="26">
-        <v>1834</v>
-      </c>
-      <c r="F8" s="26">
-        <v>1814</v>
-      </c>
-      <c r="G8" s="26">
-        <f t="shared" si="0"/>
-        <v>-20</v>
-      </c>
-      <c r="H8" s="26">
-        <v>2368</v>
-      </c>
-      <c r="I8" s="26">
-        <v>2368</v>
-      </c>
-      <c r="J8" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K8" s="26">
-        <v>1825</v>
-      </c>
-      <c r="L8" s="26">
-        <v>1825</v>
-      </c>
-      <c r="M8" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="A8" s="19"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
     </row>
     <row r="9" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A9" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>902</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>903</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E9" s="26">
-        <v>1859</v>
-      </c>
-      <c r="F9" s="26">
-        <v>1859</v>
-      </c>
-      <c r="G9" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A9" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
       <c r="H9" s="26"/>
       <c r="I9" s="26"/>
-      <c r="J9" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="26">
-        <v>1819</v>
-      </c>
-      <c r="L9" s="26">
-        <v>1804</v>
-      </c>
-      <c r="M9" s="26">
-        <f t="shared" si="2"/>
-        <v>-15</v>
-      </c>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
     </row>
     <row r="10" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A10" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>1599</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>1600</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E10" s="26">
-        <v>1819</v>
-      </c>
-      <c r="F10" s="26">
-        <v>1819</v>
-      </c>
-      <c r="G10" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="26"/>
       <c r="I10" s="26"/>
-      <c r="J10" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="26">
-        <v>1809</v>
-      </c>
-      <c r="L10" s="26">
-        <v>1819</v>
-      </c>
-      <c r="M10" s="26">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
     </row>
     <row r="11" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A11" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>686</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>687</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E11" s="26">
-        <v>1837</v>
-      </c>
-      <c r="F11" s="26">
-        <v>1837</v>
-      </c>
-      <c r="G11" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A11" s="19"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
-      <c r="J11" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="26">
-        <v>1808</v>
-      </c>
-      <c r="L11" s="26">
-        <v>1793</v>
-      </c>
-      <c r="M11" s="26">
-        <f t="shared" si="2"/>
-        <v>-15</v>
-      </c>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
     </row>
     <row r="12" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A12" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>482</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>483</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E12" s="26">
-        <v>1845</v>
-      </c>
-      <c r="F12" s="26">
-        <v>1845</v>
-      </c>
-      <c r="G12" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A12" s="19"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="26"/>
       <c r="I12" s="26"/>
-      <c r="J12" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="26">
-        <v>1839</v>
-      </c>
-      <c r="L12" s="26">
-        <v>1824</v>
-      </c>
-      <c r="M12" s="26">
-        <f t="shared" si="2"/>
-        <v>-15</v>
-      </c>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
     </row>
     <row r="13" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A13" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>1659</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E13" s="26">
-        <v>1899</v>
-      </c>
-      <c r="F13" s="26">
-        <v>1869</v>
-      </c>
-      <c r="G13" s="26">
-        <f t="shared" si="0"/>
-        <v>-30</v>
-      </c>
+      <c r="A13" s="19"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
       <c r="H13" s="26"/>
       <c r="I13" s="26"/>
-      <c r="J13" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="26">
-        <v>1849</v>
-      </c>
-      <c r="L13" s="26">
-        <v>1849</v>
-      </c>
-      <c r="M13" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
     </row>
     <row r="14" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A14" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>788</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>789</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E14" s="26">
-        <v>1859</v>
-      </c>
-      <c r="F14" s="26">
-        <v>2199</v>
-      </c>
-      <c r="G14" s="26">
-        <f t="shared" si="0"/>
-        <v>340</v>
-      </c>
+      <c r="A14" s="19"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
-      <c r="J14" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="26">
-        <v>1849</v>
-      </c>
-      <c r="L14" s="26">
-        <v>2199</v>
-      </c>
-      <c r="M14" s="26">
-        <f t="shared" si="2"/>
-        <v>350</v>
-      </c>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
     </row>
     <row r="15" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A15" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>863</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>864</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E15" s="26">
-        <v>1885</v>
-      </c>
-      <c r="F15" s="26">
-        <v>1885</v>
-      </c>
-      <c r="G15" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
       <c r="H15" s="26"/>
       <c r="I15" s="26"/>
-      <c r="J15" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="26">
-        <v>1875</v>
-      </c>
-      <c r="L15" s="26">
-        <v>1845</v>
-      </c>
-      <c r="M15" s="26">
-        <f t="shared" si="2"/>
-        <v>-30</v>
-      </c>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
     </row>
     <row r="16" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A16" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>1319</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E16" s="26">
-        <v>1887</v>
-      </c>
-      <c r="F16" s="26">
-        <v>1887</v>
-      </c>
-      <c r="G16" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A16" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
       <c r="H16" s="26"/>
       <c r="I16" s="26"/>
-      <c r="J16" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="26">
-        <v>1853</v>
-      </c>
-      <c r="L16" s="26">
-        <v>1868</v>
-      </c>
-      <c r="M16" s="26">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
     </row>
     <row r="17" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A17" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>908</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>909</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E17" s="26">
-        <v>1889</v>
-      </c>
-      <c r="F17" s="26">
-        <v>1889</v>
-      </c>
-      <c r="G17" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A17" s="19"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
       <c r="H17" s="26"/>
       <c r="I17" s="26"/>
-      <c r="J17" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="26">
-        <v>1889</v>
-      </c>
-      <c r="L17" s="26">
-        <v>1879</v>
-      </c>
-      <c r="M17" s="26">
-        <f t="shared" si="2"/>
-        <v>-10</v>
-      </c>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
     </row>
     <row r="18" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A18" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>828</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>829</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E18" s="26">
-        <v>1949</v>
-      </c>
-      <c r="F18" s="26">
-        <v>1949</v>
-      </c>
-      <c r="G18" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A18" s="19"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
       <c r="H18" s="26"/>
       <c r="I18" s="26"/>
-      <c r="J18" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="26">
-        <v>2039</v>
-      </c>
-      <c r="L18" s="26">
-        <v>1939</v>
-      </c>
-      <c r="M18" s="26">
-        <f t="shared" si="2"/>
-        <v>-100</v>
-      </c>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
     </row>
     <row r="19" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A19" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>569</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E19" s="26">
-        <v>1969</v>
-      </c>
+      <c r="A19" s="19"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="26"/>
       <c r="F19" s="26"/>
-      <c r="G19" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
-      <c r="J19" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="26">
-        <v>1899</v>
-      </c>
-      <c r="L19" s="26">
-        <v>1899</v>
-      </c>
-      <c r="M19" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
     </row>
     <row r="20" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A20" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E20" s="26">
-        <v>1814</v>
-      </c>
-      <c r="F20" s="26">
-        <v>1814</v>
-      </c>
-      <c r="G20" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A20" s="19"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
       <c r="H20" s="26"/>
       <c r="I20" s="26"/>
-      <c r="J20" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="26">
-        <v>1999</v>
-      </c>
-      <c r="L20" s="26">
-        <v>1794</v>
-      </c>
-      <c r="M20" s="26">
-        <f t="shared" si="2"/>
-        <v>-205</v>
-      </c>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
     </row>
     <row r="21" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A21" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>629</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>630</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E21" s="26">
-        <v>1819</v>
-      </c>
-      <c r="F21" s="26">
-        <v>1809</v>
-      </c>
-      <c r="G21" s="26">
-        <f t="shared" si="0"/>
-        <v>-10</v>
-      </c>
+      <c r="A21" s="19"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
       <c r="H21" s="26"/>
       <c r="I21" s="26"/>
-      <c r="J21" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="26">
-        <v>1789</v>
-      </c>
-      <c r="L21" s="26">
-        <v>1789</v>
-      </c>
-      <c r="M21" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="26"/>
+      <c r="M21" s="26"/>
     </row>
     <row r="22" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A22" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>386</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E22" s="26">
-        <v>1829</v>
-      </c>
-      <c r="F22" s="26">
-        <v>1819</v>
-      </c>
-      <c r="G22" s="26">
-        <f t="shared" si="0"/>
-        <v>-10</v>
-      </c>
+      <c r="A22" s="19"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
       <c r="H22" s="26"/>
       <c r="I22" s="26"/>
-      <c r="J22" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="26">
-        <v>1828</v>
-      </c>
-      <c r="L22" s="26">
-        <v>1818</v>
-      </c>
-      <c r="M22" s="26">
-        <f t="shared" si="2"/>
-        <v>-10</v>
-      </c>
+      <c r="J22" s="26"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
     </row>
     <row r="23" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A23" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E23" s="26">
-        <v>1838</v>
-      </c>
-      <c r="F23" s="26">
-        <v>1858</v>
-      </c>
-      <c r="G23" s="26">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
+      <c r="A23" s="19"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
       <c r="H23" s="26"/>
       <c r="I23" s="26"/>
-      <c r="J23" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="26">
-        <v>1818</v>
-      </c>
-      <c r="L23" s="26">
-        <v>1838</v>
-      </c>
-      <c r="M23" s="26">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
     </row>
     <row r="24" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A24" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>1203</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>1204</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E24" s="26">
-        <v>1839</v>
-      </c>
-      <c r="F24" s="26">
-        <v>1829</v>
-      </c>
-      <c r="G24" s="26">
-        <f t="shared" si="0"/>
-        <v>-10</v>
-      </c>
+      <c r="A24" s="19"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
       <c r="H24" s="26"/>
       <c r="I24" s="26"/>
-      <c r="J24" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="26">
-        <v>1828</v>
-      </c>
-      <c r="L24" s="26">
-        <v>1818</v>
-      </c>
-      <c r="M24" s="26">
-        <f t="shared" si="2"/>
-        <v>-10</v>
-      </c>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
     </row>
     <row r="25" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A25" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E25" s="26">
-        <v>1842</v>
-      </c>
-      <c r="F25" s="26">
-        <v>1822</v>
-      </c>
-      <c r="G25" s="26">
-        <f t="shared" si="0"/>
-        <v>-20</v>
-      </c>
+      <c r="A25" s="19"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
       <c r="H25" s="26"/>
       <c r="I25" s="26"/>
-      <c r="J25" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="26">
-        <v>1832</v>
-      </c>
-      <c r="L25" s="26">
-        <v>1802</v>
-      </c>
-      <c r="M25" s="26">
-        <f t="shared" si="2"/>
-        <v>-30</v>
-      </c>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="26"/>
     </row>
     <row r="26" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A26" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E26" s="26">
-        <v>1842</v>
-      </c>
-      <c r="F26" s="26">
-        <v>1824</v>
-      </c>
-      <c r="G26" s="26">
-        <f t="shared" si="0"/>
-        <v>-18</v>
-      </c>
+      <c r="A26" s="19"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
       <c r="H26" s="26"/>
       <c r="I26" s="26"/>
-      <c r="J26" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="26">
-        <v>1842</v>
-      </c>
-      <c r="L26" s="26">
-        <v>1824</v>
-      </c>
-      <c r="M26" s="26">
-        <f t="shared" si="2"/>
-        <v>-18</v>
-      </c>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
     </row>
     <row r="27" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A27" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>739</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>740</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E27" s="26">
-        <v>1843</v>
-      </c>
-      <c r="F27" s="26">
-        <v>1843</v>
-      </c>
-      <c r="G27" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A27" s="19"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
       <c r="H27" s="26"/>
       <c r="I27" s="26"/>
-      <c r="J27" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="26">
-        <v>1828</v>
-      </c>
-      <c r="L27" s="26">
-        <v>1823</v>
-      </c>
-      <c r="M27" s="26">
-        <f t="shared" si="2"/>
-        <v>-5</v>
-      </c>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
     </row>
     <row r="28" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A28" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>1207</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>1208</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E28" s="26">
-        <v>1844</v>
-      </c>
-      <c r="F28" s="26">
-        <v>1842</v>
-      </c>
-      <c r="G28" s="26">
-        <f t="shared" si="0"/>
-        <v>-2</v>
-      </c>
+      <c r="A28" s="19"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
       <c r="H28" s="26"/>
       <c r="I28" s="26"/>
-      <c r="J28" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="26">
-        <v>1815</v>
-      </c>
-      <c r="L28" s="26">
-        <v>1825</v>
-      </c>
-      <c r="M28" s="26">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
     </row>
     <row r="29" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A29" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>772</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>773</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E29" s="26">
-        <v>1845</v>
-      </c>
-      <c r="F29" s="26">
-        <v>1825</v>
-      </c>
-      <c r="G29" s="26">
-        <f t="shared" si="0"/>
-        <v>-20</v>
-      </c>
+      <c r="A29" s="19"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
       <c r="H29" s="26"/>
       <c r="I29" s="26"/>
-      <c r="J29" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="26">
-        <v>1815</v>
-      </c>
-      <c r="L29" s="26">
-        <v>1799</v>
-      </c>
-      <c r="M29" s="26">
-        <f t="shared" si="2"/>
-        <v>-16</v>
-      </c>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
     </row>
     <row r="30" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A30" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>459</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>460</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E30" s="26">
-        <v>1870</v>
-      </c>
-      <c r="F30" s="26">
-        <v>1870</v>
-      </c>
-      <c r="G30" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A30" s="19"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="26"/>
       <c r="I30" s="26"/>
-      <c r="J30" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="26">
-        <v>1900</v>
-      </c>
-      <c r="L30" s="26">
-        <v>1860</v>
-      </c>
-      <c r="M30" s="26">
-        <f t="shared" si="2"/>
-        <v>-40</v>
-      </c>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
     </row>
     <row r="31" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A31" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>876</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>877</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E31" s="26">
-        <v>1875</v>
-      </c>
-      <c r="F31" s="26">
-        <v>1855</v>
-      </c>
-      <c r="G31" s="26">
-        <f t="shared" si="0"/>
-        <v>-20</v>
-      </c>
+      <c r="A31" s="19"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
       <c r="H31" s="26"/>
       <c r="I31" s="26"/>
-      <c r="J31" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="26">
-        <v>1825</v>
-      </c>
-      <c r="L31" s="26">
-        <v>1825</v>
-      </c>
-      <c r="M31" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
     </row>
     <row r="32" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A32" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>1660</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>1661</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E32" s="26">
-        <v>1889</v>
-      </c>
-      <c r="F32" s="26">
-        <v>1889</v>
-      </c>
-      <c r="G32" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A32" s="19"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="26"/>
       <c r="I32" s="26"/>
-      <c r="J32" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="26">
-        <v>1824</v>
-      </c>
-      <c r="L32" s="26">
-        <v>1869</v>
-      </c>
-      <c r="M32" s="26">
-        <f t="shared" si="2"/>
-        <v>45</v>
-      </c>
+      <c r="J32" s="26"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
     </row>
     <row r="33" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A33" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>649</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>650</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E33" s="26">
-        <v>1889</v>
-      </c>
-      <c r="F33" s="26">
-        <v>1889</v>
-      </c>
-      <c r="G33" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A33" s="19"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
       <c r="H33" s="26"/>
       <c r="I33" s="26"/>
-      <c r="J33" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="26">
-        <v>1879</v>
-      </c>
-      <c r="L33" s="26">
-        <v>1859</v>
-      </c>
-      <c r="M33" s="26">
-        <f t="shared" si="2"/>
-        <v>-20</v>
-      </c>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
     </row>
     <row r="34" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A34" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>1162</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E34" s="26">
-        <v>1895</v>
-      </c>
-      <c r="F34" s="26">
-        <v>1885</v>
-      </c>
-      <c r="G34" s="26">
-        <f t="shared" si="0"/>
-        <v>-10</v>
-      </c>
+      <c r="A34" s="19"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="26"/>
       <c r="I34" s="26"/>
-      <c r="J34" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="26">
-        <v>1875</v>
-      </c>
-      <c r="L34" s="26">
-        <v>1875</v>
-      </c>
-      <c r="M34" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J34" s="26"/>
+      <c r="K34" s="26"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
     </row>
     <row r="35" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A35" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B35" s="20" t="s">
-        <v>1125</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E35" s="26">
-        <v>1909</v>
-      </c>
-      <c r="F35" s="26">
-        <v>1909</v>
-      </c>
-      <c r="G35" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A35" s="19"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
       <c r="H35" s="26"/>
       <c r="I35" s="26"/>
-      <c r="J35" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="26">
-        <v>1899</v>
-      </c>
-      <c r="L35" s="26">
-        <v>1860</v>
-      </c>
-      <c r="M35" s="26">
-        <f t="shared" si="2"/>
-        <v>-39</v>
-      </c>
+      <c r="J35" s="26"/>
+      <c r="K35" s="26"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="26"/>
     </row>
     <row r="36" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A36" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>1117</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>1118</v>
-      </c>
-      <c r="D36" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E36" s="26">
-        <v>1949</v>
-      </c>
-      <c r="F36" s="26">
-        <v>1899</v>
-      </c>
-      <c r="G36" s="26">
-        <f t="shared" si="0"/>
-        <v>-50</v>
-      </c>
+      <c r="A36" s="19"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
       <c r="H36" s="26"/>
       <c r="I36" s="26"/>
-      <c r="J36" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="26">
-        <v>1929</v>
-      </c>
-      <c r="L36" s="26">
-        <v>1929</v>
-      </c>
-      <c r="M36" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J36" s="26"/>
+      <c r="K36" s="26"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="26"/>
     </row>
     <row r="37" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A37" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>1678</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>1680</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>1766</v>
-      </c>
-      <c r="E37" s="26">
-        <v>1824</v>
-      </c>
+      <c r="A37" s="19"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="26"/>
       <c r="F37" s="26"/>
-      <c r="G37" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="G37" s="26"/>
       <c r="H37" s="26"/>
       <c r="I37" s="26"/>
-      <c r="J37" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="26">
-        <v>1813</v>
-      </c>
+      <c r="J37" s="26"/>
+      <c r="K37" s="26"/>
       <c r="L37" s="26"/>
-      <c r="M37" s="26" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="M37" s="26"/>
     </row>
     <row r="38" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
       <c r="A38" s="19"/>
@@ -79974,7 +79101,7 @@
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
-  <conditionalFormatting sqref="G4:G37">
+  <conditionalFormatting sqref="G4">
     <cfRule type="cellIs" dxfId="5" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -79982,7 +79109,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J37">
+  <conditionalFormatting sqref="J4">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -79990,7 +79117,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M37">
+  <conditionalFormatting sqref="M4">
     <cfRule type="cellIs" dxfId="1" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>

--- a/fuel_cost_chungcheong.xlsx
+++ b/fuel_cost_chungcheong.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5102" uniqueCount="1766">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4706" uniqueCount="1766">
   <si>
     <t>유류비 계산(혼유, 지역화폐 등)</t>
   </si>
@@ -57631,19 +57631,19 @@
         <v/>
       </c>
       <c r="B655" s="11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C655" s="11" t="s">
-        <v>1077</v>
-      </c>
-      <c r="D655" s="11" t="s">
-        <v>71</v>
+        <v>1193</v>
+      </c>
+      <c r="D655" s="15" t="s">
+        <v>80</v>
       </c>
       <c r="E655" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F655" s="11" t="s">
-        <v>1078</v>
+        <v>1194</v>
       </c>
       <c r="G655" s="12">
         <v>1838</v>
@@ -57651,7 +57651,7 @@
       <c r="H655" s="12"/>
       <c r="I655" s="12"/>
       <c r="J655" s="12">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="K655" s="12">
         <f t="shared" ref="K655:K718" si="131">IF(AND(IFERROR(SEARCH("현대오일뱅크",$C655),0)&gt;0,IFERROR(SEARCH("직영",$C655),0)&gt;0),$B$13,0)</f>
@@ -57667,7 +57667,7 @@
       </c>
       <c r="N655" s="12">
         <f t="shared" ref="N655:N718" si="134">IF($J655="","",$J655+$K655)</f>
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="O655" s="12" t="str">
         <f t="shared" ref="O655:O718" si="135">IF($B$10=0,"",IFERROR(IF($B$4&gt;0,"휘발유 "&amp;TEXT(IF($L655="",1/0,$L655*$B$4),"#,##0")&amp;"원","")&amp;IF($B$5&gt;0,IF($B$4&gt;0," / ","")&amp;"고급유 "&amp;TEXT(IF($M655="",1/0,$M655*$B$5),"#,##0")&amp;"원","")&amp;IF($B$6&gt;0,IF(OR($B$4&gt;0,$B$5&gt;0)," / ","")&amp;"경유 "&amp;TEXT(IF($N655="",1/0,$N655*$B$6),"#,##0")&amp;"원",""),""))</f>
@@ -57709,19 +57709,19 @@
         <v/>
       </c>
       <c r="B656" s="11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C656" s="11" t="s">
-        <v>1193</v>
-      </c>
-      <c r="D656" s="15" t="s">
-        <v>80</v>
+        <v>1077</v>
+      </c>
+      <c r="D656" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="E656" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F656" s="11" t="s">
-        <v>1194</v>
+        <v>1078</v>
       </c>
       <c r="G656" s="12">
         <v>1838</v>
@@ -57729,7 +57729,7 @@
       <c r="H656" s="12"/>
       <c r="I656" s="12"/>
       <c r="J656" s="12">
-        <v>1848</v>
+        <v>1819</v>
       </c>
       <c r="K656" s="12">
         <f t="shared" si="131"/>
@@ -57745,7 +57745,7 @@
       </c>
       <c r="N656" s="12">
         <f t="shared" si="134"/>
-        <v>1848</v>
+        <v>1819</v>
       </c>
       <c r="O656" s="12" t="str">
         <f t="shared" si="135"/>
@@ -75586,4107 +75586,1528 @@
     </row>
     <row r="4" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
       <c r="A4" s="19" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>725</v>
+        <v>1193</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>726</v>
+        <v>1194</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>1763</v>
       </c>
       <c r="E4" s="26">
-        <v>1833</v>
+        <v>1838</v>
       </c>
       <c r="F4" s="26">
-        <v>1833</v>
+        <v>1838</v>
       </c>
       <c r="G4" s="26">
-        <f t="shared" ref="G4:G67" si="0">IF(OR(E4="",F4=""),"",F4-E4)</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="26">
-        <v>2294</v>
-      </c>
-      <c r="I4" s="26">
-        <v>2278</v>
-      </c>
-      <c r="J4" s="26">
-        <f t="shared" ref="J4:J67" si="1">IF(OR(H4="",I4=""),"",I4-H4)</f>
-        <v>-16</v>
+        <f>IF(OR(E4="",F4=""),"",F4-E4)</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26" t="str">
+        <f>IF(OR(H4="",I4=""),"",I4-H4)</f>
+        <v/>
       </c>
       <c r="K4" s="26">
-        <v>1813</v>
+        <v>1848</v>
       </c>
       <c r="L4" s="26">
-        <v>1813</v>
+        <v>1818</v>
       </c>
       <c r="M4" s="26">
-        <f t="shared" ref="M4:M67" si="2">IF(OR(K4="",L4=""),"",L4-K4)</f>
-        <v>0</v>
+        <f>IF(OR(K4="",L4=""),"",L4-K4)</f>
+        <v>-30</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A5" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E5" s="26">
-        <v>1849</v>
-      </c>
-      <c r="F5" s="26">
-        <v>1839</v>
-      </c>
-      <c r="G5" s="26">
-        <f t="shared" si="0"/>
-        <v>-10</v>
-      </c>
-      <c r="H5" s="26">
-        <v>2328</v>
-      </c>
-      <c r="I5" s="26">
-        <v>2308</v>
-      </c>
-      <c r="J5" s="26">
-        <f t="shared" si="1"/>
-        <v>-20</v>
-      </c>
-      <c r="K5" s="26">
-        <v>1839</v>
-      </c>
-      <c r="L5" s="26">
-        <v>1829</v>
-      </c>
-      <c r="M5" s="26">
-        <f t="shared" si="2"/>
-        <v>-10</v>
-      </c>
+      <c r="A5" s="19"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
     </row>
     <row r="6" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A6" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>586</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>587</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E6" s="26">
-        <v>1810</v>
-      </c>
-      <c r="F6" s="26">
-        <v>1810</v>
-      </c>
-      <c r="G6" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="26">
-        <v>2235</v>
-      </c>
-      <c r="I6" s="26">
-        <v>2235</v>
-      </c>
-      <c r="J6" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="26">
-        <v>1809</v>
-      </c>
-      <c r="L6" s="26">
-        <v>1799</v>
-      </c>
-      <c r="M6" s="26">
-        <f t="shared" si="2"/>
-        <v>-10</v>
-      </c>
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
     </row>
     <row r="7" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A7" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>1175</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>1176</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E7" s="26">
-        <v>1860</v>
-      </c>
-      <c r="F7" s="26">
-        <v>1850</v>
-      </c>
-      <c r="G7" s="26">
-        <f t="shared" si="0"/>
-        <v>-10</v>
-      </c>
-      <c r="H7" s="26">
-        <v>2190</v>
-      </c>
-      <c r="I7" s="26">
-        <v>2190</v>
-      </c>
-      <c r="J7" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K7" s="26">
-        <v>1819</v>
-      </c>
-      <c r="L7" s="26">
-        <v>1810</v>
-      </c>
-      <c r="M7" s="26">
-        <f t="shared" si="2"/>
-        <v>-9</v>
-      </c>
+      <c r="A7" s="19"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
     </row>
     <row r="8" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A8" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>392</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E8" s="26">
-        <v>1832</v>
-      </c>
-      <c r="F8" s="26">
-        <v>1832</v>
-      </c>
-      <c r="G8" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="26">
-        <v>2249</v>
-      </c>
-      <c r="I8" s="26">
-        <v>2249</v>
-      </c>
-      <c r="J8" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K8" s="26">
-        <v>1812</v>
-      </c>
-      <c r="L8" s="26">
-        <v>1822</v>
-      </c>
-      <c r="M8" s="26">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+      <c r="A8" s="19"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
     </row>
     <row r="9" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A9" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>747</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>748</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E9" s="26">
-        <v>1829</v>
-      </c>
-      <c r="F9" s="26">
-        <v>1829</v>
-      </c>
-      <c r="G9" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="26">
-        <v>2259</v>
-      </c>
-      <c r="I9" s="26">
-        <v>2219</v>
-      </c>
-      <c r="J9" s="26">
-        <f t="shared" si="1"/>
-        <v>-40</v>
-      </c>
-      <c r="K9" s="26">
-        <v>1809</v>
-      </c>
-      <c r="L9" s="26">
-        <v>1809</v>
-      </c>
-      <c r="M9" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="A9" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
     </row>
     <row r="10" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A10" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>264</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E10" s="26">
-        <v>1858</v>
-      </c>
-      <c r="F10" s="26">
-        <v>1858</v>
-      </c>
-      <c r="G10" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="26">
-        <v>2229</v>
-      </c>
-      <c r="I10" s="26">
-        <v>2229</v>
-      </c>
-      <c r="J10" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="26">
-        <v>1808</v>
-      </c>
-      <c r="L10" s="26">
-        <v>1819</v>
-      </c>
-      <c r="M10" s="26">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
+      <c r="A10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
     </row>
     <row r="11" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A11" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>253</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E11" s="26">
-        <v>1858</v>
-      </c>
-      <c r="F11" s="26">
-        <v>1858</v>
-      </c>
-      <c r="G11" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="26">
-        <v>2229</v>
-      </c>
-      <c r="I11" s="26">
-        <v>2229</v>
-      </c>
-      <c r="J11" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="26">
-        <v>1809</v>
-      </c>
-      <c r="L11" s="26">
-        <v>1819</v>
-      </c>
-      <c r="M11" s="26">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+      <c r="A11" s="19"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
     </row>
     <row r="12" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A12" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>324</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E12" s="26">
-        <v>1825</v>
-      </c>
-      <c r="F12" s="26">
-        <v>1815</v>
-      </c>
-      <c r="G12" s="26">
-        <f t="shared" si="0"/>
-        <v>-10</v>
-      </c>
-      <c r="H12" s="26">
-        <v>2278</v>
-      </c>
-      <c r="I12" s="26">
-        <v>2248</v>
-      </c>
-      <c r="J12" s="26">
-        <f t="shared" si="1"/>
-        <v>-30</v>
-      </c>
-      <c r="K12" s="26">
-        <v>1809</v>
-      </c>
-      <c r="L12" s="26">
-        <v>1809</v>
-      </c>
-      <c r="M12" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="A12" s="19"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
     </row>
     <row r="13" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A13" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>269</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E13" s="26">
-        <v>1868</v>
-      </c>
-      <c r="F13" s="26">
-        <v>1868</v>
-      </c>
-      <c r="G13" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="26">
-        <v>2229</v>
-      </c>
-      <c r="I13" s="26">
-        <v>2229</v>
-      </c>
-      <c r="J13" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="26">
-        <v>1809</v>
-      </c>
-      <c r="L13" s="26">
-        <v>1819</v>
-      </c>
-      <c r="M13" s="26">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+      <c r="A13" s="19"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
     </row>
     <row r="14" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A14" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>1575</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>1576</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E14" s="26">
-        <v>1829</v>
-      </c>
-      <c r="F14" s="26">
-        <v>1829</v>
-      </c>
-      <c r="G14" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="26">
-        <v>2280</v>
-      </c>
-      <c r="I14" s="26">
-        <v>2270</v>
-      </c>
-      <c r="J14" s="26">
-        <f t="shared" si="1"/>
-        <v>-10</v>
-      </c>
-      <c r="K14" s="26">
-        <v>1829</v>
-      </c>
-      <c r="L14" s="26">
-        <v>1815</v>
-      </c>
-      <c r="M14" s="26">
-        <f t="shared" si="2"/>
-        <v>-14</v>
-      </c>
+      <c r="A14" s="19"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
     </row>
     <row r="15" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A15" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>464</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>465</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E15" s="26">
-        <v>1835</v>
-      </c>
-      <c r="F15" s="26">
-        <v>1835</v>
-      </c>
-      <c r="G15" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="26">
-        <v>2275</v>
-      </c>
-      <c r="I15" s="26">
-        <v>2285</v>
-      </c>
-      <c r="J15" s="26">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="K15" s="26">
-        <v>1832</v>
-      </c>
-      <c r="L15" s="26">
-        <v>1832</v>
-      </c>
-      <c r="M15" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="A15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
     </row>
     <row r="16" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A16" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>1415</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>1416</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E16" s="26">
-        <v>1839</v>
-      </c>
-      <c r="F16" s="26">
-        <v>1839</v>
-      </c>
-      <c r="G16" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="26">
-        <v>2275</v>
-      </c>
-      <c r="I16" s="26">
-        <v>2285</v>
-      </c>
-      <c r="J16" s="26">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="K16" s="26">
-        <v>1829</v>
-      </c>
-      <c r="L16" s="26">
-        <v>1840</v>
-      </c>
-      <c r="M16" s="26">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
+      <c r="A16" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
     </row>
     <row r="17" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A17" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E17" s="26">
-        <v>1836</v>
-      </c>
-      <c r="F17" s="26">
-        <v>1836</v>
-      </c>
-      <c r="G17" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="26">
-        <v>2287</v>
-      </c>
-      <c r="I17" s="26">
-        <v>2257</v>
-      </c>
-      <c r="J17" s="26">
-        <f t="shared" si="1"/>
-        <v>-30</v>
-      </c>
-      <c r="K17" s="26">
-        <v>1799</v>
-      </c>
-      <c r="L17" s="26">
-        <v>1799</v>
-      </c>
-      <c r="M17" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="A17" s="19"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
     </row>
     <row r="18" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A18" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E18" s="26">
-        <v>1878</v>
-      </c>
-      <c r="F18" s="26">
-        <v>1878</v>
-      </c>
-      <c r="G18" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H18" s="26">
-        <v>2239</v>
-      </c>
-      <c r="I18" s="26">
-        <v>2239</v>
-      </c>
-      <c r="J18" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="26">
-        <v>1819</v>
-      </c>
-      <c r="L18" s="26">
-        <v>1829</v>
-      </c>
-      <c r="M18" s="26">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+      <c r="A18" s="19"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
     </row>
     <row r="19" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A19" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>258</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E19" s="26">
-        <v>1855</v>
-      </c>
-      <c r="F19" s="26">
-        <v>1855</v>
-      </c>
-      <c r="G19" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="26">
-        <v>2278</v>
-      </c>
-      <c r="I19" s="26">
-        <v>2269</v>
-      </c>
-      <c r="J19" s="26">
-        <f t="shared" si="1"/>
-        <v>-9</v>
-      </c>
-      <c r="K19" s="26">
-        <v>1815</v>
-      </c>
-      <c r="L19" s="26">
-        <v>1819</v>
-      </c>
-      <c r="M19" s="26">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
+      <c r="A19" s="19"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
     </row>
     <row r="20" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A20" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>267</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E20" s="26">
-        <v>1887</v>
-      </c>
-      <c r="F20" s="26">
-        <v>1887</v>
-      </c>
-      <c r="G20" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="26">
-        <v>2239</v>
-      </c>
-      <c r="I20" s="26">
-        <v>2239</v>
-      </c>
-      <c r="J20" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="26">
-        <v>1823</v>
-      </c>
-      <c r="L20" s="26">
-        <v>1839</v>
-      </c>
-      <c r="M20" s="26">
-        <f t="shared" si="2"/>
-        <v>16</v>
-      </c>
+      <c r="A20" s="19"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
     </row>
     <row r="21" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A21" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>1413</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>1414</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E21" s="26">
-        <v>1825</v>
-      </c>
-      <c r="F21" s="26">
-        <v>1835</v>
-      </c>
-      <c r="G21" s="26">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="H21" s="26">
-        <v>2320</v>
-      </c>
-      <c r="I21" s="26">
-        <v>2320</v>
-      </c>
-      <c r="J21" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="26">
-        <v>1815</v>
-      </c>
-      <c r="L21" s="26">
-        <v>1825</v>
-      </c>
-      <c r="M21" s="26">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+      <c r="A21" s="19"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="26"/>
+      <c r="M21" s="26"/>
     </row>
     <row r="22" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A22" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>1403</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>1404</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E22" s="26">
-        <v>1830</v>
-      </c>
-      <c r="F22" s="26">
-        <v>1840</v>
-      </c>
-      <c r="G22" s="26">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="H22" s="26">
-        <v>2320</v>
-      </c>
-      <c r="I22" s="26">
-        <v>2320</v>
-      </c>
-      <c r="J22" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="26">
-        <v>1819</v>
-      </c>
-      <c r="L22" s="26">
-        <v>1830</v>
-      </c>
-      <c r="M22" s="26">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
+      <c r="A22" s="19"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="26"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
     </row>
     <row r="23" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A23" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>936</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>937</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E23" s="26">
-        <v>1859</v>
-      </c>
-      <c r="F23" s="26">
-        <v>1859</v>
-      </c>
-      <c r="G23" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="26">
-        <v>2288</v>
-      </c>
-      <c r="I23" s="26">
-        <v>2288</v>
-      </c>
-      <c r="J23" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="26">
-        <v>1839</v>
-      </c>
-      <c r="L23" s="26">
-        <v>1849</v>
-      </c>
-      <c r="M23" s="26">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+      <c r="A23" s="19"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
     </row>
     <row r="24" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A24" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>1444</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>1445</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E24" s="26">
-        <v>1865</v>
-      </c>
-      <c r="F24" s="26">
-        <v>1865</v>
-      </c>
-      <c r="G24" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H24" s="26">
-        <v>2292</v>
-      </c>
-      <c r="I24" s="26">
-        <v>2252</v>
-      </c>
-      <c r="J24" s="26">
-        <f t="shared" si="1"/>
-        <v>-40</v>
-      </c>
-      <c r="K24" s="26">
-        <v>1849</v>
-      </c>
-      <c r="L24" s="26">
-        <v>1849</v>
-      </c>
-      <c r="M24" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="A24" s="19"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
     </row>
     <row r="25" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A25" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>1511</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>1512</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E25" s="26">
-        <v>1814</v>
-      </c>
-      <c r="F25" s="26">
-        <v>1834</v>
-      </c>
-      <c r="G25" s="26">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="H25" s="26">
-        <v>2368</v>
-      </c>
-      <c r="I25" s="26">
-        <v>2368</v>
-      </c>
-      <c r="J25" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="26">
-        <v>1825</v>
-      </c>
-      <c r="L25" s="26">
-        <v>1825</v>
-      </c>
-      <c r="M25" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="A25" s="19"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="26"/>
     </row>
     <row r="26" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A26" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E26" s="26">
-        <v>1815</v>
-      </c>
-      <c r="F26" s="26">
-        <v>1815</v>
-      </c>
-      <c r="G26" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="26">
-        <v>2369</v>
-      </c>
-      <c r="I26" s="26">
-        <v>2339</v>
-      </c>
-      <c r="J26" s="26">
-        <f t="shared" si="1"/>
-        <v>-30</v>
-      </c>
-      <c r="K26" s="26">
-        <v>1798</v>
-      </c>
-      <c r="L26" s="26">
-        <v>1798</v>
-      </c>
-      <c r="M26" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="A26" s="19"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
     </row>
     <row r="27" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A27" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E27" s="26">
-        <v>1815</v>
-      </c>
-      <c r="F27" s="26">
-        <v>1815</v>
-      </c>
-      <c r="G27" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H27" s="26">
-        <v>2369</v>
-      </c>
-      <c r="I27" s="26">
-        <v>2339</v>
-      </c>
-      <c r="J27" s="26">
-        <f t="shared" si="1"/>
-        <v>-30</v>
-      </c>
-      <c r="K27" s="26">
-        <v>1799</v>
-      </c>
-      <c r="L27" s="26">
-        <v>1809</v>
-      </c>
-      <c r="M27" s="26">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+      <c r="A27" s="19"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
     </row>
     <row r="28" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A28" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>730</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>731</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E28" s="26">
-        <v>1832</v>
-      </c>
-      <c r="F28" s="26">
-        <v>1835</v>
-      </c>
-      <c r="G28" s="26">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="H28" s="26">
-        <v>2368</v>
-      </c>
-      <c r="I28" s="26">
-        <v>2368</v>
-      </c>
-      <c r="J28" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K28" s="26">
-        <v>1823</v>
-      </c>
-      <c r="L28" s="26">
-        <v>1828</v>
-      </c>
-      <c r="M28" s="26">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
+      <c r="A28" s="19"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
     </row>
     <row r="29" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A29" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E29" s="26">
-        <v>1835</v>
-      </c>
-      <c r="F29" s="26">
-        <v>1795</v>
-      </c>
-      <c r="G29" s="26">
-        <f t="shared" si="0"/>
-        <v>-40</v>
-      </c>
-      <c r="H29" s="26">
-        <v>2495</v>
-      </c>
-      <c r="I29" s="26">
-        <v>2495</v>
-      </c>
-      <c r="J29" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="26">
-        <v>1825</v>
-      </c>
-      <c r="L29" s="26">
-        <v>1795</v>
-      </c>
-      <c r="M29" s="26">
-        <f t="shared" si="2"/>
-        <v>-30</v>
-      </c>
+      <c r="A29" s="19"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
     </row>
     <row r="30" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A30" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>627</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>628</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E30" s="26">
-        <v>1844</v>
-      </c>
-      <c r="F30" s="26">
-        <v>1844</v>
-      </c>
-      <c r="G30" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A30" s="19"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="26"/>
       <c r="I30" s="26"/>
-      <c r="J30" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="26">
-        <v>1794</v>
-      </c>
-      <c r="L30" s="26">
-        <v>1814</v>
-      </c>
-      <c r="M30" s="26">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
     </row>
     <row r="31" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A31" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>480</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>481</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E31" s="26">
-        <v>1847</v>
-      </c>
-      <c r="F31" s="26">
-        <v>1847</v>
-      </c>
-      <c r="G31" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A31" s="19"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
       <c r="H31" s="26"/>
       <c r="I31" s="26"/>
-      <c r="J31" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="26">
-        <v>1837</v>
-      </c>
-      <c r="L31" s="26">
-        <v>1817</v>
-      </c>
-      <c r="M31" s="26">
-        <f t="shared" si="2"/>
-        <v>-20</v>
-      </c>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
     </row>
     <row r="32" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A32" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>1638</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>1639</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E32" s="26">
-        <v>1807</v>
-      </c>
-      <c r="F32" s="26">
-        <v>1807</v>
-      </c>
-      <c r="G32" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A32" s="19"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="26"/>
       <c r="I32" s="26"/>
-      <c r="J32" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="26">
-        <v>1793</v>
-      </c>
-      <c r="L32" s="26">
-        <v>1787</v>
-      </c>
-      <c r="M32" s="26">
-        <f t="shared" si="2"/>
-        <v>-6</v>
-      </c>
+      <c r="J32" s="26"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
     </row>
     <row r="33" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A33" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>417</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>418</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E33" s="26">
-        <v>1852</v>
-      </c>
-      <c r="F33" s="26">
-        <v>1852</v>
-      </c>
-      <c r="G33" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A33" s="19"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
       <c r="H33" s="26"/>
       <c r="I33" s="26"/>
-      <c r="J33" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="26">
-        <v>1812</v>
-      </c>
-      <c r="L33" s="26">
-        <v>1822</v>
-      </c>
-      <c r="M33" s="26">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
     </row>
     <row r="34" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A34" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>1486</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>1487</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E34" s="26">
-        <v>1855</v>
-      </c>
-      <c r="F34" s="26">
-        <v>1855</v>
-      </c>
-      <c r="G34" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A34" s="19"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="26"/>
       <c r="I34" s="26"/>
-      <c r="J34" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="26">
-        <v>1835</v>
-      </c>
-      <c r="L34" s="26">
-        <v>1820</v>
-      </c>
-      <c r="M34" s="26">
-        <f t="shared" si="2"/>
-        <v>-15</v>
-      </c>
+      <c r="J34" s="26"/>
+      <c r="K34" s="26"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
     </row>
     <row r="35" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A35" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B35" s="20" t="s">
-        <v>886</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>887</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E35" s="26">
-        <v>1859</v>
-      </c>
-      <c r="F35" s="26">
-        <v>1859</v>
-      </c>
-      <c r="G35" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A35" s="19"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
       <c r="H35" s="26"/>
       <c r="I35" s="26"/>
-      <c r="J35" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="26">
-        <v>1869</v>
-      </c>
-      <c r="L35" s="26">
-        <v>1849</v>
-      </c>
-      <c r="M35" s="26">
-        <f t="shared" si="2"/>
-        <v>-20</v>
-      </c>
+      <c r="J35" s="26"/>
+      <c r="K35" s="26"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="26"/>
     </row>
     <row r="36" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A36" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>362</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>363</v>
-      </c>
-      <c r="D36" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E36" s="26">
-        <v>1819</v>
-      </c>
-      <c r="F36" s="26">
-        <v>1819</v>
-      </c>
-      <c r="G36" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A36" s="19"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
       <c r="H36" s="26"/>
       <c r="I36" s="26"/>
-      <c r="J36" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="26">
-        <v>1799</v>
-      </c>
-      <c r="L36" s="26">
-        <v>1793</v>
-      </c>
-      <c r="M36" s="26">
-        <f t="shared" si="2"/>
-        <v>-6</v>
-      </c>
+      <c r="J36" s="26"/>
+      <c r="K36" s="26"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="26"/>
     </row>
     <row r="37" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A37" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>1599</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>1600</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E37" s="26">
-        <v>1819</v>
-      </c>
-      <c r="F37" s="26">
-        <v>1819</v>
-      </c>
-      <c r="G37" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A37" s="19"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
       <c r="H37" s="26"/>
       <c r="I37" s="26"/>
-      <c r="J37" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="26">
-        <v>1819</v>
-      </c>
-      <c r="L37" s="26">
-        <v>1809</v>
-      </c>
-      <c r="M37" s="26">
-        <f t="shared" si="2"/>
-        <v>-10</v>
-      </c>
+      <c r="J37" s="26"/>
+      <c r="K37" s="26"/>
+      <c r="L37" s="26"/>
+      <c r="M37" s="26"/>
     </row>
     <row r="38" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A38" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>982</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>983</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E38" s="26">
-        <v>1867</v>
-      </c>
-      <c r="F38" s="26">
-        <v>1857</v>
-      </c>
-      <c r="G38" s="26">
-        <f t="shared" si="0"/>
-        <v>-10</v>
-      </c>
+      <c r="A38" s="19"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
       <c r="H38" s="26"/>
       <c r="I38" s="26"/>
-      <c r="J38" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="26">
-        <v>1827</v>
-      </c>
-      <c r="L38" s="26">
-        <v>1827</v>
-      </c>
-      <c r="M38" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J38" s="26"/>
+      <c r="K38" s="26"/>
+      <c r="L38" s="26"/>
+      <c r="M38" s="26"/>
     </row>
     <row r="39" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A39" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>1171</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E39" s="26">
-        <v>1827</v>
-      </c>
-      <c r="F39" s="26">
-        <v>1817</v>
-      </c>
-      <c r="G39" s="26">
-        <f t="shared" si="0"/>
-        <v>-10</v>
-      </c>
+      <c r="A39" s="19"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
       <c r="H39" s="26"/>
       <c r="I39" s="26"/>
-      <c r="J39" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="26">
-        <v>1797</v>
-      </c>
-      <c r="L39" s="26">
-        <v>1817</v>
-      </c>
-      <c r="M39" s="26">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
+      <c r="J39" s="26"/>
+      <c r="K39" s="26"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="26"/>
     </row>
     <row r="40" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A40" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C40" s="20" t="s">
-        <v>1370</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E40" s="26">
-        <v>1870</v>
-      </c>
-      <c r="F40" s="26">
-        <v>1870</v>
-      </c>
-      <c r="G40" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A40" s="19"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
       <c r="H40" s="26"/>
       <c r="I40" s="26"/>
-      <c r="J40" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="26">
-        <v>1840</v>
-      </c>
-      <c r="L40" s="26">
-        <v>1820</v>
-      </c>
-      <c r="M40" s="26">
-        <f t="shared" si="2"/>
-        <v>-20</v>
-      </c>
+      <c r="J40" s="26"/>
+      <c r="K40" s="26"/>
+      <c r="L40" s="26"/>
+      <c r="M40" s="26"/>
     </row>
     <row r="41" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A41" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" s="20" t="s">
-        <v>637</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>638</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E41" s="26">
-        <v>1834</v>
-      </c>
-      <c r="F41" s="26">
-        <v>1854</v>
-      </c>
-      <c r="G41" s="26">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
+      <c r="A41" s="19"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
       <c r="H41" s="26"/>
       <c r="I41" s="26"/>
-      <c r="J41" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="26">
-        <v>1817</v>
-      </c>
-      <c r="L41" s="26">
-        <v>1792</v>
-      </c>
-      <c r="M41" s="26">
-        <f t="shared" si="2"/>
-        <v>-25</v>
-      </c>
+      <c r="J41" s="26"/>
+      <c r="K41" s="26"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
     </row>
     <row r="42" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A42" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B42" s="20" t="s">
-        <v>734</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>735</v>
-      </c>
-      <c r="D42" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E42" s="26">
-        <v>1837</v>
-      </c>
-      <c r="F42" s="26">
-        <v>1827</v>
-      </c>
-      <c r="G42" s="26">
-        <f t="shared" si="0"/>
-        <v>-10</v>
-      </c>
+      <c r="A42" s="19"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
       <c r="H42" s="26"/>
       <c r="I42" s="26"/>
-      <c r="J42" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="26">
-        <v>1819</v>
-      </c>
-      <c r="L42" s="26">
-        <v>1819</v>
-      </c>
-      <c r="M42" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
     </row>
     <row r="43" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A43" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B43" s="20" t="s">
-        <v>1497</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>1498</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E43" s="26">
-        <v>1890</v>
-      </c>
-      <c r="F43" s="26">
-        <v>1870</v>
-      </c>
-      <c r="G43" s="26">
-        <f t="shared" si="0"/>
-        <v>-20</v>
-      </c>
+      <c r="A43" s="19"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
       <c r="H43" s="26"/>
       <c r="I43" s="26"/>
-      <c r="J43" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="26">
-        <v>1870</v>
-      </c>
-      <c r="L43" s="26">
-        <v>1850</v>
-      </c>
-      <c r="M43" s="26">
-        <f t="shared" si="2"/>
-        <v>-20</v>
-      </c>
+      <c r="J43" s="26"/>
+      <c r="K43" s="26"/>
+      <c r="L43" s="26"/>
+      <c r="M43" s="26"/>
     </row>
     <row r="44" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A44" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B44" s="20" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C44" s="20" t="s">
-        <v>1659</v>
-      </c>
-      <c r="D44" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E44" s="26">
-        <v>1899</v>
-      </c>
-      <c r="F44" s="26">
-        <v>1869</v>
-      </c>
-      <c r="G44" s="26">
-        <f t="shared" si="0"/>
-        <v>-30</v>
-      </c>
+      <c r="A44" s="19"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="26"/>
       <c r="H44" s="26"/>
       <c r="I44" s="26"/>
-      <c r="J44" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="26">
-        <v>1849</v>
-      </c>
-      <c r="L44" s="26">
-        <v>1849</v>
-      </c>
-      <c r="M44" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J44" s="26"/>
+      <c r="K44" s="26"/>
+      <c r="L44" s="26"/>
+      <c r="M44" s="26"/>
     </row>
     <row r="45" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A45" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B45" s="20" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>1083</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E45" s="26">
-        <v>1858</v>
-      </c>
-      <c r="F45" s="26">
-        <v>1828</v>
-      </c>
-      <c r="G45" s="26">
-        <f t="shared" si="0"/>
-        <v>-30</v>
-      </c>
+      <c r="A45" s="19"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
       <c r="H45" s="26"/>
       <c r="I45" s="26"/>
-      <c r="J45" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="26">
-        <v>1828</v>
-      </c>
-      <c r="L45" s="26">
-        <v>1798</v>
-      </c>
-      <c r="M45" s="26">
-        <f t="shared" si="2"/>
-        <v>-30</v>
-      </c>
+      <c r="J45" s="26"/>
+      <c r="K45" s="26"/>
+      <c r="L45" s="26"/>
+      <c r="M45" s="26"/>
     </row>
     <row r="46" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A46" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B46" s="20" t="s">
-        <v>674</v>
-      </c>
-      <c r="C46" s="20" t="s">
-        <v>675</v>
-      </c>
-      <c r="D46" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E46" s="26">
-        <v>1867</v>
-      </c>
-      <c r="F46" s="26">
-        <v>1867</v>
-      </c>
-      <c r="G46" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A46" s="19"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
       <c r="H46" s="26"/>
       <c r="I46" s="26"/>
-      <c r="J46" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="26">
-        <v>1817</v>
-      </c>
-      <c r="L46" s="26">
-        <v>1837</v>
-      </c>
-      <c r="M46" s="26">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
+      <c r="J46" s="26"/>
+      <c r="K46" s="26"/>
+      <c r="L46" s="26"/>
+      <c r="M46" s="26"/>
     </row>
     <row r="47" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A47" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B47" s="20" t="s">
-        <v>451</v>
-      </c>
-      <c r="C47" s="20" t="s">
-        <v>452</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E47" s="26">
-        <v>1869</v>
-      </c>
-      <c r="F47" s="26">
-        <v>1869</v>
-      </c>
-      <c r="G47" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A47" s="19"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
       <c r="H47" s="26"/>
       <c r="I47" s="26"/>
-      <c r="J47" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="26">
-        <v>1839</v>
-      </c>
-      <c r="L47" s="26">
-        <v>1824</v>
-      </c>
-      <c r="M47" s="26">
-        <f t="shared" si="2"/>
-        <v>-15</v>
-      </c>
+      <c r="J47" s="26"/>
+      <c r="K47" s="26"/>
+      <c r="L47" s="26"/>
+      <c r="M47" s="26"/>
     </row>
     <row r="48" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A48" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B48" s="20" t="s">
-        <v>916</v>
-      </c>
-      <c r="C48" s="20" t="s">
-        <v>917</v>
-      </c>
-      <c r="D48" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E48" s="26">
-        <v>1869</v>
-      </c>
-      <c r="F48" s="26">
-        <v>1857</v>
-      </c>
-      <c r="G48" s="26">
-        <f t="shared" si="0"/>
-        <v>-12</v>
-      </c>
+      <c r="A48" s="19"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="26"/>
       <c r="H48" s="26"/>
       <c r="I48" s="26"/>
-      <c r="J48" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="26">
-        <v>1856</v>
-      </c>
-      <c r="L48" s="26">
-        <v>1846</v>
-      </c>
-      <c r="M48" s="26">
-        <f t="shared" si="2"/>
-        <v>-10</v>
-      </c>
+      <c r="J48" s="26"/>
+      <c r="K48" s="26"/>
+      <c r="L48" s="26"/>
+      <c r="M48" s="26"/>
     </row>
     <row r="49" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A49" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B49" s="20" t="s">
-        <v>1509</v>
-      </c>
-      <c r="C49" s="20" t="s">
-        <v>1510</v>
-      </c>
-      <c r="D49" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E49" s="26">
-        <v>1869</v>
-      </c>
-      <c r="F49" s="26">
-        <v>1869</v>
-      </c>
-      <c r="G49" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A49" s="19"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="26"/>
       <c r="H49" s="26"/>
       <c r="I49" s="26"/>
-      <c r="J49" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="26">
-        <v>1897</v>
-      </c>
-      <c r="L49" s="26">
-        <v>1847</v>
-      </c>
-      <c r="M49" s="26">
-        <f t="shared" si="2"/>
-        <v>-50</v>
-      </c>
+      <c r="J49" s="26"/>
+      <c r="K49" s="26"/>
+      <c r="L49" s="26"/>
+      <c r="M49" s="26"/>
     </row>
     <row r="50" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A50" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B50" s="20" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C50" s="20" t="s">
-        <v>1319</v>
-      </c>
-      <c r="D50" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E50" s="26">
-        <v>1887</v>
-      </c>
-      <c r="F50" s="26">
-        <v>1887</v>
-      </c>
-      <c r="G50" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A50" s="19"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="26"/>
+      <c r="G50" s="26"/>
       <c r="H50" s="26"/>
       <c r="I50" s="26"/>
-      <c r="J50" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="26">
-        <v>1853</v>
-      </c>
-      <c r="L50" s="26">
-        <v>1868</v>
-      </c>
-      <c r="M50" s="26">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
+      <c r="J50" s="26"/>
+      <c r="K50" s="26"/>
+      <c r="L50" s="26"/>
+      <c r="M50" s="26"/>
     </row>
     <row r="51" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A51" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B51" s="20" t="s">
-        <v>1733</v>
-      </c>
-      <c r="C51" s="20" t="s">
-        <v>1734</v>
-      </c>
-      <c r="D51" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E51" s="26">
-        <v>1890</v>
-      </c>
-      <c r="F51" s="26">
-        <v>1890</v>
-      </c>
-      <c r="G51" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A51" s="19"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="26"/>
+      <c r="G51" s="26"/>
       <c r="H51" s="26"/>
       <c r="I51" s="26"/>
-      <c r="J51" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="26">
-        <v>1870</v>
-      </c>
-      <c r="L51" s="26">
-        <v>1840</v>
-      </c>
-      <c r="M51" s="26">
-        <f t="shared" si="2"/>
-        <v>-30</v>
-      </c>
+      <c r="J51" s="26"/>
+      <c r="K51" s="26"/>
+      <c r="L51" s="26"/>
+      <c r="M51" s="26"/>
     </row>
     <row r="52" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A52" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B52" s="20" t="s">
-        <v>1674</v>
-      </c>
-      <c r="C52" s="20" t="s">
-        <v>1675</v>
-      </c>
-      <c r="D52" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E52" s="26">
-        <v>1989</v>
-      </c>
-      <c r="F52" s="26">
-        <v>1865</v>
-      </c>
-      <c r="G52" s="26">
-        <f t="shared" si="0"/>
-        <v>-124</v>
-      </c>
+      <c r="A52" s="19"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="26"/>
       <c r="H52" s="26"/>
       <c r="I52" s="26"/>
-      <c r="J52" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="26">
-        <v>1825</v>
-      </c>
-      <c r="L52" s="26">
-        <v>1825</v>
-      </c>
-      <c r="M52" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J52" s="26"/>
+      <c r="K52" s="26"/>
+      <c r="L52" s="26"/>
+      <c r="M52" s="26"/>
     </row>
     <row r="53" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A53" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B53" s="20" t="s">
-        <v>1597</v>
-      </c>
-      <c r="C53" s="20" t="s">
-        <v>1598</v>
-      </c>
-      <c r="D53" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E53" s="26">
-        <v>1797</v>
-      </c>
-      <c r="F53" s="26">
-        <v>1792</v>
-      </c>
-      <c r="G53" s="26">
-        <f t="shared" si="0"/>
-        <v>-5</v>
-      </c>
+      <c r="A53" s="19"/>
+      <c r="B53" s="20"/>
+      <c r="C53" s="20"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+      <c r="G53" s="26"/>
       <c r="H53" s="26"/>
       <c r="I53" s="26"/>
-      <c r="J53" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="26">
-        <v>1782</v>
-      </c>
-      <c r="L53" s="26">
-        <v>1812</v>
-      </c>
-      <c r="M53" s="26">
-        <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
+      <c r="J53" s="26"/>
+      <c r="K53" s="26"/>
+      <c r="L53" s="26"/>
+      <c r="M53" s="26"/>
     </row>
     <row r="54" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A54" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B54" s="20" t="s">
-        <v>743</v>
-      </c>
-      <c r="C54" s="20" t="s">
-        <v>744</v>
-      </c>
-      <c r="D54" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E54" s="26">
-        <v>1805</v>
-      </c>
-      <c r="F54" s="26">
-        <v>1815</v>
-      </c>
-      <c r="G54" s="26">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
+      <c r="A54" s="19"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="26"/>
       <c r="H54" s="26"/>
       <c r="I54" s="26"/>
-      <c r="J54" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="26">
-        <v>1805</v>
-      </c>
-      <c r="L54" s="26">
-        <v>1815</v>
-      </c>
-      <c r="M54" s="26">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+      <c r="J54" s="26"/>
+      <c r="K54" s="26"/>
+      <c r="L54" s="26"/>
+      <c r="M54" s="26"/>
     </row>
     <row r="55" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A55" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B55" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="C55" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="D55" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E55" s="26">
-        <v>1805</v>
-      </c>
-      <c r="F55" s="26">
-        <v>1832</v>
-      </c>
-      <c r="G55" s="26">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
+      <c r="A55" s="19"/>
+      <c r="B55" s="20"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="26"/>
       <c r="H55" s="26"/>
       <c r="I55" s="26"/>
-      <c r="J55" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="26">
-        <v>1812</v>
-      </c>
-      <c r="L55" s="26">
-        <v>1792</v>
-      </c>
-      <c r="M55" s="26">
-        <f t="shared" si="2"/>
-        <v>-20</v>
-      </c>
+      <c r="J55" s="26"/>
+      <c r="K55" s="26"/>
+      <c r="L55" s="26"/>
+      <c r="M55" s="26"/>
     </row>
     <row r="56" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A56" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B56" s="20" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C56" s="20" t="s">
-        <v>1028</v>
-      </c>
-      <c r="D56" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E56" s="26">
-        <v>1805</v>
-      </c>
-      <c r="F56" s="26">
-        <v>1815</v>
-      </c>
-      <c r="G56" s="26">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
+      <c r="A56" s="19"/>
+      <c r="B56" s="20"/>
+      <c r="C56" s="20"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
       <c r="H56" s="26"/>
       <c r="I56" s="26"/>
-      <c r="J56" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="26">
-        <v>1815</v>
-      </c>
-      <c r="L56" s="26">
-        <v>1815</v>
-      </c>
-      <c r="M56" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J56" s="26"/>
+      <c r="K56" s="26"/>
+      <c r="L56" s="26"/>
+      <c r="M56" s="26"/>
     </row>
     <row r="57" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A57" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B57" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="C57" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="D57" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E57" s="26">
-        <v>1809</v>
-      </c>
-      <c r="F57" s="26">
-        <v>1819</v>
-      </c>
-      <c r="G57" s="26">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
+      <c r="A57" s="19"/>
+      <c r="B57" s="20"/>
+      <c r="C57" s="20"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
       <c r="H57" s="26"/>
       <c r="I57" s="26"/>
-      <c r="J57" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="26">
-        <v>1795</v>
-      </c>
-      <c r="L57" s="26">
-        <v>1809</v>
-      </c>
-      <c r="M57" s="26">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
+      <c r="J57" s="26"/>
+      <c r="K57" s="26"/>
+      <c r="L57" s="26"/>
+      <c r="M57" s="26"/>
     </row>
     <row r="58" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A58" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B58" s="20" t="s">
-        <v>980</v>
-      </c>
-      <c r="C58" s="20" t="s">
-        <v>981</v>
-      </c>
-      <c r="D58" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E58" s="26">
-        <v>1809</v>
-      </c>
-      <c r="F58" s="26">
-        <v>1805</v>
-      </c>
-      <c r="G58" s="26">
-        <f t="shared" si="0"/>
-        <v>-4</v>
-      </c>
+      <c r="A58" s="19"/>
+      <c r="B58" s="20"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
       <c r="H58" s="26"/>
       <c r="I58" s="26"/>
-      <c r="J58" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="26">
-        <v>1795</v>
-      </c>
-      <c r="L58" s="26">
-        <v>1795</v>
-      </c>
-      <c r="M58" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J58" s="26"/>
+      <c r="K58" s="26"/>
+      <c r="L58" s="26"/>
+      <c r="M58" s="26"/>
     </row>
     <row r="59" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A59" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B59" s="20" t="s">
-        <v>336</v>
-      </c>
-      <c r="C59" s="20" t="s">
-        <v>337</v>
-      </c>
-      <c r="D59" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E59" s="26">
-        <v>1818</v>
-      </c>
-      <c r="F59" s="26">
-        <v>1815</v>
-      </c>
-      <c r="G59" s="26">
-        <f t="shared" si="0"/>
-        <v>-3</v>
-      </c>
+      <c r="A59" s="19"/>
+      <c r="B59" s="20"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
       <c r="H59" s="26"/>
       <c r="I59" s="26"/>
-      <c r="J59" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="26">
-        <v>1799</v>
-      </c>
-      <c r="L59" s="26">
-        <v>1795</v>
-      </c>
-      <c r="M59" s="26">
-        <f t="shared" si="2"/>
-        <v>-4</v>
-      </c>
+      <c r="J59" s="26"/>
+      <c r="K59" s="26"/>
+      <c r="L59" s="26"/>
+      <c r="M59" s="26"/>
     </row>
     <row r="60" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A60" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B60" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="C60" s="20" t="s">
-        <v>307</v>
-      </c>
-      <c r="D60" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E60" s="26">
-        <v>1819</v>
-      </c>
-      <c r="F60" s="26">
-        <v>1824</v>
-      </c>
-      <c r="G60" s="26">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
+      <c r="A60" s="19"/>
+      <c r="B60" s="20"/>
+      <c r="C60" s="20"/>
+      <c r="D60" s="20"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="26"/>
       <c r="H60" s="26"/>
       <c r="I60" s="26"/>
-      <c r="J60" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="26">
-        <v>1794</v>
-      </c>
-      <c r="L60" s="26">
-        <v>1794</v>
-      </c>
-      <c r="M60" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J60" s="26"/>
+      <c r="K60" s="26"/>
+      <c r="L60" s="26"/>
+      <c r="M60" s="26"/>
     </row>
     <row r="61" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A61" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B61" s="20" t="s">
-        <v>1179</v>
-      </c>
-      <c r="C61" s="20" t="s">
-        <v>1180</v>
-      </c>
-      <c r="D61" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E61" s="26">
-        <v>1819</v>
-      </c>
-      <c r="F61" s="26">
-        <v>1829</v>
-      </c>
-      <c r="G61" s="26">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
+      <c r="A61" s="19"/>
+      <c r="B61" s="20"/>
+      <c r="C61" s="20"/>
+      <c r="D61" s="20"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
       <c r="H61" s="26"/>
       <c r="I61" s="26"/>
-      <c r="J61" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="26">
-        <v>1799</v>
-      </c>
-      <c r="L61" s="26">
-        <v>1809</v>
-      </c>
-      <c r="M61" s="26">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+      <c r="J61" s="26"/>
+      <c r="K61" s="26"/>
+      <c r="L61" s="26"/>
+      <c r="M61" s="26"/>
     </row>
     <row r="62" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A62" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B62" s="20" t="s">
-        <v>396</v>
-      </c>
-      <c r="C62" s="20" t="s">
-        <v>397</v>
-      </c>
-      <c r="D62" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E62" s="26">
-        <v>1822</v>
-      </c>
-      <c r="F62" s="26">
-        <v>1822</v>
-      </c>
-      <c r="G62" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A62" s="19"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="26"/>
+      <c r="G62" s="26"/>
       <c r="H62" s="26"/>
       <c r="I62" s="26"/>
-      <c r="J62" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="26">
-        <v>1802</v>
-      </c>
-      <c r="L62" s="26">
-        <v>1797</v>
-      </c>
-      <c r="M62" s="26">
-        <f t="shared" si="2"/>
-        <v>-5</v>
-      </c>
+      <c r="J62" s="26"/>
+      <c r="K62" s="26"/>
+      <c r="L62" s="26"/>
+      <c r="M62" s="26"/>
     </row>
     <row r="63" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A63" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B63" s="20" t="s">
-        <v>394</v>
-      </c>
-      <c r="C63" s="20" t="s">
-        <v>395</v>
-      </c>
-      <c r="D63" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E63" s="26">
-        <v>1823</v>
-      </c>
-      <c r="F63" s="26">
-        <v>1838</v>
-      </c>
-      <c r="G63" s="26">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
+      <c r="A63" s="19"/>
+      <c r="B63" s="20"/>
+      <c r="C63" s="20"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="26"/>
+      <c r="G63" s="26"/>
       <c r="H63" s="26"/>
       <c r="I63" s="26"/>
-      <c r="J63" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="26">
-        <v>1823</v>
-      </c>
-      <c r="L63" s="26">
-        <v>1818</v>
-      </c>
-      <c r="M63" s="26">
-        <f t="shared" si="2"/>
-        <v>-5</v>
-      </c>
+      <c r="J63" s="26"/>
+      <c r="K63" s="26"/>
+      <c r="L63" s="26"/>
+      <c r="M63" s="26"/>
     </row>
     <row r="64" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A64" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B64" s="20" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C64" s="20" t="s">
-        <v>1103</v>
-      </c>
-      <c r="D64" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E64" s="26">
-        <v>1824</v>
-      </c>
-      <c r="F64" s="26">
-        <v>1844</v>
-      </c>
-      <c r="G64" s="26">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
+      <c r="A64" s="19"/>
+      <c r="B64" s="20"/>
+      <c r="C64" s="20"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="26"/>
+      <c r="G64" s="26"/>
       <c r="H64" s="26"/>
       <c r="I64" s="26"/>
-      <c r="J64" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="26">
-        <v>1814</v>
-      </c>
-      <c r="L64" s="26">
-        <v>1834</v>
-      </c>
-      <c r="M64" s="26">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
+      <c r="J64" s="26"/>
+      <c r="K64" s="26"/>
+      <c r="L64" s="26"/>
+      <c r="M64" s="26"/>
     </row>
     <row r="65" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A65" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B65" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="C65" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="D65" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E65" s="26">
-        <v>1825</v>
-      </c>
-      <c r="F65" s="26">
-        <v>1825</v>
-      </c>
-      <c r="G65" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A65" s="19"/>
+      <c r="B65" s="20"/>
+      <c r="C65" s="20"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
+      <c r="G65" s="26"/>
       <c r="H65" s="26"/>
       <c r="I65" s="26"/>
-      <c r="J65" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="26">
-        <v>1789</v>
-      </c>
-      <c r="L65" s="26">
-        <v>1795</v>
-      </c>
-      <c r="M65" s="26">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
+      <c r="J65" s="26"/>
+      <c r="K65" s="26"/>
+      <c r="L65" s="26"/>
+      <c r="M65" s="26"/>
     </row>
     <row r="66" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A66" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B66" s="20" t="s">
-        <v>322</v>
-      </c>
-      <c r="C66" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="D66" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E66" s="26">
-        <v>1825</v>
-      </c>
-      <c r="F66" s="26">
-        <v>1822</v>
-      </c>
-      <c r="G66" s="26">
-        <f t="shared" si="0"/>
-        <v>-3</v>
-      </c>
+      <c r="A66" s="19"/>
+      <c r="B66" s="20"/>
+      <c r="C66" s="20"/>
+      <c r="D66" s="20"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="26"/>
+      <c r="G66" s="26"/>
       <c r="H66" s="26"/>
       <c r="I66" s="26"/>
-      <c r="J66" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="26">
-        <v>1808</v>
-      </c>
-      <c r="L66" s="26">
-        <v>1807</v>
-      </c>
-      <c r="M66" s="26">
-        <f t="shared" si="2"/>
-        <v>-1</v>
-      </c>
+      <c r="J66" s="26"/>
+      <c r="K66" s="26"/>
+      <c r="L66" s="26"/>
+      <c r="M66" s="26"/>
     </row>
     <row r="67" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A67" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B67" s="20" t="s">
-        <v>352</v>
-      </c>
-      <c r="C67" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="D67" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E67" s="26">
-        <v>1825</v>
-      </c>
-      <c r="F67" s="26">
-        <v>1825</v>
-      </c>
-      <c r="G67" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A67" s="19"/>
+      <c r="B67" s="20"/>
+      <c r="C67" s="20"/>
+      <c r="D67" s="20"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
+      <c r="G67" s="26"/>
       <c r="H67" s="26"/>
       <c r="I67" s="26"/>
-      <c r="J67" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="26">
-        <v>1909</v>
-      </c>
-      <c r="L67" s="26">
-        <v>1809</v>
-      </c>
-      <c r="M67" s="26">
-        <f t="shared" si="2"/>
-        <v>-100</v>
-      </c>
+      <c r="J67" s="26"/>
+      <c r="K67" s="26"/>
+      <c r="L67" s="26"/>
+      <c r="M67" s="26"/>
     </row>
     <row r="68" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A68" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B68" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="C68" s="20" t="s">
-        <v>319</v>
-      </c>
-      <c r="D68" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E68" s="26">
-        <v>1829</v>
-      </c>
-      <c r="F68" s="26">
-        <v>1829</v>
-      </c>
-      <c r="G68" s="26">
-        <f t="shared" ref="G68:G103" si="3">IF(OR(E68="",F68=""),"",F68-E68)</f>
-        <v>0</v>
-      </c>
+      <c r="A68" s="19"/>
+      <c r="B68" s="20"/>
+      <c r="C68" s="20"/>
+      <c r="D68" s="20"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="26"/>
+      <c r="G68" s="26"/>
       <c r="H68" s="26"/>
       <c r="I68" s="26"/>
-      <c r="J68" s="26" t="str">
-        <f t="shared" ref="J68:J103" si="4">IF(OR(H68="",I68=""),"",I68-H68)</f>
-        <v/>
-      </c>
-      <c r="K68" s="26">
-        <v>1809</v>
-      </c>
-      <c r="L68" s="26">
-        <v>1819</v>
-      </c>
-      <c r="M68" s="26">
-        <f t="shared" ref="M68:M103" si="5">IF(OR(K68="",L68=""),"",L68-K68)</f>
-        <v>10</v>
-      </c>
+      <c r="J68" s="26"/>
+      <c r="K68" s="26"/>
+      <c r="L68" s="26"/>
+      <c r="M68" s="26"/>
     </row>
     <row r="69" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A69" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B69" s="20" t="s">
-        <v>616</v>
-      </c>
-      <c r="C69" s="20" t="s">
-        <v>618</v>
-      </c>
-      <c r="D69" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E69" s="26">
-        <v>1829</v>
-      </c>
-      <c r="F69" s="26">
-        <v>1829</v>
-      </c>
-      <c r="G69" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="A69" s="19"/>
+      <c r="B69" s="20"/>
+      <c r="C69" s="20"/>
+      <c r="D69" s="20"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="26"/>
+      <c r="G69" s="26"/>
       <c r="H69" s="26"/>
-      <c r="I69" s="26">
-        <v>2289</v>
-      </c>
-      <c r="J69" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K69" s="26">
-        <v>1815</v>
-      </c>
-      <c r="L69" s="26">
-        <v>1815</v>
-      </c>
-      <c r="M69" s="26">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="I69" s="26"/>
+      <c r="J69" s="26"/>
+      <c r="K69" s="26"/>
+      <c r="L69" s="26"/>
+      <c r="M69" s="26"/>
     </row>
     <row r="70" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A70" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B70" s="20" t="s">
-        <v>1203</v>
-      </c>
-      <c r="C70" s="20" t="s">
-        <v>1204</v>
-      </c>
-      <c r="D70" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E70" s="26">
-        <v>1829</v>
-      </c>
-      <c r="F70" s="26">
-        <v>1836</v>
-      </c>
-      <c r="G70" s="26">
-        <f t="shared" si="3"/>
-        <v>7</v>
-      </c>
+      <c r="A70" s="19"/>
+      <c r="B70" s="20"/>
+      <c r="C70" s="20"/>
+      <c r="D70" s="20"/>
+      <c r="E70" s="26"/>
+      <c r="F70" s="26"/>
+      <c r="G70" s="26"/>
       <c r="H70" s="26"/>
       <c r="I70" s="26"/>
-      <c r="J70" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K70" s="26">
-        <v>1818</v>
-      </c>
-      <c r="L70" s="26">
-        <v>1818</v>
-      </c>
-      <c r="M70" s="26">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="J70" s="26"/>
+      <c r="K70" s="26"/>
+      <c r="L70" s="26"/>
+      <c r="M70" s="26"/>
     </row>
     <row r="71" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A71" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B71" s="20" t="s">
-        <v>928</v>
-      </c>
-      <c r="C71" s="20" t="s">
-        <v>929</v>
-      </c>
-      <c r="D71" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E71" s="26">
-        <v>1829</v>
-      </c>
-      <c r="F71" s="26">
-        <v>1819</v>
-      </c>
-      <c r="G71" s="26">
-        <f t="shared" si="3"/>
-        <v>-10</v>
-      </c>
+      <c r="A71" s="19"/>
+      <c r="B71" s="20"/>
+      <c r="C71" s="20"/>
+      <c r="D71" s="20"/>
+      <c r="E71" s="26"/>
+      <c r="F71" s="26"/>
+      <c r="G71" s="26"/>
       <c r="H71" s="26"/>
       <c r="I71" s="26"/>
-      <c r="J71" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K71" s="26">
-        <v>1829</v>
-      </c>
-      <c r="L71" s="26">
-        <v>1829</v>
-      </c>
-      <c r="M71" s="26">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="J71" s="26"/>
+      <c r="K71" s="26"/>
+      <c r="L71" s="26"/>
+      <c r="M71" s="26"/>
     </row>
     <row r="72" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A72" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B72" s="20" t="s">
-        <v>1501</v>
-      </c>
-      <c r="C72" s="20" t="s">
-        <v>1502</v>
-      </c>
-      <c r="D72" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E72" s="26">
-        <v>1829</v>
-      </c>
-      <c r="F72" s="26">
-        <v>1795</v>
-      </c>
-      <c r="G72" s="26">
-        <f t="shared" si="3"/>
-        <v>-34</v>
-      </c>
+      <c r="A72" s="19"/>
+      <c r="B72" s="20"/>
+      <c r="C72" s="20"/>
+      <c r="D72" s="20"/>
+      <c r="E72" s="26"/>
+      <c r="F72" s="26"/>
+      <c r="G72" s="26"/>
       <c r="H72" s="26"/>
       <c r="I72" s="26"/>
-      <c r="J72" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K72" s="26">
-        <v>1837</v>
-      </c>
-      <c r="L72" s="26">
-        <v>1795</v>
-      </c>
-      <c r="M72" s="26">
-        <f t="shared" si="5"/>
-        <v>-42</v>
-      </c>
+      <c r="J72" s="26"/>
+      <c r="K72" s="26"/>
+      <c r="L72" s="26"/>
+      <c r="M72" s="26"/>
     </row>
     <row r="73" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A73" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B73" s="20" t="s">
-        <v>1503</v>
-      </c>
-      <c r="C73" s="20" t="s">
-        <v>1504</v>
-      </c>
-      <c r="D73" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E73" s="26">
-        <v>1829</v>
-      </c>
-      <c r="F73" s="26">
-        <v>1795</v>
-      </c>
-      <c r="G73" s="26">
-        <f t="shared" si="3"/>
-        <v>-34</v>
-      </c>
+      <c r="A73" s="19"/>
+      <c r="B73" s="20"/>
+      <c r="C73" s="20"/>
+      <c r="D73" s="20"/>
+      <c r="E73" s="26"/>
+      <c r="F73" s="26"/>
+      <c r="G73" s="26"/>
       <c r="H73" s="26"/>
       <c r="I73" s="26"/>
-      <c r="J73" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K73" s="26">
-        <v>1837</v>
-      </c>
-      <c r="L73" s="26">
-        <v>1795</v>
-      </c>
-      <c r="M73" s="26">
-        <f t="shared" si="5"/>
-        <v>-42</v>
-      </c>
+      <c r="J73" s="26"/>
+      <c r="K73" s="26"/>
+      <c r="L73" s="26"/>
+      <c r="M73" s="26"/>
     </row>
     <row r="74" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A74" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B74" s="20" t="s">
-        <v>1505</v>
-      </c>
-      <c r="C74" s="20" t="s">
-        <v>1506</v>
-      </c>
-      <c r="D74" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E74" s="26">
-        <v>1829</v>
-      </c>
-      <c r="F74" s="26">
-        <v>1795</v>
-      </c>
-      <c r="G74" s="26">
-        <f t="shared" si="3"/>
-        <v>-34</v>
-      </c>
+      <c r="A74" s="19"/>
+      <c r="B74" s="20"/>
+      <c r="C74" s="20"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="26"/>
+      <c r="F74" s="26"/>
+      <c r="G74" s="26"/>
       <c r="H74" s="26"/>
       <c r="I74" s="26"/>
-      <c r="J74" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K74" s="26">
-        <v>1837</v>
-      </c>
-      <c r="L74" s="26">
-        <v>1795</v>
-      </c>
-      <c r="M74" s="26">
-        <f t="shared" si="5"/>
-        <v>-42</v>
-      </c>
+      <c r="J74" s="26"/>
+      <c r="K74" s="26"/>
+      <c r="L74" s="26"/>
+      <c r="M74" s="26"/>
     </row>
     <row r="75" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A75" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B75" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="C75" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="D75" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E75" s="26">
-        <v>1834</v>
-      </c>
-      <c r="F75" s="26">
-        <v>1825</v>
-      </c>
-      <c r="G75" s="26">
-        <f t="shared" si="3"/>
-        <v>-9</v>
-      </c>
+      <c r="A75" s="19"/>
+      <c r="B75" s="20"/>
+      <c r="C75" s="20"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="26"/>
+      <c r="F75" s="26"/>
+      <c r="G75" s="26"/>
       <c r="H75" s="26"/>
       <c r="I75" s="26"/>
-      <c r="J75" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K75" s="26">
-        <v>1810</v>
-      </c>
-      <c r="L75" s="26">
-        <v>1810</v>
-      </c>
-      <c r="M75" s="26">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="J75" s="26"/>
+      <c r="K75" s="26"/>
+      <c r="L75" s="26"/>
+      <c r="M75" s="26"/>
     </row>
     <row r="76" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A76" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B76" s="20" t="s">
-        <v>368</v>
-      </c>
-      <c r="C76" s="20" t="s">
-        <v>369</v>
-      </c>
-      <c r="D76" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E76" s="26">
-        <v>1834</v>
-      </c>
-      <c r="F76" s="26">
-        <v>1814</v>
-      </c>
-      <c r="G76" s="26">
-        <f t="shared" si="3"/>
-        <v>-20</v>
-      </c>
+      <c r="A76" s="19"/>
+      <c r="B76" s="20"/>
+      <c r="C76" s="20"/>
+      <c r="D76" s="20"/>
+      <c r="E76" s="26"/>
+      <c r="F76" s="26"/>
+      <c r="G76" s="26"/>
       <c r="H76" s="26"/>
       <c r="I76" s="26"/>
-      <c r="J76" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K76" s="26">
-        <v>1814</v>
-      </c>
-      <c r="L76" s="26">
-        <v>1814</v>
-      </c>
-      <c r="M76" s="26">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="J76" s="26"/>
+      <c r="K76" s="26"/>
+      <c r="L76" s="26"/>
+      <c r="M76" s="26"/>
     </row>
     <row r="77" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A77" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B77" s="20" t="s">
-        <v>653</v>
-      </c>
-      <c r="C77" s="20" t="s">
-        <v>654</v>
-      </c>
-      <c r="D77" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E77" s="26">
-        <v>1837</v>
-      </c>
-      <c r="F77" s="26">
-        <v>1817</v>
-      </c>
-      <c r="G77" s="26">
-        <f t="shared" si="3"/>
-        <v>-20</v>
-      </c>
+      <c r="A77" s="19"/>
+      <c r="B77" s="20"/>
+      <c r="C77" s="20"/>
+      <c r="D77" s="20"/>
+      <c r="E77" s="26"/>
+      <c r="F77" s="26"/>
+      <c r="G77" s="26"/>
       <c r="H77" s="26"/>
       <c r="I77" s="26"/>
-      <c r="J77" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K77" s="26">
-        <v>1812</v>
-      </c>
-      <c r="L77" s="26">
-        <v>1792</v>
-      </c>
-      <c r="M77" s="26">
-        <f t="shared" si="5"/>
-        <v>-20</v>
-      </c>
+      <c r="J77" s="26"/>
+      <c r="K77" s="26"/>
+      <c r="L77" s="26"/>
+      <c r="M77" s="26"/>
     </row>
     <row r="78" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A78" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B78" s="20" t="s">
-        <v>1193</v>
-      </c>
-      <c r="C78" s="20" t="s">
-        <v>1194</v>
-      </c>
-      <c r="D78" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E78" s="26">
-        <v>1838</v>
-      </c>
-      <c r="F78" s="26">
-        <v>1838</v>
-      </c>
-      <c r="G78" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="A78" s="19"/>
+      <c r="B78" s="20"/>
+      <c r="C78" s="20"/>
+      <c r="D78" s="20"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
       <c r="H78" s="26"/>
       <c r="I78" s="26"/>
-      <c r="J78" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K78" s="26">
-        <v>1818</v>
-      </c>
-      <c r="L78" s="26">
-        <v>1848</v>
-      </c>
-      <c r="M78" s="26">
-        <f t="shared" si="5"/>
-        <v>30</v>
-      </c>
+      <c r="J78" s="26"/>
+      <c r="K78" s="26"/>
+      <c r="L78" s="26"/>
+      <c r="M78" s="26"/>
     </row>
     <row r="79" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A79" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B79" s="20" t="s">
-        <v>1360</v>
-      </c>
-      <c r="C79" s="20" t="s">
-        <v>1361</v>
-      </c>
-      <c r="D79" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E79" s="26">
-        <v>1839</v>
-      </c>
-      <c r="F79" s="26">
-        <v>1829</v>
-      </c>
-      <c r="G79" s="26">
-        <f t="shared" si="3"/>
-        <v>-10</v>
-      </c>
+      <c r="A79" s="19"/>
+      <c r="B79" s="20"/>
+      <c r="C79" s="20"/>
+      <c r="D79" s="20"/>
+      <c r="E79" s="26"/>
+      <c r="F79" s="26"/>
+      <c r="G79" s="26"/>
       <c r="H79" s="26"/>
       <c r="I79" s="26"/>
-      <c r="J79" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K79" s="26">
-        <v>1829</v>
-      </c>
-      <c r="L79" s="26">
-        <v>1829</v>
-      </c>
-      <c r="M79" s="26">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="J79" s="26"/>
+      <c r="K79" s="26"/>
+      <c r="L79" s="26"/>
+      <c r="M79" s="26"/>
     </row>
     <row r="80" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A80" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B80" s="20" t="s">
-        <v>680</v>
-      </c>
-      <c r="C80" s="20" t="s">
-        <v>681</v>
-      </c>
-      <c r="D80" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E80" s="26">
-        <v>1840</v>
-      </c>
-      <c r="F80" s="26">
-        <v>1840</v>
-      </c>
-      <c r="G80" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="A80" s="19"/>
+      <c r="B80" s="20"/>
+      <c r="C80" s="20"/>
+      <c r="D80" s="20"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
       <c r="H80" s="26"/>
       <c r="I80" s="26"/>
-      <c r="J80" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K80" s="26">
-        <v>1875</v>
-      </c>
-      <c r="L80" s="26">
-        <v>1830</v>
-      </c>
-      <c r="M80" s="26">
-        <f t="shared" si="5"/>
-        <v>-45</v>
-      </c>
+      <c r="J80" s="26"/>
+      <c r="K80" s="26"/>
+      <c r="L80" s="26"/>
+      <c r="M80" s="26"/>
     </row>
     <row r="81" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A81" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B81" s="20" t="s">
-        <v>1207</v>
-      </c>
-      <c r="C81" s="20" t="s">
-        <v>1208</v>
-      </c>
-      <c r="D81" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E81" s="26">
-        <v>1842</v>
-      </c>
-      <c r="F81" s="26">
-        <v>1842</v>
-      </c>
-      <c r="G81" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="A81" s="19"/>
+      <c r="B81" s="20"/>
+      <c r="C81" s="20"/>
+      <c r="D81" s="20"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="26"/>
+      <c r="G81" s="26"/>
       <c r="H81" s="26"/>
       <c r="I81" s="26"/>
-      <c r="J81" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K81" s="26">
-        <v>1825</v>
-      </c>
-      <c r="L81" s="26">
-        <v>1822</v>
-      </c>
-      <c r="M81" s="26">
-        <f t="shared" si="5"/>
-        <v>-3</v>
-      </c>
+      <c r="J81" s="26"/>
+      <c r="K81" s="26"/>
+      <c r="L81" s="26"/>
+      <c r="M81" s="26"/>
     </row>
     <row r="82" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A82" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B82" s="20" t="s">
-        <v>1100</v>
-      </c>
-      <c r="C82" s="20" t="s">
-        <v>1101</v>
-      </c>
-      <c r="D82" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E82" s="26">
-        <v>1842</v>
-      </c>
-      <c r="F82" s="26">
-        <v>1852</v>
-      </c>
-      <c r="G82" s="26">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
+      <c r="A82" s="19"/>
+      <c r="B82" s="20"/>
+      <c r="C82" s="20"/>
+      <c r="D82" s="20"/>
+      <c r="E82" s="26"/>
+      <c r="F82" s="26"/>
+      <c r="G82" s="26"/>
       <c r="H82" s="26"/>
       <c r="I82" s="26"/>
-      <c r="J82" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K82" s="26">
-        <v>1829</v>
-      </c>
-      <c r="L82" s="26">
-        <v>1839</v>
-      </c>
-      <c r="M82" s="26">
-        <f t="shared" si="5"/>
-        <v>10</v>
-      </c>
+      <c r="J82" s="26"/>
+      <c r="K82" s="26"/>
+      <c r="L82" s="26"/>
+      <c r="M82" s="26"/>
     </row>
     <row r="83" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A83" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B83" s="20" t="s">
-        <v>1366</v>
-      </c>
-      <c r="C83" s="20" t="s">
-        <v>1368</v>
-      </c>
-      <c r="D83" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E83" s="26">
-        <v>1842</v>
-      </c>
-      <c r="F83" s="26">
-        <v>1842</v>
-      </c>
-      <c r="G83" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="A83" s="19"/>
+      <c r="B83" s="20"/>
+      <c r="C83" s="20"/>
+      <c r="D83" s="20"/>
+      <c r="E83" s="26"/>
+      <c r="F83" s="26"/>
+      <c r="G83" s="26"/>
       <c r="H83" s="26"/>
       <c r="I83" s="26"/>
-      <c r="J83" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K83" s="26">
-        <v>1850</v>
-      </c>
-      <c r="L83" s="26">
-        <v>1832</v>
-      </c>
-      <c r="M83" s="26">
-        <f t="shared" si="5"/>
-        <v>-18</v>
-      </c>
+      <c r="J83" s="26"/>
+      <c r="K83" s="26"/>
+      <c r="L83" s="26"/>
+      <c r="M83" s="26"/>
     </row>
     <row r="84" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A84" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B84" s="20" t="s">
-        <v>739</v>
-      </c>
-      <c r="C84" s="20" t="s">
-        <v>740</v>
-      </c>
-      <c r="D84" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E84" s="26">
-        <v>1843</v>
-      </c>
-      <c r="F84" s="26">
-        <v>1843</v>
-      </c>
-      <c r="G84" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="A84" s="19"/>
+      <c r="B84" s="20"/>
+      <c r="C84" s="20"/>
+      <c r="D84" s="20"/>
+      <c r="E84" s="26"/>
+      <c r="F84" s="26"/>
+      <c r="G84" s="26"/>
       <c r="H84" s="26"/>
       <c r="I84" s="26"/>
-      <c r="J84" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K84" s="26">
-        <v>1828</v>
-      </c>
-      <c r="L84" s="26">
-        <v>1823</v>
-      </c>
-      <c r="M84" s="26">
-        <f t="shared" si="5"/>
-        <v>-5</v>
-      </c>
+      <c r="J84" s="26"/>
+      <c r="K84" s="26"/>
+      <c r="L84" s="26"/>
+      <c r="M84" s="26"/>
     </row>
     <row r="85" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A85" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B85" s="20" t="s">
-        <v>1624</v>
-      </c>
-      <c r="C85" s="20" t="s">
-        <v>1625</v>
-      </c>
-      <c r="D85" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E85" s="26">
-        <v>1844</v>
-      </c>
-      <c r="F85" s="26">
-        <v>1840</v>
-      </c>
-      <c r="G85" s="26">
-        <f t="shared" si="3"/>
-        <v>-4</v>
-      </c>
+      <c r="A85" s="19"/>
+      <c r="B85" s="20"/>
+      <c r="C85" s="20"/>
+      <c r="D85" s="20"/>
+      <c r="E85" s="26"/>
+      <c r="F85" s="26"/>
+      <c r="G85" s="26"/>
       <c r="H85" s="26"/>
       <c r="I85" s="26"/>
-      <c r="J85" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K85" s="26">
-        <v>1837</v>
-      </c>
-      <c r="L85" s="26">
-        <v>1831</v>
-      </c>
-      <c r="M85" s="26">
-        <f t="shared" si="5"/>
-        <v>-6</v>
-      </c>
+      <c r="J85" s="26"/>
+      <c r="K85" s="26"/>
+      <c r="L85" s="26"/>
+      <c r="M85" s="26"/>
     </row>
     <row r="86" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A86" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B86" s="20" t="s">
-        <v>1626</v>
-      </c>
-      <c r="C86" s="20" t="s">
-        <v>1627</v>
-      </c>
-      <c r="D86" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E86" s="26">
-        <v>1844</v>
-      </c>
-      <c r="F86" s="26">
-        <v>1840</v>
-      </c>
-      <c r="G86" s="26">
-        <f t="shared" si="3"/>
-        <v>-4</v>
-      </c>
+      <c r="A86" s="19"/>
+      <c r="B86" s="20"/>
+      <c r="C86" s="20"/>
+      <c r="D86" s="20"/>
+      <c r="E86" s="26"/>
+      <c r="F86" s="26"/>
+      <c r="G86" s="26"/>
       <c r="H86" s="26"/>
       <c r="I86" s="26"/>
-      <c r="J86" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K86" s="26">
-        <v>1837</v>
-      </c>
-      <c r="L86" s="26">
-        <v>1831</v>
-      </c>
-      <c r="M86" s="26">
-        <f t="shared" si="5"/>
-        <v>-6</v>
-      </c>
+      <c r="J86" s="26"/>
+      <c r="K86" s="26"/>
+      <c r="L86" s="26"/>
+      <c r="M86" s="26"/>
     </row>
     <row r="87" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A87" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B87" s="20" t="s">
-        <v>1609</v>
-      </c>
-      <c r="C87" s="20" t="s">
-        <v>1610</v>
-      </c>
-      <c r="D87" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E87" s="26">
-        <v>1848</v>
-      </c>
-      <c r="F87" s="26">
-        <v>1848</v>
-      </c>
-      <c r="G87" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="A87" s="19"/>
+      <c r="B87" s="20"/>
+      <c r="C87" s="20"/>
+      <c r="D87" s="20"/>
+      <c r="E87" s="26"/>
+      <c r="F87" s="26"/>
+      <c r="G87" s="26"/>
       <c r="H87" s="26"/>
       <c r="I87" s="26"/>
-      <c r="J87" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K87" s="26">
-        <v>1823</v>
-      </c>
-      <c r="L87" s="26">
-        <v>1838</v>
-      </c>
-      <c r="M87" s="26">
-        <f t="shared" si="5"/>
-        <v>15</v>
-      </c>
+      <c r="J87" s="26"/>
+      <c r="K87" s="26"/>
+      <c r="L87" s="26"/>
+      <c r="M87" s="26"/>
     </row>
     <row r="88" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A88" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B88" s="20" t="s">
-        <v>468</v>
-      </c>
-      <c r="C88" s="20" t="s">
-        <v>469</v>
-      </c>
-      <c r="D88" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E88" s="26">
-        <v>1852</v>
-      </c>
-      <c r="F88" s="26">
-        <v>1849</v>
-      </c>
-      <c r="G88" s="26">
-        <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
+      <c r="A88" s="19"/>
+      <c r="B88" s="20"/>
+      <c r="C88" s="20"/>
+      <c r="D88" s="20"/>
+      <c r="E88" s="26"/>
+      <c r="F88" s="26"/>
+      <c r="G88" s="26"/>
       <c r="H88" s="26"/>
       <c r="I88" s="26"/>
-      <c r="J88" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K88" s="26">
-        <v>1842</v>
-      </c>
-      <c r="L88" s="26">
-        <v>1842</v>
-      </c>
-      <c r="M88" s="26">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="J88" s="26"/>
+      <c r="K88" s="26"/>
+      <c r="L88" s="26"/>
+      <c r="M88" s="26"/>
     </row>
     <row r="89" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A89" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B89" s="20" t="s">
-        <v>466</v>
-      </c>
-      <c r="C89" s="20" t="s">
-        <v>467</v>
-      </c>
-      <c r="D89" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E89" s="26">
-        <v>1852</v>
-      </c>
-      <c r="F89" s="26">
-        <v>1849</v>
-      </c>
-      <c r="G89" s="26">
-        <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
+      <c r="A89" s="19"/>
+      <c r="B89" s="20"/>
+      <c r="C89" s="20"/>
+      <c r="D89" s="20"/>
+      <c r="E89" s="26"/>
+      <c r="F89" s="26"/>
+      <c r="G89" s="26"/>
       <c r="H89" s="26"/>
       <c r="I89" s="26"/>
-      <c r="J89" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K89" s="26">
-        <v>1842</v>
-      </c>
-      <c r="L89" s="26">
-        <v>1842</v>
-      </c>
-      <c r="M89" s="26">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="J89" s="26"/>
+      <c r="K89" s="26"/>
+      <c r="L89" s="26"/>
+      <c r="M89" s="26"/>
     </row>
     <row r="90" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A90" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B90" s="20" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C90" s="20" t="s">
-        <v>1037</v>
-      </c>
-      <c r="D90" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E90" s="26">
-        <v>1859</v>
-      </c>
-      <c r="F90" s="26">
-        <v>1859</v>
-      </c>
-      <c r="G90" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="A90" s="19"/>
+      <c r="B90" s="20"/>
+      <c r="C90" s="20"/>
+      <c r="D90" s="20"/>
+      <c r="E90" s="26"/>
+      <c r="F90" s="26"/>
+      <c r="G90" s="26"/>
       <c r="H90" s="26"/>
       <c r="I90" s="26"/>
-      <c r="J90" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K90" s="26">
-        <v>1819</v>
-      </c>
-      <c r="L90" s="26">
-        <v>1829</v>
-      </c>
-      <c r="M90" s="26">
-        <f t="shared" si="5"/>
-        <v>10</v>
-      </c>
+      <c r="J90" s="26"/>
+      <c r="K90" s="26"/>
+      <c r="L90" s="26"/>
+      <c r="M90" s="26"/>
     </row>
     <row r="91" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A91" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B91" s="20" t="s">
-        <v>358</v>
-      </c>
-      <c r="C91" s="20" t="s">
-        <v>359</v>
-      </c>
-      <c r="D91" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E91" s="26">
-        <v>1869</v>
-      </c>
-      <c r="F91" s="26">
-        <v>1869</v>
-      </c>
-      <c r="G91" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="A91" s="19"/>
+      <c r="B91" s="20"/>
+      <c r="C91" s="20"/>
+      <c r="D91" s="20"/>
+      <c r="E91" s="26"/>
+      <c r="F91" s="26"/>
+      <c r="G91" s="26"/>
       <c r="H91" s="26"/>
       <c r="I91" s="26"/>
-      <c r="J91" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K91" s="26">
-        <v>1833</v>
-      </c>
-      <c r="L91" s="26">
-        <v>1823</v>
-      </c>
-      <c r="M91" s="26">
-        <f t="shared" si="5"/>
-        <v>-10</v>
-      </c>
+      <c r="J91" s="26"/>
+      <c r="K91" s="26"/>
+      <c r="L91" s="26"/>
+      <c r="M91" s="26"/>
     </row>
     <row r="92" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A92" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B92" s="20" t="s">
-        <v>360</v>
-      </c>
-      <c r="C92" s="20" t="s">
-        <v>361</v>
-      </c>
-      <c r="D92" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E92" s="26">
-        <v>1869</v>
-      </c>
-      <c r="F92" s="26">
-        <v>1869</v>
-      </c>
-      <c r="G92" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="A92" s="19"/>
+      <c r="B92" s="20"/>
+      <c r="C92" s="20"/>
+      <c r="D92" s="20"/>
+      <c r="E92" s="26"/>
+      <c r="F92" s="26"/>
+      <c r="G92" s="26"/>
       <c r="H92" s="26"/>
       <c r="I92" s="26"/>
-      <c r="J92" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K92" s="26">
-        <v>1833</v>
-      </c>
-      <c r="L92" s="26">
-        <v>1823</v>
-      </c>
-      <c r="M92" s="26">
-        <f t="shared" si="5"/>
-        <v>-10</v>
-      </c>
+      <c r="J92" s="26"/>
+      <c r="K92" s="26"/>
+      <c r="L92" s="26"/>
+      <c r="M92" s="26"/>
     </row>
     <row r="93" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A93" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B93" s="20" t="s">
-        <v>1354</v>
-      </c>
-      <c r="C93" s="20" t="s">
-        <v>1355</v>
-      </c>
-      <c r="D93" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E93" s="26">
-        <v>1869</v>
-      </c>
-      <c r="F93" s="26">
-        <v>1869</v>
-      </c>
-      <c r="G93" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="A93" s="19"/>
+      <c r="B93" s="20"/>
+      <c r="C93" s="20"/>
+      <c r="D93" s="20"/>
+      <c r="E93" s="26"/>
+      <c r="F93" s="26"/>
+      <c r="G93" s="26"/>
       <c r="H93" s="26"/>
       <c r="I93" s="26"/>
-      <c r="J93" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K93" s="26">
-        <v>1834</v>
-      </c>
-      <c r="L93" s="26">
-        <v>1829</v>
-      </c>
-      <c r="M93" s="26">
-        <f t="shared" si="5"/>
-        <v>-5</v>
-      </c>
+      <c r="J93" s="26"/>
+      <c r="K93" s="26"/>
+      <c r="L93" s="26"/>
+      <c r="M93" s="26"/>
     </row>
     <row r="94" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A94" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B94" s="20" t="s">
-        <v>790</v>
-      </c>
-      <c r="C94" s="20" t="s">
-        <v>791</v>
-      </c>
-      <c r="D94" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E94" s="26">
-        <v>1869</v>
-      </c>
-      <c r="F94" s="26">
-        <v>1869</v>
-      </c>
-      <c r="G94" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="A94" s="19"/>
+      <c r="B94" s="20"/>
+      <c r="C94" s="20"/>
+      <c r="D94" s="20"/>
+      <c r="E94" s="26"/>
+      <c r="F94" s="26"/>
+      <c r="G94" s="26"/>
       <c r="H94" s="26"/>
       <c r="I94" s="26"/>
-      <c r="J94" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K94" s="26">
-        <v>1869</v>
-      </c>
-      <c r="L94" s="26">
-        <v>1839</v>
-      </c>
-      <c r="M94" s="26">
-        <f t="shared" si="5"/>
-        <v>-30</v>
-      </c>
+      <c r="J94" s="26"/>
+      <c r="K94" s="26"/>
+      <c r="L94" s="26"/>
+      <c r="M94" s="26"/>
     </row>
     <row r="95" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A95" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B95" s="20" t="s">
-        <v>459</v>
-      </c>
-      <c r="C95" s="20" t="s">
-        <v>460</v>
-      </c>
-      <c r="D95" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E95" s="26">
-        <v>1870</v>
-      </c>
-      <c r="F95" s="26">
-        <v>1870</v>
-      </c>
-      <c r="G95" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="A95" s="19"/>
+      <c r="B95" s="20"/>
+      <c r="C95" s="20"/>
+      <c r="D95" s="20"/>
+      <c r="E95" s="26"/>
+      <c r="F95" s="26"/>
+      <c r="G95" s="26"/>
       <c r="H95" s="26"/>
       <c r="I95" s="26"/>
-      <c r="J95" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K95" s="26">
-        <v>1900</v>
-      </c>
-      <c r="L95" s="26">
-        <v>1860</v>
-      </c>
-      <c r="M95" s="26">
-        <f t="shared" si="5"/>
-        <v>-40</v>
-      </c>
+      <c r="J95" s="26"/>
+      <c r="K95" s="26"/>
+      <c r="L95" s="26"/>
+      <c r="M95" s="26"/>
     </row>
     <row r="96" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A96" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B96" s="20" t="s">
-        <v>541</v>
-      </c>
-      <c r="C96" s="20" t="s">
-        <v>542</v>
-      </c>
-      <c r="D96" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E96" s="26">
-        <v>1874</v>
-      </c>
-      <c r="F96" s="26">
-        <v>1855</v>
-      </c>
-      <c r="G96" s="26">
-        <f t="shared" si="3"/>
-        <v>-19</v>
-      </c>
+      <c r="A96" s="19"/>
+      <c r="B96" s="20"/>
+      <c r="C96" s="20"/>
+      <c r="D96" s="20"/>
+      <c r="E96" s="26"/>
+      <c r="F96" s="26"/>
+      <c r="G96" s="26"/>
       <c r="H96" s="26"/>
       <c r="I96" s="26"/>
-      <c r="J96" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K96" s="26">
-        <v>1855</v>
-      </c>
-      <c r="L96" s="26">
-        <v>1855</v>
-      </c>
-      <c r="M96" s="26">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="J96" s="26"/>
+      <c r="K96" s="26"/>
+      <c r="L96" s="26"/>
+      <c r="M96" s="26"/>
     </row>
     <row r="97" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A97" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B97" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="C97" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="D97" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E97" s="26">
-        <v>1878</v>
-      </c>
-      <c r="F97" s="26">
-        <v>1878</v>
-      </c>
-      <c r="G97" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="A97" s="19"/>
+      <c r="B97" s="20"/>
+      <c r="C97" s="20"/>
+      <c r="D97" s="20"/>
+      <c r="E97" s="26"/>
+      <c r="F97" s="26"/>
+      <c r="G97" s="26"/>
       <c r="H97" s="26"/>
       <c r="I97" s="26"/>
-      <c r="J97" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K97" s="26">
-        <v>1822</v>
-      </c>
-      <c r="L97" s="26">
-        <v>1839</v>
-      </c>
-      <c r="M97" s="26">
-        <f t="shared" si="5"/>
-        <v>17</v>
-      </c>
+      <c r="J97" s="26"/>
+      <c r="K97" s="26"/>
+      <c r="L97" s="26"/>
+      <c r="M97" s="26"/>
     </row>
     <row r="98" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A98" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B98" s="20" t="s">
-        <v>1350</v>
-      </c>
-      <c r="C98" s="20" t="s">
-        <v>1351</v>
-      </c>
-      <c r="D98" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E98" s="26">
-        <v>1878</v>
-      </c>
-      <c r="F98" s="26">
-        <v>1858</v>
-      </c>
-      <c r="G98" s="26">
-        <f t="shared" si="3"/>
-        <v>-20</v>
-      </c>
+      <c r="A98" s="19"/>
+      <c r="B98" s="20"/>
+      <c r="C98" s="20"/>
+      <c r="D98" s="20"/>
+      <c r="E98" s="26"/>
+      <c r="F98" s="26"/>
+      <c r="G98" s="26"/>
       <c r="H98" s="26"/>
       <c r="I98" s="26"/>
-      <c r="J98" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K98" s="26">
-        <v>1857</v>
-      </c>
-      <c r="L98" s="26">
-        <v>1877</v>
-      </c>
-      <c r="M98" s="26">
-        <f t="shared" si="5"/>
-        <v>20</v>
-      </c>
+      <c r="J98" s="26"/>
+      <c r="K98" s="26"/>
+      <c r="L98" s="26"/>
+      <c r="M98" s="26"/>
     </row>
     <row r="99" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A99" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B99" s="20" t="s">
-        <v>378</v>
-      </c>
-      <c r="C99" s="20" t="s">
-        <v>379</v>
-      </c>
-      <c r="D99" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E99" s="26">
-        <v>1879</v>
-      </c>
-      <c r="F99" s="26">
-        <v>1859</v>
-      </c>
-      <c r="G99" s="26">
-        <f t="shared" si="3"/>
-        <v>-20</v>
-      </c>
+      <c r="A99" s="19"/>
+      <c r="B99" s="20"/>
+      <c r="C99" s="20"/>
+      <c r="D99" s="20"/>
+      <c r="E99" s="26"/>
+      <c r="F99" s="26"/>
+      <c r="G99" s="26"/>
       <c r="H99" s="26"/>
       <c r="I99" s="26"/>
-      <c r="J99" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K99" s="26">
-        <v>1859</v>
-      </c>
-      <c r="L99" s="26">
-        <v>1839</v>
-      </c>
-      <c r="M99" s="26">
-        <f t="shared" si="5"/>
-        <v>-20</v>
-      </c>
+      <c r="J99" s="26"/>
+      <c r="K99" s="26"/>
+      <c r="L99" s="26"/>
+      <c r="M99" s="26"/>
     </row>
     <row r="100" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A100" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B100" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="C100" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="D100" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E100" s="26">
-        <v>1889</v>
-      </c>
-      <c r="F100" s="26">
-        <v>1889</v>
-      </c>
-      <c r="G100" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="A100" s="19"/>
+      <c r="B100" s="20"/>
+      <c r="C100" s="20"/>
+      <c r="D100" s="20"/>
+      <c r="E100" s="26"/>
+      <c r="F100" s="26"/>
+      <c r="G100" s="26"/>
       <c r="H100" s="26"/>
       <c r="I100" s="26"/>
-      <c r="J100" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K100" s="26">
-        <v>1828</v>
-      </c>
-      <c r="L100" s="26">
-        <v>1839</v>
-      </c>
-      <c r="M100" s="26">
-        <f t="shared" si="5"/>
-        <v>11</v>
-      </c>
+      <c r="J100" s="26"/>
+      <c r="K100" s="26"/>
+      <c r="L100" s="26"/>
+      <c r="M100" s="26"/>
     </row>
     <row r="101" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A101" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B101" s="20" t="s">
-        <v>832</v>
-      </c>
-      <c r="C101" s="20" t="s">
-        <v>833</v>
-      </c>
-      <c r="D101" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E101" s="26">
-        <v>1895</v>
-      </c>
-      <c r="F101" s="26">
-        <v>1865</v>
-      </c>
-      <c r="G101" s="26">
-        <f t="shared" si="3"/>
-        <v>-30</v>
-      </c>
+      <c r="A101" s="19"/>
+      <c r="B101" s="20"/>
+      <c r="C101" s="20"/>
+      <c r="D101" s="20"/>
+      <c r="E101" s="26"/>
+      <c r="F101" s="26"/>
+      <c r="G101" s="26"/>
       <c r="H101" s="26"/>
       <c r="I101" s="26"/>
-      <c r="J101" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K101" s="26">
-        <v>1885</v>
-      </c>
-      <c r="L101" s="26">
-        <v>1835</v>
-      </c>
-      <c r="M101" s="26">
-        <f t="shared" si="5"/>
-        <v>-50</v>
-      </c>
+      <c r="J101" s="26"/>
+      <c r="K101" s="26"/>
+      <c r="L101" s="26"/>
+      <c r="M101" s="26"/>
     </row>
     <row r="102" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A102" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B102" s="20" t="s">
-        <v>1541</v>
-      </c>
-      <c r="C102" s="20" t="s">
-        <v>1542</v>
-      </c>
-      <c r="D102" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E102" s="26">
-        <v>1895</v>
-      </c>
-      <c r="F102" s="26">
-        <v>1875</v>
-      </c>
-      <c r="G102" s="26">
-        <f t="shared" si="3"/>
-        <v>-20</v>
-      </c>
+      <c r="A102" s="19"/>
+      <c r="B102" s="20"/>
+      <c r="C102" s="20"/>
+      <c r="D102" s="20"/>
+      <c r="E102" s="26"/>
+      <c r="F102" s="26"/>
+      <c r="G102" s="26"/>
       <c r="H102" s="26"/>
       <c r="I102" s="26"/>
-      <c r="J102" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K102" s="26">
-        <v>1885</v>
-      </c>
-      <c r="L102" s="26">
-        <v>1865</v>
-      </c>
-      <c r="M102" s="26">
-        <f t="shared" si="5"/>
-        <v>-20</v>
-      </c>
+      <c r="J102" s="26"/>
+      <c r="K102" s="26"/>
+      <c r="L102" s="26"/>
+      <c r="M102" s="26"/>
     </row>
     <row r="103" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A103" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B103" s="20" t="s">
-        <v>569</v>
-      </c>
-      <c r="C103" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="D103" s="20" t="s">
-        <v>1763</v>
-      </c>
+      <c r="A103" s="19"/>
+      <c r="B103" s="20"/>
+      <c r="C103" s="20"/>
+      <c r="D103" s="20"/>
       <c r="E103" s="26"/>
-      <c r="F103" s="26">
-        <v>1969</v>
-      </c>
-      <c r="G103" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="F103" s="26"/>
+      <c r="G103" s="26"/>
       <c r="H103" s="26"/>
       <c r="I103" s="26"/>
-      <c r="J103" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K103" s="26">
-        <v>1899</v>
-      </c>
-      <c r="L103" s="26">
-        <v>1899</v>
-      </c>
-      <c r="M103" s="26">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="J103" s="26"/>
+      <c r="K103" s="26"/>
+      <c r="L103" s="26"/>
+      <c r="M103" s="26"/>
     </row>
     <row r="104" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
       <c r="A104" s="19"/>
@@ -81793,7 +79214,7 @@
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
-  <conditionalFormatting sqref="G4:G103">
+  <conditionalFormatting sqref="G4">
     <cfRule type="cellIs" dxfId="5" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -81801,7 +79222,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J103">
+  <conditionalFormatting sqref="J4">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -81809,7 +79230,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M103">
+  <conditionalFormatting sqref="M4">
     <cfRule type="cellIs" dxfId="1" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>

--- a/fuel_cost_chungcheong.xlsx
+++ b/fuel_cost_chungcheong.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4706" uniqueCount="1766">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4702" uniqueCount="1765">
   <si>
     <t>유류비 계산(혼유, 지역화폐 등)</t>
   </si>
@@ -5383,9 +5383,6 @@
   </si>
   <si>
     <t>충북 청주시 청원구 직지대로 830</t>
-  </si>
-  <si>
-    <t>가격변동</t>
   </si>
   <si>
     <t>세종시 부강면 시목부강로 423</t>
@@ -49609,7 +49606,7 @@
         <v>26</v>
       </c>
       <c r="F552" s="11" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="G552" s="12">
         <v>1824</v>
@@ -75540,7 +75537,7 @@
     </row>
     <row r="2" spans="1:13" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="16" customFormat="1" ht="27.75" customHeight="1">
@@ -75585,44 +75582,19 @@
       </c>
     </row>
     <row r="4" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A4" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>1193</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>1194</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="E4" s="26">
-        <v>1838</v>
-      </c>
-      <c r="F4" s="26">
-        <v>1838</v>
-      </c>
-      <c r="G4" s="26">
-        <f>IF(OR(E4="",F4=""),"",F4-E4)</f>
-        <v>0</v>
-      </c>
+      <c r="A4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
       <c r="H4" s="26"/>
       <c r="I4" s="26"/>
-      <c r="J4" s="26" t="str">
-        <f>IF(OR(H4="",I4=""),"",I4-H4)</f>
-        <v/>
-      </c>
-      <c r="K4" s="26">
-        <v>1848</v>
-      </c>
-      <c r="L4" s="26">
-        <v>1818</v>
-      </c>
-      <c r="M4" s="26">
-        <f>IF(OR(K4="",L4=""),"",L4-K4)</f>
-        <v>-30</v>
-      </c>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
     </row>
     <row r="5" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
       <c r="A5" s="19"/>

--- a/fuel_cost_chungcheong.xlsx
+++ b/fuel_cost_chungcheong.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4685" uniqueCount="1758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4681" uniqueCount="1757">
   <si>
     <t>유류비 계산(혼유, 지역화폐 등)</t>
   </si>
@@ -5362,9 +5362,6 @@
   </si>
   <si>
     <t>세종시 부강면 시목부강로 423</t>
-  </si>
-  <si>
-    <t>가격변동</t>
   </si>
   <si>
     <t>현행화 일자: 2026-09-09</t>
@@ -75198,7 +75195,7 @@
     </row>
     <row r="2" spans="1:13" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="16" customFormat="1" ht="27.75" customHeight="1">
@@ -75243,44 +75240,19 @@
       </c>
     </row>
     <row r="4" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A4" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>910</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>911</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>1756</v>
-      </c>
-      <c r="E4" s="26">
-        <v>1814</v>
-      </c>
-      <c r="F4" s="26">
-        <v>1799</v>
-      </c>
-      <c r="G4" s="26">
-        <f>IF(OR(E4="",F4=""),"",F4-E4)</f>
-        <v>-15</v>
-      </c>
+      <c r="A4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
       <c r="H4" s="26"/>
       <c r="I4" s="26"/>
-      <c r="J4" s="26" t="str">
-        <f>IF(OR(H4="",I4=""),"",I4-H4)</f>
-        <v/>
-      </c>
-      <c r="K4" s="26">
-        <v>1794</v>
-      </c>
-      <c r="L4" s="26">
-        <v>1794</v>
-      </c>
-      <c r="M4" s="26">
-        <f>IF(OR(K4="",L4=""),"",L4-K4)</f>
-        <v>0</v>
-      </c>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
     </row>
     <row r="5" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
       <c r="A5" s="19"/>
